--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -563,7 +563,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C2">
-        <v>68.06005859375</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -574,7 +574,7 @@
         <v>54.10009765625</v>
       </c>
       <c r="C3">
-        <v>54.10009765625</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -585,7 +585,7 @@
         <v>38.260009765625</v>
       </c>
       <c r="C4">
-        <v>38.260009765625</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -596,7 +596,7 @@
         <v>74.06005859375</v>
       </c>
       <c r="C5">
-        <v>74.06005859375</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -607,7 +607,7 @@
         <v>62.260009765625</v>
       </c>
       <c r="C6">
-        <v>62.260009765625</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -618,7 +618,7 @@
         <v>71.7099609375</v>
       </c>
       <c r="C7">
-        <v>71.7099609375</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -629,7 +629,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C8">
-        <v>61.56005859375</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -640,7 +640,7 @@
         <v>73.759765625</v>
       </c>
       <c r="C9">
-        <v>73.759765625</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -651,7 +651,7 @@
         <v>72.85986328125</v>
       </c>
       <c r="C10">
-        <v>72.85986328125</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -662,7 +662,7 @@
         <v>60.199951171875</v>
       </c>
       <c r="C11">
-        <v>60.199951171875</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -673,7 +673,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="C12">
-        <v>72.7001953125</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -684,7 +684,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C13">
-        <v>53.659912109375</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -695,7 +695,7 @@
         <v>56.9599609375</v>
       </c>
       <c r="C14">
-        <v>56.9599609375</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -706,7 +706,7 @@
         <v>37.820068359375</v>
       </c>
       <c r="C15">
-        <v>37.820068359375</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -717,7 +717,7 @@
         <v>56.260009765625</v>
       </c>
       <c r="C16">
-        <v>56.260009765625</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -728,7 +728,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="C17">
-        <v>63.89990234375</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -739,7 +739,7 @@
         <v>44.06005859375</v>
       </c>
       <c r="C18">
-        <v>44.06005859375</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -750,7 +750,7 @@
         <v>54.159912109375</v>
       </c>
       <c r="C19">
-        <v>54.159912109375</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -761,7 +761,7 @@
         <v>40.60009765625</v>
       </c>
       <c r="C20">
-        <v>40.60009765625</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -772,7 +772,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="C21">
-        <v>57.449951171875</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -783,7 +783,7 @@
         <v>57.60009765625</v>
       </c>
       <c r="C22">
-        <v>57.60009765625</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -794,7 +794,7 @@
         <v>54.60009765625</v>
       </c>
       <c r="C23">
-        <v>54.60009765625</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -805,7 +805,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C24">
-        <v>47.860107421875</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -816,7 +816,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C25">
-        <v>47.860107421875</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -827,7 +827,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C26">
-        <v>62.56005859375</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -838,7 +838,7 @@
         <v>65.009765625</v>
       </c>
       <c r="C27">
-        <v>65.009765625</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -849,7 +849,7 @@
         <v>58.510009765625</v>
       </c>
       <c r="C28">
-        <v>58.510009765625</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -860,7 +860,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="C29">
-        <v>73.9599609375</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -871,7 +871,7 @@
         <v>51.56005859375</v>
       </c>
       <c r="C30">
-        <v>51.56005859375</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -882,7 +882,7 @@
         <v>49.760009765625</v>
       </c>
       <c r="C31">
-        <v>49.760009765625</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -893,7 +893,7 @@
         <v>44.260009765625</v>
       </c>
       <c r="C32">
-        <v>44.260009765625</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -904,7 +904,7 @@
         <v>84.259765625</v>
       </c>
       <c r="C33">
-        <v>84.259765625</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -915,7 +915,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C34">
-        <v>64.56005859375</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -926,7 +926,7 @@
         <v>43.510009765625</v>
       </c>
       <c r="C35">
-        <v>43.510009765625</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -937,7 +937,7 @@
         <v>57.4599609375</v>
       </c>
       <c r="C36">
-        <v>57.4599609375</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -948,7 +948,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C37">
-        <v>64.56005859375</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -959,7 +959,7 @@
         <v>59.25</v>
       </c>
       <c r="C38">
-        <v>59.25</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -970,7 +970,7 @@
         <v>84.85986328125</v>
       </c>
       <c r="C39">
-        <v>84.85986328125</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -981,7 +981,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="C40">
-        <v>60.159912109375</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -992,7 +992,7 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1003,7 +1003,7 @@
         <v>61.659912109375</v>
       </c>
       <c r="C42">
-        <v>61.659912109375</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1014,7 +1014,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="C43">
-        <v>42.9599609375</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1025,7 +1025,7 @@
         <v>54.10009765625</v>
       </c>
       <c r="C44">
-        <v>54.10009765625</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1036,7 +1036,7 @@
         <v>61.9599609375</v>
       </c>
       <c r="C45">
-        <v>61.9599609375</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1047,7 +1047,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="C46">
-        <v>64.2001953125</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1058,7 +1058,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="C47">
-        <v>66.85986328125</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1069,7 +1069,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="C48">
-        <v>58.9599609375</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1080,7 +1080,7 @@
         <v>70</v>
       </c>
       <c r="C49">
-        <v>70</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1091,7 +1091,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C50">
-        <v>68.06005859375</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1102,7 +1102,7 @@
         <v>51.260009765625</v>
       </c>
       <c r="C51">
-        <v>51.260009765625</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1113,7 +1113,7 @@
         <v>72.16015625</v>
       </c>
       <c r="C52">
-        <v>72.16015625</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1124,7 +1124,7 @@
         <v>55.89990234375</v>
       </c>
       <c r="C53">
-        <v>55.89990234375</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2292,58 +2292,58 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>84.85986328125</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>84.259765625</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>74.06005859375</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B5">
-        <v>73.9599609375</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B6">
-        <v>73.759765625</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B7">
-        <v>72.85986328125</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>72.7001953125</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2351,271 +2351,271 @@
         <v>52</v>
       </c>
       <c r="B9">
-        <v>72.16015625</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>71.7099609375</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B11">
-        <v>70</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B12">
-        <v>68.06005859375</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>68.06005859375</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>66.85986328125</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>65.009765625</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B16">
-        <v>64.56005859375</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B17">
-        <v>64.56005859375</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B18">
-        <v>64.2001953125</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>63.89990234375</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>62.56005859375</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B21">
-        <v>62.260009765625</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B22">
-        <v>61.9599609375</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B23">
-        <v>61.659912109375</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>61.56005859375</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B25">
-        <v>60.199951171875</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B26">
-        <v>60.159912109375</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>59.25</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B28">
-        <v>58.9599609375</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B29">
-        <v>58.510009765625</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B30">
-        <v>57.60009765625</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B31">
-        <v>57.4599609375</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>57.449951171875</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B33">
-        <v>56.9599609375</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B34">
-        <v>56.260009765625</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B35">
-        <v>55.89990234375</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B36">
-        <v>54.60009765625</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B37">
-        <v>54.159912109375</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38">
-        <v>54.10009765625</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B39">
-        <v>54.10009765625</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B40">
-        <v>53.659912109375</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B41">
-        <v>51.56005859375</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B42">
-        <v>51.260009765625</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2623,87 +2623,87 @@
         <v>31</v>
       </c>
       <c r="B43">
-        <v>49.760009765625</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B44">
-        <v>49</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B45">
-        <v>47.860107421875</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B46">
-        <v>47.860107421875</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B47">
-        <v>44.260009765625</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B48">
-        <v>44.06005859375</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B49">
-        <v>43.510009765625</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B50">
-        <v>42.9599609375</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B51">
-        <v>40.60009765625</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B52">
-        <v>38.260009765625</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B53">
-        <v>37.820068359375</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -805,7 +805,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C24">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -816,7 +816,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C25">
-        <v>49.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -849,7 +849,7 @@
         <v>58.510009765625</v>
       </c>
       <c r="C28">
-        <v>46.25</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -915,7 +915,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C34">
-        <v>74.25</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2308,26 +2308,26 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B4">
-        <v>75.15000000000001</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>75.05</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B6">
-        <v>74.25</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2452,98 +2452,98 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B23">
-        <v>53.9</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B24">
-        <v>52.8</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B25">
-        <v>51.48</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>50.35</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27">
-        <v>50.3</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B28">
-        <v>49.8</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B29">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30">
-        <v>46.95</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B31">
-        <v>46.65</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B32">
-        <v>46.35</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>46.25</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="34" spans="1:2">

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -563,7 +563,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C2">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -574,7 +574,7 @@
         <v>54.10009765625</v>
       </c>
       <c r="C3">
-        <v>65.5</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -585,7 +585,7 @@
         <v>38.260009765625</v>
       </c>
       <c r="C4">
-        <v>66.55</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -596,7 +596,7 @@
         <v>74.06005859375</v>
       </c>
       <c r="C5">
-        <v>83.55</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -607,7 +607,7 @@
         <v>62.260009765625</v>
       </c>
       <c r="C6">
-        <v>43.46</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -618,7 +618,7 @@
         <v>71.7099609375</v>
       </c>
       <c r="C7">
-        <v>28.8</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -629,7 +629,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C8">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -640,7 +640,7 @@
         <v>73.759765625</v>
       </c>
       <c r="C9">
-        <v>53.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -651,7 +651,7 @@
         <v>72.85986328125</v>
       </c>
       <c r="C10">
-        <v>46.95</v>
+        <v>50.55</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -662,7 +662,7 @@
         <v>60.199951171875</v>
       </c>
       <c r="C11">
-        <v>45.9</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -673,7 +673,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="C12">
-        <v>15.7</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -684,7 +684,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C13">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -695,7 +695,7 @@
         <v>56.9599609375</v>
       </c>
       <c r="C14">
-        <v>75.15000000000001</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -706,7 +706,7 @@
         <v>37.820068359375</v>
       </c>
       <c r="C15">
-        <v>38.88</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -717,7 +717,7 @@
         <v>56.260009765625</v>
       </c>
       <c r="C16">
-        <v>46.65</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -728,7 +728,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="C17">
-        <v>63.55</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -739,7 +739,7 @@
         <v>44.06005859375</v>
       </c>
       <c r="C18">
-        <v>75.05</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -750,7 +750,7 @@
         <v>54.159912109375</v>
       </c>
       <c r="C19">
-        <v>59.95</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -761,7 +761,7 @@
         <v>40.60009765625</v>
       </c>
       <c r="C20">
-        <v>12.2</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -772,7 +772,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="C21">
-        <v>35.75</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -794,7 +794,7 @@
         <v>54.60009765625</v>
       </c>
       <c r="C23">
-        <v>69.2</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -805,7 +805,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C24">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -816,7 +816,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C25">
-        <v>52.8</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -827,7 +827,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C26">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -838,7 +838,7 @@
         <v>65.009765625</v>
       </c>
       <c r="C27">
-        <v>44.05</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -849,7 +849,7 @@
         <v>58.510009765625</v>
       </c>
       <c r="C28">
-        <v>54.3</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -860,7 +860,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="C29">
-        <v>65.40000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -871,7 +871,7 @@
         <v>51.56005859375</v>
       </c>
       <c r="C30">
-        <v>27.55</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -882,7 +882,7 @@
         <v>49.760009765625</v>
       </c>
       <c r="C31">
-        <v>38.7</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -893,7 +893,7 @@
         <v>44.260009765625</v>
       </c>
       <c r="C32">
-        <v>46.35</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -904,7 +904,7 @@
         <v>84.259765625</v>
       </c>
       <c r="C33">
-        <v>50.3</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -915,7 +915,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C34">
-        <v>78.75</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -926,7 +926,7 @@
         <v>43.510009765625</v>
       </c>
       <c r="C35">
-        <v>51.48</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -937,7 +937,7 @@
         <v>57.4599609375</v>
       </c>
       <c r="C36">
-        <v>59.1</v>
+        <v>68.20999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -948,7 +948,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C37">
-        <v>62.25</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -959,7 +959,7 @@
         <v>59.25</v>
       </c>
       <c r="C38">
-        <v>37.8</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -970,7 +970,7 @@
         <v>84.85986328125</v>
       </c>
       <c r="C39">
-        <v>45.15</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -981,7 +981,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="C40">
-        <v>26.1</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -992,7 +992,7 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1003,7 +1003,7 @@
         <v>61.659912109375</v>
       </c>
       <c r="C42">
-        <v>28.65</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1014,7 +1014,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="C43">
-        <v>62.4</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1025,7 +1025,7 @@
         <v>54.10009765625</v>
       </c>
       <c r="C44">
-        <v>63.7</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1036,7 +1036,7 @@
         <v>61.9599609375</v>
       </c>
       <c r="C45">
-        <v>42.5</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1047,7 +1047,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="C46">
-        <v>65.8</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1058,7 +1058,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="C47">
-        <v>50.35</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1069,7 +1069,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="C48">
-        <v>38.8</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1080,7 +1080,7 @@
         <v>70</v>
       </c>
       <c r="C49">
-        <v>63.25</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1091,7 +1091,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C50">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1102,7 +1102,7 @@
         <v>51.260009765625</v>
       </c>
       <c r="C51">
-        <v>71.65000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1113,7 +1113,7 @@
         <v>72.16015625</v>
       </c>
       <c r="C52">
-        <v>68.65000000000001</v>
+        <v>76.86</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1124,7 +1124,7 @@
         <v>55.89990234375</v>
       </c>
       <c r="C53">
-        <v>19.4</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2295,15 +2295,15 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>83.55</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>79.59999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2311,375 +2311,375 @@
         <v>34</v>
       </c>
       <c r="B4">
-        <v>78.75</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <v>75.15000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>75.05</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>71.65000000000001</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B8">
-        <v>69.2</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B9">
-        <v>68.65000000000001</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B10">
-        <v>66.55</v>
+        <v>76.86</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>65.8</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>65.5</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B13">
-        <v>65.40000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>63.7</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B15">
-        <v>63.55</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B16">
-        <v>63.25</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>62.4</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>62.25</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B19">
-        <v>59.95</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B20">
-        <v>59.1</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>58.3</v>
+        <v>68.20999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B22">
-        <v>56.2</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B23">
-        <v>55.9</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B24">
-        <v>54.3</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B25">
-        <v>53.9</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B26">
-        <v>52.8</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B27">
-        <v>51.48</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B28">
-        <v>50.35</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B29">
-        <v>50.3</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>49.8</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>46.95</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B32">
-        <v>46.65</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B33">
-        <v>46.35</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34">
-        <v>45.9</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B35">
-        <v>45.15</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B36">
-        <v>44.05</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B37">
-        <v>43.46</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B38">
-        <v>42.5</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B39">
-        <v>41.7</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B40">
-        <v>41.7</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B41">
-        <v>38.88</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B42">
-        <v>38.8</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B43">
-        <v>38.7</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B44">
-        <v>37.8</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B45">
-        <v>35.75</v>
+        <v>50.55</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B46">
-        <v>28.8</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B47">
-        <v>28.65</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B48">
-        <v>27.55</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B49">
-        <v>26.1</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B50">
-        <v>19.4</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2687,23 +2687,23 @@
         <v>12</v>
       </c>
       <c r="B51">
-        <v>15.7</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B52">
-        <v>12.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>35.15</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -563,7 +563,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C2">
-        <v>59.2</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -574,7 +574,7 @@
         <v>54.10009765625</v>
       </c>
       <c r="C3">
-        <v>66.40000000000001</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -585,7 +585,7 @@
         <v>38.260009765625</v>
       </c>
       <c r="C4">
-        <v>78.84999999999999</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -596,7 +596,7 @@
         <v>74.06005859375</v>
       </c>
       <c r="C5">
-        <v>88.36</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -607,7 +607,7 @@
         <v>62.260009765625</v>
       </c>
       <c r="C6">
-        <v>54.76</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -618,7 +618,7 @@
         <v>71.7099609375</v>
       </c>
       <c r="C7">
-        <v>35.5</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -629,7 +629,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C8">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -640,7 +640,7 @@
         <v>73.759765625</v>
       </c>
       <c r="C9">
-        <v>58.2</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -651,7 +651,7 @@
         <v>72.85986328125</v>
       </c>
       <c r="C10">
-        <v>50.55</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -662,7 +662,7 @@
         <v>60.199951171875</v>
       </c>
       <c r="C11">
-        <v>66.11</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -673,7 +673,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="C12">
-        <v>39.71</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -684,7 +684,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C13">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -695,7 +695,7 @@
         <v>56.9599609375</v>
       </c>
       <c r="C14">
-        <v>79.45</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -706,7 +706,7 @@
         <v>37.820068359375</v>
       </c>
       <c r="C15">
-        <v>47.68</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -717,7 +717,7 @@
         <v>56.260009765625</v>
       </c>
       <c r="C16">
-        <v>55.65</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -728,7 +728,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="C17">
-        <v>75.16</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -739,7 +739,7 @@
         <v>44.06005859375</v>
       </c>
       <c r="C18">
-        <v>74.75</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -750,7 +750,7 @@
         <v>54.159912109375</v>
       </c>
       <c r="C19">
-        <v>63.95</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -761,7 +761,7 @@
         <v>40.60009765625</v>
       </c>
       <c r="C20">
-        <v>49.26</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -772,7 +772,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="C21">
-        <v>49.15</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -783,7 +783,7 @@
         <v>57.60009765625</v>
       </c>
       <c r="C22">
-        <v>79.59999999999999</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -794,7 +794,7 @@
         <v>54.60009765625</v>
       </c>
       <c r="C23">
-        <v>73.70999999999999</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -805,7 +805,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C24">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -816,7 +816,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C25">
-        <v>61.91</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -827,7 +827,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C26">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -838,7 +838,7 @@
         <v>65.009765625</v>
       </c>
       <c r="C27">
-        <v>73.34999999999999</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -849,7 +849,7 @@
         <v>58.510009765625</v>
       </c>
       <c r="C28">
-        <v>62.4</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -860,7 +860,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="C29">
-        <v>69.7</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -871,7 +871,7 @@
         <v>51.56005859375</v>
       </c>
       <c r="C30">
-        <v>52.95</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -882,7 +882,7 @@
         <v>49.760009765625</v>
       </c>
       <c r="C31">
-        <v>55.81</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -893,7 +893,7 @@
         <v>44.260009765625</v>
       </c>
       <c r="C32">
-        <v>87.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -904,7 +904,7 @@
         <v>84.259765625</v>
       </c>
       <c r="C33">
-        <v>77.52</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -915,7 +915,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C34">
-        <v>82.75</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -926,7 +926,7 @@
         <v>43.510009765625</v>
       </c>
       <c r="C35">
-        <v>55.88</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -937,7 +937,7 @@
         <v>57.4599609375</v>
       </c>
       <c r="C36">
-        <v>68.20999999999999</v>
+        <v>88.18000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -948,7 +948,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C37">
-        <v>66.25</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -959,7 +959,7 @@
         <v>59.25</v>
       </c>
       <c r="C38">
-        <v>53.11</v>
+        <v>73.78</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -970,7 +970,7 @@
         <v>84.85986328125</v>
       </c>
       <c r="C39">
-        <v>61.95</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -981,7 +981,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="C40">
-        <v>48.01</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -992,7 +992,7 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>40.21</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1003,7 +1003,7 @@
         <v>61.659912109375</v>
       </c>
       <c r="C42">
-        <v>35.15</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1014,7 +1014,7 @@
         <v>42.9599609375</v>
       </c>
       <c r="C43">
-        <v>71.51000000000001</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1025,7 +1025,7 @@
         <v>54.10009765625</v>
       </c>
       <c r="C44">
-        <v>64.59999999999999</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1036,7 +1036,7 @@
         <v>61.9599609375</v>
       </c>
       <c r="C45">
-        <v>54.01</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1047,7 +1047,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="C46">
-        <v>73.70999999999999</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1058,7 +1058,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="C47">
-        <v>65.15000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1069,7 +1069,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="C48">
-        <v>56.91</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1080,7 +1080,7 @@
         <v>70</v>
       </c>
       <c r="C49">
-        <v>73.75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1091,7 +1091,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C50">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1102,7 +1102,7 @@
         <v>51.260009765625</v>
       </c>
       <c r="C51">
-        <v>74.75</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1113,7 +1113,7 @@
         <v>72.16015625</v>
       </c>
       <c r="C52">
-        <v>76.86</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1124,7 +1124,7 @@
         <v>55.89990234375</v>
       </c>
       <c r="C53">
-        <v>78.41</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2292,378 +2292,378 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <v>88.36</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>87.5</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B4">
-        <v>82.75</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>79.59999999999999</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B6">
-        <v>79.45</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B7">
-        <v>78.84999999999999</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>78.41</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B9">
-        <v>77.52</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>76.86</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B11">
-        <v>75.16</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B12">
-        <v>74.75</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>74.75</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B14">
-        <v>74.01000000000001</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>73.75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B16">
-        <v>73.70999999999999</v>
+        <v>88.18000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B17">
-        <v>73.70999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>73.34999999999999</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B19">
-        <v>71.51000000000001</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>69.7</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B21">
-        <v>68.20999999999999</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <v>66.40000000000001</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23">
-        <v>66.25</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B24">
-        <v>66.11</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>65.15000000000001</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B26">
-        <v>64.59999999999999</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B27">
-        <v>63.95</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="B28">
-        <v>62.4</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B29">
-        <v>61.95</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B30">
-        <v>61.91</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B31">
-        <v>61.91</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B32">
-        <v>61.41</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>59.81</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B34">
-        <v>59.81</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B35">
-        <v>59.2</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B36">
-        <v>58.2</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B37">
-        <v>56.91</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B38">
-        <v>55.88</v>
+        <v>73.78</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B39">
-        <v>55.81</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B40">
-        <v>55.65</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B41">
-        <v>54.76</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B42">
-        <v>54.01</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>53.11</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B44">
-        <v>52.95</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B45">
-        <v>50.55</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B46">
-        <v>49.26</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B47">
-        <v>49.15</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B48">
-        <v>48.01</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2671,23 +2671,23 @@
         <v>15</v>
       </c>
       <c r="B49">
-        <v>47.68</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B50">
-        <v>40.21</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B51">
-        <v>39.71</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2695,15 +2695,15 @@
         <v>7</v>
       </c>
       <c r="B52">
-        <v>35.5</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53">
-        <v>35.15</v>
+        <v>36.43</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="56">
   <si>
     <t>Rodada 1</t>
   </si>
   <si>
     <t>Rodada 2</t>
+  </si>
+  <si>
+    <t>Rodada 3</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -544,31 +547,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
       </c>
       <c r="C2">
-        <v>72.56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>72.7001953125</v>
+      </c>
+      <c r="D2">
+        <v>72.7001953125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -576,10 +585,13 @@
       <c r="C3">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -587,197 +599,251 @@
       <c r="C4">
         <v>99.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
       </c>
       <c r="C5">
-        <v>93.78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>93.77978515625</v>
+      </c>
+      <c r="D5">
+        <v>93.77978515625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
       </c>
       <c r="C6">
-        <v>73.91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>73.91015625</v>
+      </c>
+      <c r="D6">
+        <v>73.91015625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
       </c>
       <c r="C7">
-        <v>56.86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>57</v>
+      </c>
+      <c r="D7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
       </c>
       <c r="C8">
-        <v>82.18000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>82.18017578125</v>
+      </c>
+      <c r="D8">
+        <v>82.18017578125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
       </c>
       <c r="C9">
-        <v>81.26000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>81.39990234375</v>
+      </c>
+      <c r="D9">
+        <v>81.39990234375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
       </c>
       <c r="C10">
-        <v>65.15000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>65.14990234375</v>
+      </c>
+      <c r="D10">
+        <v>65.14990234375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
       </c>
       <c r="C11">
-        <v>92.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>92.330078125</v>
+      </c>
+      <c r="D11">
+        <v>92.330078125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
       </c>
       <c r="C12">
-        <v>64.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>64.580078125</v>
+      </c>
+      <c r="D12">
+        <v>64.580078125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
       </c>
       <c r="C13">
-        <v>81.48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>81.47998046875</v>
+      </c>
+      <c r="D13">
+        <v>81.47998046875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
       </c>
       <c r="C14">
-        <v>96.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>96.0498046875</v>
+      </c>
+      <c r="D14">
+        <v>96.0498046875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
       </c>
       <c r="C15">
-        <v>64.03</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>64.02978515625</v>
+      </c>
+      <c r="D15">
+        <v>64.02978515625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
       </c>
       <c r="C16">
-        <v>74.90000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>74.89990234375</v>
+      </c>
+      <c r="D16">
+        <v>74.89990234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
       </c>
       <c r="C17">
-        <v>92.78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>92.77978515625</v>
+      </c>
+      <c r="D17">
+        <v>92.77978515625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
       </c>
       <c r="C18">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>85.7001953125</v>
+      </c>
+      <c r="D18">
+        <v>85.7001953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
       </c>
       <c r="C19">
-        <v>86.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>86.7001953125</v>
+      </c>
+      <c r="D19">
+        <v>86.7001953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
       </c>
       <c r="C20">
-        <v>67.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>67.8701171875</v>
+      </c>
+      <c r="D20">
+        <v>67.8701171875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
       </c>
       <c r="C21">
-        <v>83.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>83.2001953125</v>
+      </c>
+      <c r="D21">
+        <v>83.2001953125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -785,109 +851,139 @@
       <c r="C22">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
       </c>
       <c r="C23">
-        <v>85.58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>85.580078125</v>
+      </c>
+      <c r="D23">
+        <v>85.580078125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
       </c>
       <c r="C24">
-        <v>72.18000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>72.18017578125</v>
+      </c>
+      <c r="D24">
+        <v>72.18017578125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
       </c>
       <c r="C25">
-        <v>81.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>81.8798828125</v>
+      </c>
+      <c r="D25">
+        <v>81.8798828125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
       </c>
       <c r="C26">
-        <v>96.48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>96.47998046875</v>
+      </c>
+      <c r="D26">
+        <v>96.47998046875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
       </c>
       <c r="C27">
-        <v>70.15000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>70.14990234375</v>
+      </c>
+      <c r="D27">
+        <v>70.14990234375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
       </c>
       <c r="C28">
-        <v>68.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>68.2998046875</v>
+      </c>
+      <c r="D28">
+        <v>68.2998046875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
       </c>
       <c r="C29">
-        <v>92.76000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>92.89990234375</v>
+      </c>
+      <c r="D29">
+        <v>92.89990234375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
       </c>
       <c r="C30">
-        <v>63.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>63.39990234375</v>
+      </c>
+      <c r="D30">
+        <v>63.39990234375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
       </c>
       <c r="C31">
-        <v>77.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>77.47998046875</v>
+      </c>
+      <c r="D31">
+        <v>77.47998046875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32">
         <v>44.260009765625</v>
@@ -895,21 +991,27 @@
       <c r="C32">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33">
         <v>84.259765625</v>
       </c>
       <c r="C33">
-        <v>82.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>82.60986328125</v>
+      </c>
+      <c r="D33">
+        <v>82.60986328125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34">
         <v>64.56005859375</v>
@@ -917,87 +1019,111 @@
       <c r="C34">
         <v>105.5</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>43.510009765625</v>
       </c>
       <c r="C35">
-        <v>60.88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>60.8798828125</v>
+      </c>
+      <c r="D35">
+        <v>60.8798828125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36">
         <v>57.4599609375</v>
       </c>
       <c r="C36">
-        <v>88.18000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>88.18017578125</v>
+      </c>
+      <c r="D36">
+        <v>88.18017578125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37">
         <v>64.56005859375</v>
       </c>
       <c r="C37">
-        <v>86.59999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>86.60009765625</v>
+      </c>
+      <c r="D37">
+        <v>86.60009765625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>59.25</v>
       </c>
       <c r="C38">
-        <v>73.78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>73.77978515625</v>
+      </c>
+      <c r="D38">
+        <v>73.77978515625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
       </c>
       <c r="C39">
-        <v>79.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>79.4501953125</v>
+      </c>
+      <c r="D39">
+        <v>79.4501953125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
       </c>
       <c r="C40">
-        <v>64.58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>64.580078125</v>
+      </c>
+      <c r="D40">
+        <v>64.580078125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <v>49</v>
       </c>
       <c r="C41">
-        <v>36.43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>36.429931640625</v>
+      </c>
+      <c r="D41">
+        <v>36.429931640625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -1005,21 +1131,27 @@
       <c r="C42">
         <v>69.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
       </c>
       <c r="C43">
-        <v>91.48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>91.47998046875</v>
+      </c>
+      <c r="D43">
+        <v>91.47998046875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -1027,54 +1159,69 @@
       <c r="C44">
         <v>71.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
       </c>
       <c r="C45">
-        <v>84.48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>84.47998046875</v>
+      </c>
+      <c r="D45">
+        <v>84.47998046875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
       </c>
       <c r="C46">
-        <v>95.38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>95.3798828125</v>
+      </c>
+      <c r="D46">
+        <v>95.3798828125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
       </c>
       <c r="C47">
-        <v>92.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>92.7001953125</v>
+      </c>
+      <c r="D47">
+        <v>92.7001953125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
       </c>
       <c r="C48">
-        <v>79.28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>79.27978515625</v>
+      </c>
+      <c r="D48">
+        <v>79.27978515625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -1082,21 +1229,27 @@
       <c r="C49">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
       </c>
       <c r="C50">
-        <v>82.18000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>82.18017578125</v>
+      </c>
+      <c r="D50">
+        <v>82.18017578125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -1104,37 +1257,49 @@
       <c r="C51">
         <v>95.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
       </c>
       <c r="C52">
-        <v>93.48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>93.47998046875</v>
+      </c>
+      <c r="D52">
+        <v>93.47998046875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
       </c>
       <c r="C53">
-        <v>77.38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>77.3798828125</v>
+      </c>
+      <c r="D53">
+        <v>77.3798828125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
         <v>0</v>
       </c>
     </row>
@@ -1150,267 +1315,267 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1595,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1438,7 +1603,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1446,7 +1611,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1454,7 +1619,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1462,7 +1627,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1470,7 +1635,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1478,7 +1643,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1486,7 +1651,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1494,7 +1659,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1502,7 +1667,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1510,7 +1675,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1518,7 +1683,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1526,7 +1691,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1534,7 +1699,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1542,7 +1707,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1550,7 +1715,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1558,7 +1723,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1566,7 +1731,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1574,7 +1739,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1582,7 +1747,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1590,7 +1755,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1598,7 +1763,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1606,7 +1771,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1614,7 +1779,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1622,7 +1787,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1630,7 +1795,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1638,7 +1803,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1646,7 +1811,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1654,7 +1819,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1662,7 +1827,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1670,7 +1835,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1678,7 +1843,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1686,7 +1851,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1694,7 +1859,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1702,7 +1867,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1710,7 +1875,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1718,7 +1883,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1726,7 +1891,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1734,7 +1899,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1742,7 +1907,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1750,7 +1915,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1758,7 +1923,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1766,7 +1931,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1774,7 +1939,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1782,7 +1947,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1790,7 +1955,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1798,7 +1963,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1806,7 +1971,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1814,7 +1979,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1822,7 +1987,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1830,7 +1995,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1838,7 +2003,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1861,7 +2026,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -1869,7 +2034,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -1877,7 +2042,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -1885,7 +2050,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -1893,7 +2058,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -1901,7 +2066,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -1909,7 +2074,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -1917,7 +2082,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -1925,7 +2090,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -1933,7 +2098,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -1941,7 +2106,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -1949,7 +2114,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -1957,7 +2122,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -1965,7 +2130,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -1973,7 +2138,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -1981,7 +2146,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -1989,7 +2154,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -1997,7 +2162,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -2005,7 +2170,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -2013,7 +2178,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -2021,7 +2186,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -2029,7 +2194,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -2037,7 +2202,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -2045,7 +2210,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -2053,7 +2218,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -2061,7 +2226,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -2069,7 +2234,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -2077,7 +2242,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -2085,7 +2250,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30">
         <v>57.60009765625</v>
@@ -2093,7 +2258,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31">
         <v>57.4599609375</v>
@@ -2101,7 +2266,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>57.449951171875</v>
@@ -2109,7 +2274,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33">
         <v>56.9599609375</v>
@@ -2117,7 +2282,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <v>56.260009765625</v>
@@ -2125,7 +2290,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35">
         <v>55.89990234375</v>
@@ -2133,7 +2298,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36">
         <v>54.60009765625</v>
@@ -2141,7 +2306,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>54.159912109375</v>
@@ -2149,7 +2314,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38">
         <v>54.10009765625</v>
@@ -2157,7 +2322,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -2165,7 +2330,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>53.659912109375</v>
@@ -2173,7 +2338,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41">
         <v>51.56005859375</v>
@@ -2181,7 +2346,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>51.260009765625</v>
@@ -2189,7 +2354,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B43">
         <v>49.760009765625</v>
@@ -2197,7 +2362,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44">
         <v>49</v>
@@ -2205,7 +2370,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B45">
         <v>47.860107421875</v>
@@ -2213,7 +2378,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -2221,7 +2386,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B47">
         <v>44.260009765625</v>
@@ -2229,7 +2394,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48">
         <v>44.06005859375</v>
@@ -2237,7 +2402,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B49">
         <v>43.510009765625</v>
@@ -2245,7 +2410,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50">
         <v>42.9599609375</v>
@@ -2253,7 +2418,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51">
         <v>40.60009765625</v>
@@ -2261,7 +2426,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52">
         <v>38.260009765625</v>
@@ -2269,7 +2434,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B53">
         <v>37.820068359375</v>
@@ -2292,418 +2457,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2">
-        <v>105.5</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>99.5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>96.48</v>
+        <v>192.9599609375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>96.05</v>
+        <v>192.099609375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6">
-        <v>95.5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7">
-        <v>95.38</v>
+        <v>190.759765625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>93.78</v>
+        <v>187.5595703125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9">
-        <v>93.48</v>
+        <v>186.9599609375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>92.78</v>
+        <v>185.7998046875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>92.76000000000001</v>
+        <v>185.5595703125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>92.7</v>
+        <v>185.400390625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>92.33</v>
+        <v>184.66015625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>91.48</v>
+        <v>182.9599609375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16">
-        <v>88.18000000000001</v>
+        <v>176.3603515625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17">
-        <v>87.5</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>86.7</v>
+        <v>173.400390625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19">
-        <v>86.59999999999999</v>
+        <v>173.2001953125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>85.7</v>
+        <v>171.400390625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>85.58</v>
+        <v>171.16015625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22">
-        <v>84.5</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>84.48</v>
+        <v>168.9599609375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>83.2</v>
+        <v>166.400390625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25">
-        <v>82.61</v>
+        <v>165.2197265625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26">
-        <v>82.18000000000001</v>
+        <v>164.3603515625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27">
-        <v>82.18000000000001</v>
+        <v>164.3603515625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28">
-        <v>82</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29">
-        <v>81.88</v>
+        <v>163.759765625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B30">
-        <v>81.48</v>
+        <v>162.9599609375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31">
-        <v>81.26000000000001</v>
+        <v>162.7998046875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>79.45</v>
+        <v>158.900390625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>79.28</v>
+        <v>158.5595703125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>77.48</v>
+        <v>154.9599609375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35">
-        <v>77.38</v>
+        <v>154.759765625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B36">
-        <v>74.90000000000001</v>
+        <v>149.7998046875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37">
-        <v>73.91</v>
+        <v>147.8203125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38">
-        <v>73.78</v>
+        <v>147.5595703125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B39">
-        <v>72.56</v>
+        <v>145.400390625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B40">
-        <v>72.18000000000001</v>
+        <v>144.3603515625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41">
-        <v>71.5</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
-        <v>70.15000000000001</v>
+        <v>140.2998046875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43">
-        <v>69.5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B44">
-        <v>68.3</v>
+        <v>136.599609375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45">
-        <v>67.87</v>
+        <v>135.740234375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46">
-        <v>65.15000000000001</v>
+        <v>130.2998046875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>64.58</v>
+        <v>129.16015625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48">
-        <v>64.58</v>
+        <v>129.16015625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B49">
-        <v>64.03</v>
+        <v>128.0595703125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50">
-        <v>63.4</v>
+        <v>126.7998046875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B51">
-        <v>60.88</v>
+        <v>121.759765625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B52">
-        <v>56.86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B53">
-        <v>36.43</v>
+        <v>72.85986328125</v>
       </c>
     </row>
   </sheetData>
@@ -2723,7 +2888,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2731,7 +2896,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2739,7 +2904,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2747,7 +2912,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2755,7 +2920,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2763,7 +2928,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2771,7 +2936,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2779,7 +2944,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2787,7 +2952,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2795,7 +2960,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2803,7 +2968,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2811,7 +2976,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2819,7 +2984,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2827,7 +2992,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2835,7 +3000,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2843,7 +3008,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2851,7 +3016,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2859,7 +3024,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2867,7 +3032,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2875,7 +3040,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2883,7 +3048,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2891,7 +3056,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2899,7 +3064,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2907,7 +3072,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2915,7 +3080,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2923,7 +3088,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2931,7 +3096,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2939,7 +3104,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2947,7 +3112,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2955,7 +3120,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2963,7 +3128,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2971,7 +3136,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2979,7 +3144,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2987,7 +3152,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2995,7 +3160,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3003,7 +3168,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3011,7 +3176,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3019,7 +3184,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3027,7 +3192,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3035,7 +3200,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3043,7 +3208,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3051,7 +3216,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3059,7 +3224,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3067,7 +3232,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3075,7 +3240,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3083,7 +3248,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3091,7 +3256,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3099,7 +3264,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3107,7 +3272,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3115,7 +3280,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3123,7 +3288,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3131,7 +3296,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3154,7 +3319,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3162,7 +3327,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3170,7 +3335,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3178,7 +3343,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3186,7 +3351,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3194,7 +3359,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3202,7 +3367,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3210,7 +3375,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3218,7 +3383,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3226,7 +3391,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3234,7 +3399,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3242,7 +3407,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3250,7 +3415,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3258,7 +3423,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3266,7 +3431,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3274,7 +3439,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3282,7 +3447,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3290,7 +3455,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3298,7 +3463,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3306,7 +3471,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3314,7 +3479,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3322,7 +3487,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3330,7 +3495,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3338,7 +3503,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3346,7 +3511,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3354,7 +3519,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3362,7 +3527,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3370,7 +3535,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3378,7 +3543,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3386,7 +3551,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3394,7 +3559,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3402,7 +3567,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3410,7 +3575,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3418,7 +3583,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3426,7 +3591,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3434,7 +3599,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3442,7 +3607,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3450,7 +3615,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3458,7 +3623,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3466,7 +3631,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3474,7 +3639,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3482,7 +3647,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3490,7 +3655,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3498,7 +3663,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3506,7 +3671,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3514,7 +3679,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3522,7 +3687,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3530,7 +3695,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3538,7 +3703,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3546,7 +3711,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3554,7 +3719,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3562,7 +3727,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3585,7 +3750,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3593,7 +3758,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3601,7 +3766,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3609,7 +3774,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3617,7 +3782,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3625,7 +3790,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3633,7 +3798,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3641,7 +3806,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3649,7 +3814,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3657,7 +3822,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3665,7 +3830,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3673,7 +3838,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3681,7 +3846,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3689,7 +3854,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3697,7 +3862,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3705,7 +3870,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3713,7 +3878,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3721,7 +3886,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3729,7 +3894,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3737,7 +3902,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3745,7 +3910,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3753,7 +3918,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3761,7 +3926,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3769,7 +3934,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3777,7 +3942,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3785,7 +3950,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3793,7 +3958,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3801,7 +3966,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3809,7 +3974,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3817,7 +3982,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3825,7 +3990,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3833,7 +3998,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3841,7 +4006,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3849,7 +4014,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3857,7 +4022,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3865,7 +4030,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3873,7 +4038,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3881,7 +4046,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3889,7 +4054,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3897,7 +4062,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3905,7 +4070,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3913,7 +4078,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3921,7 +4086,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3929,7 +4094,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3937,7 +4102,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3945,7 +4110,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3953,7 +4118,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3961,7 +4126,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3969,7 +4134,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3977,7 +4142,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3985,7 +4150,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3993,7 +4158,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4016,7 +4181,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4024,7 +4189,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4032,7 +4197,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4040,7 +4205,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4048,7 +4213,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4056,7 +4221,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4064,7 +4229,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4072,7 +4237,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4080,7 +4245,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4088,7 +4253,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4096,7 +4261,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4104,7 +4269,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4112,7 +4277,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4120,7 +4285,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4128,7 +4293,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4136,7 +4301,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4144,7 +4309,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4152,7 +4317,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4160,7 +4325,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4168,7 +4333,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4176,7 +4341,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4184,7 +4349,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4192,7 +4357,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4200,7 +4365,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4208,7 +4373,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4216,7 +4381,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4224,7 +4389,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4232,7 +4397,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4240,7 +4405,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4248,7 +4413,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4256,7 +4421,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4264,7 +4429,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4272,7 +4437,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4280,7 +4445,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4288,7 +4453,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4296,7 +4461,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4304,7 +4469,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4312,7 +4477,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4320,7 +4485,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4328,7 +4493,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4336,7 +4501,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4344,7 +4509,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4352,7 +4517,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4360,7 +4525,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4368,7 +4533,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4376,7 +4541,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4384,7 +4549,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4392,7 +4557,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4400,7 +4565,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4408,7 +4573,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4416,7 +4581,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4424,7 +4589,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -572,7 +572,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="D2">
-        <v>72.7001953125</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -586,7 +586,7 @@
         <v>82</v>
       </c>
       <c r="D3">
-        <v>82</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,7 +600,7 @@
         <v>99.5</v>
       </c>
       <c r="D4">
-        <v>99.5</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -614,7 +614,7 @@
         <v>93.77978515625</v>
       </c>
       <c r="D5">
-        <v>93.77978515625</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -628,7 +628,7 @@
         <v>73.91015625</v>
       </c>
       <c r="D6">
-        <v>73.91015625</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -642,7 +642,7 @@
         <v>57</v>
       </c>
       <c r="D7">
-        <v>57</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -656,7 +656,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D8">
-        <v>82.18017578125</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -670,7 +670,7 @@
         <v>81.39990234375</v>
       </c>
       <c r="D9">
-        <v>81.39990234375</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -684,7 +684,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="D10">
-        <v>65.14990234375</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -698,7 +698,7 @@
         <v>92.330078125</v>
       </c>
       <c r="D11">
-        <v>92.330078125</v>
+        <v>38.27</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -712,7 +712,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D12">
-        <v>64.580078125</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -726,7 +726,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D13">
-        <v>81.47998046875</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -740,7 +740,7 @@
         <v>96.0498046875</v>
       </c>
       <c r="D14">
-        <v>96.0498046875</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -754,7 +754,7 @@
         <v>64.02978515625</v>
       </c>
       <c r="D15">
-        <v>64.02978515625</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -768,7 +768,7 @@
         <v>74.89990234375</v>
       </c>
       <c r="D16">
-        <v>74.89990234375</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -782,7 +782,7 @@
         <v>92.77978515625</v>
       </c>
       <c r="D17">
-        <v>92.77978515625</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -796,7 +796,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="D18">
-        <v>85.7001953125</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -810,7 +810,7 @@
         <v>86.7001953125</v>
       </c>
       <c r="D19">
-        <v>86.7001953125</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -824,7 +824,7 @@
         <v>67.8701171875</v>
       </c>
       <c r="D20">
-        <v>67.8701171875</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -838,7 +838,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="D21">
-        <v>83.2001953125</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -852,7 +852,7 @@
         <v>84.5</v>
       </c>
       <c r="D22">
-        <v>84.5</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -866,7 +866,7 @@
         <v>85.580078125</v>
       </c>
       <c r="D23">
-        <v>85.580078125</v>
+        <v>58.37</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -880,7 +880,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D24">
-        <v>72.18017578125</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -894,7 +894,7 @@
         <v>81.8798828125</v>
       </c>
       <c r="D25">
-        <v>81.8798828125</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -908,7 +908,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D26">
-        <v>96.47998046875</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -922,7 +922,7 @@
         <v>70.14990234375</v>
       </c>
       <c r="D27">
-        <v>70.14990234375</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -936,7 +936,7 @@
         <v>68.2998046875</v>
       </c>
       <c r="D28">
-        <v>68.2998046875</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -950,7 +950,7 @@
         <v>92.89990234375</v>
       </c>
       <c r="D29">
-        <v>92.89990234375</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -964,7 +964,7 @@
         <v>63.39990234375</v>
       </c>
       <c r="D30">
-        <v>63.39990234375</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -978,7 +978,7 @@
         <v>77.47998046875</v>
       </c>
       <c r="D31">
-        <v>77.47998046875</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -992,7 +992,7 @@
         <v>90</v>
       </c>
       <c r="D32">
-        <v>90</v>
+        <v>42.47</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1006,7 +1006,7 @@
         <v>82.60986328125</v>
       </c>
       <c r="D33">
-        <v>82.60986328125</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1020,7 +1020,7 @@
         <v>105.5</v>
       </c>
       <c r="D34">
-        <v>105.5</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1034,7 +1034,7 @@
         <v>60.8798828125</v>
       </c>
       <c r="D35">
-        <v>60.8798828125</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1048,7 +1048,7 @@
         <v>88.18017578125</v>
       </c>
       <c r="D36">
-        <v>88.18017578125</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1062,7 +1062,7 @@
         <v>86.60009765625</v>
       </c>
       <c r="D37">
-        <v>86.60009765625</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1076,7 +1076,7 @@
         <v>73.77978515625</v>
       </c>
       <c r="D38">
-        <v>73.77978515625</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1090,7 +1090,7 @@
         <v>79.4501953125</v>
       </c>
       <c r="D39">
-        <v>79.4501953125</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1104,7 +1104,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D40">
-        <v>64.580078125</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1118,7 +1118,7 @@
         <v>36.429931640625</v>
       </c>
       <c r="D41">
-        <v>36.429931640625</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1132,7 +1132,7 @@
         <v>69.5</v>
       </c>
       <c r="D42">
-        <v>69.5</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1146,7 +1146,7 @@
         <v>91.47998046875</v>
       </c>
       <c r="D43">
-        <v>91.47998046875</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1160,7 +1160,7 @@
         <v>71.5</v>
       </c>
       <c r="D44">
-        <v>71.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1174,7 +1174,7 @@
         <v>84.47998046875</v>
       </c>
       <c r="D45">
-        <v>84.47998046875</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1188,7 +1188,7 @@
         <v>95.3798828125</v>
       </c>
       <c r="D46">
-        <v>95.3798828125</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1202,7 +1202,7 @@
         <v>92.7001953125</v>
       </c>
       <c r="D47">
-        <v>92.7001953125</v>
+        <v>55.19</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1216,7 +1216,7 @@
         <v>79.27978515625</v>
       </c>
       <c r="D48">
-        <v>79.27978515625</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1230,7 +1230,7 @@
         <v>87.5</v>
       </c>
       <c r="D49">
-        <v>87.5</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1244,7 +1244,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D50">
-        <v>82.18017578125</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1258,7 +1258,7 @@
         <v>95.5</v>
       </c>
       <c r="D51">
-        <v>95.5</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1272,7 +1272,7 @@
         <v>93.47998046875</v>
       </c>
       <c r="D52">
-        <v>93.47998046875</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1286,7 +1286,7 @@
         <v>77.3798828125</v>
       </c>
       <c r="D53">
-        <v>77.3798828125</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2457,282 +2457,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>211</v>
+        <v>166.77</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B3">
-        <v>199</v>
+        <v>156.27</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>192.9599609375</v>
+        <v>152.77</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>192.099609375</v>
+        <v>151.1498828125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>191</v>
+        <v>150.24998046875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7">
-        <v>190.759765625</v>
+        <v>149.94998046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>187.5595703125</v>
+        <v>149.83990234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>186.9599609375</v>
+        <v>148.74978515625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B10">
-        <v>185.7998046875</v>
+        <v>147.8901953125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B11">
-        <v>185.5595703125</v>
+        <v>147.84998046875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B12">
-        <v>185.400390625</v>
+        <v>146.5701953125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>184.66015625</v>
+        <v>143.950078125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>182.9599609375</v>
+        <v>140.46990234375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B15">
-        <v>180</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16">
-        <v>176.3603515625</v>
+        <v>136.67009765625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>175</v>
+        <v>136.6198046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B18">
-        <v>173.400390625</v>
+        <v>136.2498828125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B19">
-        <v>173.2001953125</v>
+        <v>134.98017578125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B20">
-        <v>171.400390625</v>
+        <v>134.04998046875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>171.16015625</v>
+        <v>133.37978515625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B22">
-        <v>169</v>
+        <v>132.77</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B23">
-        <v>168.9599609375</v>
+        <v>132.47</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B24">
-        <v>166.400390625</v>
+        <v>132.05017578125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B25">
-        <v>165.2197265625</v>
+        <v>131.38990234375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B26">
-        <v>164.3603515625</v>
+        <v>130.600078125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B27">
-        <v>164.3603515625</v>
+        <v>128.04978515625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="B28">
-        <v>164</v>
+        <v>127.35017578125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B29">
-        <v>163.759765625</v>
+        <v>127.35017578125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B30">
-        <v>162.9599609375</v>
+        <v>127.2701953125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B31">
-        <v>162.7998046875</v>
+        <v>125.04978515625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B32">
-        <v>158.900390625</v>
+        <v>124.37</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B33">
-        <v>158.5595703125</v>
+        <v>122.980078125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>154.9599609375</v>
+        <v>122.050078125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B35">
-        <v>154.759765625</v>
+        <v>121.96990234375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B36">
-        <v>149.7998046875</v>
+        <v>119.97998046875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2740,119 +2740,119 @@
         <v>7</v>
       </c>
       <c r="B37">
-        <v>147.8203125</v>
+        <v>119.71015625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B38">
-        <v>147.5595703125</v>
+        <v>119.54998046875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B39">
-        <v>145.400390625</v>
+        <v>111.80986328125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B40">
-        <v>144.3603515625</v>
+        <v>111.1001953125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="B41">
-        <v>143</v>
+        <v>110.7701953125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B42">
-        <v>140.2998046875</v>
+        <v>107.60990234375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B43">
-        <v>139</v>
+        <v>106.71978515625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>136.599609375</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B45">
-        <v>135.740234375</v>
+        <v>103.8898828125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B46">
-        <v>130.2998046875</v>
+        <v>103.6498828125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47">
-        <v>129.16015625</v>
+        <v>101.0501953125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B48">
-        <v>129.16015625</v>
+        <v>101.0498046875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B49">
-        <v>128.0595703125</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B50">
-        <v>126.7998046875</v>
+        <v>99.27011718750001</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B51">
-        <v>121.759765625</v>
+        <v>94.76990234375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2860,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="B52">
-        <v>114</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2868,7 +2868,7 @@
         <v>42</v>
       </c>
       <c r="B53">
-        <v>72.85986328125</v>
+        <v>53.929931640625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -572,7 +572,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="D2">
-        <v>38.07</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -586,7 +586,7 @@
         <v>82</v>
       </c>
       <c r="D3">
-        <v>50.77</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -600,7 +600,7 @@
         <v>99.5</v>
       </c>
       <c r="D4">
-        <v>67.27</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -614,7 +614,7 @@
         <v>93.77978515625</v>
       </c>
       <c r="D5">
-        <v>54.97</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -628,7 +628,7 @@
         <v>73.91015625</v>
       </c>
       <c r="D6">
-        <v>45.8</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -642,7 +642,7 @@
         <v>57</v>
       </c>
       <c r="D7">
-        <v>28.8</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -656,7 +656,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D8">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -670,7 +670,7 @@
         <v>81.39990234375</v>
       </c>
       <c r="D9">
-        <v>40.57</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -684,7 +684,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="D10">
-        <v>42.46</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -698,7 +698,7 @@
         <v>92.330078125</v>
       </c>
       <c r="D11">
-        <v>38.27</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -712,7 +712,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D12">
-        <v>58.4</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -726,7 +726,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D13">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -740,7 +740,7 @@
         <v>96.0498046875</v>
       </c>
       <c r="D14">
-        <v>40.57</v>
+        <v>70.76000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -754,7 +754,7 @@
         <v>64.02978515625</v>
       </c>
       <c r="D15">
-        <v>42.69</v>
+        <v>78.98999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -768,7 +768,7 @@
         <v>74.89990234375</v>
       </c>
       <c r="D16">
-        <v>56.49</v>
+        <v>87.34</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -782,7 +782,7 @@
         <v>92.77978515625</v>
       </c>
       <c r="D17">
-        <v>40.6</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -796,7 +796,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="D18">
-        <v>41.57</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -810,7 +810,7 @@
         <v>86.7001953125</v>
       </c>
       <c r="D19">
-        <v>59.87</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -824,7 +824,7 @@
         <v>67.8701171875</v>
       </c>
       <c r="D20">
-        <v>31.4</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -838,7 +838,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="D21">
-        <v>27.9</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -852,7 +852,7 @@
         <v>84.5</v>
       </c>
       <c r="D22">
-        <v>39.87</v>
+        <v>78.86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -866,7 +866,7 @@
         <v>85.580078125</v>
       </c>
       <c r="D23">
-        <v>58.37</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -880,7 +880,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D24">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -894,7 +894,7 @@
         <v>81.8798828125</v>
       </c>
       <c r="D25">
-        <v>69.27</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -908,7 +908,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D26">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -922,7 +922,7 @@
         <v>70.14990234375</v>
       </c>
       <c r="D27">
-        <v>79.69</v>
+        <v>102.44</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -936,7 +936,7 @@
         <v>68.2998046875</v>
       </c>
       <c r="D28">
-        <v>32.75</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -950,7 +950,7 @@
         <v>92.89990234375</v>
       </c>
       <c r="D29">
-        <v>47.57</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -964,7 +964,7 @@
         <v>63.39990234375</v>
       </c>
       <c r="D30">
-        <v>31.37</v>
+        <v>65.26000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -978,7 +978,7 @@
         <v>77.47998046875</v>
       </c>
       <c r="D31">
-        <v>70.37</v>
+        <v>80.45999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -992,7 +992,7 @@
         <v>90</v>
       </c>
       <c r="D32">
-        <v>42.47</v>
+        <v>68.26000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1006,7 +1006,7 @@
         <v>82.60986328125</v>
       </c>
       <c r="D33">
-        <v>29.2</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1020,7 +1020,7 @@
         <v>105.5</v>
       </c>
       <c r="D34">
-        <v>50.77</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1034,7 +1034,7 @@
         <v>60.8798828125</v>
       </c>
       <c r="D35">
-        <v>42.77</v>
+        <v>77.45999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1048,7 +1048,7 @@
         <v>88.18017578125</v>
       </c>
       <c r="D36">
-        <v>43.87</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1062,7 +1062,7 @@
         <v>86.60009765625</v>
       </c>
       <c r="D37">
-        <v>50.07</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1076,7 +1076,7 @@
         <v>73.77978515625</v>
       </c>
       <c r="D38">
-        <v>54.27</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1090,7 +1090,7 @@
         <v>79.4501953125</v>
       </c>
       <c r="D39">
-        <v>21.6</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1104,7 +1104,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D40">
-        <v>57.47</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1118,7 +1118,7 @@
         <v>36.429931640625</v>
       </c>
       <c r="D41">
-        <v>17.5</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1132,7 +1132,7 @@
         <v>69.5</v>
       </c>
       <c r="D42">
-        <v>36.36</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1146,7 +1146,7 @@
         <v>91.47998046875</v>
       </c>
       <c r="D43">
-        <v>58.47</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1160,7 +1160,7 @@
         <v>71.5</v>
       </c>
       <c r="D44">
-        <v>28.6</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1174,7 +1174,7 @@
         <v>84.47998046875</v>
       </c>
       <c r="D45">
-        <v>35.5</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1188,7 +1188,7 @@
         <v>95.3798828125</v>
       </c>
       <c r="D46">
-        <v>40.87</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1202,7 +1202,7 @@
         <v>92.7001953125</v>
       </c>
       <c r="D47">
-        <v>55.19</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1216,7 +1216,7 @@
         <v>79.27978515625</v>
       </c>
       <c r="D48">
-        <v>45.77</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1230,7 +1230,7 @@
         <v>87.5</v>
       </c>
       <c r="D49">
-        <v>49.27</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1244,7 +1244,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D50">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1258,7 +1258,7 @@
         <v>95.5</v>
       </c>
       <c r="D51">
-        <v>57.27</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1272,7 +1272,7 @@
         <v>93.47998046875</v>
       </c>
       <c r="D52">
-        <v>40.57</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1286,7 +1286,7 @@
         <v>77.3798828125</v>
       </c>
       <c r="D53">
-        <v>26.51</v>
+        <v>43.11</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2457,314 +2457,314 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B2">
-        <v>166.77</v>
+        <v>190.03998046875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B3">
-        <v>156.27</v>
+        <v>187.94017578125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>152.77</v>
+        <v>187.94017578125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>151.1498828125</v>
+        <v>187.23978515625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>150.24998046875</v>
+        <v>185.86</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>149.94998046875</v>
+        <v>183.93998046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8">
-        <v>149.83990234375</v>
+        <v>179.6398828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="B9">
-        <v>148.74978515625</v>
+        <v>178.73998046875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10">
-        <v>147.8901953125</v>
+        <v>175.56</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11">
-        <v>147.84998046875</v>
+        <v>174.65990234375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>146.5701953125</v>
+        <v>172.58990234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>143.950078125</v>
+        <v>172.090078125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B14">
-        <v>140.46990234375</v>
+        <v>171.87998046875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B15">
-        <v>136.77</v>
+        <v>171.17978515625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B16">
-        <v>136.67009765625</v>
+        <v>170.56</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B17">
-        <v>136.6198046875</v>
+        <v>169.58017578125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>136.2498828125</v>
+        <v>166.8098046875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B19">
-        <v>134.98017578125</v>
+        <v>166.73978515625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>134.04998046875</v>
+        <v>165.9401953125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B21">
-        <v>133.37978515625</v>
+        <v>165.93978515625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>132.77</v>
+        <v>165.44017578125</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23">
-        <v>132.47</v>
+        <v>163.85986328125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>132.05017578125</v>
+        <v>163.36</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B25">
-        <v>131.38990234375</v>
+        <v>163.230078125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B26">
-        <v>130.600078125</v>
+        <v>162.23990234375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B27">
-        <v>128.04978515625</v>
+        <v>161.95990234375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="B28">
-        <v>127.35017578125</v>
+        <v>161.4601953125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>127.35017578125</v>
+        <v>159.93998046875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B30">
-        <v>127.2701953125</v>
+        <v>159.3501953125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B31">
-        <v>125.04978515625</v>
+        <v>159.01015625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B32">
-        <v>124.37</v>
+        <v>158.26</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>122.980078125</v>
+        <v>157.93998046875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B34">
-        <v>122.050078125</v>
+        <v>156.26009765625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B35">
-        <v>121.96990234375</v>
+        <v>155.86</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B36">
-        <v>119.97998046875</v>
+        <v>154.36</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B37">
-        <v>119.71015625</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B38">
-        <v>119.54998046875</v>
+        <v>154.0001953125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>111.80986328125</v>
+        <v>153.340078125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B40">
-        <v>111.1001953125</v>
+        <v>152.540078125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2772,95 +2772,95 @@
         <v>3</v>
       </c>
       <c r="B41">
-        <v>110.7701953125</v>
+        <v>151.7601953125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B42">
-        <v>107.60990234375</v>
+        <v>151.5398828125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B43">
-        <v>106.71978515625</v>
+        <v>150.1601953125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B44">
-        <v>105.86</v>
+        <v>145.85990234375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B45">
-        <v>103.8898828125</v>
+        <v>143.01978515625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B46">
-        <v>103.6498828125</v>
+        <v>140.7201171875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B47">
-        <v>101.0501953125</v>
+        <v>138.3398828125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B48">
-        <v>101.0498046875</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B49">
-        <v>100.1</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B50">
-        <v>99.27011718750001</v>
+        <v>128.65990234375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B51">
-        <v>94.76990234375</v>
+        <v>120.4898828125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B52">
-        <v>85.8</v>
+        <v>106.8898046875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2868,7 +2868,7 @@
         <v>42</v>
       </c>
       <c r="B53">
-        <v>53.929931640625</v>
+        <v>89.57993164062501</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="57">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>Rodada 3</t>
+  </si>
+  <si>
+    <t>Rodada 4</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -547,10 +550,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,10 +563,13 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -572,12 +578,15 @@
         <v>72.7001953125</v>
       </c>
       <c r="D2">
-        <v>79.06</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>79.85986328125</v>
+      </c>
+      <c r="E2">
+        <v>79.85986328125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -586,12 +595,15 @@
         <v>82</v>
       </c>
       <c r="D3">
-        <v>72.16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>72.9599609375</v>
+      </c>
+      <c r="E3">
+        <v>72.9599609375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -600,12 +612,15 @@
         <v>99.5</v>
       </c>
       <c r="D4">
-        <v>71.06</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>71.85986328125</v>
+      </c>
+      <c r="E4">
+        <v>71.85986328125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -614,12 +629,15 @@
         <v>93.77978515625</v>
       </c>
       <c r="D5">
-        <v>93.45999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>94.259765625</v>
+      </c>
+      <c r="E5">
+        <v>94.259765625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -628,12 +646,15 @@
         <v>73.91015625</v>
       </c>
       <c r="D6">
-        <v>85.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>85.10009765625</v>
+      </c>
+      <c r="E6">
+        <v>85.10009765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -642,12 +663,15 @@
         <v>57</v>
       </c>
       <c r="D7">
-        <v>79.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>80.2001953125</v>
+      </c>
+      <c r="E7">
+        <v>80.2001953125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -656,12 +680,15 @@
         <v>82.18017578125</v>
       </c>
       <c r="D8">
-        <v>105.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>105.759765625</v>
+      </c>
+      <c r="E8">
+        <v>105.759765625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -670,12 +697,15 @@
         <v>81.39990234375</v>
       </c>
       <c r="D9">
-        <v>80.56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>81.35986328125</v>
+      </c>
+      <c r="E9">
+        <v>81.35986328125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -684,12 +714,15 @@
         <v>65.14990234375</v>
       </c>
       <c r="D10">
-        <v>80.70999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>80.2998046875</v>
+      </c>
+      <c r="E10">
+        <v>80.2998046875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -698,12 +731,15 @@
         <v>92.330078125</v>
       </c>
       <c r="D11">
-        <v>79.76000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>80.56005859375</v>
+      </c>
+      <c r="E11">
+        <v>80.56005859375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -712,12 +748,15 @@
         <v>64.580078125</v>
       </c>
       <c r="D12">
-        <v>98.65000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>98.64990234375</v>
+      </c>
+      <c r="E12">
+        <v>98.64990234375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -726,12 +765,15 @@
         <v>81.47998046875</v>
       </c>
       <c r="D13">
-        <v>78.45999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>79.259765625</v>
+      </c>
+      <c r="E13">
+        <v>79.259765625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -740,12 +782,15 @@
         <v>96.0498046875</v>
       </c>
       <c r="D14">
-        <v>70.76000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>71.56005859375</v>
+      </c>
+      <c r="E14">
+        <v>71.56005859375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -754,12 +799,15 @@
         <v>64.02978515625</v>
       </c>
       <c r="D15">
-        <v>78.98999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>78.990234375</v>
+      </c>
+      <c r="E15">
+        <v>78.990234375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -768,12 +816,15 @@
         <v>74.89990234375</v>
       </c>
       <c r="D16">
-        <v>87.34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>87.33984375</v>
+      </c>
+      <c r="E16">
+        <v>87.33984375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -782,12 +833,15 @@
         <v>92.77978515625</v>
       </c>
       <c r="D17">
-        <v>78.40000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>78.39990234375</v>
+      </c>
+      <c r="E17">
+        <v>78.39990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -796,12 +850,15 @@
         <v>85.7001953125</v>
       </c>
       <c r="D18">
-        <v>64.45999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>65.259765625</v>
+      </c>
+      <c r="E18">
+        <v>65.259765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -810,12 +867,15 @@
         <v>86.7001953125</v>
       </c>
       <c r="D19">
-        <v>74.76000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>75.56005859375</v>
+      </c>
+      <c r="E19">
+        <v>75.56005859375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -824,12 +884,15 @@
         <v>67.8701171875</v>
       </c>
       <c r="D20">
-        <v>72.84999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>73.64990234375</v>
+      </c>
+      <c r="E20">
+        <v>73.64990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -838,12 +901,15 @@
         <v>83.2001953125</v>
       </c>
       <c r="D21">
-        <v>70.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>70.7998046875</v>
+      </c>
+      <c r="E21">
+        <v>70.7998046875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -852,12 +918,15 @@
         <v>84.5</v>
       </c>
       <c r="D22">
-        <v>78.86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>78.85986328125</v>
+      </c>
+      <c r="E22">
+        <v>78.85986328125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -866,12 +935,15 @@
         <v>85.580078125</v>
       </c>
       <c r="D23">
-        <v>66.95999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>67.759765625</v>
+      </c>
+      <c r="E23">
+        <v>67.759765625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -880,12 +952,15 @@
         <v>72.18017578125</v>
       </c>
       <c r="D24">
-        <v>97.40000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>97.39990234375</v>
+      </c>
+      <c r="E24">
+        <v>97.39990234375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -894,12 +969,15 @@
         <v>81.8798828125</v>
       </c>
       <c r="D25">
-        <v>97.76000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>97.759765625</v>
+      </c>
+      <c r="E25">
+        <v>97.759765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -908,12 +986,15 @@
         <v>96.47998046875</v>
       </c>
       <c r="D26">
-        <v>87.45999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>87.4599609375</v>
+      </c>
+      <c r="E26">
+        <v>87.4599609375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -922,12 +1003,15 @@
         <v>70.14990234375</v>
       </c>
       <c r="D27">
-        <v>102.44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>101.740234375</v>
+      </c>
+      <c r="E27">
+        <v>101.740234375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -936,12 +1020,15 @@
         <v>68.2998046875</v>
       </c>
       <c r="D28">
-        <v>38.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>38.590087890625</v>
+      </c>
+      <c r="E28">
+        <v>38.590087890625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -950,12 +1037,15 @@
         <v>92.89990234375</v>
       </c>
       <c r="D29">
-        <v>81.76000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>81.759765625</v>
+      </c>
+      <c r="E29">
+        <v>81.759765625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -964,12 +1054,15 @@
         <v>63.39990234375</v>
       </c>
       <c r="D30">
-        <v>65.26000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>65.259765625</v>
+      </c>
+      <c r="E30">
+        <v>65.259765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -978,12 +1071,15 @@
         <v>77.47998046875</v>
       </c>
       <c r="D31">
-        <v>80.45999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>81.259765625</v>
+      </c>
+      <c r="E31">
+        <v>81.259765625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>44.260009765625</v>
@@ -992,12 +1088,15 @@
         <v>90</v>
       </c>
       <c r="D32">
-        <v>68.26000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>68.9599609375</v>
+      </c>
+      <c r="E32">
+        <v>68.9599609375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>84.259765625</v>
@@ -1008,10 +1107,13 @@
       <c r="D33">
         <v>81.25</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33">
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>64.56005859375</v>
@@ -1020,12 +1122,15 @@
         <v>105.5</v>
       </c>
       <c r="D34">
-        <v>80.36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>81.16015625</v>
+      </c>
+      <c r="E34">
+        <v>81.16015625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>43.510009765625</v>
@@ -1034,12 +1139,15 @@
         <v>60.8798828125</v>
       </c>
       <c r="D35">
-        <v>77.45999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>78.259765625</v>
+      </c>
+      <c r="E35">
+        <v>78.259765625</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>57.4599609375</v>
@@ -1048,12 +1156,15 @@
         <v>88.18017578125</v>
       </c>
       <c r="D36">
-        <v>77.26000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>77.259765625</v>
+      </c>
+      <c r="E36">
+        <v>77.259765625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>64.56005859375</v>
@@ -1062,12 +1173,15 @@
         <v>86.60009765625</v>
       </c>
       <c r="D37">
-        <v>69.66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>70.35986328125</v>
+      </c>
+      <c r="E37">
+        <v>70.35986328125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>59.25</v>
@@ -1076,12 +1190,15 @@
         <v>73.77978515625</v>
       </c>
       <c r="D38">
-        <v>92.95999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>93.759765625</v>
+      </c>
+      <c r="E38">
+        <v>93.759765625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -1090,12 +1207,15 @@
         <v>79.4501953125</v>
       </c>
       <c r="D39">
-        <v>79.90000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>78.93994140625</v>
+      </c>
+      <c r="E39">
+        <v>78.93994140625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -1104,12 +1224,15 @@
         <v>64.580078125</v>
       </c>
       <c r="D40">
-        <v>88.76000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>88.759765625</v>
+      </c>
+      <c r="E40">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -1118,12 +1241,15 @@
         <v>36.429931640625</v>
       </c>
       <c r="D41">
-        <v>53.15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>54.35009765625</v>
+      </c>
+      <c r="E41">
+        <v>54.35009765625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -1132,12 +1258,15 @@
         <v>69.5</v>
       </c>
       <c r="D42">
-        <v>84.86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>83.64990234375</v>
+      </c>
+      <c r="E42">
+        <v>83.64990234375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -1146,12 +1275,15 @@
         <v>91.47998046875</v>
       </c>
       <c r="D43">
-        <v>98.56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>99.35986328125</v>
+      </c>
+      <c r="E43">
+        <v>99.35986328125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -1160,12 +1292,15 @@
         <v>71.5</v>
       </c>
       <c r="D44">
-        <v>66.59999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>67.39990234375</v>
+      </c>
+      <c r="E44">
+        <v>67.39990234375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -1174,12 +1309,15 @@
         <v>84.47998046875</v>
       </c>
       <c r="D45">
-        <v>87.40000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>87.39990234375</v>
+      </c>
+      <c r="E45">
+        <v>87.39990234375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -1188,12 +1326,15 @@
         <v>95.3798828125</v>
       </c>
       <c r="D46">
-        <v>56.16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>56.9599609375</v>
+      </c>
+      <c r="E46">
+        <v>56.9599609375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -1202,12 +1343,15 @@
         <v>92.7001953125</v>
       </c>
       <c r="D47">
-        <v>73.23999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>72.740234375</v>
+      </c>
+      <c r="E47">
+        <v>72.740234375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -1216,12 +1360,15 @@
         <v>79.27978515625</v>
       </c>
       <c r="D48">
-        <v>86.66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>86.66015625</v>
+      </c>
+      <c r="E48">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -1230,12 +1377,15 @@
         <v>87.5</v>
       </c>
       <c r="D49">
-        <v>88.06</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>88.06005859375</v>
+      </c>
+      <c r="E49">
+        <v>88.06005859375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -1244,12 +1394,15 @@
         <v>82.18017578125</v>
       </c>
       <c r="D50">
-        <v>105.76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>105.759765625</v>
+      </c>
+      <c r="E50">
+        <v>105.759765625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -1258,12 +1411,15 @@
         <v>95.5</v>
       </c>
       <c r="D51">
-        <v>60.36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>61.159912109375</v>
+      </c>
+      <c r="E51">
+        <v>61.159912109375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -1272,12 +1428,15 @@
         <v>93.47998046875</v>
       </c>
       <c r="D52">
-        <v>85.26000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>85.259765625</v>
+      </c>
+      <c r="E52">
+        <v>85.259765625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -1286,12 +1445,15 @@
         <v>77.3798828125</v>
       </c>
       <c r="D53">
-        <v>43.11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>43.909912109375</v>
+      </c>
+      <c r="E53">
+        <v>43.909912109375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1300,6 +1462,9 @@
         <v>0</v>
       </c>
       <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
         <v>0</v>
       </c>
     </row>
@@ -1315,267 +1480,267 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1595,7 +1760,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1603,7 +1768,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1611,7 +1776,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1619,7 +1784,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1627,7 +1792,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1635,7 +1800,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1643,7 +1808,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1651,7 +1816,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1659,7 +1824,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1667,7 +1832,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1675,7 +1840,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1683,7 +1848,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1691,7 +1856,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1699,7 +1864,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1707,7 +1872,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1715,7 +1880,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1723,7 +1888,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1731,7 +1896,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1739,7 +1904,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1747,7 +1912,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1755,7 +1920,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1763,7 +1928,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1771,7 +1936,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1779,7 +1944,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1787,7 +1952,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1795,7 +1960,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1803,7 +1968,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1811,7 +1976,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1819,7 +1984,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1827,7 +1992,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1835,7 +2000,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1843,7 +2008,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1851,7 +2016,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1859,7 +2024,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1867,7 +2032,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1875,7 +2040,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1883,7 +2048,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1891,7 +2056,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1899,7 +2064,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1907,7 +2072,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1915,7 +2080,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1923,7 +2088,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1931,7 +2096,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1939,7 +2104,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1947,7 +2112,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1955,7 +2120,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1963,7 +2128,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1971,7 +2136,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1979,7 +2144,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1987,7 +2152,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1995,7 +2160,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2003,7 +2168,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2026,7 +2191,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -2034,7 +2199,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -2042,7 +2207,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -2050,7 +2215,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -2058,7 +2223,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -2066,7 +2231,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -2074,7 +2239,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -2082,7 +2247,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -2090,7 +2255,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -2098,7 +2263,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -2106,7 +2271,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -2114,7 +2279,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -2122,7 +2287,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -2130,7 +2295,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -2138,7 +2303,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -2146,7 +2311,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -2154,7 +2319,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -2162,7 +2327,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -2170,7 +2335,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -2178,7 +2343,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -2186,7 +2351,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -2194,7 +2359,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -2202,7 +2367,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -2210,7 +2375,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -2218,7 +2383,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -2226,7 +2391,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -2234,7 +2399,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -2242,7 +2407,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -2250,7 +2415,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30">
         <v>57.60009765625</v>
@@ -2258,7 +2423,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>57.4599609375</v>
@@ -2266,7 +2431,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32">
         <v>57.449951171875</v>
@@ -2274,7 +2439,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>56.9599609375</v>
@@ -2282,7 +2447,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>56.260009765625</v>
@@ -2290,7 +2455,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>55.89990234375</v>
@@ -2298,7 +2463,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36">
         <v>54.60009765625</v>
@@ -2306,7 +2471,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37">
         <v>54.159912109375</v>
@@ -2314,7 +2479,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38">
         <v>54.10009765625</v>
@@ -2322,7 +2487,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -2330,7 +2495,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>53.659912109375</v>
@@ -2338,7 +2503,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B41">
         <v>51.56005859375</v>
@@ -2346,7 +2511,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42">
         <v>51.260009765625</v>
@@ -2354,7 +2519,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B43">
         <v>49.760009765625</v>
@@ -2362,7 +2527,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>49</v>
@@ -2370,7 +2535,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45">
         <v>47.860107421875</v>
@@ -2378,7 +2543,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -2386,7 +2551,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B47">
         <v>44.260009765625</v>
@@ -2394,7 +2559,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48">
         <v>44.06005859375</v>
@@ -2402,7 +2567,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B49">
         <v>43.510009765625</v>
@@ -2410,7 +2575,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50">
         <v>42.9599609375</v>
@@ -2418,7 +2583,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B51">
         <v>40.60009765625</v>
@@ -2426,7 +2591,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B52">
         <v>38.260009765625</v>
@@ -2434,7 +2599,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B53">
         <v>37.820068359375</v>
@@ -2457,418 +2622,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B2">
-        <v>190.03998046875</v>
+        <v>293.69970703125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>187.94017578125</v>
+        <v>293.69970703125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B4">
-        <v>187.94017578125</v>
+        <v>290.19970703125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>187.23978515625</v>
+        <v>282.29931640625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>185.86</v>
+        <v>277.3994140625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>183.93998046875</v>
+        <v>273.63037109375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>179.6398828125</v>
+        <v>271.39990234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B9">
-        <v>178.73998046875</v>
+        <v>267.8203125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>175.56</v>
+        <v>266.97998046875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B11">
-        <v>174.65990234375</v>
+        <v>263.99951171875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="B12">
-        <v>172.58990234375</v>
+        <v>263.6201171875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>172.090078125</v>
+        <v>261.8798828125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B14">
-        <v>171.87998046875</v>
+        <v>261.29931640625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B15">
-        <v>171.17978515625</v>
+        <v>259.27978515625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>170.56</v>
+        <v>256.41943359375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B17">
-        <v>169.58017578125</v>
+        <v>253.4501953125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B18">
-        <v>166.8098046875</v>
+        <v>252.60009765625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>166.73978515625</v>
+        <v>249.57958984375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>165.9401953125</v>
+        <v>249.57958984375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>165.93978515625</v>
+        <v>245.10986328125</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B22">
-        <v>165.44017578125</v>
+        <v>244.11962890625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B23">
-        <v>163.85986328125</v>
+        <v>244.1103515625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>163.36</v>
+        <v>243.2197265625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B25">
-        <v>163.230078125</v>
+        <v>242.69970703125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B26">
-        <v>162.23990234375</v>
+        <v>242.2197265625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>161.95990234375</v>
+        <v>242.099609375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B28">
-        <v>161.4601953125</v>
+        <v>239.99951171875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29">
-        <v>159.93998046875</v>
+        <v>239.99951171875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B30">
-        <v>159.3501953125</v>
+        <v>239.169921875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B31">
-        <v>159.01015625</v>
+        <v>238.1806640625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B32">
-        <v>158.26</v>
+        <v>237.8203125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B33">
-        <v>157.93998046875</v>
+        <v>237.330078125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B34">
-        <v>156.26009765625</v>
+        <v>236.7998046875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B35">
-        <v>155.86</v>
+        <v>232.419921875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B36">
-        <v>154.36</v>
+        <v>227.919921875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37">
-        <v>154.16</v>
+        <v>227.919921875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B38">
-        <v>154.0001953125</v>
+        <v>227.31982421875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>153.340078125</v>
+        <v>225.74951171875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B40">
-        <v>152.540078125</v>
+        <v>224.7998046875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B41">
-        <v>151.7601953125</v>
+        <v>222.01025390625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B42">
-        <v>151.5398828125</v>
+        <v>221.099609375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B43">
-        <v>150.1601953125</v>
+        <v>217.81982421875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B44">
-        <v>145.85990234375</v>
+        <v>217.400390625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B45">
-        <v>143.01978515625</v>
+        <v>217.3994140625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46">
-        <v>140.7201171875</v>
+        <v>216.2197265625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B47">
-        <v>138.3398828125</v>
+        <v>215.169921875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B48">
-        <v>138.1</v>
+        <v>209.2998046875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B49">
-        <v>136.4</v>
+        <v>206.2998046875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B50">
-        <v>128.65990234375</v>
+        <v>193.91943359375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51">
-        <v>120.4898828125</v>
+        <v>165.19970703125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52">
-        <v>106.8898046875</v>
+        <v>145.47998046875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53">
-        <v>89.57993164062501</v>
+        <v>145.130126953125</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +3053,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2896,7 +3061,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2904,7 +3069,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2912,7 +3077,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2920,7 +3085,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2928,7 +3093,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2936,7 +3101,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2944,7 +3109,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2952,7 +3117,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2960,7 +3125,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2968,7 +3133,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2976,7 +3141,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2984,7 +3149,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2992,7 +3157,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3000,7 +3165,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3008,7 +3173,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3016,7 +3181,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3024,7 +3189,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3032,7 +3197,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3040,7 +3205,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3048,7 +3213,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3056,7 +3221,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3064,7 +3229,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3072,7 +3237,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3080,7 +3245,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3088,7 +3253,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3096,7 +3261,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3104,7 +3269,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3112,7 +3277,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3120,7 +3285,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3128,7 +3293,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3136,7 +3301,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3144,7 +3309,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3152,7 +3317,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3160,7 +3325,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3168,7 +3333,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3176,7 +3341,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3184,7 +3349,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3192,7 +3357,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3200,7 +3365,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3208,7 +3373,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3216,7 +3381,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3224,7 +3389,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3232,7 +3397,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3240,7 +3405,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3248,7 +3413,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3256,7 +3421,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3264,7 +3429,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3272,7 +3437,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3280,7 +3445,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3288,7 +3453,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3296,7 +3461,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3319,7 +3484,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3327,7 +3492,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3335,7 +3500,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3343,7 +3508,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3351,7 +3516,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3359,7 +3524,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3367,7 +3532,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3375,7 +3540,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3383,7 +3548,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3391,7 +3556,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3399,7 +3564,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3407,7 +3572,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3415,7 +3580,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3423,7 +3588,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3431,7 +3596,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3439,7 +3604,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3447,7 +3612,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3455,7 +3620,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3463,7 +3628,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3471,7 +3636,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3479,7 +3644,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3487,7 +3652,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3495,7 +3660,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3503,7 +3668,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3511,7 +3676,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3519,7 +3684,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3527,7 +3692,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3535,7 +3700,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3543,7 +3708,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3551,7 +3716,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3559,7 +3724,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3567,7 +3732,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3575,7 +3740,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3583,7 +3748,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3591,7 +3756,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3599,7 +3764,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3607,7 +3772,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3615,7 +3780,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3623,7 +3788,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3631,7 +3796,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3639,7 +3804,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3647,7 +3812,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3655,7 +3820,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3663,7 +3828,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3671,7 +3836,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3679,7 +3844,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3687,7 +3852,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3695,7 +3860,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3703,7 +3868,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3711,7 +3876,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3719,7 +3884,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3727,7 +3892,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3750,7 +3915,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3758,7 +3923,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3766,7 +3931,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3774,7 +3939,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3782,7 +3947,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3790,7 +3955,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3798,7 +3963,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3806,7 +3971,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3814,7 +3979,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3822,7 +3987,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3830,7 +3995,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3838,7 +4003,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3846,7 +4011,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3854,7 +4019,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3862,7 +4027,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3870,7 +4035,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3878,7 +4043,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3886,7 +4051,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3894,7 +4059,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3902,7 +4067,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3910,7 +4075,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3918,7 +4083,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3926,7 +4091,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3934,7 +4099,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3942,7 +4107,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3950,7 +4115,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3958,7 +4123,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3966,7 +4131,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3974,7 +4139,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3982,7 +4147,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3990,7 +4155,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3998,7 +4163,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4006,7 +4171,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4014,7 +4179,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4022,7 +4187,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4030,7 +4195,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4038,7 +4203,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4046,7 +4211,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4054,7 +4219,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4062,7 +4227,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4070,7 +4235,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4078,7 +4243,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4086,7 +4251,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4094,7 +4259,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4102,7 +4267,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4110,7 +4275,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4118,7 +4283,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4126,7 +4291,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4134,7 +4299,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4142,7 +4307,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4150,7 +4315,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4158,7 +4323,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4181,7 +4346,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4189,7 +4354,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4197,7 +4362,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4205,7 +4370,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4213,7 +4378,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4221,7 +4386,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4229,7 +4394,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4237,7 +4402,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4245,7 +4410,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4253,7 +4418,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4261,7 +4426,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4269,7 +4434,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4277,7 +4442,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4285,7 +4450,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4293,7 +4458,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4301,7 +4466,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4309,7 +4474,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4317,7 +4482,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4325,7 +4490,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4333,7 +4498,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4341,7 +4506,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4349,7 +4514,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4357,7 +4522,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4365,7 +4530,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4373,7 +4538,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4381,7 +4546,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4389,7 +4554,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4397,7 +4562,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4405,7 +4570,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4413,7 +4578,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4421,7 +4586,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4429,7 +4594,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4437,7 +4602,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4445,7 +4610,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4453,7 +4618,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4461,7 +4626,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4469,7 +4634,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4477,7 +4642,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4485,7 +4650,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4493,7 +4658,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4501,7 +4666,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4509,7 +4674,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4517,7 +4682,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4525,7 +4690,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4533,7 +4698,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4541,7 +4706,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4549,7 +4714,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4557,7 +4722,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4565,7 +4730,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4573,7 +4738,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4581,7 +4746,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4589,7 +4754,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="58">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Rolo Compressor ZN</t>
+  </si>
+  <si>
+    <t>RS Expressões da Arte</t>
   </si>
   <si>
     <t>S.E.R. GRILLO</t>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1201,16 +1204,16 @@
         <v>41</v>
       </c>
       <c r="B39">
-        <v>84.85986328125</v>
+        <v>58.25</v>
       </c>
       <c r="C39">
-        <v>79.4501953125</v>
+        <v>63.780029296875</v>
       </c>
       <c r="D39">
-        <v>78.93994140625</v>
+        <v>68.43994140625</v>
       </c>
       <c r="E39">
-        <v>78.93994140625</v>
+        <v>68.43994140625</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1218,16 +1221,16 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>60.159912109375</v>
+        <v>84.85986328125</v>
       </c>
       <c r="C40">
-        <v>64.580078125</v>
+        <v>79.4501953125</v>
       </c>
       <c r="D40">
-        <v>88.759765625</v>
+        <v>78.93994140625</v>
       </c>
       <c r="E40">
-        <v>88.759765625</v>
+        <v>78.93994140625</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1235,16 +1238,16 @@
         <v>43</v>
       </c>
       <c r="B41">
-        <v>49</v>
+        <v>60.159912109375</v>
       </c>
       <c r="C41">
-        <v>36.429931640625</v>
+        <v>64.580078125</v>
       </c>
       <c r="D41">
-        <v>54.35009765625</v>
+        <v>88.759765625</v>
       </c>
       <c r="E41">
-        <v>54.35009765625</v>
+        <v>88.759765625</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1252,16 +1255,16 @@
         <v>44</v>
       </c>
       <c r="B42">
-        <v>61.659912109375</v>
+        <v>49</v>
       </c>
       <c r="C42">
-        <v>69.5</v>
+        <v>36.429931640625</v>
       </c>
       <c r="D42">
-        <v>83.64990234375</v>
+        <v>54.35009765625</v>
       </c>
       <c r="E42">
-        <v>83.64990234375</v>
+        <v>54.35009765625</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1269,16 +1272,16 @@
         <v>45</v>
       </c>
       <c r="B43">
-        <v>42.9599609375</v>
+        <v>61.659912109375</v>
       </c>
       <c r="C43">
-        <v>91.47998046875</v>
+        <v>69.5</v>
       </c>
       <c r="D43">
-        <v>99.35986328125</v>
+        <v>83.64990234375</v>
       </c>
       <c r="E43">
-        <v>99.35986328125</v>
+        <v>83.64990234375</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1286,16 +1289,16 @@
         <v>46</v>
       </c>
       <c r="B44">
-        <v>54.10009765625</v>
+        <v>42.9599609375</v>
       </c>
       <c r="C44">
-        <v>71.5</v>
+        <v>91.47998046875</v>
       </c>
       <c r="D44">
-        <v>67.39990234375</v>
+        <v>99.35986328125</v>
       </c>
       <c r="E44">
-        <v>67.39990234375</v>
+        <v>99.35986328125</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1303,16 +1306,16 @@
         <v>47</v>
       </c>
       <c r="B45">
-        <v>61.9599609375</v>
+        <v>54.10009765625</v>
       </c>
       <c r="C45">
-        <v>84.47998046875</v>
+        <v>71.5</v>
       </c>
       <c r="D45">
-        <v>87.39990234375</v>
+        <v>67.39990234375</v>
       </c>
       <c r="E45">
-        <v>87.39990234375</v>
+        <v>67.39990234375</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1320,16 +1323,16 @@
         <v>48</v>
       </c>
       <c r="B46">
-        <v>64.2001953125</v>
+        <v>61.9599609375</v>
       </c>
       <c r="C46">
-        <v>95.3798828125</v>
+        <v>84.47998046875</v>
       </c>
       <c r="D46">
-        <v>56.9599609375</v>
+        <v>87.39990234375</v>
       </c>
       <c r="E46">
-        <v>56.9599609375</v>
+        <v>87.39990234375</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1337,16 +1340,16 @@
         <v>49</v>
       </c>
       <c r="B47">
-        <v>66.85986328125</v>
+        <v>64.2001953125</v>
       </c>
       <c r="C47">
-        <v>92.7001953125</v>
+        <v>95.3798828125</v>
       </c>
       <c r="D47">
-        <v>72.740234375</v>
+        <v>56.9599609375</v>
       </c>
       <c r="E47">
-        <v>72.740234375</v>
+        <v>56.9599609375</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1354,16 +1357,16 @@
         <v>50</v>
       </c>
       <c r="B48">
-        <v>58.9599609375</v>
+        <v>66.85986328125</v>
       </c>
       <c r="C48">
-        <v>79.27978515625</v>
+        <v>92.7001953125</v>
       </c>
       <c r="D48">
-        <v>86.66015625</v>
+        <v>72.740234375</v>
       </c>
       <c r="E48">
-        <v>86.66015625</v>
+        <v>72.740234375</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1371,16 +1374,16 @@
         <v>51</v>
       </c>
       <c r="B49">
-        <v>70</v>
+        <v>58.9599609375</v>
       </c>
       <c r="C49">
-        <v>87.5</v>
+        <v>79.27978515625</v>
       </c>
       <c r="D49">
-        <v>88.06005859375</v>
+        <v>86.66015625</v>
       </c>
       <c r="E49">
-        <v>88.06005859375</v>
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1388,16 +1391,16 @@
         <v>52</v>
       </c>
       <c r="B50">
-        <v>68.06005859375</v>
+        <v>70</v>
       </c>
       <c r="C50">
-        <v>82.18017578125</v>
+        <v>87.5</v>
       </c>
       <c r="D50">
-        <v>105.759765625</v>
+        <v>88.06005859375</v>
       </c>
       <c r="E50">
-        <v>105.759765625</v>
+        <v>88.06005859375</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1405,16 +1408,16 @@
         <v>53</v>
       </c>
       <c r="B51">
-        <v>51.260009765625</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C51">
-        <v>95.5</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D51">
-        <v>61.159912109375</v>
+        <v>105.759765625</v>
       </c>
       <c r="E51">
-        <v>61.159912109375</v>
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1422,16 +1425,16 @@
         <v>54</v>
       </c>
       <c r="B52">
-        <v>72.16015625</v>
+        <v>51.260009765625</v>
       </c>
       <c r="C52">
-        <v>93.47998046875</v>
+        <v>95.5</v>
       </c>
       <c r="D52">
-        <v>85.259765625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="E52">
-        <v>85.259765625</v>
+        <v>61.159912109375</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1439,16 +1442,16 @@
         <v>55</v>
       </c>
       <c r="B53">
-        <v>55.89990234375</v>
+        <v>72.16015625</v>
       </c>
       <c r="C53">
-        <v>77.3798828125</v>
+        <v>93.47998046875</v>
       </c>
       <c r="D53">
-        <v>43.909912109375</v>
+        <v>85.259765625</v>
       </c>
       <c r="E53">
-        <v>43.909912109375</v>
+        <v>85.259765625</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1456,15 +1459,32 @@
         <v>56</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>55.89990234375</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>77.3798828125</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>43.909912109375</v>
       </c>
       <c r="E54">
+        <v>43.909912109375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
         <v>0</v>
       </c>
     </row>
@@ -1475,7 +1495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:A54"/>
+  <dimension ref="A2:A55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:1">
@@ -1741,6 +1761,11 @@
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1768,7 +1793,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1776,7 +1801,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1784,7 +1809,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1792,7 +1817,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1800,7 +1825,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1808,7 +1833,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1816,7 +1841,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1824,7 +1849,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1832,7 +1857,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1840,7 +1865,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1848,7 +1873,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1856,7 +1881,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1864,7 +1889,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1872,7 +1897,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1880,7 +1905,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1888,7 +1913,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1896,7 +1921,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1904,7 +1929,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1912,7 +1937,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1920,7 +1945,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1928,7 +1953,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1936,7 +1961,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1944,7 +1969,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1952,7 +1977,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1960,7 +1985,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1976,7 +2001,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1984,7 +2009,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2072,7 +2097,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2080,7 +2105,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2168,9 +2193,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -2181,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2191,7 +2224,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -2247,7 +2280,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -2263,7 +2296,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -2271,7 +2304,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -2287,7 +2320,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -2319,7 +2352,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -2351,7 +2384,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -2359,7 +2392,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -2383,7 +2416,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -2399,7 +2432,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -2415,79 +2448,79 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>57.60009765625</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>57.4599609375</v>
+        <v>57.60009765625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B32">
-        <v>57.449951171875</v>
+        <v>57.4599609375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>56.9599609375</v>
+        <v>57.449951171875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B34">
-        <v>56.260009765625</v>
+        <v>56.9599609375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B35">
-        <v>55.89990234375</v>
+        <v>56.260009765625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B36">
-        <v>54.60009765625</v>
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B37">
-        <v>54.159912109375</v>
+        <v>54.60009765625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B38">
-        <v>54.10009765625</v>
+        <v>54.159912109375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -2495,55 +2528,55 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B40">
-        <v>53.659912109375</v>
+        <v>54.10009765625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B41">
-        <v>51.56005859375</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B42">
-        <v>51.260009765625</v>
+        <v>51.56005859375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B43">
-        <v>49.760009765625</v>
+        <v>51.260009765625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B44">
-        <v>49</v>
+        <v>49.760009765625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>47.860107421875</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -2551,57 +2584,65 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B47">
-        <v>44.260009765625</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B48">
-        <v>44.06005859375</v>
+        <v>44.260009765625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B49">
-        <v>43.510009765625</v>
+        <v>44.06005859375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B50">
-        <v>42.9599609375</v>
+        <v>43.510009765625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B51">
-        <v>40.60009765625</v>
+        <v>42.9599609375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B52">
-        <v>38.260009765625</v>
+        <v>40.60009765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53">
+        <v>38.260009765625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>37.820068359375</v>
       </c>
     </row>
@@ -2612,7 +2653,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2622,7 +2663,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>293.69970703125</v>
@@ -2638,7 +2679,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>290.19970703125</v>
@@ -2694,7 +2735,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>263.99951171875</v>
@@ -2702,7 +2743,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>263.6201171875</v>
@@ -2726,7 +2767,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>259.27978515625</v>
@@ -2750,7 +2791,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>252.60009765625</v>
@@ -2822,7 +2863,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>242.099609375</v>
@@ -2830,7 +2871,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B28">
         <v>239.99951171875</v>
@@ -2838,7 +2879,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>239.99951171875</v>
@@ -2854,7 +2895,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>238.1806640625</v>
@@ -2870,7 +2911,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>237.330078125</v>
@@ -2878,7 +2919,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>236.7998046875</v>
@@ -2950,7 +2991,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43">
         <v>217.81982421875</v>
@@ -2990,7 +3031,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48">
         <v>209.2998046875</v>
@@ -2998,7 +3039,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49">
         <v>206.2998046875</v>
@@ -3006,33 +3047,41 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B50">
-        <v>193.91943359375</v>
+        <v>200.659912109375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B51">
-        <v>165.19970703125</v>
+        <v>193.91943359375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B52">
-        <v>145.47998046875</v>
+        <v>165.19970703125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B53">
+        <v>145.47998046875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54">
         <v>145.130126953125</v>
       </c>
     </row>
@@ -3043,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3061,7 +3110,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3069,7 +3118,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3077,7 +3126,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3085,7 +3134,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3093,7 +3142,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3101,7 +3150,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3109,7 +3158,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3117,7 +3166,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3125,7 +3174,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3133,7 +3182,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3141,7 +3190,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3149,7 +3198,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3157,7 +3206,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3165,7 +3214,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3173,7 +3222,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3181,7 +3230,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3189,7 +3238,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3197,7 +3246,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3205,7 +3254,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3213,7 +3262,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3221,7 +3270,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3229,7 +3278,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3237,7 +3286,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3245,7 +3294,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3253,7 +3302,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3269,7 +3318,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3277,7 +3326,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3365,7 +3414,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3373,7 +3422,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3461,9 +3510,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -3474,7 +3531,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3492,7 +3549,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3500,7 +3557,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3508,7 +3565,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3516,7 +3573,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3524,7 +3581,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3532,7 +3589,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3540,7 +3597,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3548,7 +3605,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3556,7 +3613,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3564,7 +3621,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3572,7 +3629,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3580,7 +3637,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3588,7 +3645,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3596,7 +3653,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3604,7 +3661,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3612,7 +3669,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3620,7 +3677,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3628,7 +3685,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3636,7 +3693,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3644,7 +3701,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3652,7 +3709,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3660,7 +3717,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3668,7 +3725,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3676,7 +3733,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3684,7 +3741,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3700,7 +3757,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3708,7 +3765,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3796,7 +3853,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3804,7 +3861,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3892,9 +3949,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -3905,7 +3970,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3923,7 +3988,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3931,7 +3996,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3939,7 +4004,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3947,7 +4012,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3955,7 +4020,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3963,7 +4028,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3971,7 +4036,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3979,7 +4044,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3987,7 +4052,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3995,7 +4060,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4003,7 +4068,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4011,7 +4076,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4019,7 +4084,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4027,7 +4092,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4035,7 +4100,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4043,7 +4108,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4051,7 +4116,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4059,7 +4124,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4067,7 +4132,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4075,7 +4140,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4083,7 +4148,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4091,7 +4156,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4099,7 +4164,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4107,7 +4172,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4115,7 +4180,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4131,7 +4196,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4139,7 +4204,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4227,7 +4292,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4235,7 +4300,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4323,9 +4388,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -4336,7 +4409,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4354,7 +4427,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4362,7 +4435,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4370,7 +4443,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4378,7 +4451,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4386,7 +4459,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4394,7 +4467,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4402,7 +4475,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4410,7 +4483,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4418,7 +4491,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4426,7 +4499,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4434,7 +4507,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4442,7 +4515,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4450,7 +4523,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4458,7 +4531,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4466,7 +4539,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4474,7 +4547,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4482,7 +4555,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4490,7 +4563,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4498,7 +4571,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4506,7 +4579,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4514,7 +4587,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4522,7 +4595,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4530,7 +4603,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4538,7 +4611,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4546,7 +4619,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4562,7 +4635,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4570,7 +4643,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4658,7 +4731,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4666,7 +4739,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4754,9 +4827,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -584,7 +584,7 @@
         <v>79.85986328125</v>
       </c>
       <c r="E2">
-        <v>79.85986328125</v>
+        <v>32.73</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -601,7 +601,7 @@
         <v>72.9599609375</v>
       </c>
       <c r="E3">
-        <v>72.9599609375</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -618,7 +618,7 @@
         <v>71.85986328125</v>
       </c>
       <c r="E4">
-        <v>71.85986328125</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -635,7 +635,7 @@
         <v>94.259765625</v>
       </c>
       <c r="E5">
-        <v>94.259765625</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -652,7 +652,7 @@
         <v>85.10009765625</v>
       </c>
       <c r="E6">
-        <v>85.10009765625</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -669,7 +669,7 @@
         <v>80.2001953125</v>
       </c>
       <c r="E7">
-        <v>80.2001953125</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -686,7 +686,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E8">
-        <v>105.759765625</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -703,7 +703,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="E9">
-        <v>81.35986328125</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -720,7 +720,7 @@
         <v>80.2998046875</v>
       </c>
       <c r="E10">
-        <v>80.2998046875</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -737,7 +737,7 @@
         <v>80.56005859375</v>
       </c>
       <c r="E11">
-        <v>80.56005859375</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -754,7 +754,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="E12">
-        <v>98.64990234375</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -771,7 +771,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E13">
-        <v>79.259765625</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -788,7 +788,7 @@
         <v>71.56005859375</v>
       </c>
       <c r="E14">
-        <v>71.56005859375</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -805,7 +805,7 @@
         <v>78.990234375</v>
       </c>
       <c r="E15">
-        <v>78.990234375</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -822,7 +822,7 @@
         <v>87.33984375</v>
       </c>
       <c r="E16">
-        <v>87.33984375</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -839,7 +839,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="E17">
-        <v>78.39990234375</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -856,7 +856,7 @@
         <v>65.259765625</v>
       </c>
       <c r="E18">
-        <v>65.259765625</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -873,7 +873,7 @@
         <v>75.56005859375</v>
       </c>
       <c r="E19">
-        <v>75.56005859375</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -890,7 +890,7 @@
         <v>73.64990234375</v>
       </c>
       <c r="E20">
-        <v>73.64990234375</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -907,7 +907,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="E21">
-        <v>70.7998046875</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -924,7 +924,7 @@
         <v>78.85986328125</v>
       </c>
       <c r="E22">
-        <v>78.85986328125</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -941,7 +941,7 @@
         <v>67.759765625</v>
       </c>
       <c r="E23">
-        <v>67.759765625</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -958,7 +958,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E24">
-        <v>97.39990234375</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -975,7 +975,7 @@
         <v>97.759765625</v>
       </c>
       <c r="E25">
-        <v>97.759765625</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -992,7 +992,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E26">
-        <v>87.4599609375</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1009,7 +1009,7 @@
         <v>101.740234375</v>
       </c>
       <c r="E27">
-        <v>101.740234375</v>
+        <v>39.73</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1026,7 +1026,7 @@
         <v>38.590087890625</v>
       </c>
       <c r="E28">
-        <v>38.590087890625</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1043,7 +1043,7 @@
         <v>81.759765625</v>
       </c>
       <c r="E29">
-        <v>81.759765625</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1060,7 +1060,7 @@
         <v>65.259765625</v>
       </c>
       <c r="E30">
-        <v>65.259765625</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1077,7 +1077,7 @@
         <v>81.259765625</v>
       </c>
       <c r="E31">
-        <v>81.259765625</v>
+        <v>47.98</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1094,7 +1094,7 @@
         <v>68.9599609375</v>
       </c>
       <c r="E32">
-        <v>68.9599609375</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1111,7 +1111,7 @@
         <v>81.25</v>
       </c>
       <c r="E33">
-        <v>81.25</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1128,7 +1128,7 @@
         <v>81.16015625</v>
       </c>
       <c r="E34">
-        <v>81.16015625</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1145,7 +1145,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E35">
-        <v>78.259765625</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1162,7 +1162,7 @@
         <v>77.259765625</v>
       </c>
       <c r="E36">
-        <v>77.259765625</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1179,7 +1179,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="E37">
-        <v>70.35986328125</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1196,7 +1196,7 @@
         <v>93.759765625</v>
       </c>
       <c r="E38">
-        <v>93.759765625</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1213,7 +1213,7 @@
         <v>68.43994140625</v>
       </c>
       <c r="E39">
-        <v>68.43994140625</v>
+        <v>52.13</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1230,7 +1230,7 @@
         <v>78.93994140625</v>
       </c>
       <c r="E40">
-        <v>78.93994140625</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1247,7 +1247,7 @@
         <v>88.759765625</v>
       </c>
       <c r="E41">
-        <v>88.759765625</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1264,7 +1264,7 @@
         <v>54.35009765625</v>
       </c>
       <c r="E42">
-        <v>54.35009765625</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1281,7 +1281,7 @@
         <v>83.64990234375</v>
       </c>
       <c r="E43">
-        <v>83.64990234375</v>
+        <v>46.53</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1298,7 +1298,7 @@
         <v>99.35986328125</v>
       </c>
       <c r="E44">
-        <v>99.35986328125</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1315,7 +1315,7 @@
         <v>67.39990234375</v>
       </c>
       <c r="E45">
-        <v>67.39990234375</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1332,7 +1332,7 @@
         <v>87.39990234375</v>
       </c>
       <c r="E46">
-        <v>87.39990234375</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1349,7 +1349,7 @@
         <v>56.9599609375</v>
       </c>
       <c r="E47">
-        <v>56.9599609375</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1366,7 +1366,7 @@
         <v>72.740234375</v>
       </c>
       <c r="E48">
-        <v>72.740234375</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1383,7 +1383,7 @@
         <v>86.66015625</v>
       </c>
       <c r="E49">
-        <v>86.66015625</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1400,7 +1400,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="E50">
-        <v>88.06005859375</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1417,7 +1417,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E51">
-        <v>105.759765625</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1434,7 +1434,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="E52">
-        <v>61.159912109375</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1451,7 +1451,7 @@
         <v>85.259765625</v>
       </c>
       <c r="E53">
-        <v>85.259765625</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1468,7 +1468,7 @@
         <v>43.909912109375</v>
       </c>
       <c r="E54">
-        <v>43.909912109375</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2663,74 +2663,74 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>293.69970703125</v>
+        <v>245.1896484375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>293.69970703125</v>
+        <v>237.18986328125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B4">
-        <v>290.19970703125</v>
+        <v>236.33994140625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>282.29931640625</v>
+        <v>235.130078125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>277.3994140625</v>
+        <v>234.58955078125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B7">
-        <v>273.63037109375</v>
+        <v>233.91015625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B8">
-        <v>271.39990234375</v>
+        <v>232.38984375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B9">
-        <v>267.8203125</v>
+        <v>231.73994140625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>266.97998046875</v>
+        <v>231.73994140625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2738,31 +2738,31 @@
         <v>55</v>
       </c>
       <c r="B11">
-        <v>263.99951171875</v>
+        <v>228.68974609375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>263.6201171875</v>
+        <v>228.53994140625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>261.8798828125</v>
+        <v>222.8796875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>261.29931640625</v>
+        <v>220.26974609375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2770,311 +2770,311 @@
         <v>48</v>
       </c>
       <c r="B15">
-        <v>259.27978515625</v>
+        <v>217.2298828125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B16">
-        <v>256.41943359375</v>
+        <v>214.3304296875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>253.4501953125</v>
+        <v>212.88986328125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>252.60009765625</v>
+        <v>211.62013671875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B19">
-        <v>249.57958984375</v>
+        <v>211.60955078125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B20">
-        <v>249.57958984375</v>
+        <v>211.53984375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B21">
-        <v>245.10986328125</v>
+        <v>210.10986328125</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B22">
-        <v>244.11962890625</v>
+        <v>209.99013671875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B23">
-        <v>244.1103515625</v>
+        <v>206.71974609375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B24">
-        <v>243.2197265625</v>
+        <v>205.52998046875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>242.69970703125</v>
+        <v>205.19</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B26">
-        <v>242.2197265625</v>
+        <v>204.63974609375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B27">
-        <v>242.099609375</v>
+        <v>204.41005859375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>239.99951171875</v>
+        <v>204.259765625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B29">
-        <v>239.99951171875</v>
+        <v>203.75994140625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B30">
-        <v>239.169921875</v>
+        <v>201.84970703125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B31">
-        <v>238.1806640625</v>
+        <v>200.159912109375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>237.8203125</v>
+        <v>199.95966796875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B33">
-        <v>237.330078125</v>
+        <v>199.67990234375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B34">
-        <v>236.7998046875</v>
+        <v>197.16025390625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B35">
-        <v>232.419921875</v>
+        <v>196.86025390625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>227.919921875</v>
+        <v>190.17013671875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B37">
-        <v>227.919921875</v>
+        <v>189.93984375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>227.31982421875</v>
+        <v>189.2896484375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B39">
-        <v>225.74951171875</v>
+        <v>189.2599609375</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B40">
-        <v>224.7998046875</v>
+        <v>189.03984375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B41">
-        <v>222.01025390625</v>
+        <v>188.69990234375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B42">
-        <v>221.099609375</v>
+        <v>188.4599609375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B43">
-        <v>217.81982421875</v>
+        <v>185.29005859375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B44">
-        <v>217.400390625</v>
+        <v>185.0099609375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B45">
-        <v>217.3994140625</v>
+        <v>184.349970703125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B46">
-        <v>216.2197265625</v>
+        <v>183.45001953125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B47">
-        <v>215.169921875</v>
+        <v>182.8599609375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B48">
-        <v>209.2998046875</v>
+        <v>182.25986328125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B49">
-        <v>206.2998046875</v>
+        <v>177.9001953125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B50">
-        <v>200.659912109375</v>
+        <v>177.72966796875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B51">
-        <v>193.91943359375</v>
+        <v>161.12001953125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B52">
-        <v>165.19970703125</v>
+        <v>160.639892578125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B53">
-        <v>145.47998046875</v>
+        <v>152.689794921875</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>44</v>
       </c>
       <c r="B54">
-        <v>145.130126953125</v>
+        <v>112.430029296875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -584,7 +584,7 @@
         <v>79.85986328125</v>
       </c>
       <c r="E2">
-        <v>32.73</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -601,7 +601,7 @@
         <v>72.9599609375</v>
       </c>
       <c r="E3">
-        <v>33.5</v>
+        <v>33.95</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -618,7 +618,7 @@
         <v>71.85986328125</v>
       </c>
       <c r="E4">
-        <v>38.75</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -635,7 +635,7 @@
         <v>94.259765625</v>
       </c>
       <c r="E5">
-        <v>46.55</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -652,7 +652,7 @@
         <v>85.10009765625</v>
       </c>
       <c r="E6">
-        <v>37.85</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -686,7 +686,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E8">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -703,7 +703,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="E9">
-        <v>41.5</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -720,7 +720,7 @@
         <v>80.2998046875</v>
       </c>
       <c r="E10">
-        <v>56.4</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -737,7 +737,7 @@
         <v>80.56005859375</v>
       </c>
       <c r="E11">
-        <v>37.1</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -754,7 +754,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="E12">
-        <v>42.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -771,7 +771,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E13">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -788,7 +788,7 @@
         <v>71.56005859375</v>
       </c>
       <c r="E14">
-        <v>45.28</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -805,7 +805,7 @@
         <v>78.990234375</v>
       </c>
       <c r="E15">
-        <v>40.43</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -822,7 +822,7 @@
         <v>87.33984375</v>
       </c>
       <c r="E16">
-        <v>42.4</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -839,7 +839,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="E17">
-        <v>51.7</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -873,7 +873,7 @@
         <v>75.56005859375</v>
       </c>
       <c r="E19">
-        <v>34.9</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -907,7 +907,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="E21">
-        <v>51.19</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -924,7 +924,7 @@
         <v>78.85986328125</v>
       </c>
       <c r="E22">
-        <v>73.83</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -941,7 +941,7 @@
         <v>67.759765625</v>
       </c>
       <c r="E23">
-        <v>35.7</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -958,7 +958,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E24">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -975,7 +975,7 @@
         <v>97.759765625</v>
       </c>
       <c r="E25">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -992,7 +992,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E26">
-        <v>44.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1009,7 +1009,7 @@
         <v>101.740234375</v>
       </c>
       <c r="E27">
-        <v>39.73</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1026,7 +1026,7 @@
         <v>38.590087890625</v>
       </c>
       <c r="E28">
-        <v>53.75</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1043,7 +1043,7 @@
         <v>81.759765625</v>
       </c>
       <c r="E29">
-        <v>25.3</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1060,7 +1060,7 @@
         <v>65.259765625</v>
       </c>
       <c r="E30">
-        <v>49.07</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1077,7 +1077,7 @@
         <v>81.259765625</v>
       </c>
       <c r="E31">
-        <v>47.98</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1094,7 +1094,7 @@
         <v>68.9599609375</v>
       </c>
       <c r="E32">
-        <v>23.9</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1111,7 +1111,7 @@
         <v>81.25</v>
       </c>
       <c r="E33">
-        <v>18.4</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1128,7 +1128,7 @@
         <v>81.16015625</v>
       </c>
       <c r="E34">
-        <v>47.25</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1145,7 +1145,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E35">
-        <v>50.15</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1162,7 +1162,7 @@
         <v>77.259765625</v>
       </c>
       <c r="E36">
-        <v>38.32</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1179,7 +1179,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="E37">
-        <v>32.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1196,7 +1196,7 @@
         <v>93.759765625</v>
       </c>
       <c r="E38">
-        <v>44.07</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1213,7 +1213,7 @@
         <v>68.43994140625</v>
       </c>
       <c r="E39">
-        <v>52.13</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1230,7 +1230,7 @@
         <v>78.93994140625</v>
       </c>
       <c r="E40">
-        <v>31.78</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1247,7 +1247,7 @@
         <v>88.759765625</v>
       </c>
       <c r="E41">
-        <v>58.2</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1264,7 +1264,7 @@
         <v>54.35009765625</v>
       </c>
       <c r="E42">
-        <v>21.65</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1281,7 +1281,7 @@
         <v>83.64990234375</v>
       </c>
       <c r="E43">
-        <v>46.53</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1298,7 +1298,7 @@
         <v>99.35986328125</v>
       </c>
       <c r="E44">
-        <v>41.55</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1315,7 +1315,7 @@
         <v>67.39990234375</v>
       </c>
       <c r="E45">
-        <v>49.8</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1332,7 +1332,7 @@
         <v>87.39990234375</v>
       </c>
       <c r="E46">
-        <v>45.35</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1349,7 +1349,7 @@
         <v>56.9599609375</v>
       </c>
       <c r="E47">
-        <v>37.6</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1366,7 +1366,7 @@
         <v>72.740234375</v>
       </c>
       <c r="E48">
-        <v>48.89</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1383,7 +1383,7 @@
         <v>86.66015625</v>
       </c>
       <c r="E49">
-        <v>70.40000000000001</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1400,7 +1400,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="E50">
-        <v>28.85</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1417,7 +1417,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E51">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1434,7 +1434,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="E52">
-        <v>43.5</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1451,7 +1451,7 @@
         <v>85.259765625</v>
       </c>
       <c r="E53">
-        <v>49.95</v>
+        <v>68.34999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2666,271 +2666,271 @@
         <v>27</v>
       </c>
       <c r="B2">
-        <v>245.1896484375</v>
+        <v>261.2896484375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>237.18986328125</v>
+        <v>251.230078125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>236.33994140625</v>
+        <v>249.33986328125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="B5">
-        <v>235.130078125</v>
+        <v>247.08974609375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>234.58955078125</v>
+        <v>245.38984375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B7">
-        <v>233.91015625</v>
+        <v>244.59994140625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>232.38984375</v>
+        <v>243.78955078125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B9">
-        <v>231.73994140625</v>
+        <v>241.93994140625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B10">
-        <v>231.73994140625</v>
+        <v>236.58984375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B11">
-        <v>228.68974609375</v>
+        <v>235.2296875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B12">
-        <v>228.53994140625</v>
+        <v>234.58994140625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>222.8796875</v>
+        <v>234.58994140625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B14">
-        <v>220.26974609375</v>
+        <v>234.21015625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>217.2298828125</v>
+        <v>229.46974609375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>214.3304296875</v>
+        <v>225.0298828125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>212.88986328125</v>
+        <v>224.41025390625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>211.62013671875</v>
+        <v>221.78986328125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>211.60955078125</v>
+        <v>221.26</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B20">
-        <v>211.53984375</v>
+        <v>220.4396484375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>210.10986328125</v>
+        <v>220.14013671875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>209.99013671875</v>
+        <v>218.41994140625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B23">
-        <v>206.71974609375</v>
+        <v>215.11955078125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>205.52998046875</v>
+        <v>214.32013671875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B25">
-        <v>205.19</v>
+        <v>214.30986328125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B26">
-        <v>204.63974609375</v>
+        <v>213.709912109375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B27">
-        <v>204.41005859375</v>
+        <v>212.49970703125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B28">
-        <v>204.259765625</v>
+        <v>212.26025390625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B29">
-        <v>203.75994140625</v>
+        <v>211.3804296875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B30">
-        <v>201.84970703125</v>
+        <v>210.48974609375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B31">
-        <v>200.159912109375</v>
+        <v>208.609765625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B32">
-        <v>199.95966796875</v>
+        <v>208.46005859375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>199.67990234375</v>
+        <v>206.41974609375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B34">
-        <v>197.16025390625</v>
+        <v>205.80966796875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B35">
-        <v>196.86025390625</v>
+        <v>204.87990234375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2938,55 +2938,55 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>190.17013671875</v>
+        <v>203.02013671875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B37">
-        <v>189.93984375</v>
+        <v>201.72998046875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B38">
-        <v>189.2896484375</v>
+        <v>198.299970703125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B39">
-        <v>189.2599609375</v>
+        <v>196.2599609375</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B40">
-        <v>189.03984375</v>
+        <v>195.78984375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B41">
-        <v>188.69990234375</v>
+        <v>193.38984375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B42">
-        <v>188.4599609375</v>
+        <v>192.5599609375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2994,63 +2994,63 @@
         <v>4</v>
       </c>
       <c r="B43">
-        <v>185.29005859375</v>
+        <v>189.64005859375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B44">
-        <v>185.0099609375</v>
+        <v>188.9099609375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B45">
-        <v>184.349970703125</v>
+        <v>187.64990234375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B46">
-        <v>183.45001953125</v>
+        <v>186.28966796875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B47">
-        <v>182.8599609375</v>
+        <v>186.00986328125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B48">
-        <v>182.25986328125</v>
+        <v>185.0099609375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B49">
-        <v>177.9001953125</v>
+        <v>179.40001953125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B50">
-        <v>177.72966796875</v>
+        <v>177.9001953125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3066,7 +3066,7 @@
         <v>30</v>
       </c>
       <c r="B52">
-        <v>160.639892578125</v>
+        <v>159.439892578125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>44</v>
       </c>
       <c r="B54">
-        <v>112.430029296875</v>
+        <v>115.030029296875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -584,7 +584,7 @@
         <v>79.85986328125</v>
       </c>
       <c r="E2">
-        <v>37.08</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -601,7 +601,7 @@
         <v>72.9599609375</v>
       </c>
       <c r="E3">
-        <v>33.95</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -618,7 +618,7 @@
         <v>71.85986328125</v>
       </c>
       <c r="E4">
-        <v>42.95</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -635,7 +635,7 @@
         <v>94.259765625</v>
       </c>
       <c r="E5">
-        <v>55.75</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -652,7 +652,7 @@
         <v>85.10009765625</v>
       </c>
       <c r="E6">
-        <v>53.25</v>
+        <v>82.45</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -669,7 +669,7 @@
         <v>80.2001953125</v>
       </c>
       <c r="E7">
-        <v>40.7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -686,7 +686,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E8">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -703,7 +703,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="E9">
-        <v>45.85</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -720,7 +720,7 @@
         <v>80.2998046875</v>
       </c>
       <c r="E10">
-        <v>67.05</v>
+        <v>77.05</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -737,7 +737,7 @@
         <v>80.56005859375</v>
       </c>
       <c r="E11">
-        <v>47.25</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -754,7 +754,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="E12">
-        <v>38.5</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -771,7 +771,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E13">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -788,7 +788,7 @@
         <v>71.56005859375</v>
       </c>
       <c r="E14">
-        <v>54.18</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -805,7 +805,7 @@
         <v>78.990234375</v>
       </c>
       <c r="E15">
-        <v>36.38</v>
+        <v>36.58</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -822,7 +822,7 @@
         <v>87.33984375</v>
       </c>
       <c r="E16">
-        <v>48.25</v>
+        <v>69.65000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -839,7 +839,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="E17">
-        <v>64.05</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -856,7 +856,7 @@
         <v>65.259765625</v>
       </c>
       <c r="E18">
-        <v>34.05</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -873,7 +873,7 @@
         <v>75.56005859375</v>
       </c>
       <c r="E19">
-        <v>62.15</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -890,7 +890,7 @@
         <v>73.64990234375</v>
       </c>
       <c r="E20">
-        <v>19.6</v>
+        <v>74.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -907,7 +907,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="E21">
-        <v>67.26000000000001</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -941,7 +941,7 @@
         <v>67.759765625</v>
       </c>
       <c r="E23">
-        <v>40.05</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -992,7 +992,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E26">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1009,7 +1009,7 @@
         <v>101.740234375</v>
       </c>
       <c r="E27">
-        <v>42.43</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1043,7 +1043,7 @@
         <v>81.759765625</v>
       </c>
       <c r="E29">
-        <v>31.15</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1060,7 +1060,7 @@
         <v>65.259765625</v>
       </c>
       <c r="E30">
-        <v>57.63</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1077,7 +1077,7 @@
         <v>81.259765625</v>
       </c>
       <c r="E31">
-        <v>47.68</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1094,7 +1094,7 @@
         <v>68.9599609375</v>
       </c>
       <c r="E32">
-        <v>37.3</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1111,7 +1111,7 @@
         <v>81.25</v>
       </c>
       <c r="E33">
-        <v>22.15</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1128,7 +1128,7 @@
         <v>81.16015625</v>
       </c>
       <c r="E34">
-        <v>47.55</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1145,7 +1145,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E35">
-        <v>81.3</v>
+        <v>99.73</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1179,7 +1179,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="E37">
-        <v>35.6</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1196,7 +1196,7 @@
         <v>93.759765625</v>
       </c>
       <c r="E38">
-        <v>47.58</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1213,7 +1213,7 @@
         <v>68.43994140625</v>
       </c>
       <c r="E39">
-        <v>66.08</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1230,7 +1230,7 @@
         <v>78.93994140625</v>
       </c>
       <c r="E40">
-        <v>44.63</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1247,7 +1247,7 @@
         <v>88.759765625</v>
       </c>
       <c r="E41">
-        <v>92.05</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1264,7 +1264,7 @@
         <v>54.35009765625</v>
       </c>
       <c r="E42">
-        <v>24.25</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1298,7 +1298,7 @@
         <v>99.35986328125</v>
       </c>
       <c r="E44">
-        <v>45.75</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1349,7 +1349,7 @@
         <v>56.9599609375</v>
       </c>
       <c r="E47">
-        <v>43.45</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1366,7 +1366,7 @@
         <v>72.740234375</v>
       </c>
       <c r="E48">
-        <v>45.94</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1383,7 +1383,7 @@
         <v>86.66015625</v>
       </c>
       <c r="E49">
-        <v>78.66</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1400,7 +1400,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="E50">
-        <v>32.9</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1417,7 +1417,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E51">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1434,7 +1434,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="E52">
-        <v>57.05</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1451,7 +1451,7 @@
         <v>85.259765625</v>
       </c>
       <c r="E53">
-        <v>68.34999999999999</v>
+        <v>103.05</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1468,7 +1468,7 @@
         <v>43.909912109375</v>
       </c>
       <c r="E54">
-        <v>31.4</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2663,154 +2663,154 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B2">
-        <v>261.2896484375</v>
+        <v>281.78974609375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B3">
-        <v>251.230078125</v>
+        <v>265.38984375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>249.33986328125</v>
+        <v>265.36994140625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B5">
-        <v>247.08974609375</v>
+        <v>263.08984375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>245.38984375</v>
+        <v>262.98955078125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>244.59994140625</v>
+        <v>261.2896484375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>243.78955078125</v>
+        <v>258.8296875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>241.93994140625</v>
+        <v>254.50986328125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B10">
-        <v>236.58984375</v>
+        <v>253.41015625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B11">
-        <v>235.2296875</v>
+        <v>253.08994140625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>234.58994140625</v>
+        <v>253.08994140625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B13">
-        <v>234.58994140625</v>
+        <v>251.230078125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B14">
-        <v>234.21015625</v>
+        <v>249.33986328125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>229.46974609375</v>
+        <v>248.70998046875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>225.0298828125</v>
+        <v>247.16974609375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B17">
-        <v>224.41025390625</v>
+        <v>246.29994140625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B18">
-        <v>221.78986328125</v>
+        <v>244.31025390625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>221.26</v>
+        <v>243.61974609375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B20">
-        <v>220.4396484375</v>
+        <v>241.46025390625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2818,23 +2818,23 @@
         <v>13</v>
       </c>
       <c r="B21">
-        <v>220.14013671875</v>
+        <v>239.54013671875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>218.41994140625</v>
+        <v>238.8696484375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B23">
-        <v>215.11955078125</v>
+        <v>238.78986328125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2842,239 +2842,239 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>214.32013671875</v>
+        <v>235.02013671875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B25">
-        <v>214.30986328125</v>
+        <v>234.09005859375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B26">
-        <v>213.709912109375</v>
+        <v>232.1899609375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B27">
-        <v>212.49970703125</v>
+        <v>231.88974609375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B28">
-        <v>212.26025390625</v>
+        <v>231.26</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B29">
-        <v>211.3804296875</v>
+        <v>227.90966796875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B30">
-        <v>210.48974609375</v>
+        <v>227.809765625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B31">
-        <v>208.609765625</v>
+        <v>225.2099609375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>208.46005859375</v>
+        <v>225.0298828125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B33">
-        <v>206.41974609375</v>
+        <v>224.409912109375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B34">
-        <v>205.80966796875</v>
+        <v>222.49970703125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B35">
-        <v>204.87990234375</v>
+        <v>219.46955078125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B36">
-        <v>203.02013671875</v>
+        <v>218.41994140625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B37">
-        <v>201.72998046875</v>
+        <v>216.38984375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B38">
-        <v>198.299970703125</v>
+        <v>216.0304296875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B39">
-        <v>196.2599609375</v>
+        <v>215.55001953125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B40">
-        <v>195.78984375</v>
+        <v>212.2099609375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B41">
-        <v>193.38984375</v>
+        <v>211.24005859375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B42">
-        <v>192.5599609375</v>
+        <v>209.50986328125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>189.64005859375</v>
+        <v>206.12013671875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B44">
-        <v>188.9099609375</v>
+        <v>205.58984375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B45">
-        <v>187.64990234375</v>
+        <v>204.87990234375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B46">
-        <v>186.28966796875</v>
+        <v>199.2001953125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>186.00986328125</v>
+        <v>198.499970703125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B48">
-        <v>185.0099609375</v>
+        <v>197.369794921875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B49">
-        <v>179.40001953125</v>
+        <v>191.8599609375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B50">
-        <v>177.9001953125</v>
+        <v>187.64990234375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B51">
-        <v>161.12001953125</v>
+        <v>186.46966796875</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B52">
-        <v>159.439892578125</v>
+        <v>179.60001953125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B53">
-        <v>152.689794921875</v>
+        <v>159.439892578125</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3082,7 +3082,7 @@
         <v>44</v>
       </c>
       <c r="B54">
-        <v>115.030029296875</v>
+        <v>120.630029296875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="59">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Rodada 4</t>
+  </si>
+  <si>
+    <t>Rodada 5</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -553,10 +556,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,10 +572,13 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -584,12 +590,15 @@
         <v>79.85986328125</v>
       </c>
       <c r="E2">
-        <v>58.68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>58.679931640625</v>
+      </c>
+      <c r="F2">
+        <v>58.679931640625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -603,10 +612,13 @@
       <c r="E3">
         <v>57.25</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>57.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -618,12 +630,15 @@
         <v>71.85986328125</v>
       </c>
       <c r="E4">
-        <v>83.15000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>83.14990234375</v>
+      </c>
+      <c r="F4">
+        <v>83.14990234375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -635,12 +650,15 @@
         <v>94.259765625</v>
       </c>
       <c r="E5">
-        <v>74.95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>74.9501953125</v>
+      </c>
+      <c r="F5">
+        <v>74.9501953125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -652,12 +670,15 @@
         <v>85.10009765625</v>
       </c>
       <c r="E6">
-        <v>82.45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>82.4501953125</v>
+      </c>
+      <c r="F6">
+        <v>82.4501953125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -671,10 +692,13 @@
       <c r="E7">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -686,12 +710,15 @@
         <v>105.759765625</v>
       </c>
       <c r="E8">
-        <v>65.15000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F8">
+        <v>65.14990234375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -703,12 +730,15 @@
         <v>81.35986328125</v>
       </c>
       <c r="E9">
-        <v>65.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>65.0498046875</v>
+      </c>
+      <c r="F9">
+        <v>65.0498046875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -720,12 +750,15 @@
         <v>80.2998046875</v>
       </c>
       <c r="E10">
-        <v>77.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>77.0498046875</v>
+      </c>
+      <c r="F10">
+        <v>77.0498046875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -737,12 +770,15 @@
         <v>80.56005859375</v>
       </c>
       <c r="E11">
-        <v>66.65000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>66.64990234375</v>
+      </c>
+      <c r="F11">
+        <v>66.64990234375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -754,12 +790,15 @@
         <v>98.64990234375</v>
       </c>
       <c r="E12">
-        <v>85.48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>85.47998046875</v>
+      </c>
+      <c r="F12">
+        <v>85.47998046875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -771,12 +810,15 @@
         <v>79.259765625</v>
       </c>
       <c r="E13">
-        <v>86.43000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>86.43017578125</v>
+      </c>
+      <c r="F13">
+        <v>86.43017578125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -788,12 +830,15 @@
         <v>71.56005859375</v>
       </c>
       <c r="E14">
-        <v>71.18000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>71.18017578125</v>
+      </c>
+      <c r="F14">
+        <v>71.18017578125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -805,12 +850,15 @@
         <v>78.990234375</v>
       </c>
       <c r="E15">
-        <v>36.58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>36.580078125</v>
+      </c>
+      <c r="F15">
+        <v>36.580078125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -822,12 +870,15 @@
         <v>87.33984375</v>
       </c>
       <c r="E16">
-        <v>69.65000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>69.64990234375</v>
+      </c>
+      <c r="F16">
+        <v>69.64990234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -839,12 +890,15 @@
         <v>78.39990234375</v>
       </c>
       <c r="E17">
-        <v>87.65000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>87.64990234375</v>
+      </c>
+      <c r="F17">
+        <v>87.64990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -858,10 +912,13 @@
       <c r="E18">
         <v>74.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>74.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -873,12 +930,15 @@
         <v>75.56005859375</v>
       </c>
       <c r="E19">
-        <v>82.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>82.0498046875</v>
+      </c>
+      <c r="F19">
+        <v>82.0498046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -890,12 +950,15 @@
         <v>73.64990234375</v>
       </c>
       <c r="E20">
-        <v>74.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>74.02978515625</v>
+      </c>
+      <c r="F20">
+        <v>74.02978515625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -907,12 +970,15 @@
         <v>70.7998046875</v>
       </c>
       <c r="E21">
-        <v>77.26000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>77.259765625</v>
+      </c>
+      <c r="F21">
+        <v>77.259765625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -924,12 +990,15 @@
         <v>78.85986328125</v>
       </c>
       <c r="E22">
-        <v>85.98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>85.97998046875</v>
+      </c>
+      <c r="F22">
+        <v>85.97998046875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -943,10 +1012,13 @@
       <c r="E23">
         <v>52.25</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -958,12 +1030,15 @@
         <v>97.39990234375</v>
       </c>
       <c r="E24">
-        <v>81.65000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>81.64990234375</v>
+      </c>
+      <c r="F24">
+        <v>81.64990234375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -975,12 +1050,15 @@
         <v>97.759765625</v>
       </c>
       <c r="E25">
-        <v>81.65000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>81.64990234375</v>
+      </c>
+      <c r="F25">
+        <v>81.64990234375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -992,12 +1070,15 @@
         <v>87.4599609375</v>
       </c>
       <c r="E26">
-        <v>81.43000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>81.43017578125</v>
+      </c>
+      <c r="F26">
+        <v>81.43017578125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1009,12 +1090,15 @@
         <v>101.740234375</v>
       </c>
       <c r="E27">
-        <v>63.13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>63.1298828125</v>
+      </c>
+      <c r="F27">
+        <v>63.1298828125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1026,12 +1110,15 @@
         <v>38.590087890625</v>
       </c>
       <c r="E28">
-        <v>52.55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>52.550048828125</v>
+      </c>
+      <c r="F28">
+        <v>52.550048828125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1045,10 +1132,13 @@
       <c r="E29">
         <v>53.25</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29">
+        <v>53.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1060,12 +1150,15 @@
         <v>65.259765625</v>
       </c>
       <c r="E30">
-        <v>57.81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>57.81005859375</v>
+      </c>
+      <c r="F30">
+        <v>57.81005859375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1077,12 +1170,15 @@
         <v>81.259765625</v>
       </c>
       <c r="E31">
-        <v>84.88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>84.8798828125</v>
+      </c>
+      <c r="F31">
+        <v>84.8798828125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>44.260009765625</v>
@@ -1094,12 +1190,15 @@
         <v>68.9599609375</v>
       </c>
       <c r="E32">
-        <v>73.23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>73.22998046875</v>
+      </c>
+      <c r="F32">
+        <v>73.22998046875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33">
         <v>84.259765625</v>
@@ -1111,12 +1210,15 @@
         <v>81.25</v>
       </c>
       <c r="E33">
-        <v>45.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>45.64990234375</v>
+      </c>
+      <c r="F33">
+        <v>45.64990234375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34">
         <v>64.56005859375</v>
@@ -1130,10 +1232,13 @@
       <c r="E34">
         <v>66.75</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34">
+        <v>66.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>43.510009765625</v>
@@ -1145,12 +1250,15 @@
         <v>78.259765625</v>
       </c>
       <c r="E35">
-        <v>99.73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>99.72998046875</v>
+      </c>
+      <c r="F35">
+        <v>99.72998046875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>57.4599609375</v>
@@ -1162,12 +1270,15 @@
         <v>77.259765625</v>
       </c>
       <c r="E36">
-        <v>52.98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>52.97998046875</v>
+      </c>
+      <c r="F36">
+        <v>52.97998046875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37">
         <v>64.56005859375</v>
@@ -1179,12 +1290,15 @@
         <v>70.35986328125</v>
       </c>
       <c r="E37">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>34.89990234375</v>
+      </c>
+      <c r="F37">
+        <v>34.89990234375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38">
         <v>59.25</v>
@@ -1196,12 +1310,15 @@
         <v>93.759765625</v>
       </c>
       <c r="E38">
-        <v>51.93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>51.929931640625</v>
+      </c>
+      <c r="F38">
+        <v>51.929931640625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39">
         <v>58.25</v>
@@ -1213,12 +1330,15 @@
         <v>68.43994140625</v>
       </c>
       <c r="E39">
-        <v>66.28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>66.27978515625</v>
+      </c>
+      <c r="F39">
+        <v>66.27978515625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40">
         <v>84.85986328125</v>
@@ -1230,12 +1350,15 @@
         <v>78.93994140625</v>
       </c>
       <c r="E40">
-        <v>47.73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>47.72998046875</v>
+      </c>
+      <c r="F40">
+        <v>47.72998046875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41">
         <v>60.159912109375</v>
@@ -1249,10 +1372,13 @@
       <c r="E41">
         <v>109.75</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41">
+        <v>109.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42">
         <v>49</v>
@@ -1264,12 +1390,15 @@
         <v>54.35009765625</v>
       </c>
       <c r="E42">
-        <v>29.85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>29.8499755859375</v>
+      </c>
+      <c r="F42">
+        <v>29.8499755859375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>61.659912109375</v>
@@ -1281,12 +1410,15 @@
         <v>83.64990234375</v>
       </c>
       <c r="E43">
-        <v>51.73</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>51.72998046875</v>
+      </c>
+      <c r="F43">
+        <v>51.72998046875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>42.9599609375</v>
@@ -1298,12 +1430,15 @@
         <v>99.35986328125</v>
       </c>
       <c r="E44">
-        <v>74.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>74.5498046875</v>
+      </c>
+      <c r="F44">
+        <v>74.5498046875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45">
         <v>54.10009765625</v>
@@ -1317,10 +1452,13 @@
       <c r="E45">
         <v>48.75</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45">
+        <v>48.75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46">
         <v>61.9599609375</v>
@@ -1332,12 +1470,15 @@
         <v>87.39990234375</v>
       </c>
       <c r="E46">
-        <v>53.15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>53.14990234375</v>
+      </c>
+      <c r="F46">
+        <v>53.14990234375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47">
         <v>64.2001953125</v>
@@ -1349,12 +1490,15 @@
         <v>56.9599609375</v>
       </c>
       <c r="E47">
-        <v>64.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>64.0498046875</v>
+      </c>
+      <c r="F47">
+        <v>64.0498046875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>66.85986328125</v>
@@ -1366,12 +1510,15 @@
         <v>72.740234375</v>
       </c>
       <c r="E48">
-        <v>50.59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>50.590087890625</v>
+      </c>
+      <c r="F48">
+        <v>50.590087890625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49">
         <v>58.9599609375</v>
@@ -1383,12 +1530,15 @@
         <v>86.66015625</v>
       </c>
       <c r="E49">
-        <v>80.36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>80.35986328125</v>
+      </c>
+      <c r="F49">
+        <v>80.35986328125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>70</v>
@@ -1400,12 +1550,15 @@
         <v>88.06005859375</v>
       </c>
       <c r="E50">
-        <v>58.53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>58.530029296875</v>
+      </c>
+      <c r="F50">
+        <v>58.530029296875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <v>68.06005859375</v>
@@ -1417,12 +1570,15 @@
         <v>105.759765625</v>
       </c>
       <c r="E51">
-        <v>65.15000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F51">
+        <v>65.14990234375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52">
         <v>51.260009765625</v>
@@ -1436,10 +1592,13 @@
       <c r="E52">
         <v>67.75</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52">
+        <v>67.75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53">
         <v>72.16015625</v>
@@ -1451,12 +1610,15 @@
         <v>85.259765625</v>
       </c>
       <c r="E53">
-        <v>103.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>103.0498046875</v>
+      </c>
+      <c r="F53">
+        <v>103.0498046875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -1468,12 +1630,15 @@
         <v>43.909912109375</v>
       </c>
       <c r="E54">
-        <v>76.08</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>76.080078125</v>
+      </c>
+      <c r="F54">
+        <v>76.080078125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1485,6 +1650,9 @@
         <v>0</v>
       </c>
       <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
         <v>0</v>
       </c>
     </row>
@@ -1500,272 +1668,272 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1785,7 +1953,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1793,7 +1961,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1801,7 +1969,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1809,7 +1977,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1817,7 +1985,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1825,7 +1993,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1833,7 +2001,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1841,7 +2009,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1849,7 +2017,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1857,7 +2025,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1865,7 +2033,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1873,7 +2041,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1881,7 +2049,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1889,7 +2057,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1897,7 +2065,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1905,7 +2073,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1913,7 +2081,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1921,7 +2089,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1929,7 +2097,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1937,7 +2105,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1945,7 +2113,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1953,7 +2121,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1961,7 +2129,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1969,7 +2137,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1977,7 +2145,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1985,7 +2153,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1993,7 +2161,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2001,7 +2169,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2009,7 +2177,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2017,7 +2185,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2025,7 +2193,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2033,7 +2201,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2041,7 +2209,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2049,7 +2217,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2057,7 +2225,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2065,7 +2233,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2073,7 +2241,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2081,7 +2249,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2089,7 +2257,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2097,7 +2265,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2105,7 +2273,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2113,7 +2281,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2121,7 +2289,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2129,7 +2297,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2137,7 +2305,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2145,7 +2313,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2153,7 +2321,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2161,7 +2329,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2169,7 +2337,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2177,7 +2345,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2185,7 +2353,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2193,7 +2361,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2201,7 +2369,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2224,7 +2392,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -2232,7 +2400,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -2240,7 +2408,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -2248,7 +2416,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -2256,7 +2424,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -2264,7 +2432,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -2272,7 +2440,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -2280,7 +2448,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -2288,7 +2456,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -2296,7 +2464,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -2304,7 +2472,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -2312,7 +2480,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -2320,7 +2488,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -2328,7 +2496,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -2336,7 +2504,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -2344,7 +2512,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -2352,7 +2520,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -2360,7 +2528,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -2368,7 +2536,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -2376,7 +2544,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -2384,7 +2552,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -2392,7 +2560,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -2400,7 +2568,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -2408,7 +2576,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -2416,7 +2584,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -2424,7 +2592,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -2432,7 +2600,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -2440,7 +2608,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -2448,7 +2616,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -2456,7 +2624,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -2464,7 +2632,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -2472,7 +2640,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -2480,7 +2648,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -2488,7 +2656,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -2496,7 +2664,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -2504,7 +2672,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -2512,7 +2680,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -2520,7 +2688,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -2528,7 +2696,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -2536,7 +2704,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -2544,7 +2712,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -2552,7 +2720,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -2560,7 +2728,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -2568,7 +2736,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -2576,7 +2744,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -2584,7 +2752,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -2592,7 +2760,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B48">
         <v>44.260009765625</v>
@@ -2600,7 +2768,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B49">
         <v>44.06005859375</v>
@@ -2608,7 +2776,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B50">
         <v>43.510009765625</v>
@@ -2616,7 +2784,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B51">
         <v>42.9599609375</v>
@@ -2624,7 +2792,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B52">
         <v>40.60009765625</v>
@@ -2632,7 +2800,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B53">
         <v>38.260009765625</v>
@@ -2640,7 +2808,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B54">
         <v>37.820068359375</v>
@@ -2663,31 +2831,31 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2">
-        <v>281.78974609375</v>
+        <v>281.78955078125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>265.38984375</v>
+        <v>265.3896484375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <v>265.36994140625</v>
+        <v>265.3701171875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -2695,39 +2863,39 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>262.98955078125</v>
+        <v>262.98974609375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>261.2896484375</v>
+        <v>261.28955078125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>258.8296875</v>
+        <v>258.82958984375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>254.50986328125</v>
+        <v>254.509765625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -2735,151 +2903,151 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11">
-        <v>253.08994140625</v>
+        <v>253.08984375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>253.08994140625</v>
+        <v>253.08984375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>251.230078125</v>
+        <v>251.22998046875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>249.33986328125</v>
+        <v>249.33984375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>248.70998046875</v>
+        <v>248.7099609375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
-        <v>247.16974609375</v>
+        <v>247.169921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17">
-        <v>246.29994140625</v>
+        <v>246.2998046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
-        <v>244.31025390625</v>
+        <v>244.31005859375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>243.61974609375</v>
+        <v>243.61962890625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
-        <v>241.46025390625</v>
+        <v>241.46044921875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21">
-        <v>239.54013671875</v>
+        <v>239.5400390625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>238.8696484375</v>
+        <v>238.86962890625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23">
-        <v>238.78986328125</v>
+        <v>238.7900390625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24">
-        <v>235.02013671875</v>
+        <v>235.02001953125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25">
-        <v>234.09005859375</v>
+        <v>234.090087890625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26">
-        <v>232.1899609375</v>
+        <v>232.18994140625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B27">
-        <v>231.88974609375</v>
+        <v>231.8896484375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28">
-        <v>231.26</v>
+        <v>231.259765625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>227.90966796875</v>
@@ -2887,15 +3055,15 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30">
-        <v>227.809765625</v>
+        <v>227.8095703125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B31">
         <v>225.2099609375</v>
@@ -2903,15 +3071,15 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B32">
-        <v>225.0298828125</v>
+        <v>225.02978515625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33">
         <v>224.409912109375</v>
@@ -2919,55 +3087,55 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34">
-        <v>222.49970703125</v>
+        <v>222.49951171875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>219.46955078125</v>
+        <v>219.469482421875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36">
-        <v>218.41994140625</v>
+        <v>218.419921875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B37">
-        <v>216.38984375</v>
+        <v>216.3896484375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B38">
-        <v>216.0304296875</v>
+        <v>216.030517578125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39">
-        <v>215.55001953125</v>
+        <v>215.5498046875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B40">
         <v>212.2099609375</v>
@@ -2975,31 +3143,31 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B41">
-        <v>211.24005859375</v>
+        <v>211.239990234375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42">
-        <v>209.50986328125</v>
+        <v>209.509765625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43">
-        <v>206.12013671875</v>
+        <v>206.1201171875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44">
         <v>205.58984375</v>
@@ -3007,15 +3175,15 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45">
-        <v>204.87990234375</v>
+        <v>204.8798828125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B46">
         <v>199.2001953125</v>
@@ -3023,31 +3191,31 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47">
-        <v>198.499970703125</v>
+        <v>198.499755859375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48">
-        <v>197.369794921875</v>
+        <v>197.369873046875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B49">
-        <v>191.8599609375</v>
+        <v>191.85986328125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50">
         <v>187.64990234375</v>
@@ -3055,34 +3223,34 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51">
-        <v>186.46966796875</v>
+        <v>186.4697265625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B52">
-        <v>179.60001953125</v>
+        <v>179.60009765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53">
-        <v>159.439892578125</v>
+        <v>159.43994140625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B54">
-        <v>120.630029296875</v>
+        <v>120.6300048828125</v>
       </c>
     </row>
   </sheetData>
@@ -3102,426 +3270,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>103.0498046875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>99.72998046875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>87.64990234375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>85.97998046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>85.47998046875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>84.8798828125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>83.14990234375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>82.4501953125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>82.0498046875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>81.43017578125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>80.35986328125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>77.259765625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>77.0498046875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>76.080078125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>74.9501953125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>74.5498046875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>74.02978515625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>73.22998046875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>71.18017578125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>69.64990234375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>66.64990234375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>66.27978515625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>65.0498046875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>64.0498046875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>63.1298828125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>58.679931640625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>58.530029296875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>57.81005859375</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>53.14990234375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>52.97998046875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>52.550048828125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>51.929931640625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>51.72998046875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>50.590087890625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>47.72998046875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>45.64990234375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>36.580078125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>34.89990234375</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>29.8499755859375</v>
       </c>
     </row>
   </sheetData>
@@ -3541,7 +3709,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3549,7 +3717,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3557,7 +3725,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3565,7 +3733,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3573,7 +3741,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3581,7 +3749,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3589,7 +3757,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3597,7 +3765,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3605,7 +3773,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3613,7 +3781,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3621,7 +3789,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3629,7 +3797,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3637,7 +3805,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3645,7 +3813,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3653,7 +3821,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3661,7 +3829,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3669,7 +3837,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3677,7 +3845,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3685,7 +3853,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3693,7 +3861,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3701,7 +3869,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3709,7 +3877,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3717,7 +3885,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3725,7 +3893,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3733,7 +3901,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3741,7 +3909,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3749,7 +3917,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3757,7 +3925,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3765,7 +3933,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3773,7 +3941,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3781,7 +3949,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3789,7 +3957,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3797,7 +3965,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3805,7 +3973,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3813,7 +3981,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3821,7 +3989,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3829,7 +3997,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3837,7 +4005,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3845,7 +4013,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3853,7 +4021,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3861,7 +4029,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3869,7 +4037,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3877,7 +4045,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3885,7 +4053,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3893,7 +4061,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3901,7 +4069,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3909,7 +4077,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3917,7 +4085,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3925,7 +4093,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3933,7 +4101,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3941,7 +4109,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3949,7 +4117,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3957,7 +4125,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3980,7 +4148,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3988,7 +4156,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3996,7 +4164,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4004,7 +4172,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4012,7 +4180,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4020,7 +4188,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4028,7 +4196,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4036,7 +4204,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4044,7 +4212,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4052,7 +4220,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4060,7 +4228,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4068,7 +4236,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4076,7 +4244,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4084,7 +4252,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4092,7 +4260,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4100,7 +4268,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4108,7 +4276,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4116,7 +4284,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4124,7 +4292,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4132,7 +4300,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4140,7 +4308,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4148,7 +4316,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4156,7 +4324,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4164,7 +4332,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4172,7 +4340,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4180,7 +4348,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4188,7 +4356,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4196,7 +4364,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4204,7 +4372,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4212,7 +4380,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4220,7 +4388,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4228,7 +4396,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4236,7 +4404,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4244,7 +4412,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4252,7 +4420,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4260,7 +4428,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4268,7 +4436,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4276,7 +4444,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4284,7 +4452,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4292,7 +4460,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4300,7 +4468,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4308,7 +4476,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4316,7 +4484,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4324,7 +4492,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4332,7 +4500,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4340,7 +4508,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4348,7 +4516,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4356,7 +4524,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4364,7 +4532,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4372,7 +4540,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4380,7 +4548,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4388,7 +4556,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4396,7 +4564,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4419,7 +4587,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4427,7 +4595,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4435,7 +4603,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4443,7 +4611,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4451,7 +4619,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4459,7 +4627,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4467,7 +4635,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4475,7 +4643,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4483,7 +4651,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4491,7 +4659,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4499,7 +4667,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4507,7 +4675,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4515,7 +4683,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4523,7 +4691,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4531,7 +4699,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4539,7 +4707,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4547,7 +4715,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4555,7 +4723,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4563,7 +4731,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4571,7 +4739,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4579,7 +4747,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4587,7 +4755,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4595,7 +4763,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4603,7 +4771,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4611,7 +4779,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4619,7 +4787,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4627,7 +4795,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4635,7 +4803,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4643,7 +4811,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4651,7 +4819,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4659,7 +4827,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4667,7 +4835,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4675,7 +4843,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4683,7 +4851,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4691,7 +4859,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4699,7 +4867,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4707,7 +4875,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4715,7 +4883,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4723,7 +4891,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4731,7 +4899,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4739,7 +4907,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4747,7 +4915,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4755,7 +4923,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4763,7 +4931,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4771,7 +4939,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4779,7 +4947,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4787,7 +4955,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4795,7 +4963,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4803,7 +4971,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4811,7 +4979,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4819,7 +4987,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4827,7 +4995,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4835,7 +5003,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -593,7 +593,7 @@
         <v>58.679931640625</v>
       </c>
       <c r="F2">
-        <v>58.679931640625</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -613,7 +613,7 @@
         <v>57.25</v>
       </c>
       <c r="F3">
-        <v>57.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -633,7 +633,7 @@
         <v>83.14990234375</v>
       </c>
       <c r="F4">
-        <v>83.14990234375</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -653,7 +653,7 @@
         <v>74.9501953125</v>
       </c>
       <c r="F5">
-        <v>74.9501953125</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -673,7 +673,7 @@
         <v>82.4501953125</v>
       </c>
       <c r="F6">
-        <v>82.4501953125</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -693,7 +693,7 @@
         <v>62</v>
       </c>
       <c r="F7">
-        <v>62</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -713,7 +713,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="F8">
-        <v>65.14990234375</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -733,7 +733,7 @@
         <v>65.0498046875</v>
       </c>
       <c r="F9">
-        <v>65.0498046875</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -753,7 +753,7 @@
         <v>77.0498046875</v>
       </c>
       <c r="F10">
-        <v>77.0498046875</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -773,7 +773,7 @@
         <v>66.64990234375</v>
       </c>
       <c r="F11">
-        <v>66.64990234375</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -793,7 +793,7 @@
         <v>85.47998046875</v>
       </c>
       <c r="F12">
-        <v>85.47998046875</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -813,7 +813,7 @@
         <v>86.43017578125</v>
       </c>
       <c r="F13">
-        <v>86.43017578125</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -833,7 +833,7 @@
         <v>71.18017578125</v>
       </c>
       <c r="F14">
-        <v>71.18017578125</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -853,7 +853,7 @@
         <v>36.580078125</v>
       </c>
       <c r="F15">
-        <v>36.580078125</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -873,7 +873,7 @@
         <v>69.64990234375</v>
       </c>
       <c r="F16">
-        <v>69.64990234375</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -893,7 +893,7 @@
         <v>87.64990234375</v>
       </c>
       <c r="F17">
-        <v>87.64990234375</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -913,7 +913,7 @@
         <v>74.25</v>
       </c>
       <c r="F18">
-        <v>74.25</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -933,7 +933,7 @@
         <v>82.0498046875</v>
       </c>
       <c r="F19">
-        <v>82.0498046875</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -953,7 +953,7 @@
         <v>74.02978515625</v>
       </c>
       <c r="F20">
-        <v>74.02978515625</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -973,7 +973,7 @@
         <v>77.259765625</v>
       </c>
       <c r="F21">
-        <v>77.259765625</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -993,7 +993,7 @@
         <v>85.97998046875</v>
       </c>
       <c r="F22">
-        <v>85.97998046875</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1013,7 +1013,7 @@
         <v>52.25</v>
       </c>
       <c r="F23">
-        <v>52.25</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1033,7 +1033,7 @@
         <v>81.64990234375</v>
       </c>
       <c r="F24">
-        <v>81.64990234375</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1053,7 +1053,7 @@
         <v>81.64990234375</v>
       </c>
       <c r="F25">
-        <v>81.64990234375</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1073,7 +1073,7 @@
         <v>81.43017578125</v>
       </c>
       <c r="F26">
-        <v>81.43017578125</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1093,7 +1093,7 @@
         <v>63.1298828125</v>
       </c>
       <c r="F27">
-        <v>63.1298828125</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1113,7 +1113,7 @@
         <v>52.550048828125</v>
       </c>
       <c r="F28">
-        <v>52.550048828125</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1133,7 +1133,7 @@
         <v>53.25</v>
       </c>
       <c r="F29">
-        <v>53.25</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1153,7 +1153,7 @@
         <v>57.81005859375</v>
       </c>
       <c r="F30">
-        <v>57.81005859375</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1173,7 +1173,7 @@
         <v>84.8798828125</v>
       </c>
       <c r="F31">
-        <v>84.8798828125</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1193,7 +1193,7 @@
         <v>73.22998046875</v>
       </c>
       <c r="F32">
-        <v>73.22998046875</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1213,7 +1213,7 @@
         <v>45.64990234375</v>
       </c>
       <c r="F33">
-        <v>45.64990234375</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1233,7 +1233,7 @@
         <v>66.75</v>
       </c>
       <c r="F34">
-        <v>66.75</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1253,7 +1253,7 @@
         <v>99.72998046875</v>
       </c>
       <c r="F35">
-        <v>99.72998046875</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1273,7 +1273,7 @@
         <v>52.97998046875</v>
       </c>
       <c r="F36">
-        <v>52.97998046875</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1293,7 +1293,7 @@
         <v>34.89990234375</v>
       </c>
       <c r="F37">
-        <v>34.89990234375</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1313,7 +1313,7 @@
         <v>51.929931640625</v>
       </c>
       <c r="F38">
-        <v>51.929931640625</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1333,7 +1333,7 @@
         <v>66.27978515625</v>
       </c>
       <c r="F39">
-        <v>66.27978515625</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1353,7 +1353,7 @@
         <v>47.72998046875</v>
       </c>
       <c r="F40">
-        <v>47.72998046875</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1373,7 +1373,7 @@
         <v>109.75</v>
       </c>
       <c r="F41">
-        <v>109.75</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1393,7 +1393,7 @@
         <v>29.8499755859375</v>
       </c>
       <c r="F42">
-        <v>29.8499755859375</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1413,7 +1413,7 @@
         <v>51.72998046875</v>
       </c>
       <c r="F43">
-        <v>51.72998046875</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1433,7 +1433,7 @@
         <v>74.5498046875</v>
       </c>
       <c r="F44">
-        <v>74.5498046875</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1453,7 +1453,7 @@
         <v>48.75</v>
       </c>
       <c r="F45">
-        <v>48.75</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1473,7 +1473,7 @@
         <v>53.14990234375</v>
       </c>
       <c r="F46">
-        <v>53.14990234375</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1493,7 +1493,7 @@
         <v>64.0498046875</v>
       </c>
       <c r="F47">
-        <v>64.0498046875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1513,7 +1513,7 @@
         <v>50.590087890625</v>
       </c>
       <c r="F48">
-        <v>50.590087890625</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1533,7 +1533,7 @@
         <v>80.35986328125</v>
       </c>
       <c r="F49">
-        <v>80.35986328125</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1553,7 +1553,7 @@
         <v>58.530029296875</v>
       </c>
       <c r="F50">
-        <v>58.530029296875</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1573,7 +1573,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="F51">
-        <v>65.14990234375</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1593,7 +1593,7 @@
         <v>67.75</v>
       </c>
       <c r="F52">
-        <v>67.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1613,7 +1613,7 @@
         <v>103.0498046875</v>
       </c>
       <c r="F53">
-        <v>103.0498046875</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1633,7 +1633,7 @@
         <v>76.080078125</v>
       </c>
       <c r="F54">
-        <v>76.080078125</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3270,42 +3270,42 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B2">
-        <v>109.75</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>103.0498046875</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4">
-        <v>99.72998046875</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B5">
-        <v>87.64990234375</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>86.43017578125</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3313,151 +3313,151 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>85.97998046875</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B8">
-        <v>85.47998046875</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>84.8798828125</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B10">
-        <v>83.14990234375</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11">
-        <v>82.4501953125</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B12">
-        <v>82.0498046875</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B13">
-        <v>81.64990234375</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B14">
-        <v>81.64990234375</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>81.43017578125</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>80.35986328125</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>77.259765625</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B18">
-        <v>77.0498046875</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B19">
-        <v>76.080078125</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B20">
-        <v>74.9501953125</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B21">
-        <v>74.5498046875</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B22">
-        <v>74.25</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23">
-        <v>74.02978515625</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B24">
-        <v>73.22998046875</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B25">
-        <v>71.18017578125</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3465,231 +3465,231 @@
         <v>19</v>
       </c>
       <c r="B26">
-        <v>69.64990234375</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B27">
-        <v>67.75</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B28">
-        <v>66.75</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>66.64990234375</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B30">
-        <v>66.27978515625</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B31">
-        <v>65.14990234375</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>65.14990234375</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B33">
-        <v>65.0498046875</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B34">
-        <v>64.0498046875</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B35">
-        <v>63.1298828125</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B36">
-        <v>62</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B37">
-        <v>58.679931640625</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B38">
-        <v>58.530029296875</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B39">
-        <v>57.81005859375</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B40">
-        <v>57.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B41">
-        <v>53.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B42">
-        <v>53.14990234375</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B43">
-        <v>52.97998046875</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B44">
-        <v>52.550048828125</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B45">
-        <v>52.25</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B46">
-        <v>51.929931640625</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B47">
-        <v>51.72998046875</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B48">
-        <v>50.590087890625</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B49">
-        <v>48.75</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B50">
-        <v>47.72998046875</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B51">
-        <v>45.64990234375</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B52">
-        <v>36.580078125</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B53">
-        <v>34.89990234375</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B54">
-        <v>29.8499755859375</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="60">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Rodada 5</t>
+  </si>
+  <si>
+    <t>Rodada 6</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -556,10 +559,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,10 +578,13 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -593,12 +599,15 @@
         <v>58.679931640625</v>
       </c>
       <c r="F2">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>94.6201171875</v>
+      </c>
+      <c r="G2">
+        <v>94.6201171875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -613,12 +622,15 @@
         <v>57.25</v>
       </c>
       <c r="F3">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>79.52001953125</v>
+      </c>
+      <c r="G3">
+        <v>79.52001953125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -633,12 +645,15 @@
         <v>83.14990234375</v>
       </c>
       <c r="F4">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>77.47021484375</v>
+      </c>
+      <c r="G4">
+        <v>77.47021484375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -653,12 +668,15 @@
         <v>74.9501953125</v>
       </c>
       <c r="F5">
-        <v>41.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>103.919921875</v>
+      </c>
+      <c r="G5">
+        <v>103.919921875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -673,12 +691,15 @@
         <v>82.4501953125</v>
       </c>
       <c r="F6">
-        <v>19.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>85.31982421875</v>
+      </c>
+      <c r="G6">
+        <v>85.31982421875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -693,12 +714,15 @@
         <v>62</v>
       </c>
       <c r="F7">
-        <v>71.34999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>88.259765625</v>
+      </c>
+      <c r="G7">
+        <v>88.259765625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -713,12 +737,15 @@
         <v>65.14990234375</v>
       </c>
       <c r="F8">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>93.02001953125</v>
+      </c>
+      <c r="G8">
+        <v>93.02001953125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -733,12 +760,15 @@
         <v>65.0498046875</v>
       </c>
       <c r="F9">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>103.1201171875</v>
+      </c>
+      <c r="G9">
+        <v>103.1201171875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -753,12 +783,15 @@
         <v>77.0498046875</v>
       </c>
       <c r="F10">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>82.6201171875</v>
+      </c>
+      <c r="G10">
+        <v>82.6201171875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -773,12 +806,15 @@
         <v>66.64990234375</v>
       </c>
       <c r="F11">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>69.10986328125</v>
+      </c>
+      <c r="G11">
+        <v>69.10986328125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -793,12 +829,15 @@
         <v>85.47998046875</v>
       </c>
       <c r="F12">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>84.60986328125</v>
+      </c>
+      <c r="G12">
+        <v>84.60986328125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -813,12 +852,15 @@
         <v>86.43017578125</v>
       </c>
       <c r="F13">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>86.419921875</v>
+      </c>
+      <c r="G13">
+        <v>86.419921875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -833,12 +875,15 @@
         <v>71.18017578125</v>
       </c>
       <c r="F14">
-        <v>21.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>89.6201171875</v>
+      </c>
+      <c r="G14">
+        <v>89.6201171875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -853,12 +898,15 @@
         <v>36.580078125</v>
       </c>
       <c r="F15">
-        <v>8.949999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>61.300048828125</v>
+      </c>
+      <c r="G15">
+        <v>61.300048828125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -873,12 +921,15 @@
         <v>69.64990234375</v>
       </c>
       <c r="F16">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>88.919921875</v>
+      </c>
+      <c r="G16">
+        <v>88.919921875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -893,12 +944,15 @@
         <v>87.64990234375</v>
       </c>
       <c r="F17">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>89.02001953125</v>
+      </c>
+      <c r="G17">
+        <v>89.02001953125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -913,12 +967,15 @@
         <v>74.25</v>
       </c>
       <c r="F18">
-        <v>21.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>43.39990234375</v>
+      </c>
+      <c r="G18">
+        <v>43.39990234375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -933,12 +990,15 @@
         <v>82.0498046875</v>
       </c>
       <c r="F19">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>77.919921875</v>
+      </c>
+      <c r="G19">
+        <v>77.919921875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -953,12 +1013,15 @@
         <v>74.02978515625</v>
       </c>
       <c r="F20">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>81.6201171875</v>
+      </c>
+      <c r="G20">
+        <v>81.6201171875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -973,12 +1036,15 @@
         <v>77.259765625</v>
       </c>
       <c r="F21">
-        <v>20.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>69.3701171875</v>
+      </c>
+      <c r="G21">
+        <v>69.3701171875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -993,12 +1059,15 @@
         <v>85.97998046875</v>
       </c>
       <c r="F22">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>87.22021484375</v>
+      </c>
+      <c r="G22">
+        <v>87.22021484375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1013,12 +1082,15 @@
         <v>52.25</v>
       </c>
       <c r="F23">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>82.919921875</v>
+      </c>
+      <c r="G23">
+        <v>82.919921875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1033,12 +1105,15 @@
         <v>81.64990234375</v>
       </c>
       <c r="F24">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>84.81982421875</v>
+      </c>
+      <c r="G24">
+        <v>84.81982421875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1053,12 +1128,15 @@
         <v>81.64990234375</v>
       </c>
       <c r="F25">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>74.31982421875</v>
+      </c>
+      <c r="G25">
+        <v>74.31982421875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1073,12 +1151,15 @@
         <v>81.43017578125</v>
       </c>
       <c r="F26">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>85.669921875</v>
+      </c>
+      <c r="G26">
+        <v>85.669921875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1093,12 +1174,15 @@
         <v>63.1298828125</v>
       </c>
       <c r="F27">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>77.169921875</v>
+      </c>
+      <c r="G27">
+        <v>77.169921875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1113,12 +1197,15 @@
         <v>52.550048828125</v>
       </c>
       <c r="F28">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>83.22021484375</v>
+      </c>
+      <c r="G28">
+        <v>83.22021484375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1133,12 +1220,15 @@
         <v>53.25</v>
       </c>
       <c r="F29">
-        <v>20.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>83.31982421875</v>
+      </c>
+      <c r="G29">
+        <v>83.31982421875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1153,12 +1243,15 @@
         <v>57.81005859375</v>
       </c>
       <c r="F30">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>43.699951171875</v>
+      </c>
+      <c r="G30">
+        <v>43.699951171875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1173,12 +1266,15 @@
         <v>84.8798828125</v>
       </c>
       <c r="F31">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>77.47021484375</v>
+      </c>
+      <c r="G31">
+        <v>77.47021484375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>44.260009765625</v>
@@ -1193,12 +1289,15 @@
         <v>73.22998046875</v>
       </c>
       <c r="F32">
-        <v>16.59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>79.33984375</v>
+      </c>
+      <c r="G32">
+        <v>79.33984375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>84.259765625</v>
@@ -1213,12 +1312,15 @@
         <v>45.64990234375</v>
       </c>
       <c r="F33">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>72.27001953125</v>
+      </c>
+      <c r="G33">
+        <v>72.27001953125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34">
         <v>64.56005859375</v>
@@ -1233,12 +1335,15 @@
         <v>66.75</v>
       </c>
       <c r="F34">
-        <v>69.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>107.56005859375</v>
+      </c>
+      <c r="G34">
+        <v>107.56005859375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35">
         <v>43.510009765625</v>
@@ -1253,12 +1358,15 @@
         <v>99.72998046875</v>
       </c>
       <c r="F35">
-        <v>79.45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>109.16015625</v>
+      </c>
+      <c r="G35">
+        <v>109.16015625</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36">
         <v>57.4599609375</v>
@@ -1273,12 +1381,15 @@
         <v>52.97998046875</v>
       </c>
       <c r="F36">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>92.52001953125</v>
+      </c>
+      <c r="G36">
+        <v>92.52001953125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37">
         <v>64.56005859375</v>
@@ -1293,12 +1404,15 @@
         <v>34.89990234375</v>
       </c>
       <c r="F37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>88.6201171875</v>
+      </c>
+      <c r="G37">
+        <v>88.6201171875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38">
         <v>59.25</v>
@@ -1313,12 +1427,15 @@
         <v>51.929931640625</v>
       </c>
       <c r="F38">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>74.77001953125</v>
+      </c>
+      <c r="G38">
+        <v>74.77001953125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39">
         <v>58.25</v>
@@ -1333,12 +1450,15 @@
         <v>66.27978515625</v>
       </c>
       <c r="F39">
-        <v>21.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>75.56982421875</v>
+      </c>
+      <c r="G39">
+        <v>75.56982421875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B40">
         <v>84.85986328125</v>
@@ -1353,12 +1473,15 @@
         <v>47.72998046875</v>
       </c>
       <c r="F40">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>70.60009765625</v>
+      </c>
+      <c r="G40">
+        <v>70.60009765625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41">
         <v>60.159912109375</v>
@@ -1373,12 +1496,15 @@
         <v>109.75</v>
       </c>
       <c r="F41">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>81.47021484375</v>
+      </c>
+      <c r="G41">
+        <v>81.47021484375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42">
         <v>49</v>
@@ -1393,12 +1519,15 @@
         <v>29.8499755859375</v>
       </c>
       <c r="F42">
-        <v>18.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>83.41015625</v>
+      </c>
+      <c r="G42">
+        <v>83.41015625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>61.659912109375</v>
@@ -1413,12 +1542,15 @@
         <v>51.72998046875</v>
       </c>
       <c r="F43">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>82.1298828125</v>
+      </c>
+      <c r="G43">
+        <v>82.1298828125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <v>42.9599609375</v>
@@ -1433,12 +1565,15 @@
         <v>74.5498046875</v>
       </c>
       <c r="F44">
-        <v>18.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>96.1201171875</v>
+      </c>
+      <c r="G44">
+        <v>96.1201171875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B45">
         <v>54.10009765625</v>
@@ -1453,12 +1588,15 @@
         <v>48.75</v>
       </c>
       <c r="F45">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>73.81005859375</v>
+      </c>
+      <c r="G45">
+        <v>73.81005859375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>61.9599609375</v>
@@ -1473,12 +1611,15 @@
         <v>53.14990234375</v>
       </c>
       <c r="F46">
-        <v>47.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>87.52001953125</v>
+      </c>
+      <c r="G46">
+        <v>87.52001953125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>64.2001953125</v>
@@ -1493,12 +1634,15 @@
         <v>64.0498046875</v>
       </c>
       <c r="F47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>67.669921875</v>
+      </c>
+      <c r="G47">
+        <v>67.669921875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>66.85986328125</v>
@@ -1513,12 +1657,15 @@
         <v>50.590087890625</v>
       </c>
       <c r="F48">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>81.169921875</v>
+      </c>
+      <c r="G48">
+        <v>81.169921875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B49">
         <v>58.9599609375</v>
@@ -1533,12 +1680,15 @@
         <v>80.35986328125</v>
       </c>
       <c r="F49">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>98.52001953125</v>
+      </c>
+      <c r="G49">
+        <v>98.52001953125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>70</v>
@@ -1553,12 +1703,15 @@
         <v>58.530029296875</v>
       </c>
       <c r="F50">
-        <v>26.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>78.81982421875</v>
+      </c>
+      <c r="G50">
+        <v>78.81982421875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>68.06005859375</v>
@@ -1573,12 +1726,15 @@
         <v>65.14990234375</v>
       </c>
       <c r="F51">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>93.02001953125</v>
+      </c>
+      <c r="G51">
+        <v>93.02001953125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52">
         <v>51.260009765625</v>
@@ -1593,12 +1749,15 @@
         <v>67.75</v>
       </c>
       <c r="F52">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>75.419921875</v>
+      </c>
+      <c r="G52">
+        <v>75.419921875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B53">
         <v>72.16015625</v>
@@ -1613,12 +1772,15 @@
         <v>103.0498046875</v>
       </c>
       <c r="F53">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>89.419921875</v>
+      </c>
+      <c r="G53">
+        <v>89.419921875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -1633,12 +1795,15 @@
         <v>76.080078125</v>
       </c>
       <c r="F54">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>66.2001953125</v>
+      </c>
+      <c r="G54">
+        <v>66.2001953125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1653,6 +1818,9 @@
         <v>0</v>
       </c>
       <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
         <v>0</v>
       </c>
     </row>
@@ -1668,272 +1836,272 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1953,7 +2121,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1961,7 +2129,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1969,7 +2137,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1977,7 +2145,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1985,7 +2153,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1993,7 +2161,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2001,7 +2169,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2009,7 +2177,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2017,7 +2185,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2025,7 +2193,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2033,7 +2201,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2041,7 +2209,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2049,7 +2217,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2057,7 +2225,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2065,7 +2233,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2073,7 +2241,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2081,7 +2249,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2089,7 +2257,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2097,7 +2265,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2105,7 +2273,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2113,7 +2281,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2121,7 +2289,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2129,7 +2297,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2137,7 +2305,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2145,7 +2313,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2153,7 +2321,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2161,7 +2329,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2169,7 +2337,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2177,7 +2345,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2185,7 +2353,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2193,7 +2361,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2201,7 +2369,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2209,7 +2377,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2217,7 +2385,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2225,7 +2393,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2233,7 +2401,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2241,7 +2409,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2249,7 +2417,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2257,7 +2425,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2265,7 +2433,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2273,7 +2441,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2281,7 +2449,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2289,7 +2457,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2297,7 +2465,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2305,7 +2473,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2313,7 +2481,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2321,7 +2489,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2329,7 +2497,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2337,7 +2505,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2345,7 +2513,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2353,7 +2521,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2361,7 +2529,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2369,7 +2537,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2392,7 +2560,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -2400,7 +2568,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -2408,7 +2576,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -2416,7 +2584,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -2424,7 +2592,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -2432,7 +2600,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -2440,7 +2608,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -2448,7 +2616,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -2456,7 +2624,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -2464,7 +2632,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -2472,7 +2640,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -2480,7 +2648,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -2488,7 +2656,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -2496,7 +2664,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -2504,7 +2672,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -2512,7 +2680,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -2520,7 +2688,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -2528,7 +2696,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -2536,7 +2704,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -2544,7 +2712,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -2552,7 +2720,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -2560,7 +2728,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -2568,7 +2736,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -2576,7 +2744,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -2584,7 +2752,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -2592,7 +2760,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -2600,7 +2768,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -2608,7 +2776,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -2616,7 +2784,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -2624,7 +2792,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -2632,7 +2800,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -2640,7 +2808,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -2648,7 +2816,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -2656,7 +2824,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -2664,7 +2832,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -2672,7 +2840,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -2680,7 +2848,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -2688,7 +2856,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -2696,7 +2864,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -2704,7 +2872,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -2712,7 +2880,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -2720,7 +2888,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -2728,7 +2896,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -2736,7 +2904,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -2744,7 +2912,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -2752,7 +2920,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -2760,7 +2928,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B48">
         <v>44.260009765625</v>
@@ -2768,7 +2936,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B49">
         <v>44.06005859375</v>
@@ -2776,7 +2944,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B50">
         <v>43.510009765625</v>
@@ -2784,7 +2952,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B51">
         <v>42.9599609375</v>
@@ -2792,7 +2960,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B52">
         <v>40.60009765625</v>
@@ -2800,7 +2968,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B53">
         <v>38.260009765625</v>
@@ -2808,7 +2976,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B54">
         <v>37.820068359375</v>
@@ -2831,7 +2999,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -2839,7 +3007,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -2847,7 +3015,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -2855,7 +3023,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -2863,7 +3031,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -2871,7 +3039,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -2879,7 +3047,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -2887,7 +3055,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -2895,7 +3063,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -2903,7 +3071,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -2911,7 +3079,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -2919,7 +3087,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -2927,7 +3095,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -2935,7 +3103,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -2943,7 +3111,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -2951,7 +3119,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -2959,7 +3127,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -2967,7 +3135,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -2975,7 +3143,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -2983,7 +3151,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -2991,7 +3159,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -2999,7 +3167,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -3007,7 +3175,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -3015,7 +3183,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -3023,7 +3191,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>232.18994140625</v>
@@ -3031,7 +3199,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27">
         <v>231.8896484375</v>
@@ -3039,7 +3207,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28">
         <v>231.259765625</v>
@@ -3047,7 +3215,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>227.90966796875</v>
@@ -3055,7 +3223,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30">
         <v>227.8095703125</v>
@@ -3063,7 +3231,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31">
         <v>225.2099609375</v>
@@ -3071,7 +3239,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32">
         <v>225.02978515625</v>
@@ -3079,7 +3247,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33">
         <v>224.409912109375</v>
@@ -3087,7 +3255,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34">
         <v>222.49951171875</v>
@@ -3095,7 +3263,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>219.469482421875</v>
@@ -3103,7 +3271,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36">
         <v>218.419921875</v>
@@ -3111,7 +3279,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37">
         <v>216.3896484375</v>
@@ -3119,7 +3287,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38">
         <v>216.030517578125</v>
@@ -3127,7 +3295,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B39">
         <v>215.5498046875</v>
@@ -3135,7 +3303,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>212.2099609375</v>
@@ -3143,7 +3311,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B41">
         <v>211.239990234375</v>
@@ -3151,7 +3319,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42">
         <v>209.509765625</v>
@@ -3159,7 +3327,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43">
         <v>206.1201171875</v>
@@ -3167,7 +3335,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44">
         <v>205.58984375</v>
@@ -3175,7 +3343,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>204.8798828125</v>
@@ -3183,7 +3351,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46">
         <v>199.2001953125</v>
@@ -3191,7 +3359,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47">
         <v>198.499755859375</v>
@@ -3199,7 +3367,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B48">
         <v>197.369873046875</v>
@@ -3207,7 +3375,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49">
         <v>191.85986328125</v>
@@ -3215,7 +3383,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50">
         <v>187.64990234375</v>
@@ -3223,7 +3391,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>186.4697265625</v>
@@ -3231,7 +3399,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B52">
         <v>179.60009765625</v>
@@ -3239,7 +3407,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B53">
         <v>159.43994140625</v>
@@ -3247,7 +3415,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B54">
         <v>120.6300048828125</v>
@@ -3270,426 +3438,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2">
-        <v>79.45</v>
+        <v>218.3203125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B3">
-        <v>71.34999999999999</v>
+        <v>215.1201171875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>69.25</v>
+        <v>207.83984375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>47.8</v>
+        <v>206.240234375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B6">
-        <v>41.6</v>
+        <v>197.0400390625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B7">
-        <v>27.1</v>
+        <v>192.240234375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>26.2</v>
+        <v>189.240234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>25.7</v>
+        <v>186.0400390625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10">
-        <v>22.3</v>
+        <v>186.0400390625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B11">
-        <v>22.3</v>
+        <v>185.0400390625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>22.2</v>
+        <v>179.240234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B13">
-        <v>21.85</v>
+        <v>178.83984375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>21.35</v>
+        <v>178.0400390625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>21.3</v>
+        <v>177.83984375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B16">
-        <v>20.9</v>
+        <v>177.240234375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>20.7</v>
+        <v>176.51953125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B18">
-        <v>20.7</v>
+        <v>175.0400390625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>20.7</v>
+        <v>174.4404296875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B20">
-        <v>20.6</v>
+        <v>172.83984375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>20.4</v>
+        <v>171.33984375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B22">
-        <v>20.4</v>
+        <v>170.6396484375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B23">
-        <v>20.17</v>
+        <v>169.6396484375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B24">
-        <v>19.3</v>
+        <v>169.2197265625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25">
-        <v>18.7</v>
+        <v>166.8203125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B26">
-        <v>18.3</v>
+        <v>166.6396484375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B27">
-        <v>18.15</v>
+        <v>166.4404296875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>16.9</v>
+        <v>165.83984375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>16.59</v>
+        <v>165.240234375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B30">
-        <v>15.5</v>
+        <v>164.259765625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>14.9</v>
+        <v>163.240234375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B32">
-        <v>14.6</v>
+        <v>162.9404296875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B33">
-        <v>14.3</v>
+        <v>162.33984375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B34">
-        <v>14.3</v>
+        <v>159.0400390625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B35">
-        <v>13.9</v>
+        <v>158.6796875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B36">
-        <v>13.8</v>
+        <v>157.6396484375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B37">
-        <v>11.7</v>
+        <v>155.83984375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B38">
-        <v>11.3</v>
+        <v>154.9404296875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>11.3</v>
+        <v>154.9404296875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B40">
-        <v>10.5</v>
+        <v>154.33984375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B41">
-        <v>10.5</v>
+        <v>151.1396484375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B42">
-        <v>10.2</v>
+        <v>150.83984375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>9.300000000000001</v>
+        <v>149.5400390625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B44">
-        <v>9.300000000000001</v>
+        <v>148.6396484375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B45">
-        <v>8.949999999999999</v>
+        <v>147.6201171875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B46">
-        <v>8.800000000000001</v>
+        <v>144.5400390625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B47">
-        <v>7.7</v>
+        <v>141.2001953125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>7.1</v>
+        <v>138.740234375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B49">
-        <v>6.1</v>
+        <v>138.2197265625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>135.33984375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>132.400390625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B52">
-        <v>4.2</v>
+        <v>122.60009765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B53">
-        <v>3.57</v>
+        <v>87.39990234375</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>86.7998046875</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +3877,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3717,7 +3885,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3725,7 +3893,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3733,7 +3901,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3741,7 +3909,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3749,7 +3917,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3757,7 +3925,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3765,7 +3933,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3773,7 +3941,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3781,7 +3949,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3789,7 +3957,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3797,7 +3965,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3805,7 +3973,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3813,7 +3981,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3821,7 +3989,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3829,7 +3997,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3837,7 +4005,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3845,7 +4013,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3853,7 +4021,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3861,7 +4029,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3869,7 +4037,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3877,7 +4045,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3885,7 +4053,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3893,7 +4061,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3901,7 +4069,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3909,7 +4077,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3917,7 +4085,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3925,7 +4093,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3933,7 +4101,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3941,7 +4109,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3949,7 +4117,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3957,7 +4125,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3965,7 +4133,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3973,7 +4141,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3981,7 +4149,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3989,7 +4157,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3997,7 +4165,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4005,7 +4173,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4013,7 +4181,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4021,7 +4189,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4029,7 +4197,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4037,7 +4205,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4045,7 +4213,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4053,7 +4221,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4061,7 +4229,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4069,7 +4237,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4077,7 +4245,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4085,7 +4253,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4093,7 +4261,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4101,7 +4269,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4109,7 +4277,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4117,7 +4285,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4125,7 +4293,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4148,7 +4316,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4156,7 +4324,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4164,7 +4332,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4172,7 +4340,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4180,7 +4348,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4188,7 +4356,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4196,7 +4364,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4204,7 +4372,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4212,7 +4380,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4220,7 +4388,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4228,7 +4396,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4236,7 +4404,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4244,7 +4412,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4252,7 +4420,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4260,7 +4428,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4268,7 +4436,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4276,7 +4444,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4284,7 +4452,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4292,7 +4460,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4300,7 +4468,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4308,7 +4476,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4316,7 +4484,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4324,7 +4492,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4332,7 +4500,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4340,7 +4508,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4348,7 +4516,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4356,7 +4524,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4364,7 +4532,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4372,7 +4540,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4380,7 +4548,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4388,7 +4556,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4396,7 +4564,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4404,7 +4572,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4412,7 +4580,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4420,7 +4588,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4428,7 +4596,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4436,7 +4604,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4444,7 +4612,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4452,7 +4620,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4460,7 +4628,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4468,7 +4636,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4476,7 +4644,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4484,7 +4652,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4492,7 +4660,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4500,7 +4668,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4508,7 +4676,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4516,7 +4684,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4524,7 +4692,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4532,7 +4700,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4540,7 +4708,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4548,7 +4716,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4556,7 +4724,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -4564,7 +4732,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4587,7 +4755,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4595,7 +4763,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4603,7 +4771,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4611,7 +4779,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4619,7 +4787,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4627,7 +4795,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4635,7 +4803,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4643,7 +4811,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4651,7 +4819,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4659,7 +4827,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4667,7 +4835,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4675,7 +4843,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4683,7 +4851,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4691,7 +4859,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4699,7 +4867,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4707,7 +4875,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4715,7 +4883,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4723,7 +4891,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4731,7 +4899,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4739,7 +4907,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4747,7 +4915,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4755,7 +4923,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -4763,7 +4931,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4771,7 +4939,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4779,7 +4947,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -4787,7 +4955,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4795,7 +4963,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4803,7 +4971,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4811,7 +4979,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4819,7 +4987,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4827,7 +4995,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4835,7 +5003,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -4843,7 +5011,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -4851,7 +5019,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4859,7 +5027,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4867,7 +5035,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4875,7 +5043,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4883,7 +5051,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4891,7 +5059,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4899,7 +5067,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4907,7 +5075,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4915,7 +5083,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4923,7 +5091,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4931,7 +5099,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4939,7 +5107,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4947,7 +5115,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4955,7 +5123,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4963,7 +5131,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -4971,7 +5139,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -4979,7 +5147,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -4987,7 +5155,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4995,7 +5163,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -5003,7 +5171,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -16,13 +16,14 @@
     <sheet name="Mes - Abril" sheetId="7" r:id="rId7"/>
     <sheet name="Mes - Maio" sheetId="8" r:id="rId8"/>
     <sheet name="Mes - Julho" sheetId="9" r:id="rId9"/>
+    <sheet name="Premiados Mensais" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="66">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -202,6 +203,24 @@
   </si>
   <si>
     <t>Lider_Rodada</t>
+  </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>Posicao</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Pontos</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
   </si>
 </sst>
 </file>
@@ -1829,6 +1848,170 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2">
+        <v>84.85986328125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>84.259765625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>74.06005859375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>73.9599609375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>73.759765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7">
+        <v>281.78955078125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8">
+        <v>265.3896484375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>265.3701171875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10">
+        <v>263.08984375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>262.98974609375</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A2:A55"/>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -8,22 +8,25 @@
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="1" r:id="rId1"/>
-    <sheet name="Turno 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Classif Turno 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Mes - Janeiro" sheetId="4" r:id="rId4"/>
-    <sheet name="Mes - Fevereiro" sheetId="5" r:id="rId5"/>
-    <sheet name="Mes - Marco" sheetId="6" r:id="rId6"/>
-    <sheet name="Mes - Abril" sheetId="7" r:id="rId7"/>
-    <sheet name="Mes - Maio" sheetId="8" r:id="rId8"/>
-    <sheet name="Mes - Julho" sheetId="9" r:id="rId9"/>
-    <sheet name="Premiados Mensais" sheetId="10" r:id="rId10"/>
+    <sheet name="Turno 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Classif Turno 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Turno 2" sheetId="4" r:id="rId4"/>
+    <sheet name="Classif Turno 2" sheetId="5" r:id="rId5"/>
+    <sheet name="Mes - Janeiro" sheetId="6" r:id="rId6"/>
+    <sheet name="Mes - Fevereiro" sheetId="7" r:id="rId7"/>
+    <sheet name="Mes - Marco" sheetId="8" r:id="rId8"/>
+    <sheet name="Mes - Abril" sheetId="9" r:id="rId9"/>
+    <sheet name="Mes - Maio" sheetId="10" r:id="rId10"/>
+    <sheet name="Mes - Julho" sheetId="11" r:id="rId11"/>
+    <sheet name="Premiados Mensais" sheetId="12" r:id="rId12"/>
+    <sheet name="Campeao Turno" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="65">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -131,9 +134,6 @@
   </si>
   <si>
     <t>Máquina Laranjja</t>
-  </si>
-  <si>
-    <t>NaoVaiDescer!</t>
   </si>
   <si>
     <t>Paulo Virgili FC</t>
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -621,7 +621,7 @@
         <v>94.6201171875</v>
       </c>
       <c r="G2">
-        <v>94.6201171875</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -644,7 +644,7 @@
         <v>79.52001953125</v>
       </c>
       <c r="G3">
-        <v>79.52001953125</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -667,7 +667,7 @@
         <v>77.47021484375</v>
       </c>
       <c r="G4">
-        <v>77.47021484375</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -690,7 +690,7 @@
         <v>103.919921875</v>
       </c>
       <c r="G5">
-        <v>103.919921875</v>
+        <v>86.42</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -713,7 +713,7 @@
         <v>85.31982421875</v>
       </c>
       <c r="G6">
-        <v>85.31982421875</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -736,7 +736,7 @@
         <v>88.259765625</v>
       </c>
       <c r="G7">
-        <v>88.259765625</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -759,7 +759,7 @@
         <v>93.02001953125</v>
       </c>
       <c r="G8">
-        <v>93.02001953125</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -782,7 +782,7 @@
         <v>103.1201171875</v>
       </c>
       <c r="G9">
-        <v>103.1201171875</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -805,7 +805,7 @@
         <v>82.6201171875</v>
       </c>
       <c r="G10">
-        <v>82.6201171875</v>
+        <v>66.61</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -828,7 +828,7 @@
         <v>69.10986328125</v>
       </c>
       <c r="G11">
-        <v>69.10986328125</v>
+        <v>67.19</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -851,7 +851,7 @@
         <v>84.60986328125</v>
       </c>
       <c r="G12">
-        <v>84.60986328125</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -874,7 +874,7 @@
         <v>86.419921875</v>
       </c>
       <c r="G13">
-        <v>86.419921875</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -897,7 +897,7 @@
         <v>89.6201171875</v>
       </c>
       <c r="G14">
-        <v>89.6201171875</v>
+        <v>58.29</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -920,7 +920,7 @@
         <v>61.300048828125</v>
       </c>
       <c r="G15">
-        <v>61.300048828125</v>
+        <v>68.48999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -943,7 +943,7 @@
         <v>88.919921875</v>
       </c>
       <c r="G16">
-        <v>88.919921875</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -966,7 +966,7 @@
         <v>89.02001953125</v>
       </c>
       <c r="G17">
-        <v>89.02001953125</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -989,7 +989,7 @@
         <v>43.39990234375</v>
       </c>
       <c r="G18">
-        <v>43.39990234375</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1012,7 +1012,7 @@
         <v>77.919921875</v>
       </c>
       <c r="G19">
-        <v>77.919921875</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1035,7 +1035,7 @@
         <v>81.6201171875</v>
       </c>
       <c r="G20">
-        <v>81.6201171875</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1058,7 +1058,7 @@
         <v>69.3701171875</v>
       </c>
       <c r="G21">
-        <v>69.3701171875</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1081,7 +1081,7 @@
         <v>87.22021484375</v>
       </c>
       <c r="G22">
-        <v>87.22021484375</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1104,7 +1104,7 @@
         <v>82.919921875</v>
       </c>
       <c r="G23">
-        <v>82.919921875</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1127,7 +1127,7 @@
         <v>84.81982421875</v>
       </c>
       <c r="G24">
-        <v>84.81982421875</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1150,7 +1150,7 @@
         <v>74.31982421875</v>
       </c>
       <c r="G25">
-        <v>74.31982421875</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1173,7 +1173,7 @@
         <v>85.669921875</v>
       </c>
       <c r="G26">
-        <v>85.669921875</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1196,7 +1196,7 @@
         <v>77.169921875</v>
       </c>
       <c r="G27">
-        <v>77.169921875</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1219,7 +1219,7 @@
         <v>83.22021484375</v>
       </c>
       <c r="G28">
-        <v>83.22021484375</v>
+        <v>80.61</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1242,7 +1242,7 @@
         <v>83.31982421875</v>
       </c>
       <c r="G29">
-        <v>83.31982421875</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1265,7 +1265,7 @@
         <v>43.699951171875</v>
       </c>
       <c r="G30">
-        <v>43.699951171875</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1288,7 +1288,7 @@
         <v>77.47021484375</v>
       </c>
       <c r="G31">
-        <v>77.47021484375</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1296,22 +1296,22 @@
         <v>36</v>
       </c>
       <c r="B32">
-        <v>44.260009765625</v>
+        <v>84.259765625</v>
       </c>
       <c r="C32">
-        <v>90</v>
+        <v>82.60986328125</v>
       </c>
       <c r="D32">
-        <v>68.9599609375</v>
+        <v>81.25</v>
       </c>
       <c r="E32">
-        <v>73.22998046875</v>
+        <v>45.64990234375</v>
       </c>
       <c r="F32">
-        <v>79.33984375</v>
+        <v>72.27001953125</v>
       </c>
       <c r="G32">
-        <v>79.33984375</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1319,22 +1319,22 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>84.259765625</v>
+        <v>64.56005859375</v>
       </c>
       <c r="C33">
-        <v>82.60986328125</v>
+        <v>105.5</v>
       </c>
       <c r="D33">
-        <v>81.25</v>
+        <v>81.16015625</v>
       </c>
       <c r="E33">
-        <v>45.64990234375</v>
+        <v>66.75</v>
       </c>
       <c r="F33">
-        <v>72.27001953125</v>
+        <v>107.56005859375</v>
       </c>
       <c r="G33">
-        <v>72.27001953125</v>
+        <v>71.61</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1342,22 +1342,22 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>64.56005859375</v>
+        <v>43.510009765625</v>
       </c>
       <c r="C34">
-        <v>105.5</v>
+        <v>60.8798828125</v>
       </c>
       <c r="D34">
-        <v>81.16015625</v>
+        <v>78.259765625</v>
       </c>
       <c r="E34">
-        <v>66.75</v>
+        <v>99.72998046875</v>
       </c>
       <c r="F34">
-        <v>107.56005859375</v>
+        <v>109.16015625</v>
       </c>
       <c r="G34">
-        <v>107.56005859375</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1365,22 +1365,22 @@
         <v>39</v>
       </c>
       <c r="B35">
-        <v>43.510009765625</v>
+        <v>57.4599609375</v>
       </c>
       <c r="C35">
-        <v>60.8798828125</v>
+        <v>88.18017578125</v>
       </c>
       <c r="D35">
-        <v>78.259765625</v>
+        <v>77.259765625</v>
       </c>
       <c r="E35">
-        <v>99.72998046875</v>
+        <v>52.97998046875</v>
       </c>
       <c r="F35">
-        <v>109.16015625</v>
+        <v>92.52001953125</v>
       </c>
       <c r="G35">
-        <v>109.16015625</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1388,22 +1388,22 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>57.4599609375</v>
+        <v>64.56005859375</v>
       </c>
       <c r="C36">
-        <v>88.18017578125</v>
+        <v>86.60009765625</v>
       </c>
       <c r="D36">
-        <v>77.259765625</v>
+        <v>70.35986328125</v>
       </c>
       <c r="E36">
-        <v>52.97998046875</v>
+        <v>34.89990234375</v>
       </c>
       <c r="F36">
-        <v>92.52001953125</v>
+        <v>88.6201171875</v>
       </c>
       <c r="G36">
-        <v>92.52001953125</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1411,22 +1411,22 @@
         <v>41</v>
       </c>
       <c r="B37">
-        <v>64.56005859375</v>
+        <v>59.25</v>
       </c>
       <c r="C37">
-        <v>86.60009765625</v>
+        <v>73.77978515625</v>
       </c>
       <c r="D37">
-        <v>70.35986328125</v>
+        <v>93.759765625</v>
       </c>
       <c r="E37">
-        <v>34.89990234375</v>
+        <v>51.929931640625</v>
       </c>
       <c r="F37">
-        <v>88.6201171875</v>
+        <v>74.77001953125</v>
       </c>
       <c r="G37">
-        <v>88.6201171875</v>
+        <v>66.51000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1434,22 +1434,22 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>59.25</v>
+        <v>58.25</v>
       </c>
       <c r="C38">
-        <v>73.77978515625</v>
+        <v>63.780029296875</v>
       </c>
       <c r="D38">
-        <v>93.759765625</v>
+        <v>68.43994140625</v>
       </c>
       <c r="E38">
-        <v>51.929931640625</v>
+        <v>66.27978515625</v>
       </c>
       <c r="F38">
-        <v>74.77001953125</v>
+        <v>75.56982421875</v>
       </c>
       <c r="G38">
-        <v>74.77001953125</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1457,22 +1457,22 @@
         <v>43</v>
       </c>
       <c r="B39">
-        <v>58.25</v>
+        <v>84.85986328125</v>
       </c>
       <c r="C39">
-        <v>63.780029296875</v>
+        <v>79.4501953125</v>
       </c>
       <c r="D39">
-        <v>68.43994140625</v>
+        <v>78.93994140625</v>
       </c>
       <c r="E39">
-        <v>66.27978515625</v>
+        <v>47.72998046875</v>
       </c>
       <c r="F39">
-        <v>75.56982421875</v>
+        <v>70.60009765625</v>
       </c>
       <c r="G39">
-        <v>75.56982421875</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1480,22 +1480,22 @@
         <v>44</v>
       </c>
       <c r="B40">
-        <v>84.85986328125</v>
+        <v>60.159912109375</v>
       </c>
       <c r="C40">
-        <v>79.4501953125</v>
+        <v>64.580078125</v>
       </c>
       <c r="D40">
-        <v>78.93994140625</v>
+        <v>88.759765625</v>
       </c>
       <c r="E40">
-        <v>47.72998046875</v>
+        <v>109.75</v>
       </c>
       <c r="F40">
-        <v>70.60009765625</v>
+        <v>81.47021484375</v>
       </c>
       <c r="G40">
-        <v>70.60009765625</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1503,22 +1503,22 @@
         <v>45</v>
       </c>
       <c r="B41">
-        <v>60.159912109375</v>
+        <v>49</v>
       </c>
       <c r="C41">
-        <v>64.580078125</v>
+        <v>36.429931640625</v>
       </c>
       <c r="D41">
-        <v>88.759765625</v>
+        <v>54.35009765625</v>
       </c>
       <c r="E41">
-        <v>109.75</v>
+        <v>29.8499755859375</v>
       </c>
       <c r="F41">
-        <v>81.47021484375</v>
+        <v>83.41015625</v>
       </c>
       <c r="G41">
-        <v>81.47021484375</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1526,22 +1526,22 @@
         <v>46</v>
       </c>
       <c r="B42">
-        <v>49</v>
+        <v>61.659912109375</v>
       </c>
       <c r="C42">
-        <v>36.429931640625</v>
+        <v>69.5</v>
       </c>
       <c r="D42">
-        <v>54.35009765625</v>
+        <v>83.64990234375</v>
       </c>
       <c r="E42">
-        <v>29.8499755859375</v>
+        <v>51.72998046875</v>
       </c>
       <c r="F42">
-        <v>83.41015625</v>
+        <v>82.1298828125</v>
       </c>
       <c r="G42">
-        <v>83.41015625</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1549,22 +1549,22 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>61.659912109375</v>
+        <v>42.9599609375</v>
       </c>
       <c r="C43">
-        <v>69.5</v>
+        <v>91.47998046875</v>
       </c>
       <c r="D43">
-        <v>83.64990234375</v>
+        <v>99.35986328125</v>
       </c>
       <c r="E43">
-        <v>51.72998046875</v>
+        <v>74.5498046875</v>
       </c>
       <c r="F43">
-        <v>82.1298828125</v>
+        <v>96.1201171875</v>
       </c>
       <c r="G43">
-        <v>82.1298828125</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1572,22 +1572,22 @@
         <v>48</v>
       </c>
       <c r="B44">
-        <v>42.9599609375</v>
+        <v>54.10009765625</v>
       </c>
       <c r="C44">
-        <v>91.47998046875</v>
+        <v>71.5</v>
       </c>
       <c r="D44">
-        <v>99.35986328125</v>
+        <v>67.39990234375</v>
       </c>
       <c r="E44">
-        <v>74.5498046875</v>
+        <v>48.75</v>
       </c>
       <c r="F44">
-        <v>96.1201171875</v>
+        <v>73.81005859375</v>
       </c>
       <c r="G44">
-        <v>96.1201171875</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1595,22 +1595,22 @@
         <v>49</v>
       </c>
       <c r="B45">
-        <v>54.10009765625</v>
+        <v>61.9599609375</v>
       </c>
       <c r="C45">
-        <v>71.5</v>
+        <v>84.47998046875</v>
       </c>
       <c r="D45">
-        <v>67.39990234375</v>
+        <v>87.39990234375</v>
       </c>
       <c r="E45">
-        <v>48.75</v>
+        <v>53.14990234375</v>
       </c>
       <c r="F45">
-        <v>73.81005859375</v>
+        <v>87.52001953125</v>
       </c>
       <c r="G45">
-        <v>73.81005859375</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1618,22 +1618,22 @@
         <v>50</v>
       </c>
       <c r="B46">
-        <v>61.9599609375</v>
+        <v>64.2001953125</v>
       </c>
       <c r="C46">
-        <v>84.47998046875</v>
+        <v>95.3798828125</v>
       </c>
       <c r="D46">
-        <v>87.39990234375</v>
+        <v>56.9599609375</v>
       </c>
       <c r="E46">
-        <v>53.14990234375</v>
+        <v>64.0498046875</v>
       </c>
       <c r="F46">
-        <v>87.52001953125</v>
+        <v>67.669921875</v>
       </c>
       <c r="G46">
-        <v>87.52001953125</v>
+        <v>59.93</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1641,22 +1641,22 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>64.2001953125</v>
+        <v>66.85986328125</v>
       </c>
       <c r="C47">
-        <v>95.3798828125</v>
+        <v>92.7001953125</v>
       </c>
       <c r="D47">
-        <v>56.9599609375</v>
+        <v>72.740234375</v>
       </c>
       <c r="E47">
-        <v>64.0498046875</v>
+        <v>50.590087890625</v>
       </c>
       <c r="F47">
-        <v>67.669921875</v>
+        <v>81.169921875</v>
       </c>
       <c r="G47">
-        <v>67.669921875</v>
+        <v>62.92</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1664,22 +1664,22 @@
         <v>52</v>
       </c>
       <c r="B48">
-        <v>66.85986328125</v>
+        <v>58.9599609375</v>
       </c>
       <c r="C48">
-        <v>92.7001953125</v>
+        <v>79.27978515625</v>
       </c>
       <c r="D48">
-        <v>72.740234375</v>
+        <v>86.66015625</v>
       </c>
       <c r="E48">
-        <v>50.590087890625</v>
+        <v>80.35986328125</v>
       </c>
       <c r="F48">
-        <v>81.169921875</v>
+        <v>98.52001953125</v>
       </c>
       <c r="G48">
-        <v>81.169921875</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1687,22 +1687,22 @@
         <v>53</v>
       </c>
       <c r="B49">
-        <v>58.9599609375</v>
+        <v>70</v>
       </c>
       <c r="C49">
-        <v>79.27978515625</v>
+        <v>87.5</v>
       </c>
       <c r="D49">
-        <v>86.66015625</v>
+        <v>88.06005859375</v>
       </c>
       <c r="E49">
-        <v>80.35986328125</v>
+        <v>58.530029296875</v>
       </c>
       <c r="F49">
-        <v>98.52001953125</v>
+        <v>78.81982421875</v>
       </c>
       <c r="G49">
-        <v>98.52001953125</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1710,22 +1710,22 @@
         <v>54</v>
       </c>
       <c r="B50">
-        <v>70</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C50">
-        <v>87.5</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D50">
-        <v>88.06005859375</v>
+        <v>105.759765625</v>
       </c>
       <c r="E50">
-        <v>58.530029296875</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F50">
-        <v>78.81982421875</v>
+        <v>93.02001953125</v>
       </c>
       <c r="G50">
-        <v>78.81982421875</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1733,22 +1733,22 @@
         <v>55</v>
       </c>
       <c r="B51">
-        <v>68.06005859375</v>
+        <v>51.260009765625</v>
       </c>
       <c r="C51">
-        <v>82.18017578125</v>
+        <v>95.5</v>
       </c>
       <c r="D51">
-        <v>105.759765625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="E51">
-        <v>65.14990234375</v>
+        <v>67.75</v>
       </c>
       <c r="F51">
-        <v>93.02001953125</v>
+        <v>75.419921875</v>
       </c>
       <c r="G51">
-        <v>93.02001953125</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1756,22 +1756,22 @@
         <v>56</v>
       </c>
       <c r="B52">
-        <v>51.260009765625</v>
+        <v>72.16015625</v>
       </c>
       <c r="C52">
-        <v>95.5</v>
+        <v>93.47998046875</v>
       </c>
       <c r="D52">
-        <v>61.159912109375</v>
+        <v>85.259765625</v>
       </c>
       <c r="E52">
-        <v>67.75</v>
+        <v>103.0498046875</v>
       </c>
       <c r="F52">
-        <v>75.419921875</v>
+        <v>89.419921875</v>
       </c>
       <c r="G52">
-        <v>75.419921875</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1779,22 +1779,22 @@
         <v>57</v>
       </c>
       <c r="B53">
-        <v>72.16015625</v>
+        <v>55.89990234375</v>
       </c>
       <c r="C53">
-        <v>93.47998046875</v>
+        <v>77.3798828125</v>
       </c>
       <c r="D53">
-        <v>85.259765625</v>
+        <v>43.909912109375</v>
       </c>
       <c r="E53">
-        <v>103.0498046875</v>
+        <v>76.080078125</v>
       </c>
       <c r="F53">
-        <v>89.419921875</v>
+        <v>66.2001953125</v>
       </c>
       <c r="G53">
-        <v>89.419921875</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1802,44 +1802,21 @@
         <v>58</v>
       </c>
       <c r="B54">
-        <v>55.89990234375</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>77.3798828125</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>43.909912109375</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>76.080078125</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>66.2001953125</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>66.2001953125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
         <v>0</v>
       </c>
     </row>
@@ -1850,32 +1827,894 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -1883,13 +2722,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -1897,7 +2736,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1911,7 +2750,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1925,7 +2764,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1939,13 +2778,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -1953,13 +2792,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -1967,7 +2806,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -1981,13 +2820,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -1995,7 +2834,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -2008,283 +2847,1261 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:A55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:1">
+    <row r="1" spans="1:7">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2">
+        <v>68.06005859375</v>
+      </c>
+      <c r="C2">
+        <v>72.7001953125</v>
+      </c>
+      <c r="D2">
+        <v>79.85986328125</v>
+      </c>
+      <c r="E2">
+        <v>58.679931640625</v>
+      </c>
+      <c r="F2">
+        <v>94.6201171875</v>
+      </c>
+      <c r="G2">
+        <v>68.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3">
+        <v>54.10009765625</v>
+      </c>
+      <c r="C3">
+        <v>82</v>
+      </c>
+      <c r="D3">
+        <v>72.9599609375</v>
+      </c>
+      <c r="E3">
+        <v>57.25</v>
+      </c>
+      <c r="F3">
+        <v>79.52001953125</v>
+      </c>
+      <c r="G3">
+        <v>56.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4">
+        <v>38.260009765625</v>
+      </c>
+      <c r="C4">
+        <v>99.5</v>
+      </c>
+      <c r="D4">
+        <v>71.85986328125</v>
+      </c>
+      <c r="E4">
+        <v>83.14990234375</v>
+      </c>
+      <c r="F4">
+        <v>77.47021484375</v>
+      </c>
+      <c r="G4">
+        <v>54.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5">
+        <v>74.06005859375</v>
+      </c>
+      <c r="C5">
+        <v>93.77978515625</v>
+      </c>
+      <c r="D5">
+        <v>94.259765625</v>
+      </c>
+      <c r="E5">
+        <v>74.9501953125</v>
+      </c>
+      <c r="F5">
+        <v>103.919921875</v>
+      </c>
+      <c r="G5">
+        <v>86.42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6">
+        <v>62.260009765625</v>
+      </c>
+      <c r="C6">
+        <v>73.91015625</v>
+      </c>
+      <c r="D6">
+        <v>85.10009765625</v>
+      </c>
+      <c r="E6">
+        <v>82.4501953125</v>
+      </c>
+      <c r="F6">
+        <v>85.31982421875</v>
+      </c>
+      <c r="G6">
+        <v>73.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7">
+        <v>71.7099609375</v>
+      </c>
+      <c r="C7">
+        <v>57</v>
+      </c>
+      <c r="D7">
+        <v>80.2001953125</v>
+      </c>
+      <c r="E7">
+        <v>62</v>
+      </c>
+      <c r="F7">
+        <v>88.259765625</v>
+      </c>
+      <c r="G7">
+        <v>67.81999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8">
+        <v>61.56005859375</v>
+      </c>
+      <c r="C8">
+        <v>82.18017578125</v>
+      </c>
+      <c r="D8">
+        <v>105.759765625</v>
+      </c>
+      <c r="E8">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F8">
+        <v>93.02001953125</v>
+      </c>
+      <c r="G8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9">
+        <v>73.759765625</v>
+      </c>
+      <c r="C9">
+        <v>81.39990234375</v>
+      </c>
+      <c r="D9">
+        <v>81.35986328125</v>
+      </c>
+      <c r="E9">
+        <v>65.0498046875</v>
+      </c>
+      <c r="F9">
+        <v>103.1201171875</v>
+      </c>
+      <c r="G9">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10">
+        <v>72.85986328125</v>
+      </c>
+      <c r="C10">
+        <v>65.14990234375</v>
+      </c>
+      <c r="D10">
+        <v>80.2998046875</v>
+      </c>
+      <c r="E10">
+        <v>77.0498046875</v>
+      </c>
+      <c r="F10">
+        <v>82.6201171875</v>
+      </c>
+      <c r="G10">
+        <v>66.61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11">
+        <v>60.199951171875</v>
+      </c>
+      <c r="C11">
+        <v>92.330078125</v>
+      </c>
+      <c r="D11">
+        <v>80.56005859375</v>
+      </c>
+      <c r="E11">
+        <v>66.64990234375</v>
+      </c>
+      <c r="F11">
+        <v>69.10986328125</v>
+      </c>
+      <c r="G11">
+        <v>67.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12">
+        <v>72.7001953125</v>
+      </c>
+      <c r="C12">
+        <v>64.580078125</v>
+      </c>
+      <c r="D12">
+        <v>98.64990234375</v>
+      </c>
+      <c r="E12">
+        <v>85.47998046875</v>
+      </c>
+      <c r="F12">
+        <v>84.60986328125</v>
+      </c>
+      <c r="G12">
+        <v>72.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
+      <c r="B13">
+        <v>53.659912109375</v>
+      </c>
+      <c r="C13">
+        <v>81.47998046875</v>
+      </c>
+      <c r="D13">
+        <v>79.259765625</v>
+      </c>
+      <c r="E13">
+        <v>86.43017578125</v>
+      </c>
+      <c r="F13">
+        <v>86.419921875</v>
+      </c>
+      <c r="G13">
+        <v>47.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
+      <c r="B14">
+        <v>56.9599609375</v>
+      </c>
+      <c r="C14">
+        <v>96.0498046875</v>
+      </c>
+      <c r="D14">
+        <v>71.56005859375</v>
+      </c>
+      <c r="E14">
+        <v>71.18017578125</v>
+      </c>
+      <c r="F14">
+        <v>89.6201171875</v>
+      </c>
+      <c r="G14">
+        <v>58.29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="B15">
+        <v>37.820068359375</v>
+      </c>
+      <c r="C15">
+        <v>64.02978515625</v>
+      </c>
+      <c r="D15">
+        <v>78.990234375</v>
+      </c>
+      <c r="E15">
+        <v>36.580078125</v>
+      </c>
+      <c r="F15">
+        <v>61.300048828125</v>
+      </c>
+      <c r="G15">
+        <v>68.48999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16">
+        <v>56.260009765625</v>
+      </c>
+      <c r="C16">
+        <v>74.89990234375</v>
+      </c>
+      <c r="D16">
+        <v>87.33984375</v>
+      </c>
+      <c r="E16">
+        <v>69.64990234375</v>
+      </c>
+      <c r="F16">
+        <v>88.919921875</v>
+      </c>
+      <c r="G16">
+        <v>83.42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17">
+        <v>63.89990234375</v>
+      </c>
+      <c r="C17">
+        <v>92.77978515625</v>
+      </c>
+      <c r="D17">
+        <v>78.39990234375</v>
+      </c>
+      <c r="E17">
+        <v>87.64990234375</v>
+      </c>
+      <c r="F17">
+        <v>89.02001953125</v>
+      </c>
+      <c r="G17">
+        <v>62.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18">
+        <v>44.06005859375</v>
+      </c>
+      <c r="C18">
+        <v>85.7001953125</v>
+      </c>
+      <c r="D18">
+        <v>65.259765625</v>
+      </c>
+      <c r="E18">
+        <v>74.25</v>
+      </c>
+      <c r="F18">
+        <v>43.39990234375</v>
+      </c>
+      <c r="G18">
+        <v>58.69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19">
+        <v>54.159912109375</v>
+      </c>
+      <c r="C19">
+        <v>86.7001953125</v>
+      </c>
+      <c r="D19">
+        <v>75.56005859375</v>
+      </c>
+      <c r="E19">
+        <v>82.0498046875</v>
+      </c>
+      <c r="F19">
+        <v>77.919921875</v>
+      </c>
+      <c r="G19">
+        <v>73.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20">
+        <v>40.60009765625</v>
+      </c>
+      <c r="C20">
+        <v>67.8701171875</v>
+      </c>
+      <c r="D20">
+        <v>73.64990234375</v>
+      </c>
+      <c r="E20">
+        <v>74.02978515625</v>
+      </c>
+      <c r="F20">
+        <v>81.6201171875</v>
+      </c>
+      <c r="G20">
+        <v>41.55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21">
+        <v>57.449951171875</v>
+      </c>
+      <c r="C21">
+        <v>83.2001953125</v>
+      </c>
+      <c r="D21">
+        <v>70.7998046875</v>
+      </c>
+      <c r="E21">
+        <v>77.259765625</v>
+      </c>
+      <c r="F21">
+        <v>69.3701171875</v>
+      </c>
+      <c r="G21">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22">
+        <v>57.60009765625</v>
+      </c>
+      <c r="C22">
+        <v>84.5</v>
+      </c>
+      <c r="D22">
+        <v>78.85986328125</v>
+      </c>
+      <c r="E22">
+        <v>85.97998046875</v>
+      </c>
+      <c r="F22">
+        <v>87.22021484375</v>
+      </c>
+      <c r="G22">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23">
+        <v>54.60009765625</v>
+      </c>
+      <c r="C23">
+        <v>85.580078125</v>
+      </c>
+      <c r="D23">
+        <v>67.759765625</v>
+      </c>
+      <c r="E23">
+        <v>52.25</v>
+      </c>
+      <c r="F23">
+        <v>82.919921875</v>
+      </c>
+      <c r="G23">
+        <v>54.21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24">
+        <v>47.860107421875</v>
+      </c>
+      <c r="C24">
+        <v>72.18017578125</v>
+      </c>
+      <c r="D24">
+        <v>97.39990234375</v>
+      </c>
+      <c r="E24">
+        <v>81.64990234375</v>
+      </c>
+      <c r="F24">
+        <v>84.81982421875</v>
+      </c>
+      <c r="G24">
+        <v>62.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25">
+        <v>47.860107421875</v>
+      </c>
+      <c r="C25">
+        <v>81.8798828125</v>
+      </c>
+      <c r="D25">
+        <v>97.759765625</v>
+      </c>
+      <c r="E25">
+        <v>81.64990234375</v>
+      </c>
+      <c r="F25">
+        <v>74.31982421875</v>
+      </c>
+      <c r="G25">
+        <v>64.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26">
+        <v>62.56005859375</v>
+      </c>
+      <c r="C26">
+        <v>96.47998046875</v>
+      </c>
+      <c r="D26">
+        <v>87.4599609375</v>
+      </c>
+      <c r="E26">
+        <v>81.43017578125</v>
+      </c>
+      <c r="F26">
+        <v>85.669921875</v>
+      </c>
+      <c r="G26">
+        <v>58.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="B27">
+        <v>65.009765625</v>
+      </c>
+      <c r="C27">
+        <v>70.14990234375</v>
+      </c>
+      <c r="D27">
+        <v>101.740234375</v>
+      </c>
+      <c r="E27">
+        <v>63.1298828125</v>
+      </c>
+      <c r="F27">
+        <v>77.169921875</v>
+      </c>
+      <c r="G27">
+        <v>73.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="B28">
+        <v>58.510009765625</v>
+      </c>
+      <c r="C28">
+        <v>68.2998046875</v>
+      </c>
+      <c r="D28">
+        <v>38.590087890625</v>
+      </c>
+      <c r="E28">
+        <v>52.550048828125</v>
+      </c>
+      <c r="F28">
+        <v>83.22021484375</v>
+      </c>
+      <c r="G28">
+        <v>80.61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="B29">
+        <v>73.9599609375</v>
+      </c>
+      <c r="C29">
+        <v>92.89990234375</v>
+      </c>
+      <c r="D29">
+        <v>81.759765625</v>
+      </c>
+      <c r="E29">
+        <v>53.25</v>
+      </c>
+      <c r="F29">
+        <v>83.31982421875</v>
+      </c>
+      <c r="G29">
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="B30">
+        <v>51.56005859375</v>
+      </c>
+      <c r="C30">
+        <v>63.39990234375</v>
+      </c>
+      <c r="D30">
+        <v>65.259765625</v>
+      </c>
+      <c r="E30">
+        <v>57.81005859375</v>
+      </c>
+      <c r="F30">
+        <v>43.699951171875</v>
+      </c>
+      <c r="G30">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="B31">
+        <v>49.760009765625</v>
+      </c>
+      <c r="C31">
+        <v>77.47998046875</v>
+      </c>
+      <c r="D31">
+        <v>81.259765625</v>
+      </c>
+      <c r="E31">
+        <v>84.8798828125</v>
+      </c>
+      <c r="F31">
+        <v>77.47021484375</v>
+      </c>
+      <c r="G31">
+        <v>64.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32">
+        <v>84.259765625</v>
+      </c>
+      <c r="C32">
+        <v>82.60986328125</v>
+      </c>
+      <c r="D32">
+        <v>81.25</v>
+      </c>
+      <c r="E32">
+        <v>45.64990234375</v>
+      </c>
+      <c r="F32">
+        <v>72.27001953125</v>
+      </c>
+      <c r="G32">
+        <v>53.46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33">
+        <v>64.56005859375</v>
+      </c>
+      <c r="C33">
+        <v>105.5</v>
+      </c>
+      <c r="D33">
+        <v>81.16015625</v>
+      </c>
+      <c r="E33">
+        <v>66.75</v>
+      </c>
+      <c r="F33">
+        <v>107.56005859375</v>
+      </c>
+      <c r="G33">
+        <v>71.61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34">
+        <v>43.510009765625</v>
+      </c>
+      <c r="C34">
+        <v>60.8798828125</v>
+      </c>
+      <c r="D34">
+        <v>78.259765625</v>
+      </c>
+      <c r="E34">
+        <v>99.72998046875</v>
+      </c>
+      <c r="F34">
+        <v>109.16015625</v>
+      </c>
+      <c r="G34">
+        <v>55.59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35">
+        <v>57.4599609375</v>
+      </c>
+      <c r="C35">
+        <v>88.18017578125</v>
+      </c>
+      <c r="D35">
+        <v>77.259765625</v>
+      </c>
+      <c r="E35">
+        <v>52.97998046875</v>
+      </c>
+      <c r="F35">
+        <v>92.52001953125</v>
+      </c>
+      <c r="G35">
+        <v>53.51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36">
+        <v>64.56005859375</v>
+      </c>
+      <c r="C36">
+        <v>86.60009765625</v>
+      </c>
+      <c r="D36">
+        <v>70.35986328125</v>
+      </c>
+      <c r="E36">
+        <v>34.89990234375</v>
+      </c>
+      <c r="F36">
+        <v>88.6201171875</v>
+      </c>
+      <c r="G36">
+        <v>58.89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37">
+        <v>59.25</v>
+      </c>
+      <c r="C37">
+        <v>73.77978515625</v>
+      </c>
+      <c r="D37">
+        <v>93.759765625</v>
+      </c>
+      <c r="E37">
+        <v>51.929931640625</v>
+      </c>
+      <c r="F37">
+        <v>74.77001953125</v>
+      </c>
+      <c r="G37">
+        <v>66.51000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38">
+        <v>58.25</v>
+      </c>
+      <c r="C38">
+        <v>63.780029296875</v>
+      </c>
+      <c r="D38">
+        <v>68.43994140625</v>
+      </c>
+      <c r="E38">
+        <v>66.27978515625</v>
+      </c>
+      <c r="F38">
+        <v>75.56982421875</v>
+      </c>
+      <c r="G38">
+        <v>68.98999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39">
+        <v>84.85986328125</v>
+      </c>
+      <c r="C39">
+        <v>79.4501953125</v>
+      </c>
+      <c r="D39">
+        <v>78.93994140625</v>
+      </c>
+      <c r="E39">
+        <v>47.72998046875</v>
+      </c>
+      <c r="F39">
+        <v>70.60009765625</v>
+      </c>
+      <c r="G39">
+        <v>44.51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40">
+        <v>60.159912109375</v>
+      </c>
+      <c r="C40">
+        <v>64.580078125</v>
+      </c>
+      <c r="D40">
+        <v>88.759765625</v>
+      </c>
+      <c r="E40">
+        <v>109.75</v>
+      </c>
+      <c r="F40">
+        <v>81.47021484375</v>
+      </c>
+      <c r="G40">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41">
+        <v>49</v>
+      </c>
+      <c r="C41">
+        <v>36.429931640625</v>
+      </c>
+      <c r="D41">
+        <v>54.35009765625</v>
+      </c>
+      <c r="E41">
+        <v>29.8499755859375</v>
+      </c>
+      <c r="F41">
+        <v>83.41015625</v>
+      </c>
+      <c r="G41">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42">
+        <v>61.659912109375</v>
+      </c>
+      <c r="C42">
+        <v>69.5</v>
+      </c>
+      <c r="D42">
+        <v>83.64990234375</v>
+      </c>
+      <c r="E42">
+        <v>51.72998046875</v>
+      </c>
+      <c r="F42">
+        <v>82.1298828125</v>
+      </c>
+      <c r="G42">
+        <v>76.69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43">
+        <v>42.9599609375</v>
+      </c>
+      <c r="C43">
+        <v>91.47998046875</v>
+      </c>
+      <c r="D43">
+        <v>99.35986328125</v>
+      </c>
+      <c r="E43">
+        <v>74.5498046875</v>
+      </c>
+      <c r="F43">
+        <v>96.1201171875</v>
+      </c>
+      <c r="G43">
+        <v>65.70999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44">
+        <v>54.10009765625</v>
+      </c>
+      <c r="C44">
+        <v>71.5</v>
+      </c>
+      <c r="D44">
+        <v>67.39990234375</v>
+      </c>
+      <c r="E44">
+        <v>48.75</v>
+      </c>
+      <c r="F44">
+        <v>73.81005859375</v>
+      </c>
+      <c r="G44">
+        <v>80.51000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45">
+        <v>61.9599609375</v>
+      </c>
+      <c r="C45">
+        <v>84.47998046875</v>
+      </c>
+      <c r="D45">
+        <v>87.39990234375</v>
+      </c>
+      <c r="E45">
+        <v>53.14990234375</v>
+      </c>
+      <c r="F45">
+        <v>87.52001953125</v>
+      </c>
+      <c r="G45">
+        <v>69.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46">
+        <v>64.2001953125</v>
+      </c>
+      <c r="C46">
+        <v>95.3798828125</v>
+      </c>
+      <c r="D46">
+        <v>56.9599609375</v>
+      </c>
+      <c r="E46">
+        <v>64.0498046875</v>
+      </c>
+      <c r="F46">
+        <v>67.669921875</v>
+      </c>
+      <c r="G46">
+        <v>59.93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="B47">
+        <v>66.85986328125</v>
+      </c>
+      <c r="C47">
+        <v>92.7001953125</v>
+      </c>
+      <c r="D47">
+        <v>72.740234375</v>
+      </c>
+      <c r="E47">
+        <v>50.590087890625</v>
+      </c>
+      <c r="F47">
+        <v>81.169921875</v>
+      </c>
+      <c r="G47">
+        <v>62.92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48">
+        <v>58.9599609375</v>
+      </c>
+      <c r="C48">
+        <v>79.27978515625</v>
+      </c>
+      <c r="D48">
+        <v>86.66015625</v>
+      </c>
+      <c r="E48">
+        <v>80.35986328125</v>
+      </c>
+      <c r="F48">
+        <v>98.52001953125</v>
+      </c>
+      <c r="G48">
+        <v>77.41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49">
+        <v>70</v>
+      </c>
+      <c r="C49">
+        <v>87.5</v>
+      </c>
+      <c r="D49">
+        <v>88.06005859375</v>
+      </c>
+      <c r="E49">
+        <v>58.530029296875</v>
+      </c>
+      <c r="F49">
+        <v>78.81982421875</v>
+      </c>
+      <c r="G49">
+        <v>74.91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50">
+        <v>68.06005859375</v>
+      </c>
+      <c r="C50">
+        <v>82.18017578125</v>
+      </c>
+      <c r="D50">
+        <v>105.759765625</v>
+      </c>
+      <c r="E50">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F50">
+        <v>93.02001953125</v>
+      </c>
+      <c r="G50">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51">
+        <v>51.260009765625</v>
+      </c>
+      <c r="C51">
+        <v>95.5</v>
+      </c>
+      <c r="D51">
+        <v>61.159912109375</v>
+      </c>
+      <c r="E51">
+        <v>67.75</v>
+      </c>
+      <c r="F51">
+        <v>75.419921875</v>
+      </c>
+      <c r="G51">
+        <v>54.21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52">
+        <v>72.16015625</v>
+      </c>
+      <c r="C52">
+        <v>93.47998046875</v>
+      </c>
+      <c r="D52">
+        <v>85.259765625</v>
+      </c>
+      <c r="E52">
+        <v>103.0498046875</v>
+      </c>
+      <c r="F52">
+        <v>89.419921875</v>
+      </c>
+      <c r="G52">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53">
+        <v>55.89990234375</v>
+      </c>
+      <c r="C53">
+        <v>77.3798828125</v>
+      </c>
+      <c r="D53">
+        <v>43.909912109375</v>
+      </c>
+      <c r="E53">
+        <v>76.080078125</v>
+      </c>
+      <c r="F53">
+        <v>66.2001953125</v>
+      </c>
+      <c r="G53">
+        <v>57.78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>59</v>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2294,7 +4111,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2304,426 +4121,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>527.3897265625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>502.66962890625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>497.169921875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>497.1402734375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>490.669921875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>481.18978515625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>478.13001953125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>474.55951171875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>474.189453125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>472.21009765625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>470.1797265625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>462.150283203125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>461.119970703125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>460.489580078125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>457.819912109375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>456.26015625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>450.21970703125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>449.609892578125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>447.829482421875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>447.129794921875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>445.919912109375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>444.5894921875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>443.6601171875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>443.629765625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>442.720166015625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>439.999453125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>436.039853515625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>434.969853515625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>434.639755859375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>426.989921875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>426.980302734375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>425.359677734375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>424.859990234375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>421.90990234375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>419.999501953125</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>419.49955078125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>410.279833984375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>408.189765625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>406.090078125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>405.29984375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>403.9300390625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>401.940078125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>401.309580078125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>397.31986328125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>396.07005859375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>381.780166015625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>379.32001953125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>377.249970703125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>371.359921875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>347.21021484375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>340.329736328125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
+        <v>301.2401611328125</v>
       </c>
     </row>
   </sheetData>
@@ -2733,436 +4542,272 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A2:A54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="B1" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B2">
-        <v>84.85986328125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3">
-        <v>84.259765625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>74.06005859375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5">
-        <v>73.9599609375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <v>73.759765625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7">
-        <v>72.85986328125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>72.7001953125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B9">
-        <v>72.16015625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>71.7099609375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12">
-        <v>68.06005859375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13">
-        <v>68.06005859375</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14">
-        <v>66.85986328125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15">
-        <v>65.009765625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16">
-        <v>64.56005859375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17">
-        <v>64.56005859375</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18">
-        <v>64.2001953125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
-        <v>63.89990234375</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20">
-        <v>62.56005859375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21">
-        <v>62.260009765625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22">
-        <v>61.9599609375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23">
-        <v>61.659912109375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24">
-        <v>61.56005859375</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25">
-        <v>60.199951171875</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
-        <v>60.159912109375</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27">
-        <v>59.25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28">
-        <v>58.9599609375</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29">
-        <v>58.510009765625</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30">
-        <v>58.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31">
-        <v>57.60009765625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32">
-        <v>57.4599609375</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33">
-        <v>57.449951171875</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34">
-        <v>56.9599609375</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35">
-        <v>56.260009765625</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="1" t="s">
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B36">
-        <v>55.89990234375</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37">
-        <v>54.60009765625</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38">
-        <v>54.159912109375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39">
-        <v>54.10009765625</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40">
-        <v>54.10009765625</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41">
-        <v>53.659912109375</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42">
-        <v>51.56005859375</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43">
-        <v>51.260009765625</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44">
-        <v>49.760009765625</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46">
-        <v>47.860107421875</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B47">
-        <v>47.860107421875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48">
-        <v>44.260009765625</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49">
-        <v>44.06005859375</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50">
-        <v>43.510009765625</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51">
-        <v>42.9599609375</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B52">
-        <v>40.60009765625</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53">
-        <v>38.260009765625</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54">
-        <v>37.820068359375</v>
       </c>
     </row>
   </sheetData>
@@ -3172,7 +4817,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3182,426 +4827,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>281.78955078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>265.3896484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4">
-        <v>265.3701171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B5">
-        <v>263.08984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B6">
-        <v>262.98974609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B7">
-        <v>261.28955078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B8">
-        <v>258.82958984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B9">
-        <v>254.509765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10">
-        <v>253.41015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B11">
-        <v>253.08984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B12">
-        <v>253.08984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B13">
-        <v>251.22998046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>249.33984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B15">
-        <v>248.7099609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B16">
-        <v>247.169921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B17">
-        <v>246.2998046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B18">
-        <v>244.31005859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B19">
-        <v>243.61962890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B20">
-        <v>241.46044921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B21">
-        <v>239.5400390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B22">
-        <v>238.86962890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B23">
-        <v>238.7900390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B24">
-        <v>235.02001953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25">
-        <v>234.090087890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B26">
-        <v>232.18994140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>231.8896484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B28">
-        <v>231.259765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B29">
-        <v>227.90966796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B30">
-        <v>227.8095703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B31">
-        <v>225.2099609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B32">
-        <v>225.02978515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="B33">
-        <v>224.409912109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B34">
-        <v>222.49951171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B35">
-        <v>219.469482421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B36">
-        <v>218.419921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B37">
-        <v>216.3896484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B38">
-        <v>216.030517578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B39">
-        <v>215.5498046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B40">
-        <v>212.2099609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B41">
-        <v>211.239990234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B42">
-        <v>209.509765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B43">
-        <v>206.1201171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B44">
-        <v>205.58984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B45">
-        <v>204.8798828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B46">
-        <v>199.2001953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B47">
-        <v>198.499755859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>197.369873046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B49">
-        <v>191.85986328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B50">
-        <v>187.64990234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B51">
-        <v>186.4697265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B52">
-        <v>179.60009765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B53">
-        <v>159.43994140625</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54">
-        <v>120.6300048828125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +5248,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3621,18 +5258,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B2">
-        <v>218.3203125</v>
+        <v>84.85986328125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3">
-        <v>215.1201171875</v>
+        <v>84.259765625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3640,111 +5277,111 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>207.83984375</v>
+        <v>74.06005859375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B5">
-        <v>206.240234375</v>
+        <v>73.9599609375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>197.0400390625</v>
+        <v>73.759765625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>192.240234375</v>
+        <v>72.85986328125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>189.240234375</v>
+        <v>72.7001953125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B9">
-        <v>186.0400390625</v>
+        <v>72.16015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>186.0400390625</v>
+        <v>71.7099609375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B11">
-        <v>185.0400390625</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B12">
-        <v>179.240234375</v>
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B13">
-        <v>178.83984375</v>
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B14">
-        <v>178.0400390625</v>
+        <v>66.85986328125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>177.83984375</v>
+        <v>65.009765625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16">
-        <v>177.240234375</v>
+        <v>64.56005859375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B17">
-        <v>176.51953125</v>
+        <v>64.56005859375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3752,295 +5389,287 @@
         <v>50</v>
       </c>
       <c r="B18">
-        <v>175.0400390625</v>
+        <v>64.2001953125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B19">
-        <v>174.4404296875</v>
+        <v>63.89990234375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>172.83984375</v>
+        <v>62.56005859375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>171.33984375</v>
+        <v>62.260009765625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B22">
-        <v>170.6396484375</v>
+        <v>61.9599609375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>169.6396484375</v>
+        <v>61.659912109375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B24">
-        <v>169.2197265625</v>
+        <v>61.56005859375</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B25">
-        <v>166.8203125</v>
+        <v>60.199951171875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B26">
-        <v>166.6396484375</v>
+        <v>60.159912109375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>166.4404296875</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B28">
-        <v>165.83984375</v>
+        <v>58.9599609375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B29">
-        <v>165.240234375</v>
+        <v>58.510009765625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B30">
-        <v>164.259765625</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B31">
-        <v>163.240234375</v>
+        <v>57.60009765625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B32">
-        <v>162.9404296875</v>
+        <v>57.4599609375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B33">
-        <v>162.33984375</v>
+        <v>57.449951171875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B34">
-        <v>159.0400390625</v>
+        <v>56.9599609375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B35">
-        <v>158.6796875</v>
+        <v>56.260009765625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B36">
-        <v>157.6396484375</v>
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B37">
-        <v>155.83984375</v>
+        <v>54.60009765625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B38">
-        <v>154.9404296875</v>
+        <v>54.159912109375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B39">
-        <v>154.9404296875</v>
+        <v>54.10009765625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B40">
-        <v>154.33984375</v>
+        <v>54.10009765625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B41">
-        <v>151.1396484375</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B42">
-        <v>150.83984375</v>
+        <v>51.56005859375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B43">
-        <v>149.5400390625</v>
+        <v>51.260009765625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B44">
-        <v>148.6396484375</v>
+        <v>49.760009765625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
         <v>49</v>
-      </c>
-      <c r="B45">
-        <v>147.6201171875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B46">
-        <v>144.5400390625</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B47">
-        <v>141.2001953125</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B48">
-        <v>138.740234375</v>
+        <v>44.06005859375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B49">
-        <v>138.2197265625</v>
+        <v>43.510009765625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B50">
-        <v>135.33984375</v>
+        <v>42.9599609375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B51">
-        <v>132.400390625</v>
+        <v>40.60009765625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B52">
-        <v>122.60009765625</v>
+        <v>38.260009765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B53">
-        <v>87.39990234375</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B54">
-        <v>86.7998046875</v>
+        <v>37.820068359375</v>
       </c>
     </row>
   </sheetData>
@@ -4050,7 +5679,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4060,426 +5689,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>281.78955078125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>265.3896484375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>265.3701171875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>263.08984375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>262.98974609375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>261.28955078125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>258.82958984375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>254.509765625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>253.41015625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>253.08984375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>253.08984375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>251.22998046875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>249.33984375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>248.7099609375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>247.169921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>246.2998046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>244.31005859375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>243.61962890625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>241.46044921875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>239.5400390625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>238.86962890625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>238.7900390625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>235.02001953125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>234.090087890625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>231.8896484375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>231.259765625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>227.90966796875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>227.8095703125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>225.2099609375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>225.02978515625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>224.409912109375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>222.49951171875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>219.469482421875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>218.419921875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>216.3896484375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>216.030517578125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>215.5498046875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>212.2099609375</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>211.239990234375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>209.509765625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>206.1201171875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>205.58984375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>204.8798828125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>199.2001953125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>198.499755859375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>197.369873046875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>191.85986328125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>187.64990234375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>186.4697265625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>179.60009765625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>159.43994140625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
+        <v>120.6300048828125</v>
       </c>
     </row>
   </sheetData>
@@ -4489,7 +6110,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4499,186 +6120,186 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>190.339921875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>179.17005859375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>176.02001953125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>176.02001953125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>175.93001953125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>172.6201171875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>172.339921875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>164.75015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>163.83021484375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>163.4201171875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>161.8301171875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>158.8198828125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>158.42982421875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>156.71986328125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>156.64001953125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>156.079765625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>154.32005859375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>153.72982421875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>151.83001953125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>151.139921875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>150.189921875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>149.32021484375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>149.2301171875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4686,239 +6307,231 @@
         <v>56</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>148.719921875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>147.9101171875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>147.5101171875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>146.82982421875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>146.03001953125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>144.55982421875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>144.279921875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>144.089921875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>141.59021484375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>141.28001953125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>138.67982421875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>138.12982421875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>137.87021484375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>137.129921875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>136.29986328125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>135.63001953125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>133.809921875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>132.09021484375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>131.61015625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>129.790048828125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>129.629921875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>127.599921875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>125.73001953125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>123.9801953125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>123.1701171875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>121.5701171875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>115.11009765625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>102.299951171875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54">
-        <v>0</v>
+        <v>102.08990234375</v>
       </c>
     </row>
   </sheetData>
@@ -4928,7 +6541,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4946,7 +6559,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4954,7 +6567,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4962,7 +6575,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4970,7 +6583,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4978,7 +6591,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4986,7 +6599,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4994,7 +6607,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5002,7 +6615,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5010,7 +6623,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5018,7 +6631,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5026,7 +6639,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5034,7 +6647,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5042,7 +6655,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5050,7 +6663,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -5058,7 +6671,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -5066,7 +6679,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -5074,7 +6687,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5082,7 +6695,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5090,7 +6703,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5098,7 +6711,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5106,7 +6719,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5114,7 +6727,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5122,7 +6735,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5130,7 +6743,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -5138,7 +6751,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -5154,7 +6767,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -5162,7 +6775,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -5250,7 +6863,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5258,7 +6871,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5346,17 +6959,9 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="B53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54">
         <v>0</v>
       </c>
     </row>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="66">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>Rodada 6</t>
+  </si>
+  <si>
+    <t>Rodada 7</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -578,10 +581,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,10 +603,13 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -621,12 +627,15 @@
         <v>94.6201171875</v>
       </c>
       <c r="G2">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>68.7998046875</v>
+      </c>
+      <c r="H2">
+        <v>68.7998046875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -644,12 +653,15 @@
         <v>79.52001953125</v>
       </c>
       <c r="G3">
-        <v>56.11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>56.110107421875</v>
+      </c>
+      <c r="H3">
+        <v>56.110107421875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -667,12 +679,15 @@
         <v>77.47021484375</v>
       </c>
       <c r="G4">
-        <v>54.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>54.6201171875</v>
+      </c>
+      <c r="H4">
+        <v>54.6201171875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -690,12 +705,15 @@
         <v>103.919921875</v>
       </c>
       <c r="G5">
-        <v>86.42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>86.419921875</v>
+      </c>
+      <c r="H5">
+        <v>86.419921875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -713,12 +731,15 @@
         <v>85.31982421875</v>
       </c>
       <c r="G6">
-        <v>73.11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>73.10986328125</v>
+      </c>
+      <c r="H6">
+        <v>73.10986328125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -736,12 +757,15 @@
         <v>88.259765625</v>
       </c>
       <c r="G7">
-        <v>67.81999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>67.81982421875</v>
+      </c>
+      <c r="H7">
+        <v>67.81982421875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -761,10 +785,13 @@
       <c r="G8">
         <v>83</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -784,10 +811,13 @@
       <c r="G9">
         <v>69.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -805,12 +835,15 @@
         <v>82.6201171875</v>
       </c>
       <c r="G10">
-        <v>66.61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>66.60986328125</v>
+      </c>
+      <c r="H10">
+        <v>66.60986328125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -828,12 +861,15 @@
         <v>69.10986328125</v>
       </c>
       <c r="G11">
-        <v>67.19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>67.18994140625</v>
+      </c>
+      <c r="H11">
+        <v>67.18994140625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -851,12 +887,15 @@
         <v>84.60986328125</v>
       </c>
       <c r="G12">
-        <v>72.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>72.10986328125</v>
+      </c>
+      <c r="H12">
+        <v>72.10986328125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -874,12 +913,15 @@
         <v>86.419921875</v>
       </c>
       <c r="G13">
-        <v>47.39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>47.389892578125</v>
+      </c>
+      <c r="H13">
+        <v>47.389892578125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -897,12 +939,15 @@
         <v>89.6201171875</v>
       </c>
       <c r="G14">
-        <v>58.29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>58.2900390625</v>
+      </c>
+      <c r="H14">
+        <v>58.2900390625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -920,12 +965,15 @@
         <v>61.300048828125</v>
       </c>
       <c r="G15">
-        <v>68.48999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>68.490234375</v>
+      </c>
+      <c r="H15">
+        <v>68.490234375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -943,12 +991,15 @@
         <v>88.919921875</v>
       </c>
       <c r="G16">
-        <v>83.42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>83.419921875</v>
+      </c>
+      <c r="H16">
+        <v>83.419921875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -966,12 +1017,15 @@
         <v>89.02001953125</v>
       </c>
       <c r="G17">
-        <v>62.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>62.81005859375</v>
+      </c>
+      <c r="H17">
+        <v>62.81005859375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -989,12 +1043,15 @@
         <v>43.39990234375</v>
       </c>
       <c r="G18">
-        <v>58.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>58.68994140625</v>
+      </c>
+      <c r="H18">
+        <v>58.68994140625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -1012,12 +1069,15 @@
         <v>77.919921875</v>
       </c>
       <c r="G19">
-        <v>73.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>73.22021484375</v>
+      </c>
+      <c r="H19">
+        <v>73.22021484375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -1035,12 +1095,15 @@
         <v>81.6201171875</v>
       </c>
       <c r="G20">
-        <v>41.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>41.550048828125</v>
+      </c>
+      <c r="H20">
+        <v>41.550048828125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -1058,12 +1121,15 @@
         <v>69.3701171875</v>
       </c>
       <c r="G21">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>52.199951171875</v>
+      </c>
+      <c r="H21">
+        <v>52.199951171875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -1081,12 +1147,15 @@
         <v>87.22021484375</v>
       </c>
       <c r="G22">
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>62.10009765625</v>
+      </c>
+      <c r="H22">
+        <v>62.10009765625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1104,12 +1173,15 @@
         <v>82.919921875</v>
       </c>
       <c r="G23">
-        <v>54.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>54.2099609375</v>
+      </c>
+      <c r="H23">
+        <v>54.2099609375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1127,12 +1199,15 @@
         <v>84.81982421875</v>
       </c>
       <c r="G24">
-        <v>62.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>62.010009765625</v>
+      </c>
+      <c r="H24">
+        <v>62.010009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1150,12 +1225,15 @@
         <v>74.31982421875</v>
       </c>
       <c r="G25">
-        <v>64.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>64.35986328125</v>
+      </c>
+      <c r="H25">
+        <v>64.35986328125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1173,12 +1251,15 @@
         <v>85.669921875</v>
       </c>
       <c r="G26">
-        <v>58.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>58.610107421875</v>
+      </c>
+      <c r="H26">
+        <v>58.610107421875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1196,12 +1277,15 @@
         <v>77.169921875</v>
       </c>
       <c r="G27">
-        <v>73.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>73.02001953125</v>
+      </c>
+      <c r="H27">
+        <v>73.02001953125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1219,12 +1303,15 @@
         <v>83.22021484375</v>
       </c>
       <c r="G28">
-        <v>80.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>80.60986328125</v>
+      </c>
+      <c r="H28">
+        <v>80.60986328125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1242,12 +1329,15 @@
         <v>83.31982421875</v>
       </c>
       <c r="G29">
-        <v>54.81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>54.81005859375</v>
+      </c>
+      <c r="H29">
+        <v>54.81005859375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1265,12 +1355,15 @@
         <v>43.699951171875</v>
       </c>
       <c r="G30">
-        <v>58.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>58.60009765625</v>
+      </c>
+      <c r="H30">
+        <v>58.60009765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1288,12 +1381,15 @@
         <v>77.47021484375</v>
       </c>
       <c r="G31">
-        <v>64.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>64.1201171875</v>
+      </c>
+      <c r="H31">
+        <v>64.1201171875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1311,12 +1407,15 @@
         <v>72.27001953125</v>
       </c>
       <c r="G32">
-        <v>53.46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>53.4599609375</v>
+      </c>
+      <c r="H32">
+        <v>53.4599609375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1334,12 +1433,15 @@
         <v>107.56005859375</v>
       </c>
       <c r="G33">
-        <v>71.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>71.60986328125</v>
+      </c>
+      <c r="H33">
+        <v>71.60986328125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1357,12 +1459,15 @@
         <v>109.16015625</v>
       </c>
       <c r="G34">
-        <v>55.59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>55.590087890625</v>
+      </c>
+      <c r="H34">
+        <v>55.590087890625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -1380,12 +1485,15 @@
         <v>92.52001953125</v>
       </c>
       <c r="G35">
-        <v>53.51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>53.510009765625</v>
+      </c>
+      <c r="H35">
+        <v>53.510009765625</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -1403,12 +1511,15 @@
         <v>88.6201171875</v>
       </c>
       <c r="G36">
-        <v>58.89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>58.889892578125</v>
+      </c>
+      <c r="H36">
+        <v>58.889892578125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -1426,12 +1537,15 @@
         <v>74.77001953125</v>
       </c>
       <c r="G37">
-        <v>66.51000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>66.509765625</v>
+      </c>
+      <c r="H37">
+        <v>66.509765625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -1449,12 +1563,15 @@
         <v>75.56982421875</v>
       </c>
       <c r="G38">
-        <v>68.98999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>68.990234375</v>
+      </c>
+      <c r="H38">
+        <v>68.990234375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -1472,12 +1589,15 @@
         <v>70.60009765625</v>
       </c>
       <c r="G39">
-        <v>44.51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>44.510009765625</v>
+      </c>
+      <c r="H39">
+        <v>44.510009765625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -1495,12 +1615,15 @@
         <v>81.47021484375</v>
       </c>
       <c r="G40">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>56.39990234375</v>
+      </c>
+      <c r="H40">
+        <v>56.39990234375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -1518,12 +1641,15 @@
         <v>83.41015625</v>
       </c>
       <c r="G41">
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>48.199951171875</v>
+      </c>
+      <c r="H41">
+        <v>48.199951171875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -1541,12 +1667,15 @@
         <v>82.1298828125</v>
       </c>
       <c r="G42">
-        <v>76.69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>76.68994140625</v>
+      </c>
+      <c r="H42">
+        <v>76.68994140625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -1564,12 +1693,15 @@
         <v>96.1201171875</v>
       </c>
       <c r="G43">
-        <v>65.70999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>65.7099609375</v>
+      </c>
+      <c r="H43">
+        <v>65.7099609375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -1587,12 +1719,15 @@
         <v>73.81005859375</v>
       </c>
       <c r="G44">
-        <v>80.51000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>80.509765625</v>
+      </c>
+      <c r="H44">
+        <v>80.509765625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -1610,12 +1745,15 @@
         <v>87.52001953125</v>
       </c>
       <c r="G45">
-        <v>69.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>69.1201171875</v>
+      </c>
+      <c r="H45">
+        <v>69.1201171875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -1633,12 +1771,15 @@
         <v>67.669921875</v>
       </c>
       <c r="G46">
-        <v>59.93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>59.929931640625</v>
+      </c>
+      <c r="H46">
+        <v>59.929931640625</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -1656,12 +1797,15 @@
         <v>81.169921875</v>
       </c>
       <c r="G47">
-        <v>62.92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>62.919921875</v>
+      </c>
+      <c r="H47">
+        <v>62.919921875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -1679,12 +1823,15 @@
         <v>98.52001953125</v>
       </c>
       <c r="G48">
-        <v>77.41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>77.41015625</v>
+      </c>
+      <c r="H48">
+        <v>77.41015625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -1702,12 +1849,15 @@
         <v>78.81982421875</v>
       </c>
       <c r="G49">
-        <v>74.91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>74.91015625</v>
+      </c>
+      <c r="H49">
+        <v>74.91015625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -1727,10 +1877,13 @@
       <c r="G50">
         <v>83</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -1748,12 +1901,15 @@
         <v>75.419921875</v>
       </c>
       <c r="G51">
-        <v>54.21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>54.2099609375</v>
+      </c>
+      <c r="H51">
+        <v>54.2099609375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -1771,12 +1927,15 @@
         <v>89.419921875</v>
       </c>
       <c r="G52">
-        <v>59.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>59.300048828125</v>
+      </c>
+      <c r="H52">
+        <v>59.300048828125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -1794,12 +1953,15 @@
         <v>66.2001953125</v>
       </c>
       <c r="G53">
-        <v>57.78</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>57.780029296875</v>
+      </c>
+      <c r="H53">
+        <v>57.780029296875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1817,6 +1979,9 @@
         <v>0</v>
       </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>0</v>
       </c>
     </row>
@@ -1837,7 +2002,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1845,7 +2010,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1853,7 +2018,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1861,7 +2026,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1869,7 +2034,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1877,7 +2042,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1885,7 +2050,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1893,7 +2058,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1901,7 +2066,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1909,7 +2074,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1917,7 +2082,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1925,7 +2090,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1933,7 +2098,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1941,7 +2106,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1949,7 +2114,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1957,7 +2122,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1965,7 +2130,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1973,7 +2138,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1981,7 +2146,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1989,7 +2154,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1997,7 +2162,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2005,7 +2170,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2013,7 +2178,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2021,7 +2186,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2029,7 +2194,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2037,7 +2202,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2045,7 +2210,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2053,7 +2218,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2061,7 +2226,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2069,7 +2234,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2077,7 +2242,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2085,7 +2250,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2093,7 +2258,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2101,7 +2266,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2109,7 +2274,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2117,7 +2282,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2125,7 +2290,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2133,7 +2298,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2141,7 +2306,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2149,7 +2314,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2157,7 +2322,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2165,7 +2330,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2173,7 +2338,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2181,7 +2346,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2189,7 +2354,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2197,7 +2362,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2205,7 +2370,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2213,7 +2378,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2221,7 +2386,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2229,7 +2394,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2237,7 +2402,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2245,7 +2410,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2268,7 +2433,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2276,7 +2441,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2284,7 +2449,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2292,7 +2457,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2300,7 +2465,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2308,7 +2473,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2316,7 +2481,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2324,7 +2489,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2332,7 +2497,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2340,7 +2505,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2348,7 +2513,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2356,7 +2521,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2364,7 +2529,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2372,7 +2537,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2380,7 +2545,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2388,7 +2553,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2396,7 +2561,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2404,7 +2569,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2412,7 +2577,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2420,7 +2585,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2428,7 +2593,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2436,7 +2601,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2444,7 +2609,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2452,7 +2617,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2460,7 +2625,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2468,7 +2633,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2476,7 +2641,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2484,7 +2649,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2492,7 +2657,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2500,7 +2665,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2508,7 +2673,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2516,7 +2681,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2524,7 +2689,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2532,7 +2697,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2540,7 +2705,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2548,7 +2713,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2556,7 +2721,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2564,7 +2729,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2572,7 +2737,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2580,7 +2745,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2588,7 +2753,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2596,7 +2761,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2604,7 +2769,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2612,7 +2777,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2620,7 +2785,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2628,7 +2793,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2636,7 +2801,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2644,7 +2809,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2652,7 +2817,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2660,7 +2825,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2668,7 +2833,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2676,7 +2841,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2694,27 +2859,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -2722,13 +2887,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -2736,13 +2901,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -2750,13 +2915,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -2764,13 +2929,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -2778,13 +2943,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -2792,13 +2957,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -2806,13 +2971,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -2820,13 +2985,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -2834,13 +2999,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
@@ -2862,10 +3027,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2884,10 +3049,13 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -2905,12 +3073,15 @@
         <v>94.6201171875</v>
       </c>
       <c r="G2">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>68.7998046875</v>
+      </c>
+      <c r="H2">
+        <v>68.7998046875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -2928,12 +3099,15 @@
         <v>79.52001953125</v>
       </c>
       <c r="G3">
-        <v>56.11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>56.110107421875</v>
+      </c>
+      <c r="H3">
+        <v>56.110107421875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -2951,12 +3125,15 @@
         <v>77.47021484375</v>
       </c>
       <c r="G4">
-        <v>54.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>54.6201171875</v>
+      </c>
+      <c r="H4">
+        <v>54.6201171875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -2974,12 +3151,15 @@
         <v>103.919921875</v>
       </c>
       <c r="G5">
-        <v>86.42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>86.419921875</v>
+      </c>
+      <c r="H5">
+        <v>86.419921875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -2997,12 +3177,15 @@
         <v>85.31982421875</v>
       </c>
       <c r="G6">
-        <v>73.11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>73.10986328125</v>
+      </c>
+      <c r="H6">
+        <v>73.10986328125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -3020,12 +3203,15 @@
         <v>88.259765625</v>
       </c>
       <c r="G7">
-        <v>67.81999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>67.81982421875</v>
+      </c>
+      <c r="H7">
+        <v>67.81982421875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -3045,10 +3231,13 @@
       <c r="G8">
         <v>83</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -3068,10 +3257,13 @@
       <c r="G9">
         <v>69.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -3089,12 +3281,15 @@
         <v>82.6201171875</v>
       </c>
       <c r="G10">
-        <v>66.61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>66.60986328125</v>
+      </c>
+      <c r="H10">
+        <v>66.60986328125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -3112,12 +3307,15 @@
         <v>69.10986328125</v>
       </c>
       <c r="G11">
-        <v>67.19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>67.18994140625</v>
+      </c>
+      <c r="H11">
+        <v>67.18994140625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -3135,12 +3333,15 @@
         <v>84.60986328125</v>
       </c>
       <c r="G12">
-        <v>72.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>72.10986328125</v>
+      </c>
+      <c r="H12">
+        <v>72.10986328125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -3158,12 +3359,15 @@
         <v>86.419921875</v>
       </c>
       <c r="G13">
-        <v>47.39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>47.389892578125</v>
+      </c>
+      <c r="H13">
+        <v>47.389892578125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -3181,12 +3385,15 @@
         <v>89.6201171875</v>
       </c>
       <c r="G14">
-        <v>58.29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>58.2900390625</v>
+      </c>
+      <c r="H14">
+        <v>58.2900390625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -3204,12 +3411,15 @@
         <v>61.300048828125</v>
       </c>
       <c r="G15">
-        <v>68.48999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>68.490234375</v>
+      </c>
+      <c r="H15">
+        <v>68.490234375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -3227,12 +3437,15 @@
         <v>88.919921875</v>
       </c>
       <c r="G16">
-        <v>83.42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>83.419921875</v>
+      </c>
+      <c r="H16">
+        <v>83.419921875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -3250,12 +3463,15 @@
         <v>89.02001953125</v>
       </c>
       <c r="G17">
-        <v>62.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>62.81005859375</v>
+      </c>
+      <c r="H17">
+        <v>62.81005859375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -3273,12 +3489,15 @@
         <v>43.39990234375</v>
       </c>
       <c r="G18">
-        <v>58.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>58.68994140625</v>
+      </c>
+      <c r="H18">
+        <v>58.68994140625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -3296,12 +3515,15 @@
         <v>77.919921875</v>
       </c>
       <c r="G19">
-        <v>73.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>73.22021484375</v>
+      </c>
+      <c r="H19">
+        <v>73.22021484375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -3319,12 +3541,15 @@
         <v>81.6201171875</v>
       </c>
       <c r="G20">
-        <v>41.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>41.550048828125</v>
+      </c>
+      <c r="H20">
+        <v>41.550048828125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -3342,12 +3567,15 @@
         <v>69.3701171875</v>
       </c>
       <c r="G21">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>52.199951171875</v>
+      </c>
+      <c r="H21">
+        <v>52.199951171875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -3365,12 +3593,15 @@
         <v>87.22021484375</v>
       </c>
       <c r="G22">
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>62.10009765625</v>
+      </c>
+      <c r="H22">
+        <v>62.10009765625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -3388,12 +3619,15 @@
         <v>82.919921875</v>
       </c>
       <c r="G23">
-        <v>54.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>54.2099609375</v>
+      </c>
+      <c r="H23">
+        <v>54.2099609375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -3411,12 +3645,15 @@
         <v>84.81982421875</v>
       </c>
       <c r="G24">
-        <v>62.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>62.010009765625</v>
+      </c>
+      <c r="H24">
+        <v>62.010009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -3434,12 +3671,15 @@
         <v>74.31982421875</v>
       </c>
       <c r="G25">
-        <v>64.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>64.35986328125</v>
+      </c>
+      <c r="H25">
+        <v>64.35986328125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -3457,12 +3697,15 @@
         <v>85.669921875</v>
       </c>
       <c r="G26">
-        <v>58.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>58.610107421875</v>
+      </c>
+      <c r="H26">
+        <v>58.610107421875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -3480,12 +3723,15 @@
         <v>77.169921875</v>
       </c>
       <c r="G27">
-        <v>73.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>73.02001953125</v>
+      </c>
+      <c r="H27">
+        <v>73.02001953125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -3503,12 +3749,15 @@
         <v>83.22021484375</v>
       </c>
       <c r="G28">
-        <v>80.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>80.60986328125</v>
+      </c>
+      <c r="H28">
+        <v>80.60986328125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -3526,12 +3775,15 @@
         <v>83.31982421875</v>
       </c>
       <c r="G29">
-        <v>54.81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>54.81005859375</v>
+      </c>
+      <c r="H29">
+        <v>54.81005859375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -3549,12 +3801,15 @@
         <v>43.699951171875</v>
       </c>
       <c r="G30">
-        <v>58.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>58.60009765625</v>
+      </c>
+      <c r="H30">
+        <v>58.60009765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -3572,12 +3827,15 @@
         <v>77.47021484375</v>
       </c>
       <c r="G31">
-        <v>64.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>64.1201171875</v>
+      </c>
+      <c r="H31">
+        <v>64.1201171875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -3595,12 +3853,15 @@
         <v>72.27001953125</v>
       </c>
       <c r="G32">
-        <v>53.46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>53.4599609375</v>
+      </c>
+      <c r="H32">
+        <v>53.4599609375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -3618,12 +3879,15 @@
         <v>107.56005859375</v>
       </c>
       <c r="G33">
-        <v>71.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>71.60986328125</v>
+      </c>
+      <c r="H33">
+        <v>71.60986328125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -3641,12 +3905,15 @@
         <v>109.16015625</v>
       </c>
       <c r="G34">
-        <v>55.59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>55.590087890625</v>
+      </c>
+      <c r="H34">
+        <v>55.590087890625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -3664,12 +3931,15 @@
         <v>92.52001953125</v>
       </c>
       <c r="G35">
-        <v>53.51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>53.510009765625</v>
+      </c>
+      <c r="H35">
+        <v>53.510009765625</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -3687,12 +3957,15 @@
         <v>88.6201171875</v>
       </c>
       <c r="G36">
-        <v>58.89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>58.889892578125</v>
+      </c>
+      <c r="H36">
+        <v>58.889892578125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -3710,12 +3983,15 @@
         <v>74.77001953125</v>
       </c>
       <c r="G37">
-        <v>66.51000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>66.509765625</v>
+      </c>
+      <c r="H37">
+        <v>66.509765625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -3733,12 +4009,15 @@
         <v>75.56982421875</v>
       </c>
       <c r="G38">
-        <v>68.98999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>68.990234375</v>
+      </c>
+      <c r="H38">
+        <v>68.990234375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -3756,12 +4035,15 @@
         <v>70.60009765625</v>
       </c>
       <c r="G39">
-        <v>44.51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>44.510009765625</v>
+      </c>
+      <c r="H39">
+        <v>44.510009765625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -3779,12 +4061,15 @@
         <v>81.47021484375</v>
       </c>
       <c r="G40">
-        <v>56.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>56.39990234375</v>
+      </c>
+      <c r="H40">
+        <v>56.39990234375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -3802,12 +4087,15 @@
         <v>83.41015625</v>
       </c>
       <c r="G41">
-        <v>48.2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>48.199951171875</v>
+      </c>
+      <c r="H41">
+        <v>48.199951171875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -3825,12 +4113,15 @@
         <v>82.1298828125</v>
       </c>
       <c r="G42">
-        <v>76.69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>76.68994140625</v>
+      </c>
+      <c r="H42">
+        <v>76.68994140625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -3848,12 +4139,15 @@
         <v>96.1201171875</v>
       </c>
       <c r="G43">
-        <v>65.70999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>65.7099609375</v>
+      </c>
+      <c r="H43">
+        <v>65.7099609375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -3871,12 +4165,15 @@
         <v>73.81005859375</v>
       </c>
       <c r="G44">
-        <v>80.51000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>80.509765625</v>
+      </c>
+      <c r="H44">
+        <v>80.509765625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -3894,12 +4191,15 @@
         <v>87.52001953125</v>
       </c>
       <c r="G45">
-        <v>69.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>69.1201171875</v>
+      </c>
+      <c r="H45">
+        <v>69.1201171875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -3917,12 +4217,15 @@
         <v>67.669921875</v>
       </c>
       <c r="G46">
-        <v>59.93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>59.929931640625</v>
+      </c>
+      <c r="H46">
+        <v>59.929931640625</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -3940,12 +4243,15 @@
         <v>81.169921875</v>
       </c>
       <c r="G47">
-        <v>62.92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>62.919921875</v>
+      </c>
+      <c r="H47">
+        <v>62.919921875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -3963,12 +4269,15 @@
         <v>98.52001953125</v>
       </c>
       <c r="G48">
-        <v>77.41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>77.41015625</v>
+      </c>
+      <c r="H48">
+        <v>77.41015625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -3986,12 +4295,15 @@
         <v>78.81982421875</v>
       </c>
       <c r="G49">
-        <v>74.91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>74.91015625</v>
+      </c>
+      <c r="H49">
+        <v>74.91015625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -4011,10 +4323,13 @@
       <c r="G50">
         <v>83</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -4032,12 +4347,15 @@
         <v>75.419921875</v>
       </c>
       <c r="G51">
-        <v>54.21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>54.2099609375</v>
+      </c>
+      <c r="H51">
+        <v>54.2099609375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -4055,12 +4373,15 @@
         <v>89.419921875</v>
       </c>
       <c r="G52">
-        <v>59.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>59.300048828125</v>
+      </c>
+      <c r="H52">
+        <v>59.300048828125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -4078,12 +4399,15 @@
         <v>66.2001953125</v>
       </c>
       <c r="G53">
-        <v>57.78</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>57.780029296875</v>
+      </c>
+      <c r="H53">
+        <v>57.780029296875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4101,6 +4425,9 @@
         <v>0</v>
       </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
         <v>0</v>
       </c>
     </row>
@@ -4121,58 +4448,58 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>527.3897265625</v>
+        <v>613.8095703125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3">
-        <v>502.66962890625</v>
+        <v>580.169921875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>497.169921875</v>
+        <v>573.669921875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
-        <v>497.1402734375</v>
+        <v>568.75</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="B6">
-        <v>490.669921875</v>
+        <v>561.9697265625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7">
-        <v>481.18978515625</v>
+        <v>558.60009765625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>478.13001953125</v>
+        <v>550.23974609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4180,359 +4507,359 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>474.55951171875</v>
+        <v>543.909423828125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>474.189453125</v>
+        <v>543.689453125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>472.21009765625</v>
+        <v>537.36962890625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>470.1797265625</v>
+        <v>535.8896484375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>462.150283203125</v>
+        <v>535.260009765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B14">
-        <v>461.119970703125</v>
+        <v>532.730224609375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>460.489580078125</v>
+        <v>530.8203125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>457.819912109375</v>
+        <v>523.23974609375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>456.26015625</v>
+        <v>522.830322265625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>450.21970703125</v>
+        <v>518.3603515625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B19">
-        <v>449.609892578125</v>
+        <v>517.519775390625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B20">
-        <v>447.829482421875</v>
+        <v>512.75</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>447.129794921875</v>
+        <v>512.189208984375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B22">
-        <v>445.919912109375</v>
+        <v>511.519775390625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23">
-        <v>444.5894921875</v>
+        <v>511.19921875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>443.6601171875</v>
+        <v>507.929931640625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B25">
-        <v>443.629765625</v>
+        <v>503.229736328125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B26">
-        <v>442.720166015625</v>
+        <v>502.719970703125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B27">
-        <v>439.999453125</v>
+        <v>502.049560546875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B28">
-        <v>436.039853515625</v>
+        <v>501.9501953125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29">
-        <v>434.969853515625</v>
+        <v>499.090087890625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B30">
-        <v>434.639755859375</v>
+        <v>494.8095703125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31">
-        <v>426.989921875</v>
+        <v>494.8095703125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32">
-        <v>426.980302734375</v>
+        <v>489.900146484375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B33">
-        <v>425.359677734375</v>
+        <v>486.509033203125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B34">
-        <v>424.859990234375</v>
+        <v>482.029541015625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B35">
-        <v>421.90990234375</v>
+        <v>479.480224609375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B36">
-        <v>419.999501953125</v>
+        <v>476.57958984375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>419.49955078125</v>
+        <v>475.419921875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>410.279833984375</v>
+        <v>472.95947265625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B39">
-        <v>408.189765625</v>
+        <v>470.300048828125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B40">
-        <v>406.090078125</v>
+        <v>468.11962890625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B41">
-        <v>405.29984375</v>
+        <v>462.81982421875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B42">
-        <v>403.9300390625</v>
+        <v>462.479736328125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B43">
-        <v>401.940078125</v>
+        <v>462.389892578125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B44">
-        <v>401.309580078125</v>
+        <v>459.509765625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B45">
-        <v>397.31986328125</v>
+        <v>458.05029296875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B46">
-        <v>396.07005859375</v>
+        <v>451.52978515625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B47">
-        <v>381.780166015625</v>
+        <v>450.60009765625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B48">
-        <v>379.32001953125</v>
+        <v>435.030029296875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B49">
-        <v>377.249970703125</v>
+        <v>430.0498046875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B50">
-        <v>371.359921875</v>
+        <v>420.8701171875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51">
-        <v>347.21021484375</v>
+        <v>415.70068359375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52">
-        <v>340.329736328125</v>
+        <v>398.929931640625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B53">
-        <v>301.2401611328125</v>
+        <v>349.4400634765625</v>
       </c>
     </row>
   </sheetData>
@@ -4547,267 +4874,267 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4827,7 +5154,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4835,7 +5162,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4843,7 +5170,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4851,7 +5178,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4859,7 +5186,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4867,7 +5194,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4875,7 +5202,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4883,7 +5210,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4891,7 +5218,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4899,7 +5226,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4907,7 +5234,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -4915,7 +5242,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -4923,7 +5250,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -4931,7 +5258,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -4939,7 +5266,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -4947,7 +5274,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -4955,7 +5282,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -4963,7 +5290,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4971,7 +5298,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -4979,7 +5306,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -4987,7 +5314,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4995,7 +5322,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5003,7 +5330,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5011,7 +5338,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5019,7 +5346,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -5027,7 +5354,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -5035,7 +5362,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -5043,7 +5370,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -5051,7 +5378,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -5059,7 +5386,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -5067,7 +5394,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5075,7 +5402,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -5083,7 +5410,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -5091,7 +5418,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5099,7 +5426,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -5107,7 +5434,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5115,7 +5442,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5123,7 +5450,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -5131,7 +5458,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5139,7 +5466,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5147,7 +5474,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5155,7 +5482,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5163,7 +5490,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -5171,7 +5498,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -5179,7 +5506,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -5187,7 +5514,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5195,7 +5522,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -5203,7 +5530,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -5211,7 +5538,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -5219,7 +5546,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -5227,7 +5554,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5235,7 +5562,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -5258,7 +5585,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -5266,7 +5593,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -5274,7 +5601,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -5282,7 +5609,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -5290,7 +5617,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -5298,7 +5625,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -5306,7 +5633,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -5314,7 +5641,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -5322,7 +5649,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -5330,7 +5657,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -5338,7 +5665,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -5346,7 +5673,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -5354,7 +5681,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -5362,7 +5689,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -5370,7 +5697,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -5378,7 +5705,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -5386,7 +5713,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -5394,7 +5721,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -5402,7 +5729,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -5410,7 +5737,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -5418,7 +5745,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -5426,7 +5753,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -5434,7 +5761,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -5442,7 +5769,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -5450,7 +5777,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -5458,7 +5785,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -5466,7 +5793,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -5474,7 +5801,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -5482,7 +5809,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -5490,7 +5817,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -5498,7 +5825,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -5506,7 +5833,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -5514,7 +5841,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -5522,7 +5849,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -5530,7 +5857,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -5538,7 +5865,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -5546,7 +5873,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -5554,7 +5881,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -5562,7 +5889,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -5570,7 +5897,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -5578,7 +5905,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -5586,7 +5913,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -5594,7 +5921,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -5602,7 +5929,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -5610,7 +5937,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -5618,7 +5945,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -5626,7 +5953,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48">
         <v>44.06005859375</v>
@@ -5634,7 +5961,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49">
         <v>43.510009765625</v>
@@ -5642,7 +5969,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50">
         <v>42.9599609375</v>
@@ -5650,7 +5977,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>40.60009765625</v>
@@ -5658,7 +5985,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B52">
         <v>38.260009765625</v>
@@ -5666,7 +5993,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53">
         <v>37.820068359375</v>
@@ -5689,7 +6016,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -5697,7 +6024,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -5705,7 +6032,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -5713,7 +6040,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -5721,7 +6048,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -5729,7 +6056,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -5737,7 +6064,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -5745,7 +6072,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -5753,7 +6080,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -5761,7 +6088,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -5769,7 +6096,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -5777,7 +6104,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -5785,7 +6112,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -5793,7 +6120,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -5801,7 +6128,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -5809,7 +6136,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -5817,7 +6144,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -5825,7 +6152,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -5833,7 +6160,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -5841,7 +6168,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -5849,7 +6176,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -5857,7 +6184,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -5865,7 +6192,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -5873,7 +6200,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -5881,7 +6208,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26">
         <v>231.8896484375</v>
@@ -5889,7 +6216,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>231.259765625</v>
@@ -5897,7 +6224,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>227.90966796875</v>
@@ -5905,7 +6232,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>227.8095703125</v>
@@ -5913,7 +6240,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30">
         <v>225.2099609375</v>
@@ -5921,7 +6248,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31">
         <v>225.02978515625</v>
@@ -5929,7 +6256,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B32">
         <v>224.409912109375</v>
@@ -5937,7 +6264,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33">
         <v>222.49951171875</v>
@@ -5945,7 +6272,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34">
         <v>219.469482421875</v>
@@ -5953,7 +6280,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35">
         <v>218.419921875</v>
@@ -5961,7 +6288,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36">
         <v>216.3896484375</v>
@@ -5969,7 +6296,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37">
         <v>216.030517578125</v>
@@ -5977,7 +6304,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B38">
         <v>215.5498046875</v>
@@ -5985,7 +6312,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B39">
         <v>212.2099609375</v>
@@ -5993,7 +6320,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>211.239990234375</v>
@@ -6001,7 +6328,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41">
         <v>209.509765625</v>
@@ -6009,7 +6336,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>206.1201171875</v>
@@ -6017,7 +6344,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B43">
         <v>205.58984375</v>
@@ -6025,7 +6352,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>204.8798828125</v>
@@ -6033,7 +6360,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B45">
         <v>199.2001953125</v>
@@ -6041,7 +6368,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46">
         <v>198.499755859375</v>
@@ -6049,7 +6376,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>197.369873046875</v>
@@ -6057,7 +6384,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48">
         <v>191.85986328125</v>
@@ -6065,7 +6392,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49">
         <v>187.64990234375</v>
@@ -6073,7 +6400,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B50">
         <v>186.4697265625</v>
@@ -6081,7 +6408,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51">
         <v>179.60009765625</v>
@@ -6089,7 +6416,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>159.43994140625</v>
@@ -6097,7 +6424,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
@@ -6120,386 +6447,386 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>190.339921875</v>
+        <v>276.759765625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B3">
-        <v>179.17005859375</v>
+        <v>259.02001953125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>176.02001953125</v>
+        <v>259.02001953125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>176.02001953125</v>
+        <v>255.759765625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6">
-        <v>175.93001953125</v>
+        <v>253.34033203125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B7">
-        <v>172.6201171875</v>
+        <v>250.77978515625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B8">
-        <v>172.339921875</v>
+        <v>244.43994140625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>164.75015625</v>
+        <v>242.1201171875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B10">
-        <v>163.83021484375</v>
+        <v>235.509765625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B11">
-        <v>163.4201171875</v>
+        <v>234.82958984375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B12">
-        <v>161.8301171875</v>
+        <v>232.2197265625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>158.8198828125</v>
+        <v>231.53955078125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>158.42982421875</v>
+        <v>228.82958984375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B15">
-        <v>156.71986328125</v>
+        <v>228.64013671875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>156.64001953125</v>
+        <v>227.5400390625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B17">
-        <v>156.079765625</v>
+        <v>225.76025390625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>154.32005859375</v>
+        <v>224.3603515625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B19">
-        <v>153.72982421875</v>
+        <v>223.8994140625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B20">
-        <v>151.83001953125</v>
+        <v>223.2099609375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B21">
-        <v>151.139921875</v>
+        <v>220.34033203125</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B22">
-        <v>150.189921875</v>
+        <v>215.83984375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>149.32021484375</v>
+        <v>214.64013671875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B24">
-        <v>149.2301171875</v>
+        <v>213.55029296875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="B25">
-        <v>148.719921875</v>
+        <v>211.42041015625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>147.9101171875</v>
+        <v>208.83984375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B27">
-        <v>147.5101171875</v>
+        <v>208.02001953125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>146.82982421875</v>
+        <v>207.78955078125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B29">
-        <v>146.03001953125</v>
+        <v>207.009765625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>144.55982421875</v>
+        <v>206.39990234375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B31">
-        <v>144.279921875</v>
+        <v>206.2001953125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B32">
-        <v>144.089921875</v>
+        <v>205.71044921875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B33">
-        <v>141.59021484375</v>
+        <v>203.48974609375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B34">
-        <v>141.28001953125</v>
+        <v>203.03955078125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B35">
-        <v>138.67982421875</v>
+        <v>202.89013671875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B36">
-        <v>138.12982421875</v>
+        <v>199.5400390625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B37">
-        <v>137.87021484375</v>
+        <v>198.280517578125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B38">
-        <v>137.129921875</v>
+        <v>194.27001953125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B39">
-        <v>136.29986328125</v>
+        <v>192.93994140625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B40">
-        <v>135.63001953125</v>
+        <v>191.740234375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B41">
-        <v>133.809921875</v>
+        <v>191.33984375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="B42">
-        <v>132.09021484375</v>
+        <v>187.52978515625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B43">
-        <v>131.61015625</v>
+        <v>186.71044921875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B44">
-        <v>129.790048828125</v>
+        <v>183.83984375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B45">
-        <v>129.629921875</v>
+        <v>181.76025390625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B46">
-        <v>127.599921875</v>
+        <v>181.19970703125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>125.73001953125</v>
+        <v>179.81005859375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B48">
-        <v>123.9801953125</v>
+        <v>179.18994140625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B49">
-        <v>123.1701171875</v>
+        <v>173.77001953125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -6507,31 +6834,31 @@
         <v>25</v>
       </c>
       <c r="B50">
-        <v>121.5701171875</v>
+        <v>164.72021484375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B51">
-        <v>115.11009765625</v>
+        <v>160.900146484375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B52">
-        <v>102.299951171875</v>
+        <v>160.77978515625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B53">
-        <v>102.08990234375</v>
+        <v>159.6201171875</v>
       </c>
     </row>
   </sheetData>
@@ -6551,7 +6878,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6559,7 +6886,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6567,7 +6894,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6575,7 +6902,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6583,7 +6910,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6591,7 +6918,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6599,7 +6926,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6607,7 +6934,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6615,7 +6942,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6623,7 +6950,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6631,7 +6958,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6639,7 +6966,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6647,7 +6974,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6655,7 +6982,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6663,7 +6990,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6671,7 +6998,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6679,7 +7006,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6687,7 +7014,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6695,7 +7022,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6703,7 +7030,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6711,7 +7038,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6719,7 +7046,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6727,7 +7054,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6735,7 +7062,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6743,7 +7070,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6751,7 +7078,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6759,7 +7086,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6767,7 +7094,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6775,7 +7102,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6783,7 +7110,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6791,7 +7118,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6799,7 +7126,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -6807,7 +7134,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6815,7 +7142,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -6823,7 +7150,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -6831,7 +7158,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6839,7 +7166,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6847,7 +7174,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -6855,7 +7182,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -6863,7 +7190,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6871,7 +7198,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6879,7 +7206,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6887,7 +7214,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -6895,7 +7222,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -6903,7 +7230,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -6911,7 +7238,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -6919,7 +7246,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -6927,7 +7254,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -6935,7 +7262,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -6943,7 +7270,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -6951,7 +7278,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -6959,7 +7286,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -630,7 +630,7 @@
         <v>68.7998046875</v>
       </c>
       <c r="H2">
-        <v>68.7998046875</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -656,7 +656,7 @@
         <v>56.110107421875</v>
       </c>
       <c r="H3">
-        <v>56.110107421875</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -682,7 +682,7 @@
         <v>54.6201171875</v>
       </c>
       <c r="H4">
-        <v>54.6201171875</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -708,7 +708,7 @@
         <v>86.419921875</v>
       </c>
       <c r="H5">
-        <v>86.419921875</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -734,7 +734,7 @@
         <v>73.10986328125</v>
       </c>
       <c r="H6">
-        <v>73.10986328125</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -760,7 +760,7 @@
         <v>67.81982421875</v>
       </c>
       <c r="H7">
-        <v>67.81982421875</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -786,7 +786,7 @@
         <v>83</v>
       </c>
       <c r="H8">
-        <v>83</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -812,7 +812,7 @@
         <v>69.5</v>
       </c>
       <c r="H9">
-        <v>69.5</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -838,7 +838,7 @@
         <v>66.60986328125</v>
       </c>
       <c r="H10">
-        <v>66.60986328125</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -864,7 +864,7 @@
         <v>67.18994140625</v>
       </c>
       <c r="H11">
-        <v>67.18994140625</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -890,7 +890,7 @@
         <v>72.10986328125</v>
       </c>
       <c r="H12">
-        <v>72.10986328125</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -916,7 +916,7 @@
         <v>47.389892578125</v>
       </c>
       <c r="H13">
-        <v>47.389892578125</v>
+        <v>38.87</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -942,7 +942,7 @@
         <v>58.2900390625</v>
       </c>
       <c r="H14">
-        <v>58.2900390625</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -968,7 +968,7 @@
         <v>68.490234375</v>
       </c>
       <c r="H15">
-        <v>68.490234375</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -994,7 +994,7 @@
         <v>83.419921875</v>
       </c>
       <c r="H16">
-        <v>83.419921875</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1020,7 +1020,7 @@
         <v>62.81005859375</v>
       </c>
       <c r="H17">
-        <v>62.81005859375</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1046,7 +1046,7 @@
         <v>58.68994140625</v>
       </c>
       <c r="H18">
-        <v>58.68994140625</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1072,7 +1072,7 @@
         <v>73.22021484375</v>
       </c>
       <c r="H19">
-        <v>73.22021484375</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1098,7 +1098,7 @@
         <v>41.550048828125</v>
       </c>
       <c r="H20">
-        <v>41.550048828125</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1124,7 +1124,7 @@
         <v>52.199951171875</v>
       </c>
       <c r="H21">
-        <v>52.199951171875</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1150,7 +1150,7 @@
         <v>62.10009765625</v>
       </c>
       <c r="H22">
-        <v>62.10009765625</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1176,7 +1176,7 @@
         <v>54.2099609375</v>
       </c>
       <c r="H23">
-        <v>54.2099609375</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1202,7 +1202,7 @@
         <v>62.010009765625</v>
       </c>
       <c r="H24">
-        <v>62.010009765625</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1228,7 +1228,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="H25">
-        <v>64.35986328125</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1254,7 +1254,7 @@
         <v>58.610107421875</v>
       </c>
       <c r="H26">
-        <v>58.610107421875</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1280,7 +1280,7 @@
         <v>73.02001953125</v>
       </c>
       <c r="H27">
-        <v>73.02001953125</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1306,7 +1306,7 @@
         <v>80.60986328125</v>
       </c>
       <c r="H28">
-        <v>80.60986328125</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1332,7 +1332,7 @@
         <v>54.81005859375</v>
       </c>
       <c r="H29">
-        <v>54.81005859375</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1358,7 +1358,7 @@
         <v>58.60009765625</v>
       </c>
       <c r="H30">
-        <v>58.60009765625</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1384,7 +1384,7 @@
         <v>64.1201171875</v>
       </c>
       <c r="H31">
-        <v>64.1201171875</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1410,7 +1410,7 @@
         <v>53.4599609375</v>
       </c>
       <c r="H32">
-        <v>53.4599609375</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1436,7 +1436,7 @@
         <v>71.60986328125</v>
       </c>
       <c r="H33">
-        <v>71.60986328125</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1462,7 +1462,7 @@
         <v>55.590087890625</v>
       </c>
       <c r="H34">
-        <v>55.590087890625</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1488,7 +1488,7 @@
         <v>53.510009765625</v>
       </c>
       <c r="H35">
-        <v>53.510009765625</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1514,7 +1514,7 @@
         <v>58.889892578125</v>
       </c>
       <c r="H36">
-        <v>58.889892578125</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1540,7 +1540,7 @@
         <v>66.509765625</v>
       </c>
       <c r="H37">
-        <v>66.509765625</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1566,7 +1566,7 @@
         <v>68.990234375</v>
       </c>
       <c r="H38">
-        <v>68.990234375</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1592,7 +1592,7 @@
         <v>44.510009765625</v>
       </c>
       <c r="H39">
-        <v>44.510009765625</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1618,7 +1618,7 @@
         <v>56.39990234375</v>
       </c>
       <c r="H40">
-        <v>56.39990234375</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1644,7 +1644,7 @@
         <v>48.199951171875</v>
       </c>
       <c r="H41">
-        <v>48.199951171875</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1670,7 +1670,7 @@
         <v>76.68994140625</v>
       </c>
       <c r="H42">
-        <v>76.68994140625</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1696,7 +1696,7 @@
         <v>65.7099609375</v>
       </c>
       <c r="H43">
-        <v>65.7099609375</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1722,7 +1722,7 @@
         <v>80.509765625</v>
       </c>
       <c r="H44">
-        <v>80.509765625</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1748,7 +1748,7 @@
         <v>69.1201171875</v>
       </c>
       <c r="H45">
-        <v>69.1201171875</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1774,7 +1774,7 @@
         <v>59.929931640625</v>
       </c>
       <c r="H46">
-        <v>59.929931640625</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1800,7 +1800,7 @@
         <v>62.919921875</v>
       </c>
       <c r="H47">
-        <v>62.919921875</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1826,7 +1826,7 @@
         <v>77.41015625</v>
       </c>
       <c r="H48">
-        <v>77.41015625</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1852,7 +1852,7 @@
         <v>74.91015625</v>
       </c>
       <c r="H49">
-        <v>74.91015625</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1878,7 +1878,7 @@
         <v>83</v>
       </c>
       <c r="H50">
-        <v>83</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1904,7 +1904,7 @@
         <v>54.2099609375</v>
       </c>
       <c r="H51">
-        <v>54.2099609375</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1930,7 +1930,7 @@
         <v>59.300048828125</v>
       </c>
       <c r="H52">
-        <v>59.300048828125</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1956,7 +1956,7 @@
         <v>57.780029296875</v>
       </c>
       <c r="H53">
-        <v>57.780029296875</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3076,7 +3076,7 @@
         <v>68.7998046875</v>
       </c>
       <c r="H2">
-        <v>68.7998046875</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3102,7 +3102,7 @@
         <v>56.110107421875</v>
       </c>
       <c r="H3">
-        <v>56.110107421875</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3128,7 +3128,7 @@
         <v>54.6201171875</v>
       </c>
       <c r="H4">
-        <v>54.6201171875</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3154,7 +3154,7 @@
         <v>86.419921875</v>
       </c>
       <c r="H5">
-        <v>86.419921875</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3180,7 +3180,7 @@
         <v>73.10986328125</v>
       </c>
       <c r="H6">
-        <v>73.10986328125</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3206,7 +3206,7 @@
         <v>67.81982421875</v>
       </c>
       <c r="H7">
-        <v>67.81982421875</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3232,7 +3232,7 @@
         <v>83</v>
       </c>
       <c r="H8">
-        <v>83</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3258,7 +3258,7 @@
         <v>69.5</v>
       </c>
       <c r="H9">
-        <v>69.5</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3284,7 +3284,7 @@
         <v>66.60986328125</v>
       </c>
       <c r="H10">
-        <v>66.60986328125</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3310,7 +3310,7 @@
         <v>67.18994140625</v>
       </c>
       <c r="H11">
-        <v>67.18994140625</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3336,7 +3336,7 @@
         <v>72.10986328125</v>
       </c>
       <c r="H12">
-        <v>72.10986328125</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3362,7 +3362,7 @@
         <v>47.389892578125</v>
       </c>
       <c r="H13">
-        <v>47.389892578125</v>
+        <v>38.87</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3388,7 +3388,7 @@
         <v>58.2900390625</v>
       </c>
       <c r="H14">
-        <v>58.2900390625</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3414,7 +3414,7 @@
         <v>68.490234375</v>
       </c>
       <c r="H15">
-        <v>68.490234375</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3440,7 +3440,7 @@
         <v>83.419921875</v>
       </c>
       <c r="H16">
-        <v>83.419921875</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3466,7 +3466,7 @@
         <v>62.81005859375</v>
       </c>
       <c r="H17">
-        <v>62.81005859375</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3492,7 +3492,7 @@
         <v>58.68994140625</v>
       </c>
       <c r="H18">
-        <v>58.68994140625</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3518,7 +3518,7 @@
         <v>73.22021484375</v>
       </c>
       <c r="H19">
-        <v>73.22021484375</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3544,7 +3544,7 @@
         <v>41.550048828125</v>
       </c>
       <c r="H20">
-        <v>41.550048828125</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3570,7 +3570,7 @@
         <v>52.199951171875</v>
       </c>
       <c r="H21">
-        <v>52.199951171875</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3596,7 +3596,7 @@
         <v>62.10009765625</v>
       </c>
       <c r="H22">
-        <v>62.10009765625</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3622,7 +3622,7 @@
         <v>54.2099609375</v>
       </c>
       <c r="H23">
-        <v>54.2099609375</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3648,7 +3648,7 @@
         <v>62.010009765625</v>
       </c>
       <c r="H24">
-        <v>62.010009765625</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3674,7 +3674,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="H25">
-        <v>64.35986328125</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3700,7 +3700,7 @@
         <v>58.610107421875</v>
       </c>
       <c r="H26">
-        <v>58.610107421875</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3726,7 +3726,7 @@
         <v>73.02001953125</v>
       </c>
       <c r="H27">
-        <v>73.02001953125</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3752,7 +3752,7 @@
         <v>80.60986328125</v>
       </c>
       <c r="H28">
-        <v>80.60986328125</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3778,7 +3778,7 @@
         <v>54.81005859375</v>
       </c>
       <c r="H29">
-        <v>54.81005859375</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3804,7 +3804,7 @@
         <v>58.60009765625</v>
       </c>
       <c r="H30">
-        <v>58.60009765625</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3830,7 +3830,7 @@
         <v>64.1201171875</v>
       </c>
       <c r="H31">
-        <v>64.1201171875</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3856,7 +3856,7 @@
         <v>53.4599609375</v>
       </c>
       <c r="H32">
-        <v>53.4599609375</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3882,7 +3882,7 @@
         <v>71.60986328125</v>
       </c>
       <c r="H33">
-        <v>71.60986328125</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3908,7 +3908,7 @@
         <v>55.590087890625</v>
       </c>
       <c r="H34">
-        <v>55.590087890625</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3934,7 +3934,7 @@
         <v>53.510009765625</v>
       </c>
       <c r="H35">
-        <v>53.510009765625</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3960,7 +3960,7 @@
         <v>58.889892578125</v>
       </c>
       <c r="H36">
-        <v>58.889892578125</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3986,7 +3986,7 @@
         <v>66.509765625</v>
       </c>
       <c r="H37">
-        <v>66.509765625</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4012,7 +4012,7 @@
         <v>68.990234375</v>
       </c>
       <c r="H38">
-        <v>68.990234375</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4038,7 +4038,7 @@
         <v>44.510009765625</v>
       </c>
       <c r="H39">
-        <v>44.510009765625</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4064,7 +4064,7 @@
         <v>56.39990234375</v>
       </c>
       <c r="H40">
-        <v>56.39990234375</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4090,7 +4090,7 @@
         <v>48.199951171875</v>
       </c>
       <c r="H41">
-        <v>48.199951171875</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -4116,7 +4116,7 @@
         <v>76.68994140625</v>
       </c>
       <c r="H42">
-        <v>76.68994140625</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4142,7 +4142,7 @@
         <v>65.7099609375</v>
       </c>
       <c r="H43">
-        <v>65.7099609375</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4168,7 +4168,7 @@
         <v>80.509765625</v>
       </c>
       <c r="H44">
-        <v>80.509765625</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -4194,7 +4194,7 @@
         <v>69.1201171875</v>
       </c>
       <c r="H45">
-        <v>69.1201171875</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -4220,7 +4220,7 @@
         <v>59.929931640625</v>
       </c>
       <c r="H46">
-        <v>59.929931640625</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4246,7 +4246,7 @@
         <v>62.919921875</v>
       </c>
       <c r="H47">
-        <v>62.919921875</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -4272,7 +4272,7 @@
         <v>77.41015625</v>
       </c>
       <c r="H48">
-        <v>77.41015625</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -4298,7 +4298,7 @@
         <v>74.91015625</v>
       </c>
       <c r="H49">
-        <v>74.91015625</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -4324,7 +4324,7 @@
         <v>83</v>
       </c>
       <c r="H50">
-        <v>83</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -4350,7 +4350,7 @@
         <v>54.2099609375</v>
       </c>
       <c r="H51">
-        <v>54.2099609375</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -4376,7 +4376,7 @@
         <v>59.300048828125</v>
       </c>
       <c r="H52">
-        <v>59.300048828125</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -4402,7 +4402,7 @@
         <v>57.780029296875</v>
       </c>
       <c r="H53">
-        <v>57.780029296875</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -4451,31 +4451,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>613.8095703125</v>
+        <v>573.1596484375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>580.169921875</v>
+        <v>544.5295703125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B4">
-        <v>573.669921875</v>
+        <v>540.339921875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>568.75</v>
+        <v>533.839921875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4483,15 +4483,15 @@
         <v>57</v>
       </c>
       <c r="B6">
-        <v>561.9697265625</v>
+        <v>532.939677734375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B7">
-        <v>558.60009765625</v>
+        <v>530.41013671875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4499,239 +4499,239 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>550.23974609375</v>
+        <v>523.9998828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9">
-        <v>543.909423828125</v>
+        <v>522.27025390625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B10">
-        <v>543.689453125</v>
+        <v>521.0496875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="B11">
-        <v>537.36962890625</v>
+        <v>518.7599414062501</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B12">
-        <v>535.8896484375</v>
+        <v>517.580205078125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>535.260009765625</v>
+        <v>514.859453125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>532.730224609375</v>
+        <v>499.759501953125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B15">
-        <v>530.8203125</v>
+        <v>499.160146484375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B16">
-        <v>523.23974609375</v>
+        <v>498.480107421875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B17">
-        <v>522.830322265625</v>
+        <v>497.419873046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B18">
-        <v>518.3603515625</v>
+        <v>495.379970703125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>517.519775390625</v>
+        <v>491.33015625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B20">
-        <v>512.75</v>
+        <v>490.169267578125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B21">
-        <v>512.189208984375</v>
+        <v>488.38935546875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B22">
-        <v>511.519775390625</v>
+        <v>487.790068359375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B23">
-        <v>511.19921875</v>
+        <v>482.7998828125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B24">
-        <v>507.929931640625</v>
+        <v>482.7897265625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B25">
-        <v>503.229736328125</v>
+        <v>478.589970703125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B26">
-        <v>502.719970703125</v>
+        <v>478.499345703125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B27">
-        <v>502.049560546875</v>
+        <v>476.689921875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28">
-        <v>501.9501953125</v>
+        <v>473.5096484375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B29">
-        <v>499.090087890625</v>
+        <v>473.1998828125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B30">
-        <v>494.8095703125</v>
+        <v>468.65974609375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B31">
-        <v>494.8095703125</v>
+        <v>466.859697265625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B32">
-        <v>489.900146484375</v>
+        <v>463.66951171875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B33">
-        <v>486.509033203125</v>
+        <v>462.780224609375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B34">
-        <v>482.029541015625</v>
+        <v>461.809794921875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B35">
-        <v>479.480224609375</v>
+        <v>459.779912109375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>476.57958984375</v>
+        <v>453.090087890625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B37">
-        <v>475.419921875</v>
+        <v>452.129619140625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4739,103 +4739,103 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>472.95947265625</v>
+        <v>451.59951171875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B39">
-        <v>470.300048828125</v>
+        <v>451.260107421875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B40">
-        <v>468.11962890625</v>
+        <v>448.390068359375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B41">
-        <v>462.81982421875</v>
+        <v>444.03982421875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>462.479736328125</v>
+        <v>440.099931640625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B43">
-        <v>462.389892578125</v>
+        <v>435.0698046875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B44">
-        <v>459.509765625</v>
+        <v>433.69</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B45">
-        <v>458.05029296875</v>
+        <v>433.24978515625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B46">
-        <v>451.52978515625</v>
+        <v>426.840185546875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B47">
-        <v>450.60009765625</v>
+        <v>425.78982421875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B48">
-        <v>435.030029296875</v>
+        <v>414.559814453125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B49">
-        <v>430.0498046875</v>
+        <v>414.280029296875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B50">
-        <v>420.8701171875</v>
+        <v>398.67986328125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -4843,7 +4843,7 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>415.70068359375</v>
+        <v>378.38044921875</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -4851,7 +4851,7 @@
         <v>35</v>
       </c>
       <c r="B52">
-        <v>398.929931640625</v>
+        <v>373.069833984375</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -4859,7 +4859,7 @@
         <v>46</v>
       </c>
       <c r="B53">
-        <v>349.4400634765625</v>
+        <v>334.3401123046875</v>
       </c>
     </row>
   </sheetData>
@@ -6450,415 +6450,415 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>276.759765625</v>
+        <v>236.10984375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>259.02001953125</v>
+        <v>221.800078125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B4">
-        <v>259.02001953125</v>
+        <v>219.19001953125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>255.759765625</v>
+        <v>219.19001953125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>253.34033203125</v>
+        <v>215.3303125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B7">
-        <v>250.77978515625</v>
+        <v>213.50017578125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>244.43994140625</v>
+        <v>213.2901171875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B9">
-        <v>242.1201171875</v>
+        <v>212.700078125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B10">
-        <v>235.509765625</v>
+        <v>212.439921875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>234.82958984375</v>
+        <v>211.60984375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B12">
-        <v>232.2197265625</v>
+        <v>211.44978515625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>231.53955078125</v>
+        <v>202.5897265625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B14">
-        <v>228.82958984375</v>
+        <v>202.28982421875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>228.64013671875</v>
+        <v>202.00033203125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B16">
-        <v>227.5400390625</v>
+        <v>200.01013671875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>225.76025390625</v>
+        <v>199.289921875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B18">
-        <v>224.3603515625</v>
+        <v>197.74958984375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>223.8994140625</v>
+        <v>196.330078125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B20">
-        <v>223.2099609375</v>
+        <v>195.81013671875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>220.34033203125</v>
+        <v>195.58015625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B22">
-        <v>215.83984375</v>
+        <v>195.4396875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B23">
-        <v>214.64013671875</v>
+        <v>193.02998046875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B24">
-        <v>213.55029296875</v>
+        <v>192.240166015625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B25">
-        <v>211.42041015625</v>
+        <v>190.820244140625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B26">
-        <v>208.83984375</v>
+        <v>189.650029296875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B27">
-        <v>208.02001953125</v>
+        <v>186.269853515625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B28">
-        <v>207.78955078125</v>
+        <v>185.58982421875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B29">
-        <v>207.009765625</v>
+        <v>183.900029296875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B30">
-        <v>206.39990234375</v>
+        <v>183.69998046875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>206.2001953125</v>
+        <v>183.680009765625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>205.71044921875</v>
+        <v>182.75994140625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="B33">
-        <v>203.48974609375</v>
+        <v>180.420224609375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B34">
-        <v>203.03955078125</v>
+        <v>179.88984375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B35">
-        <v>202.89013671875</v>
+        <v>178.989970703125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B36">
-        <v>199.5400390625</v>
+        <v>177.599833984375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B37">
-        <v>198.280517578125</v>
+        <v>174.1701171875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B38">
-        <v>194.27001953125</v>
+        <v>172.679814453125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B39">
-        <v>192.93994140625</v>
+        <v>169.3496875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B40">
-        <v>191.740234375</v>
+        <v>165.5998828125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B41">
-        <v>191.33984375</v>
+        <v>164.710107421875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B42">
-        <v>187.52978515625</v>
+        <v>162.110107421875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B43">
-        <v>186.71044921875</v>
+        <v>162.0698046875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B44">
-        <v>183.83984375</v>
+        <v>161.7998828125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B45">
-        <v>181.76025390625</v>
+        <v>160.960283203125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B46">
-        <v>181.19970703125</v>
+        <v>160.530126953125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B47">
-        <v>179.81005859375</v>
+        <v>159.3998828125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B48">
-        <v>179.18994140625</v>
+        <v>158.49033203125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B49">
-        <v>173.77001953125</v>
+        <v>157.82998046875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B50">
-        <v>164.72021484375</v>
+        <v>157.81005859375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B51">
-        <v>160.900146484375</v>
+        <v>144.540068359375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B52">
-        <v>160.77978515625</v>
+        <v>135.040048828125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B53">
-        <v>159.6201171875</v>
+        <v>129.40984375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="68">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>Rodada 7</t>
+  </si>
+  <si>
+    <t>Rodada 8</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -224,6 +227,9 @@
   </si>
   <si>
     <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Marco</t>
   </si>
 </sst>
 </file>
@@ -581,10 +587,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,10 +612,13 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -630,12 +639,15 @@
         <v>68.7998046875</v>
       </c>
       <c r="H2">
-        <v>35.87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>50.570068359375</v>
+      </c>
+      <c r="I2">
+        <v>50.570068359375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -656,12 +668,15 @@
         <v>56.110107421875</v>
       </c>
       <c r="H3">
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>63.159912109375</v>
+      </c>
+      <c r="I3">
+        <v>63.159912109375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -682,12 +697,15 @@
         <v>54.6201171875</v>
       </c>
       <c r="H4">
-        <v>26.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>82.9599609375</v>
+      </c>
+      <c r="I4">
+        <v>82.9599609375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -708,12 +726,15 @@
         <v>86.419921875</v>
       </c>
       <c r="H5">
-        <v>45.77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>82.3701171875</v>
+      </c>
+      <c r="I5">
+        <v>82.3701171875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -734,12 +755,15 @@
         <v>73.10986328125</v>
       </c>
       <c r="H6">
-        <v>37.01</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>61.2099609375</v>
+      </c>
+      <c r="I6">
+        <v>61.2099609375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -760,12 +784,15 @@
         <v>67.81982421875</v>
       </c>
       <c r="H7">
-        <v>41.67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>64.669921875</v>
+      </c>
+      <c r="I7">
+        <v>64.669921875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -786,12 +813,15 @@
         <v>83</v>
       </c>
       <c r="H8">
-        <v>43.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>85.97021484375</v>
+      </c>
+      <c r="I8">
+        <v>85.97021484375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -812,12 +842,15 @@
         <v>69.5</v>
       </c>
       <c r="H9">
-        <v>40.67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>70.47021484375</v>
+      </c>
+      <c r="I9">
+        <v>70.47021484375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -838,12 +871,15 @@
         <v>66.60986328125</v>
       </c>
       <c r="H10">
-        <v>43.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>70.2099609375</v>
+      </c>
+      <c r="I10">
+        <v>70.2099609375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -864,12 +900,15 @@
         <v>67.18994140625</v>
       </c>
       <c r="H11">
-        <v>25.77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>72.1201171875</v>
+      </c>
+      <c r="I11">
+        <v>72.1201171875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -890,12 +929,15 @@
         <v>72.10986328125</v>
       </c>
       <c r="H12">
-        <v>45.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>87.1201171875</v>
+      </c>
+      <c r="I12">
+        <v>87.1201171875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -916,12 +958,15 @@
         <v>47.389892578125</v>
       </c>
       <c r="H13">
-        <v>38.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>67.27001953125</v>
+      </c>
+      <c r="I13">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -942,12 +987,15 @@
         <v>58.2900390625</v>
       </c>
       <c r="H14">
-        <v>47.67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>78.97021484375</v>
+      </c>
+      <c r="I14">
+        <v>78.97021484375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -968,12 +1016,15 @@
         <v>68.490234375</v>
       </c>
       <c r="H15">
-        <v>31.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>50.8701171875</v>
+      </c>
+      <c r="I15">
+        <v>50.8701171875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -994,12 +1045,15 @@
         <v>83.419921875</v>
       </c>
       <c r="H16">
-        <v>39.27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>68.97021484375</v>
+      </c>
+      <c r="I16">
+        <v>68.97021484375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -1020,12 +1074,15 @@
         <v>62.81005859375</v>
       </c>
       <c r="H17">
-        <v>69.97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>105.8701171875</v>
+      </c>
+      <c r="I17">
+        <v>105.8701171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -1046,12 +1103,15 @@
         <v>58.68994140625</v>
       </c>
       <c r="H18">
-        <v>27.32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>31.6199951171875</v>
+      </c>
+      <c r="I18">
+        <v>31.6199951171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -1072,12 +1132,15 @@
         <v>73.22021484375</v>
       </c>
       <c r="H19">
-        <v>48.87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>75.56982421875</v>
+      </c>
+      <c r="I19">
+        <v>75.56982421875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -1098,12 +1161,15 @@
         <v>41.550048828125</v>
       </c>
       <c r="H20">
-        <v>69.06999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>79.56982421875</v>
+      </c>
+      <c r="I20">
+        <v>79.56982421875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -1124,12 +1190,15 @@
         <v>52.199951171875</v>
       </c>
       <c r="H21">
-        <v>22.97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>39.969970703125</v>
+      </c>
+      <c r="I21">
+        <v>39.969970703125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -1150,12 +1219,15 @@
         <v>62.10009765625</v>
       </c>
       <c r="H22">
-        <v>66.01000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>82.81005859375</v>
+      </c>
+      <c r="I22">
+        <v>82.81005859375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1176,12 +1248,15 @@
         <v>54.2099609375</v>
       </c>
       <c r="H23">
-        <v>28.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>49.469970703125</v>
+      </c>
+      <c r="I23">
+        <v>49.469970703125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1202,12 +1277,15 @@
         <v>62.010009765625</v>
       </c>
       <c r="H24">
-        <v>30.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>77.06982421875</v>
+      </c>
+      <c r="I24">
+        <v>77.06982421875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1228,12 +1306,15 @@
         <v>64.35986328125</v>
       </c>
       <c r="H25">
-        <v>30.67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>76.97021484375</v>
+      </c>
+      <c r="I25">
+        <v>76.97021484375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1254,12 +1335,15 @@
         <v>58.610107421875</v>
       </c>
       <c r="H26">
-        <v>45.37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>81.56982421875</v>
+      </c>
+      <c r="I26">
+        <v>81.56982421875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1280,12 +1364,15 @@
         <v>73.02001953125</v>
       </c>
       <c r="H27">
-        <v>32.57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>64.47021484375</v>
+      </c>
+      <c r="I27">
+        <v>64.47021484375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1306,12 +1393,15 @@
         <v>80.60986328125</v>
       </c>
       <c r="H28">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>78.91015625</v>
+      </c>
+      <c r="I28">
+        <v>78.91015625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1332,12 +1422,15 @@
         <v>54.81005859375</v>
       </c>
       <c r="H29">
-        <v>23.67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>79.919921875</v>
+      </c>
+      <c r="I29">
+        <v>79.919921875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1358,12 +1451,15 @@
         <v>58.60009765625</v>
       </c>
       <c r="H30">
-        <v>32.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>53.0400390625</v>
+      </c>
+      <c r="I30">
+        <v>53.0400390625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1384,12 +1480,15 @@
         <v>64.1201171875</v>
       </c>
       <c r="H31">
-        <v>60.41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>70.60986328125</v>
+      </c>
+      <c r="I31">
+        <v>70.60986328125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1410,12 +1509,15 @@
         <v>53.4599609375</v>
       </c>
       <c r="H32">
-        <v>32.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>58.669921875</v>
+      </c>
+      <c r="I32">
+        <v>58.669921875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1436,12 +1538,15 @@
         <v>71.60986328125</v>
       </c>
       <c r="H33">
-        <v>33.27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>94.8701171875</v>
+      </c>
+      <c r="I33">
+        <v>94.8701171875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1462,12 +1567,15 @@
         <v>55.590087890625</v>
       </c>
       <c r="H34">
-        <v>26.07</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>46.570068359375</v>
+      </c>
+      <c r="I34">
+        <v>46.570068359375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -1488,12 +1596,15 @@
         <v>53.510009765625</v>
       </c>
       <c r="H35">
-        <v>37.87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>61.570068359375</v>
+      </c>
+      <c r="I35">
+        <v>61.570068359375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -1514,12 +1625,15 @@
         <v>58.889892578125</v>
       </c>
       <c r="H36">
-        <v>36.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>60.070068359375</v>
+      </c>
+      <c r="I36">
+        <v>60.070068359375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -1540,12 +1654,15 @@
         <v>66.509765625</v>
       </c>
       <c r="H37">
-        <v>70.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>82.56982421875</v>
+      </c>
+      <c r="I37">
+        <v>82.56982421875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -1566,12 +1683,15 @@
         <v>68.990234375</v>
       </c>
       <c r="H38">
-        <v>13.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>12.54998779296875</v>
+      </c>
+      <c r="I38">
+        <v>12.54998779296875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -1592,12 +1712,15 @@
         <v>44.510009765625</v>
       </c>
       <c r="H39">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>75.06005859375</v>
+      </c>
+      <c r="I39">
+        <v>75.06005859375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -1618,12 +1741,15 @@
         <v>56.39990234375</v>
       </c>
       <c r="H40">
-        <v>36.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>59.56005859375</v>
+      </c>
+      <c r="I40">
+        <v>59.56005859375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -1644,12 +1770,15 @@
         <v>48.199951171875</v>
       </c>
       <c r="H41">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>43.800048828125</v>
+      </c>
+      <c r="I41">
+        <v>43.800048828125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -1670,12 +1799,15 @@
         <v>76.68994140625</v>
       </c>
       <c r="H42">
-        <v>26.77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>50.969970703125</v>
+      </c>
+      <c r="I42">
+        <v>50.969970703125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -1696,12 +1828,15 @@
         <v>65.7099609375</v>
       </c>
       <c r="H43">
-        <v>50.87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>76.06982421875</v>
+      </c>
+      <c r="I43">
+        <v>76.06982421875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -1722,12 +1857,15 @@
         <v>80.509765625</v>
       </c>
       <c r="H44">
-        <v>47.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>58.8701171875</v>
+      </c>
+      <c r="I44">
+        <v>58.8701171875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -1748,12 +1886,15 @@
         <v>69.1201171875</v>
       </c>
       <c r="H45">
-        <v>39.17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>79.47021484375</v>
+      </c>
+      <c r="I45">
+        <v>79.47021484375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -1774,12 +1915,15 @@
         <v>59.929931640625</v>
       </c>
       <c r="H46">
-        <v>58.67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>77.419921875</v>
+      </c>
+      <c r="I46">
+        <v>77.419921875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -1800,12 +1944,15 @@
         <v>62.919921875</v>
       </c>
       <c r="H47">
-        <v>35.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>87.009765625</v>
+      </c>
+      <c r="I47">
+        <v>87.009765625</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -1826,12 +1973,15 @@
         <v>77.41015625</v>
       </c>
       <c r="H48">
-        <v>37.57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>71.3701171875</v>
+      </c>
+      <c r="I48">
+        <v>71.3701171875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -1852,12 +2002,15 @@
         <v>74.91015625</v>
       </c>
       <c r="H49">
-        <v>29.97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>60.27001953125</v>
+      </c>
+      <c r="I49">
+        <v>60.27001953125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -1878,12 +2031,15 @@
         <v>83</v>
       </c>
       <c r="H50">
-        <v>43.17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>76.97021484375</v>
+      </c>
+      <c r="I50">
+        <v>76.97021484375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -1904,12 +2060,15 @@
         <v>54.2099609375</v>
       </c>
       <c r="H51">
-        <v>29.77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>56.669921875</v>
+      </c>
+      <c r="I51">
+        <v>56.669921875</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -1930,12 +2089,15 @@
         <v>59.300048828125</v>
       </c>
       <c r="H52">
-        <v>30.27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>46.3701171875</v>
+      </c>
+      <c r="I52">
+        <v>46.3701171875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -1956,12 +2118,15 @@
         <v>57.780029296875</v>
       </c>
       <c r="H53">
-        <v>56.44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>67.33984375</v>
+      </c>
+      <c r="I53">
+        <v>67.33984375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1982,6 +2147,9 @@
         <v>0</v>
       </c>
       <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
         <v>0</v>
       </c>
     </row>
@@ -2002,7 +2170,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2010,7 +2178,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2018,7 +2186,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2026,7 +2194,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2034,7 +2202,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2042,7 +2210,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2050,7 +2218,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2058,7 +2226,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2066,7 +2234,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2074,7 +2242,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2082,7 +2250,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2090,7 +2258,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2098,7 +2266,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2106,7 +2274,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2114,7 +2282,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2122,7 +2290,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2130,7 +2298,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2138,7 +2306,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2146,7 +2314,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2154,7 +2322,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2162,7 +2330,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2170,7 +2338,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2178,7 +2346,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2186,7 +2354,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2194,7 +2362,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2202,7 +2370,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2210,7 +2378,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2218,7 +2386,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2226,7 +2394,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2234,7 +2402,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2242,7 +2410,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2250,7 +2418,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2258,7 +2426,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2266,7 +2434,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2274,7 +2442,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2282,7 +2450,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2290,7 +2458,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2298,7 +2466,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2306,7 +2474,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2314,7 +2482,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2322,7 +2490,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2330,7 +2498,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2338,7 +2506,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2346,7 +2514,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2354,7 +2522,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2362,7 +2530,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2370,7 +2538,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2378,7 +2546,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2386,7 +2554,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2394,7 +2562,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2402,7 +2570,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2410,7 +2578,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2433,7 +2601,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2441,7 +2609,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2449,7 +2617,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2457,7 +2625,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2465,7 +2633,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2473,7 +2641,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2481,7 +2649,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2489,7 +2657,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2497,7 +2665,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2505,7 +2673,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2513,7 +2681,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2521,7 +2689,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2529,7 +2697,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2537,7 +2705,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2545,7 +2713,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2553,7 +2721,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2561,7 +2729,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2569,7 +2737,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2577,7 +2745,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2585,7 +2753,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2593,7 +2761,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2601,7 +2769,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2609,7 +2777,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2617,7 +2785,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2625,7 +2793,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2633,7 +2801,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2641,7 +2809,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2649,7 +2817,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2657,7 +2825,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2665,7 +2833,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2673,7 +2841,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2681,7 +2849,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2689,7 +2857,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2697,7 +2865,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2705,7 +2873,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2713,7 +2881,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2721,7 +2889,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2729,7 +2897,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2737,7 +2905,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2745,7 +2913,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2753,7 +2921,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2761,7 +2929,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2769,7 +2937,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2777,7 +2945,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2785,7 +2953,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2793,7 +2961,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2801,7 +2969,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2809,7 +2977,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2817,7 +2985,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2825,7 +2993,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2833,7 +3001,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2841,7 +3009,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2854,32 +3022,32 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -2887,13 +3055,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -2901,13 +3069,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -2915,13 +3083,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -2929,13 +3097,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -2943,13 +3111,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -2957,13 +3125,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -2971,13 +3139,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -2985,13 +3153,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -2999,16 +3167,86 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>368.91015625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>363.5703125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>355.080078125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>347.96044921875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <v>330.9599609375</v>
       </c>
     </row>
   </sheetData>
@@ -3027,10 +3265,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3052,10 +3290,13 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -3076,12 +3317,15 @@
         <v>68.7998046875</v>
       </c>
       <c r="H2">
-        <v>35.87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>50.570068359375</v>
+      </c>
+      <c r="I2">
+        <v>50.570068359375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -3102,12 +3346,15 @@
         <v>56.110107421875</v>
       </c>
       <c r="H3">
-        <v>24.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>63.159912109375</v>
+      </c>
+      <c r="I3">
+        <v>63.159912109375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -3128,12 +3375,15 @@
         <v>54.6201171875</v>
       </c>
       <c r="H4">
-        <v>26.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>82.9599609375</v>
+      </c>
+      <c r="I4">
+        <v>82.9599609375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -3154,12 +3404,15 @@
         <v>86.419921875</v>
       </c>
       <c r="H5">
-        <v>45.77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>82.3701171875</v>
+      </c>
+      <c r="I5">
+        <v>82.3701171875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -3180,12 +3433,15 @@
         <v>73.10986328125</v>
       </c>
       <c r="H6">
-        <v>37.01</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>61.2099609375</v>
+      </c>
+      <c r="I6">
+        <v>61.2099609375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -3206,12 +3462,15 @@
         <v>67.81982421875</v>
       </c>
       <c r="H7">
-        <v>41.67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>64.669921875</v>
+      </c>
+      <c r="I7">
+        <v>64.669921875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -3232,12 +3491,15 @@
         <v>83</v>
       </c>
       <c r="H8">
-        <v>43.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>85.97021484375</v>
+      </c>
+      <c r="I8">
+        <v>85.97021484375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -3258,12 +3520,15 @@
         <v>69.5</v>
       </c>
       <c r="H9">
-        <v>40.67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>70.47021484375</v>
+      </c>
+      <c r="I9">
+        <v>70.47021484375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -3284,12 +3549,15 @@
         <v>66.60986328125</v>
       </c>
       <c r="H10">
-        <v>43.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>70.2099609375</v>
+      </c>
+      <c r="I10">
+        <v>70.2099609375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -3310,12 +3578,15 @@
         <v>67.18994140625</v>
       </c>
       <c r="H11">
-        <v>25.77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>72.1201171875</v>
+      </c>
+      <c r="I11">
+        <v>72.1201171875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -3336,12 +3607,15 @@
         <v>72.10986328125</v>
       </c>
       <c r="H12">
-        <v>45.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>87.1201171875</v>
+      </c>
+      <c r="I12">
+        <v>87.1201171875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -3362,12 +3636,15 @@
         <v>47.389892578125</v>
       </c>
       <c r="H13">
-        <v>38.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>67.27001953125</v>
+      </c>
+      <c r="I13">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -3388,12 +3665,15 @@
         <v>58.2900390625</v>
       </c>
       <c r="H14">
-        <v>47.67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>78.97021484375</v>
+      </c>
+      <c r="I14">
+        <v>78.97021484375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -3414,12 +3694,15 @@
         <v>68.490234375</v>
       </c>
       <c r="H15">
-        <v>31.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>50.8701171875</v>
+      </c>
+      <c r="I15">
+        <v>50.8701171875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -3440,12 +3723,15 @@
         <v>83.419921875</v>
       </c>
       <c r="H16">
-        <v>39.27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>68.97021484375</v>
+      </c>
+      <c r="I16">
+        <v>68.97021484375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -3466,12 +3752,15 @@
         <v>62.81005859375</v>
       </c>
       <c r="H17">
-        <v>69.97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>105.8701171875</v>
+      </c>
+      <c r="I17">
+        <v>105.8701171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -3492,12 +3781,15 @@
         <v>58.68994140625</v>
       </c>
       <c r="H18">
-        <v>27.32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>31.6199951171875</v>
+      </c>
+      <c r="I18">
+        <v>31.6199951171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -3518,12 +3810,15 @@
         <v>73.22021484375</v>
       </c>
       <c r="H19">
-        <v>48.87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>75.56982421875</v>
+      </c>
+      <c r="I19">
+        <v>75.56982421875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -3544,12 +3839,15 @@
         <v>41.550048828125</v>
       </c>
       <c r="H20">
-        <v>69.06999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>79.56982421875</v>
+      </c>
+      <c r="I20">
+        <v>79.56982421875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -3570,12 +3868,15 @@
         <v>52.199951171875</v>
       </c>
       <c r="H21">
-        <v>22.97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>39.969970703125</v>
+      </c>
+      <c r="I21">
+        <v>39.969970703125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -3596,12 +3897,15 @@
         <v>62.10009765625</v>
       </c>
       <c r="H22">
-        <v>66.01000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>82.81005859375</v>
+      </c>
+      <c r="I22">
+        <v>82.81005859375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -3622,12 +3926,15 @@
         <v>54.2099609375</v>
       </c>
       <c r="H23">
-        <v>28.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>49.469970703125</v>
+      </c>
+      <c r="I23">
+        <v>49.469970703125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -3648,12 +3955,15 @@
         <v>62.010009765625</v>
       </c>
       <c r="H24">
-        <v>30.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>77.06982421875</v>
+      </c>
+      <c r="I24">
+        <v>77.06982421875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -3674,12 +3984,15 @@
         <v>64.35986328125</v>
       </c>
       <c r="H25">
-        <v>30.67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>76.97021484375</v>
+      </c>
+      <c r="I25">
+        <v>76.97021484375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -3700,12 +4013,15 @@
         <v>58.610107421875</v>
       </c>
       <c r="H26">
-        <v>45.37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>81.56982421875</v>
+      </c>
+      <c r="I26">
+        <v>81.56982421875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -3726,12 +4042,15 @@
         <v>73.02001953125</v>
       </c>
       <c r="H27">
-        <v>32.57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>64.47021484375</v>
+      </c>
+      <c r="I27">
+        <v>64.47021484375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -3752,12 +4071,15 @@
         <v>80.60986328125</v>
       </c>
       <c r="H28">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>78.91015625</v>
+      </c>
+      <c r="I28">
+        <v>78.91015625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -3778,12 +4100,15 @@
         <v>54.81005859375</v>
       </c>
       <c r="H29">
-        <v>23.67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>79.919921875</v>
+      </c>
+      <c r="I29">
+        <v>79.919921875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -3804,12 +4129,15 @@
         <v>58.60009765625</v>
       </c>
       <c r="H30">
-        <v>32.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>53.0400390625</v>
+      </c>
+      <c r="I30">
+        <v>53.0400390625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -3830,12 +4158,15 @@
         <v>64.1201171875</v>
       </c>
       <c r="H31">
-        <v>60.41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>70.60986328125</v>
+      </c>
+      <c r="I31">
+        <v>70.60986328125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -3856,12 +4187,15 @@
         <v>53.4599609375</v>
       </c>
       <c r="H32">
-        <v>32.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>58.669921875</v>
+      </c>
+      <c r="I32">
+        <v>58.669921875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -3882,12 +4216,15 @@
         <v>71.60986328125</v>
       </c>
       <c r="H33">
-        <v>33.27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>94.8701171875</v>
+      </c>
+      <c r="I33">
+        <v>94.8701171875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -3908,12 +4245,15 @@
         <v>55.590087890625</v>
       </c>
       <c r="H34">
-        <v>26.07</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>46.570068359375</v>
+      </c>
+      <c r="I34">
+        <v>46.570068359375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -3934,12 +4274,15 @@
         <v>53.510009765625</v>
       </c>
       <c r="H35">
-        <v>37.87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>61.570068359375</v>
+      </c>
+      <c r="I35">
+        <v>61.570068359375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -3960,12 +4303,15 @@
         <v>58.889892578125</v>
       </c>
       <c r="H36">
-        <v>36.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>60.070068359375</v>
+      </c>
+      <c r="I36">
+        <v>60.070068359375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -3986,12 +4332,15 @@
         <v>66.509765625</v>
       </c>
       <c r="H37">
-        <v>70.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>82.56982421875</v>
+      </c>
+      <c r="I37">
+        <v>82.56982421875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -4012,12 +4361,15 @@
         <v>68.990234375</v>
       </c>
       <c r="H38">
-        <v>13.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>12.54998779296875</v>
+      </c>
+      <c r="I38">
+        <v>12.54998779296875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -4038,12 +4390,15 @@
         <v>44.510009765625</v>
       </c>
       <c r="H39">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>75.06005859375</v>
+      </c>
+      <c r="I39">
+        <v>75.06005859375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -4064,12 +4419,15 @@
         <v>56.39990234375</v>
       </c>
       <c r="H40">
-        <v>36.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>59.56005859375</v>
+      </c>
+      <c r="I40">
+        <v>59.56005859375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -4090,12 +4448,15 @@
         <v>48.199951171875</v>
       </c>
       <c r="H41">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>43.800048828125</v>
+      </c>
+      <c r="I41">
+        <v>43.800048828125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -4116,12 +4477,15 @@
         <v>76.68994140625</v>
       </c>
       <c r="H42">
-        <v>26.77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>50.969970703125</v>
+      </c>
+      <c r="I42">
+        <v>50.969970703125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -4142,12 +4506,15 @@
         <v>65.7099609375</v>
       </c>
       <c r="H43">
-        <v>50.87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>76.06982421875</v>
+      </c>
+      <c r="I43">
+        <v>76.06982421875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -4168,12 +4535,15 @@
         <v>80.509765625</v>
       </c>
       <c r="H44">
-        <v>47.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>58.8701171875</v>
+      </c>
+      <c r="I44">
+        <v>58.8701171875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -4194,12 +4564,15 @@
         <v>69.1201171875</v>
       </c>
       <c r="H45">
-        <v>39.17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>79.47021484375</v>
+      </c>
+      <c r="I45">
+        <v>79.47021484375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -4220,12 +4593,15 @@
         <v>59.929931640625</v>
       </c>
       <c r="H46">
-        <v>58.67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>77.419921875</v>
+      </c>
+      <c r="I46">
+        <v>77.419921875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -4246,12 +4622,15 @@
         <v>62.919921875</v>
       </c>
       <c r="H47">
-        <v>35.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>87.009765625</v>
+      </c>
+      <c r="I47">
+        <v>87.009765625</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -4272,12 +4651,15 @@
         <v>77.41015625</v>
       </c>
       <c r="H48">
-        <v>37.57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>71.3701171875</v>
+      </c>
+      <c r="I48">
+        <v>71.3701171875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -4298,12 +4680,15 @@
         <v>74.91015625</v>
       </c>
       <c r="H49">
-        <v>29.97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>60.27001953125</v>
+      </c>
+      <c r="I49">
+        <v>60.27001953125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -4324,12 +4709,15 @@
         <v>83</v>
       </c>
       <c r="H50">
-        <v>43.17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>76.97021484375</v>
+      </c>
+      <c r="I50">
+        <v>76.97021484375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -4350,12 +4738,15 @@
         <v>54.2099609375</v>
       </c>
       <c r="H51">
-        <v>29.77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>56.669921875</v>
+      </c>
+      <c r="I51">
+        <v>56.669921875</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -4376,12 +4767,15 @@
         <v>59.300048828125</v>
       </c>
       <c r="H52">
-        <v>30.27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>46.3701171875</v>
+      </c>
+      <c r="I52">
+        <v>46.3701171875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -4402,12 +4796,15 @@
         <v>57.780029296875</v>
       </c>
       <c r="H53">
-        <v>56.44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>67.33984375</v>
+      </c>
+      <c r="I53">
+        <v>67.33984375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4428,6 +4825,9 @@
         <v>0</v>
       </c>
       <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
         <v>0</v>
       </c>
     </row>
@@ -4448,418 +4848,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>573.1596484375</v>
+        <v>692.1298828125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B3">
-        <v>544.5295703125</v>
+        <v>686.88037109375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>540.339921875</v>
+        <v>686.2998046875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>533.839921875</v>
+        <v>662.6103515625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B6">
-        <v>532.939677734375</v>
+        <v>652.3701171875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B7">
-        <v>530.41013671875</v>
+        <v>651.1103515625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B8">
-        <v>523.9998828125</v>
+        <v>635.349853515625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B9">
-        <v>522.27025390625</v>
+        <v>623.93017578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10">
-        <v>521.0496875</v>
+        <v>622.3193359375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B11">
-        <v>518.7599414062501</v>
+        <v>621.88037109375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>517.580205078125</v>
+        <v>615.1298828125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B13">
-        <v>514.859453125</v>
+        <v>602.5703125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B14">
-        <v>499.759501953125</v>
+        <v>601.769775390625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>499.160146484375</v>
+        <v>601.6005859375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="B16">
-        <v>498.480107421875</v>
+        <v>600.999755859375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B17">
-        <v>497.419873046875</v>
+        <v>600.749755859375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B18">
-        <v>495.379970703125</v>
+        <v>600.0595703125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>491.33015625</v>
+        <v>599.83935546875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>490.169267578125</v>
+        <v>598.429931640625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B21">
-        <v>488.38935546875</v>
+        <v>595.409912109375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B22">
-        <v>487.790068359375</v>
+        <v>590.780029296875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B23">
-        <v>482.7998828125</v>
+        <v>585.138916015625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B24">
-        <v>482.7897265625</v>
+        <v>585.00927734375</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B25">
-        <v>478.589970703125</v>
+        <v>584.570068359375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B26">
-        <v>478.499345703125</v>
+        <v>580.280029296875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B27">
-        <v>476.689921875</v>
+        <v>580.239990234375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B28">
-        <v>473.5096484375</v>
+        <v>579.16015625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B29">
-        <v>473.1998828125</v>
+        <v>578.360107421875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B30">
-        <v>468.65974609375</v>
+        <v>576.189697265625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B31">
-        <v>466.859697265625</v>
+        <v>569.1796875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B32">
-        <v>463.66951171875</v>
+        <v>563.029541015625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B33">
-        <v>462.780224609375</v>
+        <v>556.32958984375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B34">
-        <v>461.809794921875</v>
+        <v>556.210205078125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>459.779912109375</v>
+        <v>545.050048828125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B36">
-        <v>453.090087890625</v>
+        <v>543.860107421875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>452.129619140625</v>
+        <v>540.27001953125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B38">
-        <v>451.59951171875</v>
+        <v>539.600341796875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B39">
-        <v>451.260107421875</v>
+        <v>538.459716796875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B40">
-        <v>448.390068359375</v>
+        <v>536.83935546875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B41">
-        <v>444.03982421875</v>
+        <v>528.260009765625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B42">
-        <v>440.099931640625</v>
+        <v>527.299560546875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>435.0698046875</v>
+        <v>524.070068359375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44">
-        <v>433.69</v>
+        <v>518.6396484375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B45">
-        <v>433.24978515625</v>
+        <v>513.81005859375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="B46">
-        <v>426.840185546875</v>
+        <v>511.9296875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47">
-        <v>425.78982421875</v>
+        <v>496.259765625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B48">
-        <v>414.559814453125</v>
+        <v>490.2197265625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>414.280029296875</v>
+        <v>448.95068359375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B50">
-        <v>398.67986328125</v>
+        <v>446.409912109375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B51">
-        <v>378.38044921875</v>
+        <v>434.599853515625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B52">
-        <v>373.069833984375</v>
+        <v>426.4097900390625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53">
-        <v>334.3401123046875</v>
+        <v>388.8402099609375</v>
       </c>
     </row>
   </sheetData>
@@ -4874,267 +5274,267 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5154,7 +5554,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5162,7 +5562,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5170,7 +5570,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5178,7 +5578,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5186,7 +5586,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5194,7 +5594,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5202,7 +5602,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5210,7 +5610,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5218,7 +5618,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5226,7 +5626,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5234,7 +5634,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5242,7 +5642,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5250,7 +5650,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5258,7 +5658,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5266,7 +5666,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -5274,7 +5674,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -5282,7 +5682,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -5290,7 +5690,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5298,7 +5698,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5306,7 +5706,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5314,7 +5714,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5322,7 +5722,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5330,7 +5730,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5338,7 +5738,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5346,7 +5746,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -5354,7 +5754,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -5362,7 +5762,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -5370,7 +5770,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -5378,7 +5778,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -5386,7 +5786,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -5394,7 +5794,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5402,7 +5802,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -5410,7 +5810,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -5418,7 +5818,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5426,7 +5826,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -5434,7 +5834,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5442,7 +5842,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5450,7 +5850,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -5458,7 +5858,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5466,7 +5866,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5474,7 +5874,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5482,7 +5882,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5490,7 +5890,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -5498,7 +5898,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -5506,7 +5906,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -5514,7 +5914,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5522,7 +5922,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -5530,7 +5930,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -5538,7 +5938,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -5546,7 +5946,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -5554,7 +5954,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5562,7 +5962,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -5585,7 +5985,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -5593,7 +5993,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -5601,7 +6001,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -5609,7 +6009,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -5617,7 +6017,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -5625,7 +6025,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -5633,7 +6033,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -5641,7 +6041,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -5649,7 +6049,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -5657,7 +6057,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -5665,7 +6065,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -5673,7 +6073,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -5681,7 +6081,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -5689,7 +6089,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -5697,7 +6097,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -5705,7 +6105,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -5713,7 +6113,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -5721,7 +6121,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -5729,7 +6129,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -5737,7 +6137,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -5745,7 +6145,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -5753,7 +6153,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -5761,7 +6161,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -5769,7 +6169,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -5777,7 +6177,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -5785,7 +6185,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -5793,7 +6193,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -5801,7 +6201,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -5809,7 +6209,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -5817,7 +6217,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -5825,7 +6225,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -5833,7 +6233,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -5841,7 +6241,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -5849,7 +6249,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -5857,7 +6257,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -5865,7 +6265,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -5873,7 +6273,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -5881,7 +6281,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -5889,7 +6289,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -5897,7 +6297,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -5905,7 +6305,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -5913,7 +6313,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -5921,7 +6321,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -5929,7 +6329,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -5937,7 +6337,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -5945,7 +6345,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -5953,7 +6353,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48">
         <v>44.06005859375</v>
@@ -5961,7 +6361,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B49">
         <v>43.510009765625</v>
@@ -5969,7 +6369,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50">
         <v>42.9599609375</v>
@@ -5977,7 +6377,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>40.60009765625</v>
@@ -5985,7 +6385,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52">
         <v>38.260009765625</v>
@@ -5993,7 +6393,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B53">
         <v>37.820068359375</v>
@@ -6016,7 +6416,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -6024,7 +6424,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -6032,7 +6432,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -6040,7 +6440,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -6048,7 +6448,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -6056,7 +6456,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -6064,7 +6464,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -6072,7 +6472,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -6080,7 +6480,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -6088,7 +6488,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -6096,7 +6496,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -6104,7 +6504,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -6112,7 +6512,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -6120,7 +6520,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -6128,7 +6528,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -6136,7 +6536,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -6144,7 +6544,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -6152,7 +6552,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -6160,7 +6560,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -6168,7 +6568,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -6176,7 +6576,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -6184,7 +6584,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -6192,7 +6592,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -6200,7 +6600,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -6208,7 +6608,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B26">
         <v>231.8896484375</v>
@@ -6216,7 +6616,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>231.259765625</v>
@@ -6224,7 +6624,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>227.90966796875</v>
@@ -6232,7 +6632,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29">
         <v>227.8095703125</v>
@@ -6240,7 +6640,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30">
         <v>225.2099609375</v>
@@ -6248,7 +6648,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31">
         <v>225.02978515625</v>
@@ -6256,7 +6656,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32">
         <v>224.409912109375</v>
@@ -6264,7 +6664,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>222.49951171875</v>
@@ -6272,7 +6672,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34">
         <v>219.469482421875</v>
@@ -6280,7 +6680,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>218.419921875</v>
@@ -6288,7 +6688,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>216.3896484375</v>
@@ -6296,7 +6696,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>216.030517578125</v>
@@ -6304,7 +6704,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38">
         <v>215.5498046875</v>
@@ -6312,7 +6712,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B39">
         <v>212.2099609375</v>
@@ -6320,7 +6720,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B40">
         <v>211.239990234375</v>
@@ -6328,7 +6728,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41">
         <v>209.509765625</v>
@@ -6336,7 +6736,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42">
         <v>206.1201171875</v>
@@ -6344,7 +6744,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43">
         <v>205.58984375</v>
@@ -6352,7 +6752,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <v>204.8798828125</v>
@@ -6360,7 +6760,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B45">
         <v>199.2001953125</v>
@@ -6368,7 +6768,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46">
         <v>198.499755859375</v>
@@ -6376,7 +6776,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B47">
         <v>197.369873046875</v>
@@ -6384,7 +6784,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48">
         <v>191.85986328125</v>
@@ -6392,7 +6792,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49">
         <v>187.64990234375</v>
@@ -6400,7 +6800,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B50">
         <v>186.4697265625</v>
@@ -6408,7 +6808,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B51">
         <v>179.60009765625</v>
@@ -6416,7 +6816,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52">
         <v>159.43994140625</v>
@@ -6424,7 +6824,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
@@ -6447,282 +6847,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B2">
-        <v>236.10984375</v>
+        <v>368.91015625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>221.800078125</v>
+        <v>363.5703125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>219.19001953125</v>
+        <v>355.080078125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>219.19001953125</v>
+        <v>347.96044921875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B6">
-        <v>215.3303125</v>
+        <v>330.9599609375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B7">
-        <v>213.50017578125</v>
+        <v>329.96044921875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B8">
-        <v>213.2901171875</v>
+        <v>321.650390625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B9">
-        <v>212.700078125</v>
+        <v>318.67041015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B10">
-        <v>212.439921875</v>
+        <v>318.109375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B11">
-        <v>211.60984375</v>
+        <v>315.58056640625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>211.44978515625</v>
+        <v>314.9404296875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B13">
-        <v>202.5897265625</v>
+        <v>313.9697265625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>202.28982421875</v>
+        <v>313.560546875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>202.00033203125</v>
+        <v>310.2802734375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>200.01013671875</v>
+        <v>307.419677734375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B17">
-        <v>199.289921875</v>
+        <v>306.41943359375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>197.74958984375</v>
+        <v>305.8505859375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B19">
-        <v>196.330078125</v>
+        <v>302.27978515625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>195.81013671875</v>
+        <v>300.969482421875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>195.58015625</v>
+        <v>298.01025390625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B22">
-        <v>195.4396875</v>
+        <v>297.9697265625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>193.02998046875</v>
+        <v>292.6201171875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B24">
-        <v>192.240166015625</v>
+        <v>289.64990234375</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B25">
-        <v>190.820244140625</v>
+        <v>285.41943359375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B26">
-        <v>189.650029296875</v>
+        <v>282.81005859375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27">
-        <v>186.269853515625</v>
+        <v>282.439697265625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>185.58982421875</v>
+        <v>282.309814453125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B29">
-        <v>183.900029296875</v>
+        <v>280.849609375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B30">
-        <v>183.69998046875</v>
+        <v>280.5400390625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B31">
-        <v>183.680009765625</v>
+        <v>279.13037109375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B32">
-        <v>182.75994140625</v>
+        <v>274.27001953125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B33">
-        <v>180.420224609375</v>
+        <v>272.06005859375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>179.88984375</v>
+        <v>269.170166015625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B35">
-        <v>178.989970703125</v>
+        <v>268.349853515625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>177.599833984375</v>
+        <v>267.650146484375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -6730,135 +7130,135 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>174.1701171875</v>
+        <v>265.230224609375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B38">
-        <v>172.679814453125</v>
+        <v>264.56005859375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B39">
-        <v>169.3496875</v>
+        <v>261.949951171875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B40">
-        <v>165.5998828125</v>
+        <v>260.759765625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B41">
-        <v>164.710107421875</v>
+        <v>258.659912109375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>162.110107421875</v>
+        <v>257.890380859375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B43">
-        <v>162.0698046875</v>
+        <v>256.990234375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B44">
-        <v>161.7998828125</v>
+        <v>243.06982421875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="B45">
-        <v>160.960283203125</v>
+        <v>242.9697265625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B46">
-        <v>160.530126953125</v>
+        <v>241.460205078125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B47">
-        <v>159.3998828125</v>
+        <v>236.06982421875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B48">
-        <v>158.49033203125</v>
+        <v>231.530517578125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B49">
-        <v>157.82998046875</v>
+        <v>219.210205078125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B50">
-        <v>157.81005859375</v>
+        <v>208.380126953125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51">
-        <v>144.540068359375</v>
+        <v>201.510009765625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B52">
-        <v>135.040048828125</v>
+        <v>169.6600341796875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B53">
-        <v>129.40984375</v>
+        <v>165.329833984375</v>
       </c>
     </row>
   </sheetData>
@@ -6878,7 +7278,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6886,7 +7286,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6894,7 +7294,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6902,7 +7302,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6910,7 +7310,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6918,7 +7318,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6926,7 +7326,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6934,7 +7334,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6942,7 +7342,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6950,7 +7350,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6958,7 +7358,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6966,7 +7366,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6974,7 +7374,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6982,7 +7382,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6990,7 +7390,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6998,7 +7398,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -7006,7 +7406,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -7014,7 +7414,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -7022,7 +7422,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -7030,7 +7430,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -7038,7 +7438,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -7046,7 +7446,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -7054,7 +7454,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -7062,7 +7462,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -7070,7 +7470,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -7078,7 +7478,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -7086,7 +7486,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -7094,7 +7494,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -7102,7 +7502,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -7110,7 +7510,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -7118,7 +7518,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -7126,7 +7526,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -7134,7 +7534,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -7142,7 +7542,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -7150,7 +7550,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -7158,7 +7558,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -7166,7 +7566,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -7174,7 +7574,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -7182,7 +7582,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7190,7 +7590,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -7198,7 +7598,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -7206,7 +7606,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7214,7 +7614,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -7222,7 +7622,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -7230,7 +7630,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7238,7 +7638,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7246,7 +7646,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -7254,7 +7654,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -7262,7 +7662,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -7270,7 +7670,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -7278,7 +7678,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7286,7 +7686,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="69">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Rodada 8</t>
+  </si>
+  <si>
+    <t>Rodada 9</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -587,10 +590,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,10 +618,13 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -642,12 +648,15 @@
         <v>50.570068359375</v>
       </c>
       <c r="I2">
-        <v>50.570068359375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>79.14990234375</v>
+      </c>
+      <c r="J2">
+        <v>79.14990234375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -671,12 +680,15 @@
         <v>63.159912109375</v>
       </c>
       <c r="I3">
-        <v>63.159912109375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>85.5</v>
+      </c>
+      <c r="J3">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -700,12 +712,15 @@
         <v>82.9599609375</v>
       </c>
       <c r="I4">
-        <v>82.9599609375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>65.60009765625</v>
+      </c>
+      <c r="J4">
+        <v>65.60009765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -729,12 +744,15 @@
         <v>82.3701171875</v>
       </c>
       <c r="I5">
-        <v>82.3701171875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>79.60009765625</v>
+      </c>
+      <c r="J5">
+        <v>79.60009765625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -758,12 +776,15 @@
         <v>61.2099609375</v>
       </c>
       <c r="I6">
-        <v>61.2099609375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>76.43994140625</v>
+      </c>
+      <c r="J6">
+        <v>76.43994140625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -787,12 +808,15 @@
         <v>64.669921875</v>
       </c>
       <c r="I7">
-        <v>64.669921875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>63.47998046875</v>
+      </c>
+      <c r="J7">
+        <v>63.47998046875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -816,12 +840,15 @@
         <v>85.97021484375</v>
       </c>
       <c r="I8">
-        <v>85.97021484375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>76.4501953125</v>
+      </c>
+      <c r="J8">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -845,12 +872,15 @@
         <v>70.47021484375</v>
       </c>
       <c r="I9">
-        <v>70.47021484375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>74.9501953125</v>
+      </c>
+      <c r="J9">
+        <v>74.9501953125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -874,12 +904,15 @@
         <v>70.2099609375</v>
       </c>
       <c r="I10">
-        <v>70.2099609375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>63.25</v>
+      </c>
+      <c r="J10">
+        <v>63.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -905,10 +938,13 @@
       <c r="I11">
         <v>72.1201171875</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>88.0498046875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -932,12 +968,15 @@
         <v>87.1201171875</v>
       </c>
       <c r="I12">
-        <v>87.1201171875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>55.0400390625</v>
+      </c>
+      <c r="J12">
+        <v>55.0400390625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -961,12 +1000,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="I13">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>75.75</v>
+      </c>
+      <c r="J13">
+        <v>75.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -990,12 +1032,15 @@
         <v>78.97021484375</v>
       </c>
       <c r="I14">
-        <v>78.97021484375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>72.0498046875</v>
+      </c>
+      <c r="J14">
+        <v>72.0498046875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -1019,12 +1064,15 @@
         <v>50.8701171875</v>
       </c>
       <c r="I15">
-        <v>50.8701171875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>79.35009765625</v>
+      </c>
+      <c r="J15">
+        <v>79.35009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -1048,12 +1096,15 @@
         <v>68.97021484375</v>
       </c>
       <c r="I16">
-        <v>68.97021484375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>75.9501953125</v>
+      </c>
+      <c r="J16">
+        <v>75.9501953125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -1077,12 +1128,15 @@
         <v>105.8701171875</v>
       </c>
       <c r="I17">
-        <v>105.8701171875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>76.89990234375</v>
+      </c>
+      <c r="J17">
+        <v>76.89990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -1106,12 +1160,15 @@
         <v>31.6199951171875</v>
       </c>
       <c r="I18">
-        <v>31.6199951171875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>65.35009765625</v>
+      </c>
+      <c r="J18">
+        <v>65.35009765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -1135,12 +1192,15 @@
         <v>75.56982421875</v>
       </c>
       <c r="I19">
-        <v>75.56982421875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>72.2998046875</v>
+      </c>
+      <c r="J19">
+        <v>72.2998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -1164,12 +1224,15 @@
         <v>79.56982421875</v>
       </c>
       <c r="I20">
-        <v>79.56982421875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>66.97998046875</v>
+      </c>
+      <c r="J20">
+        <v>66.97998046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -1193,12 +1256,15 @@
         <v>39.969970703125</v>
       </c>
       <c r="I21">
-        <v>39.969970703125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>60.5</v>
+      </c>
+      <c r="J21">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -1222,12 +1288,15 @@
         <v>82.81005859375</v>
       </c>
       <c r="I22">
-        <v>82.81005859375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>91.39990234375</v>
+      </c>
+      <c r="J22">
+        <v>91.39990234375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1251,12 +1320,15 @@
         <v>49.469970703125</v>
       </c>
       <c r="I23">
-        <v>49.469970703125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>57.429931640625</v>
+      </c>
+      <c r="J23">
+        <v>57.429931640625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1280,12 +1352,15 @@
         <v>77.06982421875</v>
       </c>
       <c r="I24">
-        <v>77.06982421875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>80.0498046875</v>
+      </c>
+      <c r="J24">
+        <v>80.0498046875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1309,12 +1384,15 @@
         <v>76.97021484375</v>
       </c>
       <c r="I25">
-        <v>76.97021484375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>84.85009765625</v>
+      </c>
+      <c r="J25">
+        <v>84.85009765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1338,12 +1416,15 @@
         <v>81.56982421875</v>
       </c>
       <c r="I26">
-        <v>81.56982421875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>73.35009765625</v>
+      </c>
+      <c r="J26">
+        <v>73.35009765625</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1367,12 +1448,15 @@
         <v>64.47021484375</v>
       </c>
       <c r="I27">
-        <v>64.47021484375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>73.4501953125</v>
+      </c>
+      <c r="J27">
+        <v>73.4501953125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1396,12 +1480,15 @@
         <v>78.91015625</v>
       </c>
       <c r="I28">
-        <v>78.91015625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>45.3701171875</v>
+      </c>
+      <c r="J28">
+        <v>45.3701171875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1425,12 +1512,15 @@
         <v>79.919921875</v>
       </c>
       <c r="I29">
-        <v>79.919921875</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>72.25</v>
+      </c>
+      <c r="J29">
+        <v>72.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1454,12 +1544,15 @@
         <v>53.0400390625</v>
       </c>
       <c r="I30">
-        <v>53.0400390625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>73.14013671875</v>
+      </c>
+      <c r="J30">
+        <v>73.14013671875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1483,12 +1576,15 @@
         <v>70.60986328125</v>
       </c>
       <c r="I31">
-        <v>70.60986328125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>65.60009765625</v>
+      </c>
+      <c r="J31">
+        <v>65.60009765625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1512,12 +1608,15 @@
         <v>58.669921875</v>
       </c>
       <c r="I32">
-        <v>58.669921875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>45.699951171875</v>
+      </c>
+      <c r="J32">
+        <v>45.699951171875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1541,12 +1640,15 @@
         <v>94.8701171875</v>
       </c>
       <c r="I33">
-        <v>94.8701171875</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>74.0498046875</v>
+      </c>
+      <c r="J33">
+        <v>74.0498046875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1570,12 +1672,15 @@
         <v>46.570068359375</v>
       </c>
       <c r="I34">
-        <v>46.570068359375</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>74.83984375</v>
+      </c>
+      <c r="J34">
+        <v>74.83984375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -1599,12 +1704,15 @@
         <v>61.570068359375</v>
       </c>
       <c r="I35">
-        <v>61.570068359375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>88.25</v>
+      </c>
+      <c r="J35">
+        <v>88.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -1628,12 +1736,15 @@
         <v>60.070068359375</v>
       </c>
       <c r="I36">
-        <v>60.070068359375</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>79.85009765625</v>
+      </c>
+      <c r="J36">
+        <v>79.85009765625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -1657,12 +1768,15 @@
         <v>82.56982421875</v>
       </c>
       <c r="I37">
-        <v>82.56982421875</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>76.25</v>
+      </c>
+      <c r="J37">
+        <v>76.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -1686,12 +1800,15 @@
         <v>12.54998779296875</v>
       </c>
       <c r="I38">
-        <v>12.54998779296875</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>63.949951171875</v>
+      </c>
+      <c r="J38">
+        <v>63.949951171875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -1715,12 +1832,15 @@
         <v>75.06005859375</v>
       </c>
       <c r="I39">
-        <v>75.06005859375</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>26.719970703125</v>
+      </c>
+      <c r="J39">
+        <v>26.719970703125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -1744,12 +1864,15 @@
         <v>59.56005859375</v>
       </c>
       <c r="I40">
-        <v>59.56005859375</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>75.0498046875</v>
+      </c>
+      <c r="J40">
+        <v>75.0498046875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -1773,12 +1896,15 @@
         <v>43.800048828125</v>
       </c>
       <c r="I41">
-        <v>43.800048828125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>58.85009765625</v>
+      </c>
+      <c r="J41">
+        <v>58.85009765625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -1802,12 +1928,15 @@
         <v>50.969970703125</v>
       </c>
       <c r="I42">
-        <v>50.969970703125</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>74.85009765625</v>
+      </c>
+      <c r="J42">
+        <v>74.85009765625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -1831,12 +1960,15 @@
         <v>76.06982421875</v>
       </c>
       <c r="I43">
-        <v>76.06982421875</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>78.0498046875</v>
+      </c>
+      <c r="J43">
+        <v>78.0498046875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -1860,12 +1992,15 @@
         <v>58.8701171875</v>
       </c>
       <c r="I44">
-        <v>58.8701171875</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>81.25</v>
+      </c>
+      <c r="J44">
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -1889,12 +2024,15 @@
         <v>79.47021484375</v>
       </c>
       <c r="I45">
-        <v>79.47021484375</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>80.5498046875</v>
+      </c>
+      <c r="J45">
+        <v>80.5498046875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -1918,12 +2056,15 @@
         <v>77.419921875</v>
       </c>
       <c r="I46">
-        <v>77.419921875</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>54.360107421875</v>
+      </c>
+      <c r="J46">
+        <v>54.360107421875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -1947,12 +2088,15 @@
         <v>87.009765625</v>
       </c>
       <c r="I47">
-        <v>87.009765625</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>69.89990234375</v>
+      </c>
+      <c r="J47">
+        <v>69.89990234375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -1976,12 +2120,15 @@
         <v>71.3701171875</v>
       </c>
       <c r="I48">
-        <v>71.3701171875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>80.75</v>
+      </c>
+      <c r="J48">
+        <v>80.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -2005,12 +2152,15 @@
         <v>60.27001953125</v>
       </c>
       <c r="I49">
-        <v>60.27001953125</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>75</v>
+      </c>
+      <c r="J49">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -2034,12 +2184,15 @@
         <v>76.97021484375</v>
       </c>
       <c r="I50">
-        <v>76.97021484375</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>76.4501953125</v>
+      </c>
+      <c r="J50">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -2063,12 +2216,15 @@
         <v>56.669921875</v>
       </c>
       <c r="I51">
-        <v>56.669921875</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>67.64990234375</v>
+      </c>
+      <c r="J51">
+        <v>67.64990234375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -2092,12 +2248,15 @@
         <v>46.3701171875</v>
       </c>
       <c r="I52">
-        <v>46.3701171875</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>84.25</v>
+      </c>
+      <c r="J52">
+        <v>84.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -2121,12 +2280,15 @@
         <v>67.33984375</v>
       </c>
       <c r="I53">
-        <v>67.33984375</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>94.31982421875</v>
+      </c>
+      <c r="J53">
+        <v>94.31982421875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2150,6 +2312,9 @@
         <v>0</v>
       </c>
       <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
         <v>0</v>
       </c>
     </row>
@@ -2170,7 +2335,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2178,7 +2343,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2186,7 +2351,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2194,7 +2359,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2202,7 +2367,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2210,7 +2375,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2218,7 +2383,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2226,7 +2391,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2234,7 +2399,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2242,7 +2407,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2250,7 +2415,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2258,7 +2423,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2266,7 +2431,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2274,7 +2439,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2282,7 +2447,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2290,7 +2455,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2298,7 +2463,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2306,7 +2471,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2314,7 +2479,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2322,7 +2487,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2330,7 +2495,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2338,7 +2503,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2346,7 +2511,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2354,7 +2519,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2362,7 +2527,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2370,7 +2535,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2378,7 +2543,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2386,7 +2551,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2394,7 +2559,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2402,7 +2567,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2410,7 +2575,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2418,7 +2583,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2426,7 +2591,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2434,7 +2599,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2442,7 +2607,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2450,7 +2615,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2458,7 +2623,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2466,7 +2631,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2474,7 +2639,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2482,7 +2647,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2490,7 +2655,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2498,7 +2663,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2506,7 +2671,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2514,7 +2679,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2522,7 +2687,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2530,7 +2695,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2538,7 +2703,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2546,7 +2711,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2554,7 +2719,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2562,7 +2727,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2570,7 +2735,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2578,7 +2743,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2601,7 +2766,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2609,7 +2774,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2617,7 +2782,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2625,7 +2790,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2633,7 +2798,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2641,7 +2806,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2649,7 +2814,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2657,7 +2822,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2665,7 +2830,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2673,7 +2838,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2681,7 +2846,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2689,7 +2854,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2697,7 +2862,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2705,7 +2870,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2713,7 +2878,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2721,7 +2886,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2729,7 +2894,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2737,7 +2902,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2745,7 +2910,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2753,7 +2918,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2761,7 +2926,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2769,7 +2934,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2777,7 +2942,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2785,7 +2950,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2793,7 +2958,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2801,7 +2966,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2809,7 +2974,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2817,7 +2982,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2825,7 +2990,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2833,7 +2998,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2841,7 +3006,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2849,7 +3014,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2857,7 +3022,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2865,7 +3030,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2873,7 +3038,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2881,7 +3046,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2889,7 +3054,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2897,7 +3062,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2905,7 +3070,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2913,7 +3078,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2921,7 +3086,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2929,7 +3094,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2937,7 +3102,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2945,7 +3110,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2953,7 +3118,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2961,7 +3126,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2969,7 +3134,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2977,7 +3142,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2985,7 +3150,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2993,7 +3158,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3001,7 +3166,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3009,7 +3174,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3027,27 +3192,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -3055,13 +3220,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -3069,13 +3234,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -3083,13 +3248,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -3097,13 +3262,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -3111,13 +3276,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -3125,13 +3290,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -3139,13 +3304,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -3153,13 +3318,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -3167,13 +3332,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
@@ -3181,72 +3346,72 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>368.91015625</v>
+        <v>352.31005859375</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>363.5703125</v>
+        <v>348.08984375</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>355.080078125</v>
+        <v>338.4404296875</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D15">
-        <v>347.96044921875</v>
+        <v>334.60009765625</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D16">
-        <v>330.9599609375</v>
+        <v>329.4404296875</v>
       </c>
     </row>
   </sheetData>
@@ -3265,10 +3430,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3293,10 +3458,13 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -3320,12 +3488,15 @@
         <v>50.570068359375</v>
       </c>
       <c r="I2">
-        <v>50.570068359375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>79.14990234375</v>
+      </c>
+      <c r="J2">
+        <v>79.14990234375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -3349,12 +3520,15 @@
         <v>63.159912109375</v>
       </c>
       <c r="I3">
-        <v>63.159912109375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>85.5</v>
+      </c>
+      <c r="J3">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -3378,12 +3552,15 @@
         <v>82.9599609375</v>
       </c>
       <c r="I4">
-        <v>82.9599609375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>65.60009765625</v>
+      </c>
+      <c r="J4">
+        <v>65.60009765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -3407,12 +3584,15 @@
         <v>82.3701171875</v>
       </c>
       <c r="I5">
-        <v>82.3701171875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>79.60009765625</v>
+      </c>
+      <c r="J5">
+        <v>79.60009765625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -3436,12 +3616,15 @@
         <v>61.2099609375</v>
       </c>
       <c r="I6">
-        <v>61.2099609375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>76.43994140625</v>
+      </c>
+      <c r="J6">
+        <v>76.43994140625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -3465,12 +3648,15 @@
         <v>64.669921875</v>
       </c>
       <c r="I7">
-        <v>64.669921875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>63.47998046875</v>
+      </c>
+      <c r="J7">
+        <v>63.47998046875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -3494,12 +3680,15 @@
         <v>85.97021484375</v>
       </c>
       <c r="I8">
-        <v>85.97021484375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>76.4501953125</v>
+      </c>
+      <c r="J8">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -3523,12 +3712,15 @@
         <v>70.47021484375</v>
       </c>
       <c r="I9">
-        <v>70.47021484375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>74.9501953125</v>
+      </c>
+      <c r="J9">
+        <v>74.9501953125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -3552,12 +3744,15 @@
         <v>70.2099609375</v>
       </c>
       <c r="I10">
-        <v>70.2099609375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>63.25</v>
+      </c>
+      <c r="J10">
+        <v>63.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -3583,10 +3778,13 @@
       <c r="I11">
         <v>72.1201171875</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>88.0498046875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -3610,12 +3808,15 @@
         <v>87.1201171875</v>
       </c>
       <c r="I12">
-        <v>87.1201171875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>55.0400390625</v>
+      </c>
+      <c r="J12">
+        <v>55.0400390625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -3639,12 +3840,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="I13">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>75.75</v>
+      </c>
+      <c r="J13">
+        <v>75.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -3668,12 +3872,15 @@
         <v>78.97021484375</v>
       </c>
       <c r="I14">
-        <v>78.97021484375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>72.0498046875</v>
+      </c>
+      <c r="J14">
+        <v>72.0498046875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>37.820068359375</v>
@@ -3697,12 +3904,15 @@
         <v>50.8701171875</v>
       </c>
       <c r="I15">
-        <v>50.8701171875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>79.35009765625</v>
+      </c>
+      <c r="J15">
+        <v>79.35009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>56.260009765625</v>
@@ -3726,12 +3936,15 @@
         <v>68.97021484375</v>
       </c>
       <c r="I16">
-        <v>68.97021484375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>75.9501953125</v>
+      </c>
+      <c r="J16">
+        <v>75.9501953125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>63.89990234375</v>
@@ -3755,12 +3968,15 @@
         <v>105.8701171875</v>
       </c>
       <c r="I17">
-        <v>105.8701171875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>76.89990234375</v>
+      </c>
+      <c r="J17">
+        <v>76.89990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>44.06005859375</v>
@@ -3784,12 +4000,15 @@
         <v>31.6199951171875</v>
       </c>
       <c r="I18">
-        <v>31.6199951171875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>65.35009765625</v>
+      </c>
+      <c r="J18">
+        <v>65.35009765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>54.159912109375</v>
@@ -3813,12 +4032,15 @@
         <v>75.56982421875</v>
       </c>
       <c r="I19">
-        <v>75.56982421875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>72.2998046875</v>
+      </c>
+      <c r="J19">
+        <v>72.2998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>40.60009765625</v>
@@ -3842,12 +4064,15 @@
         <v>79.56982421875</v>
       </c>
       <c r="I20">
-        <v>79.56982421875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>66.97998046875</v>
+      </c>
+      <c r="J20">
+        <v>66.97998046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>57.449951171875</v>
@@ -3871,12 +4096,15 @@
         <v>39.969970703125</v>
       </c>
       <c r="I21">
-        <v>39.969970703125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>60.5</v>
+      </c>
+      <c r="J21">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>57.60009765625</v>
@@ -3900,12 +4128,15 @@
         <v>82.81005859375</v>
       </c>
       <c r="I22">
-        <v>82.81005859375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>91.39990234375</v>
+      </c>
+      <c r="J22">
+        <v>91.39990234375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -3929,12 +4160,15 @@
         <v>49.469970703125</v>
       </c>
       <c r="I23">
-        <v>49.469970703125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>57.429931640625</v>
+      </c>
+      <c r="J23">
+        <v>57.429931640625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -3958,12 +4192,15 @@
         <v>77.06982421875</v>
       </c>
       <c r="I24">
-        <v>77.06982421875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>80.0498046875</v>
+      </c>
+      <c r="J24">
+        <v>80.0498046875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -3987,12 +4224,15 @@
         <v>76.97021484375</v>
       </c>
       <c r="I25">
-        <v>76.97021484375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>84.85009765625</v>
+      </c>
+      <c r="J25">
+        <v>84.85009765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -4016,12 +4256,15 @@
         <v>81.56982421875</v>
       </c>
       <c r="I26">
-        <v>81.56982421875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>73.35009765625</v>
+      </c>
+      <c r="J26">
+        <v>73.35009765625</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -4045,12 +4288,15 @@
         <v>64.47021484375</v>
       </c>
       <c r="I27">
-        <v>64.47021484375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>73.4501953125</v>
+      </c>
+      <c r="J27">
+        <v>73.4501953125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -4074,12 +4320,15 @@
         <v>78.91015625</v>
       </c>
       <c r="I28">
-        <v>78.91015625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>45.3701171875</v>
+      </c>
+      <c r="J28">
+        <v>45.3701171875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -4103,12 +4352,15 @@
         <v>79.919921875</v>
       </c>
       <c r="I29">
-        <v>79.919921875</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>72.25</v>
+      </c>
+      <c r="J29">
+        <v>72.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -4132,12 +4384,15 @@
         <v>53.0400390625</v>
       </c>
       <c r="I30">
-        <v>53.0400390625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>73.14013671875</v>
+      </c>
+      <c r="J30">
+        <v>73.14013671875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -4161,12 +4416,15 @@
         <v>70.60986328125</v>
       </c>
       <c r="I31">
-        <v>70.60986328125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>65.60009765625</v>
+      </c>
+      <c r="J31">
+        <v>65.60009765625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -4190,12 +4448,15 @@
         <v>58.669921875</v>
       </c>
       <c r="I32">
-        <v>58.669921875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>45.699951171875</v>
+      </c>
+      <c r="J32">
+        <v>45.699951171875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -4219,12 +4480,15 @@
         <v>94.8701171875</v>
       </c>
       <c r="I33">
-        <v>94.8701171875</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>74.0498046875</v>
+      </c>
+      <c r="J33">
+        <v>74.0498046875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -4248,12 +4512,15 @@
         <v>46.570068359375</v>
       </c>
       <c r="I34">
-        <v>46.570068359375</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>74.83984375</v>
+      </c>
+      <c r="J34">
+        <v>74.83984375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -4277,12 +4544,15 @@
         <v>61.570068359375</v>
       </c>
       <c r="I35">
-        <v>61.570068359375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>88.25</v>
+      </c>
+      <c r="J35">
+        <v>88.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -4306,12 +4576,15 @@
         <v>60.070068359375</v>
       </c>
       <c r="I36">
-        <v>60.070068359375</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>79.85009765625</v>
+      </c>
+      <c r="J36">
+        <v>79.85009765625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -4335,12 +4608,15 @@
         <v>82.56982421875</v>
       </c>
       <c r="I37">
-        <v>82.56982421875</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>76.25</v>
+      </c>
+      <c r="J37">
+        <v>76.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -4364,12 +4640,15 @@
         <v>12.54998779296875</v>
       </c>
       <c r="I38">
-        <v>12.54998779296875</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>63.949951171875</v>
+      </c>
+      <c r="J38">
+        <v>63.949951171875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -4393,12 +4672,15 @@
         <v>75.06005859375</v>
       </c>
       <c r="I39">
-        <v>75.06005859375</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>26.719970703125</v>
+      </c>
+      <c r="J39">
+        <v>26.719970703125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -4422,12 +4704,15 @@
         <v>59.56005859375</v>
       </c>
       <c r="I40">
-        <v>59.56005859375</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>75.0498046875</v>
+      </c>
+      <c r="J40">
+        <v>75.0498046875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -4451,12 +4736,15 @@
         <v>43.800048828125</v>
       </c>
       <c r="I41">
-        <v>43.800048828125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>58.85009765625</v>
+      </c>
+      <c r="J41">
+        <v>58.85009765625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -4480,12 +4768,15 @@
         <v>50.969970703125</v>
       </c>
       <c r="I42">
-        <v>50.969970703125</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>74.85009765625</v>
+      </c>
+      <c r="J42">
+        <v>74.85009765625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -4509,12 +4800,15 @@
         <v>76.06982421875</v>
       </c>
       <c r="I43">
-        <v>76.06982421875</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>78.0498046875</v>
+      </c>
+      <c r="J43">
+        <v>78.0498046875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -4538,12 +4832,15 @@
         <v>58.8701171875</v>
       </c>
       <c r="I44">
-        <v>58.8701171875</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>81.25</v>
+      </c>
+      <c r="J44">
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -4567,12 +4864,15 @@
         <v>79.47021484375</v>
       </c>
       <c r="I45">
-        <v>79.47021484375</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>80.5498046875</v>
+      </c>
+      <c r="J45">
+        <v>80.5498046875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -4596,12 +4896,15 @@
         <v>77.419921875</v>
       </c>
       <c r="I46">
-        <v>77.419921875</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>54.360107421875</v>
+      </c>
+      <c r="J46">
+        <v>54.360107421875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -4625,12 +4928,15 @@
         <v>87.009765625</v>
       </c>
       <c r="I47">
-        <v>87.009765625</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>69.89990234375</v>
+      </c>
+      <c r="J47">
+        <v>69.89990234375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -4654,12 +4960,15 @@
         <v>71.3701171875</v>
       </c>
       <c r="I48">
-        <v>71.3701171875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>80.75</v>
+      </c>
+      <c r="J48">
+        <v>80.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -4683,12 +4992,15 @@
         <v>60.27001953125</v>
       </c>
       <c r="I49">
-        <v>60.27001953125</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>75</v>
+      </c>
+      <c r="J49">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -4712,12 +5024,15 @@
         <v>76.97021484375</v>
       </c>
       <c r="I50">
-        <v>76.97021484375</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>76.4501953125</v>
+      </c>
+      <c r="J50">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -4741,12 +5056,15 @@
         <v>56.669921875</v>
       </c>
       <c r="I51">
-        <v>56.669921875</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>67.64990234375</v>
+      </c>
+      <c r="J51">
+        <v>67.64990234375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -4770,12 +5088,15 @@
         <v>46.3701171875</v>
       </c>
       <c r="I52">
-        <v>46.3701171875</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>84.25</v>
+      </c>
+      <c r="J52">
+        <v>84.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>55.89990234375</v>
@@ -4799,12 +5120,15 @@
         <v>67.33984375</v>
       </c>
       <c r="I53">
-        <v>67.33984375</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>94.31982421875</v>
+      </c>
+      <c r="J53">
+        <v>94.31982421875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -4828,6 +5152,9 @@
         <v>0</v>
       </c>
       <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
         <v>0</v>
       </c>
     </row>
@@ -4848,418 +5175,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>692.1298828125</v>
+        <v>768.9599609375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
-        <v>686.88037109375</v>
+        <v>740.10986328125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>686.2998046875</v>
+        <v>734.2294921875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>662.6103515625</v>
+        <v>729.54052734375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B6">
-        <v>652.3701171875</v>
+        <v>727.04052734375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>651.1103515625</v>
+        <v>721.8701171875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B8">
-        <v>635.349853515625</v>
+        <v>717.539794921875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9">
-        <v>623.93017578125</v>
+        <v>714.06005859375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10">
-        <v>622.3193359375</v>
+        <v>702.34912109375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B11">
-        <v>621.88037109375</v>
+        <v>700.480224609375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>615.1298828125</v>
+        <v>694.56005859375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B13">
-        <v>602.5703125</v>
+        <v>694.499755859375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B14">
-        <v>601.769775390625</v>
+        <v>684.19970703125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>601.6005859375</v>
+        <v>683.08935546875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B16">
-        <v>600.999755859375</v>
+        <v>681.360107421875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B17">
-        <v>600.749755859375</v>
+        <v>676.239990234375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>600.0595703125</v>
+        <v>675.330078125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>599.83935546875</v>
+        <v>670.779541015625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B20">
-        <v>598.429931640625</v>
+        <v>669.779541015625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>595.409912109375</v>
+        <v>668.329833984375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="B22">
-        <v>590.780029296875</v>
+        <v>668.090087890625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>585.138916015625</v>
+        <v>666.72998046875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B24">
-        <v>585.00927734375</v>
+        <v>664.41943359375</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B25">
-        <v>584.570068359375</v>
+        <v>661.59033203125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>580.280029296875</v>
+        <v>659.97998046875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27">
-        <v>580.239990234375</v>
+        <v>655.069091796875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B28">
-        <v>579.16015625</v>
+        <v>653.789794921875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B29">
-        <v>578.360107421875</v>
+        <v>653.40966796875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B30">
-        <v>576.189697265625</v>
+        <v>651.58984375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>569.1796875</v>
+        <v>643.379638671875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="B32">
-        <v>563.029541015625</v>
+        <v>641.29931640625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B33">
-        <v>556.32958984375</v>
+        <v>639.020263671875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B34">
-        <v>556.210205078125</v>
+        <v>636.780029296875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B35">
-        <v>545.050048828125</v>
+        <v>636.10009765625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>543.860107421875</v>
+        <v>633.2294921875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B37">
-        <v>540.27001953125</v>
+        <v>626.02978515625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B38">
-        <v>539.600341796875</v>
+        <v>623.7001953125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B39">
-        <v>538.459716796875</v>
+        <v>618.61962890625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B40">
-        <v>536.83935546875</v>
+        <v>617.43994140625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="B41">
-        <v>528.260009765625</v>
+        <v>597.26953125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B42">
-        <v>527.299560546875</v>
+        <v>594.329833984375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B43">
-        <v>524.070068359375</v>
+        <v>592.849853515625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B44">
-        <v>518.6396484375</v>
+        <v>571.249755859375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B45">
-        <v>513.81005859375</v>
+        <v>569.5693359375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B46">
-        <v>511.9296875</v>
+        <v>561.649658203125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B47">
-        <v>496.259765625</v>
+        <v>556.78076171875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B48">
-        <v>490.2197265625</v>
+        <v>551.430419921875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B49">
-        <v>448.95068359375</v>
+        <v>541.7597045898438</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B50">
-        <v>446.409912109375</v>
+        <v>539.650146484375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B51">
-        <v>434.599853515625</v>
+        <v>534.590087890625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B52">
-        <v>426.4097900390625</v>
+        <v>533.6800537109375</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B53">
-        <v>388.8402099609375</v>
+        <v>462.7403564453125</v>
       </c>
     </row>
   </sheetData>
@@ -5274,267 +5601,267 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5554,7 +5881,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5562,7 +5889,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5570,7 +5897,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5578,7 +5905,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5586,7 +5913,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5594,7 +5921,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5602,7 +5929,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5610,7 +5937,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5618,7 +5945,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5626,7 +5953,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5634,7 +5961,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5642,7 +5969,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5650,7 +5977,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5658,7 +5985,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5666,7 +5993,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -5674,7 +6001,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -5682,7 +6009,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -5690,7 +6017,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5698,7 +6025,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5706,7 +6033,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5714,7 +6041,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5722,7 +6049,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -5730,7 +6057,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -5738,7 +6065,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -5746,7 +6073,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -5754,7 +6081,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -5762,7 +6089,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -5770,7 +6097,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -5778,7 +6105,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -5786,7 +6113,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -5794,7 +6121,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5802,7 +6129,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -5810,7 +6137,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -5818,7 +6145,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5826,7 +6153,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -5834,7 +6161,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5842,7 +6169,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5850,7 +6177,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -5858,7 +6185,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5866,7 +6193,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5874,7 +6201,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5882,7 +6209,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5890,7 +6217,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -5898,7 +6225,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -5906,7 +6233,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -5914,7 +6241,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5922,7 +6249,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -5930,7 +6257,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -5938,7 +6265,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -5946,7 +6273,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -5954,7 +6281,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5962,7 +6289,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -5985,7 +6312,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -5993,7 +6320,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -6001,7 +6328,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -6009,7 +6336,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -6017,7 +6344,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -6025,7 +6352,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -6033,7 +6360,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -6041,7 +6368,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -6049,7 +6376,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -6057,7 +6384,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -6065,7 +6392,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -6073,7 +6400,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -6081,7 +6408,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -6089,7 +6416,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -6097,7 +6424,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -6105,7 +6432,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -6113,7 +6440,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -6121,7 +6448,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -6129,7 +6456,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -6137,7 +6464,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -6145,7 +6472,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -6153,7 +6480,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -6161,7 +6488,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -6169,7 +6496,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -6177,7 +6504,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -6185,7 +6512,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -6193,7 +6520,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -6201,7 +6528,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -6209,7 +6536,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -6217,7 +6544,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -6225,7 +6552,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -6233,7 +6560,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -6241,7 +6568,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -6249,7 +6576,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -6257,7 +6584,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -6265,7 +6592,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -6273,7 +6600,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -6281,7 +6608,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -6289,7 +6616,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -6297,7 +6624,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -6305,7 +6632,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -6313,7 +6640,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -6321,7 +6648,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -6329,7 +6656,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -6337,7 +6664,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -6345,7 +6672,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -6353,7 +6680,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B48">
         <v>44.06005859375</v>
@@ -6361,7 +6688,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49">
         <v>43.510009765625</v>
@@ -6369,7 +6696,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50">
         <v>42.9599609375</v>
@@ -6377,7 +6704,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B51">
         <v>40.60009765625</v>
@@ -6385,7 +6712,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52">
         <v>38.260009765625</v>
@@ -6393,7 +6720,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B53">
         <v>37.820068359375</v>
@@ -6416,7 +6743,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -6424,7 +6751,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -6432,7 +6759,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -6440,7 +6767,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -6448,7 +6775,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -6456,7 +6783,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -6464,7 +6791,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -6472,7 +6799,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -6480,7 +6807,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -6488,7 +6815,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -6496,7 +6823,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -6504,7 +6831,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -6512,7 +6839,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -6520,7 +6847,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -6528,7 +6855,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -6536,7 +6863,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -6544,7 +6871,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -6552,7 +6879,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -6560,7 +6887,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -6568,7 +6895,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -6576,7 +6903,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -6584,7 +6911,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -6592,7 +6919,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -6600,7 +6927,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -6608,7 +6935,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>231.8896484375</v>
@@ -6616,7 +6943,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>231.259765625</v>
@@ -6624,7 +6951,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>227.90966796875</v>
@@ -6632,7 +6959,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B29">
         <v>227.8095703125</v>
@@ -6640,7 +6967,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30">
         <v>225.2099609375</v>
@@ -6648,7 +6975,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31">
         <v>225.02978515625</v>
@@ -6656,7 +6983,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B32">
         <v>224.409912109375</v>
@@ -6664,7 +6991,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>222.49951171875</v>
@@ -6672,7 +6999,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>219.469482421875</v>
@@ -6680,7 +7007,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
         <v>218.419921875</v>
@@ -6688,7 +7015,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B36">
         <v>216.3896484375</v>
@@ -6696,7 +7023,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B37">
         <v>216.030517578125</v>
@@ -6704,7 +7031,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>215.5498046875</v>
@@ -6712,7 +7039,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39">
         <v>212.2099609375</v>
@@ -6720,7 +7047,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40">
         <v>211.239990234375</v>
@@ -6728,7 +7055,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41">
         <v>209.509765625</v>
@@ -6736,7 +7063,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42">
         <v>206.1201171875</v>
@@ -6744,7 +7071,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>205.58984375</v>
@@ -6752,7 +7079,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>204.8798828125</v>
@@ -6760,7 +7087,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45">
         <v>199.2001953125</v>
@@ -6768,7 +7095,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>198.499755859375</v>
@@ -6776,7 +7103,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B47">
         <v>197.369873046875</v>
@@ -6784,7 +7111,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48">
         <v>191.85986328125</v>
@@ -6792,7 +7119,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>187.64990234375</v>
@@ -6800,7 +7127,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B50">
         <v>186.4697265625</v>
@@ -6808,7 +7135,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B51">
         <v>179.60009765625</v>
@@ -6816,7 +7143,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52">
         <v>159.43994140625</v>
@@ -6824,7 +7151,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
@@ -6847,418 +7174,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>368.91015625</v>
+        <v>352.31005859375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B3">
-        <v>363.5703125</v>
+        <v>348.08984375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>355.080078125</v>
+        <v>338.4404296875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>347.96044921875</v>
+        <v>334.60009765625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B6">
-        <v>330.9599609375</v>
+        <v>329.4404296875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>329.96044921875</v>
+        <v>328.05029296875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B8">
-        <v>321.650390625</v>
+        <v>323.5302734375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>318.67041015625</v>
+        <v>318.04052734375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>318.109375</v>
+        <v>317.26025390625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11">
-        <v>315.58056640625</v>
+        <v>316.66015625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B12">
-        <v>314.9404296875</v>
+        <v>315.94970703125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B13">
-        <v>313.9697265625</v>
+        <v>303.949462890625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="B14">
-        <v>313.560546875</v>
+        <v>300.99951171875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>310.2802734375</v>
+        <v>300.5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>307.419677734375</v>
+        <v>300.099609375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>306.41943359375</v>
+        <v>299.199951171875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B18">
-        <v>305.8505859375</v>
+        <v>299.009765625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19">
-        <v>302.27978515625</v>
+        <v>298.93017578125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>300.969482421875</v>
+        <v>298.8798828125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>298.01025390625</v>
+        <v>296.07958984375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B22">
-        <v>297.9697265625</v>
+        <v>295.85009765625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B23">
-        <v>292.6201171875</v>
+        <v>294.43994140625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B24">
-        <v>289.64990234375</v>
+        <v>293.139892578125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B25">
-        <v>285.41943359375</v>
+        <v>290.2998046875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B26">
-        <v>282.81005859375</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B27">
-        <v>282.439697265625</v>
+        <v>288.1103515625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>282.309814453125</v>
+        <v>288.1103515625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>280.849609375</v>
+        <v>287.43017578125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>280.5400390625</v>
+        <v>286.16015625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B31">
-        <v>279.13037109375</v>
+        <v>285.639892578125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B32">
-        <v>274.27001953125</v>
+        <v>284.639892578125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B33">
-        <v>272.06005859375</v>
+        <v>284.2900390625</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B34">
-        <v>269.170166015625</v>
+        <v>284.2294921875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B35">
-        <v>268.349853515625</v>
+        <v>282.68994140625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="B36">
-        <v>267.650146484375</v>
+        <v>280.650390625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B37">
-        <v>265.230224609375</v>
+        <v>280.5400390625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="B38">
-        <v>264.56005859375</v>
+        <v>279.340087890625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>261.949951171875</v>
+        <v>277.80029296875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B40">
-        <v>260.759765625</v>
+        <v>276.829833984375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B41">
-        <v>258.659912109375</v>
+        <v>272.47998046875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B42">
-        <v>257.890380859375</v>
+        <v>269.719970703125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B43">
-        <v>256.990234375</v>
+        <v>260.010498046875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B44">
-        <v>243.06982421875</v>
+        <v>259.3798828125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B45">
-        <v>242.9697265625</v>
+        <v>253.94970703125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B46">
-        <v>241.460205078125</v>
+        <v>244.02978515625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B47">
-        <v>236.06982421875</v>
+        <v>234.26025390625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B48">
-        <v>231.530517578125</v>
+        <v>230.099853515625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B49">
-        <v>219.210205078125</v>
+        <v>228.480224609375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B50">
-        <v>208.380126953125</v>
+        <v>222.0400390625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B51">
-        <v>201.510009765625</v>
+        <v>221.0599975585938</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B52">
-        <v>169.6600341796875</v>
+        <v>216.89013671875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B53">
-        <v>165.329833984375</v>
+        <v>199.0599365234375</v>
       </c>
     </row>
   </sheetData>
@@ -7278,418 +7605,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>94.31982421875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>91.39990234375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>88.0498046875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>84.85009765625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>80.5498046875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>80.0498046875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>79.85009765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>79.60009765625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>79.35009765625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>79.14990234375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>78.0498046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>76.89990234375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>76.4501953125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>76.4501953125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>76.43994140625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>75.9501953125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>75.0498046875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>74.9501953125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>74.85009765625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>74.83984375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>74.0498046875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>73.4501953125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>73.35009765625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>73.14013671875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>72.2998046875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>72.0498046875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>69.89990234375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>67.64990234375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>66.97998046875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>65.60009765625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>65.60009765625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>65.35009765625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>63.949951171875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>63.47998046875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>58.85009765625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>57.429931640625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>55.0400390625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>54.360107421875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>45.699951171875</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>45.3701171875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>26.719970703125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -936,7 +936,7 @@
         <v>72.1201171875</v>
       </c>
       <c r="I11">
-        <v>72.1201171875</v>
+        <v>88.0498046875</v>
       </c>
       <c r="J11">
         <v>88.0498046875</v>
@@ -3776,7 +3776,7 @@
         <v>72.1201171875</v>
       </c>
       <c r="I11">
-        <v>72.1201171875</v>
+        <v>88.0498046875</v>
       </c>
       <c r="J11">
         <v>88.0498046875</v>
@@ -5271,66 +5271,66 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>684.19970703125</v>
+        <v>684.259521484375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B15">
-        <v>683.08935546875</v>
+        <v>684.19970703125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>681.360107421875</v>
+        <v>683.08935546875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>676.239990234375</v>
+        <v>681.360107421875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B18">
-        <v>675.330078125</v>
+        <v>676.239990234375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>670.779541015625</v>
+        <v>675.330078125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B20">
-        <v>669.779541015625</v>
+        <v>670.779541015625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B21">
-        <v>668.329833984375</v>
+        <v>669.779541015625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -7326,63 +7326,63 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>296.07958984375</v>
+        <v>296.4697265625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B22">
-        <v>295.85009765625</v>
+        <v>296.07958984375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B23">
-        <v>294.43994140625</v>
+        <v>295.85009765625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B24">
-        <v>293.139892578125</v>
+        <v>294.43994140625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B25">
-        <v>290.2998046875</v>
+        <v>293.139892578125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B26">
-        <v>289</v>
+        <v>290.2998046875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B27">
-        <v>288.1103515625</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>288.1103515625</v>
@@ -7390,74 +7390,74 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B29">
-        <v>287.43017578125</v>
+        <v>288.1103515625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30">
-        <v>286.16015625</v>
+        <v>287.43017578125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>285.639892578125</v>
+        <v>286.16015625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B32">
-        <v>284.639892578125</v>
+        <v>285.639892578125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>284.2900390625</v>
+        <v>284.639892578125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B34">
-        <v>284.2294921875</v>
+        <v>284.2900390625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B35">
-        <v>282.68994140625</v>
+        <v>284.2294921875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B36">
-        <v>280.650390625</v>
+        <v>282.68994140625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B37">
-        <v>280.5400390625</v>
+        <v>280.650390625</v>
       </c>
     </row>
     <row r="38" spans="1:2">

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="70">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -94,9 +94,6 @@
     <t>FBC Colorado II</t>
   </si>
   <si>
-    <t>FC castelo Branco 2</t>
-  </si>
-  <si>
     <t>FC Los Castilho</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>Grêmio imortal 37</t>
+  </si>
+  <si>
+    <t>HVCARTOLA</t>
   </si>
   <si>
     <t>JUV. KP</t>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>Time do S.A.P.O</t>
+  </si>
+  <si>
+    <t>VaiDescerkkkk!!!</t>
   </si>
   <si>
     <t>VASCO MARTINS FC</t>
@@ -590,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1043,31 +1046,31 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>37.820068359375</v>
+        <v>56.260009765625</v>
       </c>
       <c r="C15">
-        <v>64.02978515625</v>
+        <v>74.89990234375</v>
       </c>
       <c r="D15">
-        <v>78.990234375</v>
+        <v>87.33984375</v>
       </c>
       <c r="E15">
-        <v>36.580078125</v>
+        <v>69.64990234375</v>
       </c>
       <c r="F15">
-        <v>61.300048828125</v>
+        <v>88.919921875</v>
       </c>
       <c r="G15">
-        <v>68.490234375</v>
+        <v>83.419921875</v>
       </c>
       <c r="H15">
-        <v>50.8701171875</v>
+        <v>68.97021484375</v>
       </c>
       <c r="I15">
-        <v>79.35009765625</v>
+        <v>75.9501953125</v>
       </c>
       <c r="J15">
-        <v>79.35009765625</v>
+        <v>75.9501953125</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1075,31 +1078,31 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>56.260009765625</v>
+        <v>63.89990234375</v>
       </c>
       <c r="C16">
-        <v>74.89990234375</v>
+        <v>92.77978515625</v>
       </c>
       <c r="D16">
-        <v>87.33984375</v>
+        <v>78.39990234375</v>
       </c>
       <c r="E16">
-        <v>69.64990234375</v>
+        <v>87.64990234375</v>
       </c>
       <c r="F16">
-        <v>88.919921875</v>
+        <v>89.02001953125</v>
       </c>
       <c r="G16">
-        <v>83.419921875</v>
+        <v>62.81005859375</v>
       </c>
       <c r="H16">
-        <v>68.97021484375</v>
+        <v>105.8701171875</v>
       </c>
       <c r="I16">
-        <v>75.9501953125</v>
+        <v>76.89990234375</v>
       </c>
       <c r="J16">
-        <v>75.9501953125</v>
+        <v>76.89990234375</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1107,31 +1110,31 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>63.89990234375</v>
+        <v>44.06005859375</v>
       </c>
       <c r="C17">
-        <v>92.77978515625</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D17">
-        <v>78.39990234375</v>
+        <v>65.259765625</v>
       </c>
       <c r="E17">
-        <v>87.64990234375</v>
+        <v>74.25</v>
       </c>
       <c r="F17">
-        <v>89.02001953125</v>
+        <v>43.39990234375</v>
       </c>
       <c r="G17">
-        <v>62.81005859375</v>
+        <v>58.68994140625</v>
       </c>
       <c r="H17">
-        <v>105.8701171875</v>
+        <v>31.6199951171875</v>
       </c>
       <c r="I17">
-        <v>76.89990234375</v>
+        <v>65.35009765625</v>
       </c>
       <c r="J17">
-        <v>76.89990234375</v>
+        <v>65.35009765625</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1139,31 +1142,31 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>44.06005859375</v>
+        <v>54.159912109375</v>
       </c>
       <c r="C18">
-        <v>85.7001953125</v>
+        <v>86.7001953125</v>
       </c>
       <c r="D18">
-        <v>65.259765625</v>
+        <v>75.56005859375</v>
       </c>
       <c r="E18">
-        <v>74.25</v>
+        <v>82.0498046875</v>
       </c>
       <c r="F18">
-        <v>43.39990234375</v>
+        <v>77.919921875</v>
       </c>
       <c r="G18">
-        <v>58.68994140625</v>
+        <v>73.22021484375</v>
       </c>
       <c r="H18">
-        <v>31.6199951171875</v>
+        <v>75.56982421875</v>
       </c>
       <c r="I18">
-        <v>65.35009765625</v>
+        <v>72.2998046875</v>
       </c>
       <c r="J18">
-        <v>65.35009765625</v>
+        <v>72.2998046875</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1171,31 +1174,31 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>54.159912109375</v>
+        <v>40.60009765625</v>
       </c>
       <c r="C19">
-        <v>86.7001953125</v>
+        <v>67.8701171875</v>
       </c>
       <c r="D19">
-        <v>75.56005859375</v>
+        <v>73.64990234375</v>
       </c>
       <c r="E19">
-        <v>82.0498046875</v>
+        <v>74.02978515625</v>
       </c>
       <c r="F19">
-        <v>77.919921875</v>
+        <v>81.6201171875</v>
       </c>
       <c r="G19">
-        <v>73.22021484375</v>
+        <v>41.550048828125</v>
       </c>
       <c r="H19">
-        <v>75.56982421875</v>
+        <v>79.56982421875</v>
       </c>
       <c r="I19">
-        <v>72.2998046875</v>
+        <v>66.97998046875</v>
       </c>
       <c r="J19">
-        <v>72.2998046875</v>
+        <v>66.97998046875</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1203,31 +1206,31 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>40.60009765625</v>
+        <v>57.449951171875</v>
       </c>
       <c r="C20">
-        <v>67.8701171875</v>
+        <v>83.2001953125</v>
       </c>
       <c r="D20">
-        <v>73.64990234375</v>
+        <v>70.7998046875</v>
       </c>
       <c r="E20">
-        <v>74.02978515625</v>
+        <v>77.259765625</v>
       </c>
       <c r="F20">
-        <v>81.6201171875</v>
+        <v>69.3701171875</v>
       </c>
       <c r="G20">
-        <v>41.550048828125</v>
+        <v>52.199951171875</v>
       </c>
       <c r="H20">
-        <v>79.56982421875</v>
+        <v>39.969970703125</v>
       </c>
       <c r="I20">
-        <v>66.97998046875</v>
+        <v>60.5</v>
       </c>
       <c r="J20">
-        <v>66.97998046875</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1235,31 +1238,31 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>57.449951171875</v>
+        <v>57.60009765625</v>
       </c>
       <c r="C21">
-        <v>83.2001953125</v>
+        <v>84.5</v>
       </c>
       <c r="D21">
-        <v>70.7998046875</v>
+        <v>78.85986328125</v>
       </c>
       <c r="E21">
-        <v>77.259765625</v>
+        <v>85.97998046875</v>
       </c>
       <c r="F21">
-        <v>69.3701171875</v>
+        <v>87.22021484375</v>
       </c>
       <c r="G21">
-        <v>52.199951171875</v>
+        <v>62.10009765625</v>
       </c>
       <c r="H21">
-        <v>39.969970703125</v>
+        <v>82.81005859375</v>
       </c>
       <c r="I21">
-        <v>60.5</v>
+        <v>91.39990234375</v>
       </c>
       <c r="J21">
-        <v>60.5</v>
+        <v>91.39990234375</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1267,31 +1270,31 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>57.60009765625</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>84.5</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>78.85986328125</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>85.97998046875</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>87.22021484375</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>62.10009765625</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>82.81005859375</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>91.39990234375</v>
+        <v>77.18994140625</v>
       </c>
       <c r="J22">
-        <v>91.39990234375</v>
+        <v>77.18994140625</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2259,31 +2262,31 @@
         <v>60</v>
       </c>
       <c r="B53">
-        <v>55.89990234375</v>
+        <v>44.260009765625</v>
       </c>
       <c r="C53">
-        <v>77.3798828125</v>
+        <v>90</v>
       </c>
       <c r="D53">
-        <v>43.909912109375</v>
+        <v>68.9599609375</v>
       </c>
       <c r="E53">
-        <v>76.080078125</v>
+        <v>73.22998046875</v>
       </c>
       <c r="F53">
-        <v>66.2001953125</v>
+        <v>79.33984375</v>
       </c>
       <c r="G53">
-        <v>57.780029296875</v>
+        <v>68.68994140625</v>
       </c>
       <c r="H53">
-        <v>67.33984375</v>
+        <v>61.570068359375</v>
       </c>
       <c r="I53">
-        <v>94.31982421875</v>
+        <v>74.2998046875</v>
       </c>
       <c r="J53">
-        <v>94.31982421875</v>
+        <v>74.2998046875</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2291,30 +2294,62 @@
         <v>61</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>55.89990234375</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>77.3798828125</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>43.909912109375</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>76.080078125</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>66.2001953125</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>57.780029296875</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>67.33984375</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>94.31982421875</v>
       </c>
       <c r="J54">
+        <v>94.31982421875</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
         <v>0</v>
       </c>
     </row>
@@ -2325,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2343,7 +2378,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2351,7 +2386,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2359,7 +2394,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2367,7 +2402,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2375,7 +2410,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2383,7 +2418,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2391,7 +2426,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2399,7 +2434,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2407,7 +2442,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2415,7 +2450,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2423,7 +2458,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2431,7 +2466,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2439,7 +2474,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2447,7 +2482,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2455,7 +2490,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2463,7 +2498,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2471,7 +2506,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2479,7 +2514,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2487,7 +2522,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2495,7 +2530,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2503,7 +2538,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2511,7 +2546,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2519,7 +2554,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2527,7 +2562,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2535,7 +2570,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2551,7 +2586,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2559,7 +2594,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2647,7 +2682,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2655,7 +2690,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2743,9 +2778,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -2756,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2774,7 +2817,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2782,7 +2825,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2790,7 +2833,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2798,7 +2841,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2806,7 +2849,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2814,7 +2857,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2822,7 +2865,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2830,7 +2873,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2838,7 +2881,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2846,7 +2889,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2854,7 +2897,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2862,7 +2905,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2870,7 +2913,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2878,7 +2921,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2886,7 +2929,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2894,7 +2937,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2902,7 +2945,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2910,7 +2953,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2918,7 +2961,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2926,7 +2969,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2934,7 +2977,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2942,7 +2985,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2950,7 +2993,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2958,7 +3001,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2966,7 +3009,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2982,7 +3025,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2990,7 +3033,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3078,7 +3121,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3086,7 +3129,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3174,9 +3217,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -3192,21 +3243,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3220,7 +3271,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -3234,7 +3285,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3248,7 +3299,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -3262,7 +3313,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -3276,7 +3327,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3290,7 +3341,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -3304,7 +3355,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -3318,7 +3369,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -3332,7 +3383,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -3346,7 +3397,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -3360,7 +3411,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -3374,7 +3425,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3388,13 +3439,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>334.60009765625</v>
@@ -3402,7 +3453,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -3430,7 +3481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3883,31 +3934,31 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>37.820068359375</v>
+        <v>56.260009765625</v>
       </c>
       <c r="C15">
-        <v>64.02978515625</v>
+        <v>74.89990234375</v>
       </c>
       <c r="D15">
-        <v>78.990234375</v>
+        <v>87.33984375</v>
       </c>
       <c r="E15">
-        <v>36.580078125</v>
+        <v>69.64990234375</v>
       </c>
       <c r="F15">
-        <v>61.300048828125</v>
+        <v>88.919921875</v>
       </c>
       <c r="G15">
-        <v>68.490234375</v>
+        <v>83.419921875</v>
       </c>
       <c r="H15">
-        <v>50.8701171875</v>
+        <v>68.97021484375</v>
       </c>
       <c r="I15">
-        <v>79.35009765625</v>
+        <v>75.9501953125</v>
       </c>
       <c r="J15">
-        <v>79.35009765625</v>
+        <v>75.9501953125</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3915,31 +3966,31 @@
         <v>23</v>
       </c>
       <c r="B16">
-        <v>56.260009765625</v>
+        <v>63.89990234375</v>
       </c>
       <c r="C16">
-        <v>74.89990234375</v>
+        <v>92.77978515625</v>
       </c>
       <c r="D16">
-        <v>87.33984375</v>
+        <v>78.39990234375</v>
       </c>
       <c r="E16">
-        <v>69.64990234375</v>
+        <v>87.64990234375</v>
       </c>
       <c r="F16">
-        <v>88.919921875</v>
+        <v>89.02001953125</v>
       </c>
       <c r="G16">
-        <v>83.419921875</v>
+        <v>62.81005859375</v>
       </c>
       <c r="H16">
-        <v>68.97021484375</v>
+        <v>105.8701171875</v>
       </c>
       <c r="I16">
-        <v>75.9501953125</v>
+        <v>76.89990234375</v>
       </c>
       <c r="J16">
-        <v>75.9501953125</v>
+        <v>76.89990234375</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3947,31 +3998,31 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>63.89990234375</v>
+        <v>44.06005859375</v>
       </c>
       <c r="C17">
-        <v>92.77978515625</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D17">
-        <v>78.39990234375</v>
+        <v>65.259765625</v>
       </c>
       <c r="E17">
-        <v>87.64990234375</v>
+        <v>74.25</v>
       </c>
       <c r="F17">
-        <v>89.02001953125</v>
+        <v>43.39990234375</v>
       </c>
       <c r="G17">
-        <v>62.81005859375</v>
+        <v>58.68994140625</v>
       </c>
       <c r="H17">
-        <v>105.8701171875</v>
+        <v>31.6199951171875</v>
       </c>
       <c r="I17">
-        <v>76.89990234375</v>
+        <v>65.35009765625</v>
       </c>
       <c r="J17">
-        <v>76.89990234375</v>
+        <v>65.35009765625</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3979,31 +4030,31 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>44.06005859375</v>
+        <v>54.159912109375</v>
       </c>
       <c r="C18">
-        <v>85.7001953125</v>
+        <v>86.7001953125</v>
       </c>
       <c r="D18">
-        <v>65.259765625</v>
+        <v>75.56005859375</v>
       </c>
       <c r="E18">
-        <v>74.25</v>
+        <v>82.0498046875</v>
       </c>
       <c r="F18">
-        <v>43.39990234375</v>
+        <v>77.919921875</v>
       </c>
       <c r="G18">
-        <v>58.68994140625</v>
+        <v>73.22021484375</v>
       </c>
       <c r="H18">
-        <v>31.6199951171875</v>
+        <v>75.56982421875</v>
       </c>
       <c r="I18">
-        <v>65.35009765625</v>
+        <v>72.2998046875</v>
       </c>
       <c r="J18">
-        <v>65.35009765625</v>
+        <v>72.2998046875</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4011,31 +4062,31 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>54.159912109375</v>
+        <v>40.60009765625</v>
       </c>
       <c r="C19">
-        <v>86.7001953125</v>
+        <v>67.8701171875</v>
       </c>
       <c r="D19">
-        <v>75.56005859375</v>
+        <v>73.64990234375</v>
       </c>
       <c r="E19">
-        <v>82.0498046875</v>
+        <v>74.02978515625</v>
       </c>
       <c r="F19">
-        <v>77.919921875</v>
+        <v>81.6201171875</v>
       </c>
       <c r="G19">
-        <v>73.22021484375</v>
+        <v>41.550048828125</v>
       </c>
       <c r="H19">
-        <v>75.56982421875</v>
+        <v>79.56982421875</v>
       </c>
       <c r="I19">
-        <v>72.2998046875</v>
+        <v>66.97998046875</v>
       </c>
       <c r="J19">
-        <v>72.2998046875</v>
+        <v>66.97998046875</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4043,31 +4094,31 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>40.60009765625</v>
+        <v>57.449951171875</v>
       </c>
       <c r="C20">
-        <v>67.8701171875</v>
+        <v>83.2001953125</v>
       </c>
       <c r="D20">
-        <v>73.64990234375</v>
+        <v>70.7998046875</v>
       </c>
       <c r="E20">
-        <v>74.02978515625</v>
+        <v>77.259765625</v>
       </c>
       <c r="F20">
-        <v>81.6201171875</v>
+        <v>69.3701171875</v>
       </c>
       <c r="G20">
-        <v>41.550048828125</v>
+        <v>52.199951171875</v>
       </c>
       <c r="H20">
-        <v>79.56982421875</v>
+        <v>39.969970703125</v>
       </c>
       <c r="I20">
-        <v>66.97998046875</v>
+        <v>60.5</v>
       </c>
       <c r="J20">
-        <v>66.97998046875</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4075,31 +4126,31 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>57.449951171875</v>
+        <v>57.60009765625</v>
       </c>
       <c r="C21">
-        <v>83.2001953125</v>
+        <v>84.5</v>
       </c>
       <c r="D21">
-        <v>70.7998046875</v>
+        <v>78.85986328125</v>
       </c>
       <c r="E21">
-        <v>77.259765625</v>
+        <v>85.97998046875</v>
       </c>
       <c r="F21">
-        <v>69.3701171875</v>
+        <v>87.22021484375</v>
       </c>
       <c r="G21">
-        <v>52.199951171875</v>
+        <v>62.10009765625</v>
       </c>
       <c r="H21">
-        <v>39.969970703125</v>
+        <v>82.81005859375</v>
       </c>
       <c r="I21">
-        <v>60.5</v>
+        <v>91.39990234375</v>
       </c>
       <c r="J21">
-        <v>60.5</v>
+        <v>91.39990234375</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4107,31 +4158,31 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>57.60009765625</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>84.5</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>78.85986328125</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>85.97998046875</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>87.22021484375</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>62.10009765625</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>82.81005859375</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>91.39990234375</v>
+        <v>77.18994140625</v>
       </c>
       <c r="J22">
-        <v>91.39990234375</v>
+        <v>77.18994140625</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5099,31 +5150,31 @@
         <v>60</v>
       </c>
       <c r="B53">
-        <v>55.89990234375</v>
+        <v>44.260009765625</v>
       </c>
       <c r="C53">
-        <v>77.3798828125</v>
+        <v>90</v>
       </c>
       <c r="D53">
-        <v>43.909912109375</v>
+        <v>68.9599609375</v>
       </c>
       <c r="E53">
-        <v>76.080078125</v>
+        <v>73.22998046875</v>
       </c>
       <c r="F53">
-        <v>66.2001953125</v>
+        <v>79.33984375</v>
       </c>
       <c r="G53">
-        <v>57.780029296875</v>
+        <v>68.68994140625</v>
       </c>
       <c r="H53">
-        <v>67.33984375</v>
+        <v>61.570068359375</v>
       </c>
       <c r="I53">
-        <v>94.31982421875</v>
+        <v>74.2998046875</v>
       </c>
       <c r="J53">
-        <v>94.31982421875</v>
+        <v>74.2998046875</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -5131,30 +5182,62 @@
         <v>61</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>55.89990234375</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>77.3798828125</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>43.909912109375</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>76.080078125</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>66.2001953125</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>57.780029296875</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>67.33984375</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>94.31982421875</v>
       </c>
       <c r="J54">
+        <v>94.31982421875</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
         <v>0</v>
       </c>
     </row>
@@ -5165,7 +5248,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5191,7 +5274,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>734.2294921875</v>
@@ -5215,7 +5298,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>721.8701171875</v>
@@ -5295,7 +5378,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>681.360107421875</v>
@@ -5327,7 +5410,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>669.779541015625</v>
@@ -5450,95 +5533,95 @@
         <v>60</v>
       </c>
       <c r="B36">
-        <v>633.2294921875</v>
+        <v>634.6494140625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B37">
-        <v>626.02978515625</v>
+        <v>633.2294921875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B38">
-        <v>623.7001953125</v>
+        <v>626.02978515625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B39">
-        <v>618.61962890625</v>
+        <v>623.7001953125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B40">
-        <v>617.43994140625</v>
+        <v>618.61962890625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B41">
-        <v>597.26953125</v>
+        <v>617.43994140625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>594.329833984375</v>
+        <v>597.26953125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B43">
-        <v>592.849853515625</v>
+        <v>594.329833984375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B44">
-        <v>571.249755859375</v>
+        <v>592.849853515625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>569.5693359375</v>
+        <v>571.249755859375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B46">
-        <v>561.649658203125</v>
+        <v>569.5693359375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B47">
-        <v>556.78076171875</v>
+        <v>561.649658203125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -5575,7 +5658,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52">
         <v>533.6800537109375</v>
@@ -5587,6 +5670,14 @@
       </c>
       <c r="B53">
         <v>462.7403564453125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54">
+        <v>154.3798828125</v>
       </c>
     </row>
   </sheetData>
@@ -5596,7 +5687,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:A54"/>
+  <dimension ref="A2:A55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:1">
@@ -5862,6 +5953,11 @@
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5871,7 +5967,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5889,7 +5985,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5897,7 +5993,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5905,7 +6001,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5913,7 +6009,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5921,7 +6017,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5929,7 +6025,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -5937,7 +6033,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5945,7 +6041,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5953,7 +6049,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -5961,7 +6057,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5969,7 +6065,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5977,7 +6073,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5985,7 +6081,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5993,7 +6089,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6001,7 +6097,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6009,7 +6105,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6017,7 +6113,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6025,7 +6121,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6033,7 +6129,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6041,7 +6137,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6049,7 +6145,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6057,7 +6153,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6065,7 +6161,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6073,7 +6169,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6081,7 +6177,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6097,7 +6193,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6105,7 +6201,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6193,7 +6289,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6201,7 +6297,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6289,9 +6385,17 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
         <v>0</v>
       </c>
     </row>
@@ -6302,7 +6406,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6448,7 +6552,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -6544,7 +6648,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -6560,7 +6664,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -6576,7 +6680,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -6584,7 +6688,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -6600,7 +6704,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -6680,50 +6784,58 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B48">
-        <v>44.06005859375</v>
+        <v>44.260009765625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B49">
-        <v>43.510009765625</v>
+        <v>44.06005859375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B50">
-        <v>42.9599609375</v>
+        <v>43.510009765625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B51">
-        <v>40.60009765625</v>
+        <v>42.9599609375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B52">
-        <v>38.260009765625</v>
+        <v>40.60009765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B53">
-        <v>37.820068359375</v>
+        <v>38.260009765625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6733,7 +6845,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6791,7 +6903,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -6815,7 +6927,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -6823,7 +6935,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -6839,7 +6951,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -6871,7 +6983,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -6935,210 +7047,210 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B26">
-        <v>231.8896484375</v>
+        <v>232.18994140625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B27">
-        <v>231.259765625</v>
+        <v>231.8896484375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>227.90966796875</v>
+        <v>231.259765625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B29">
-        <v>227.8095703125</v>
+        <v>227.90966796875</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B30">
-        <v>225.2099609375</v>
+        <v>227.8095703125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>225.02978515625</v>
+        <v>225.2099609375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B32">
-        <v>224.409912109375</v>
+        <v>225.02978515625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B33">
-        <v>222.49951171875</v>
+        <v>224.409912109375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B34">
-        <v>219.469482421875</v>
+        <v>222.49951171875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35">
-        <v>218.419921875</v>
+        <v>219.469482421875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>216.3896484375</v>
+        <v>218.419921875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>216.030517578125</v>
+        <v>216.3896484375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>215.5498046875</v>
+        <v>216.030517578125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B39">
-        <v>212.2099609375</v>
+        <v>215.5498046875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40">
-        <v>211.239990234375</v>
+        <v>212.2099609375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B41">
-        <v>209.509765625</v>
+        <v>211.239990234375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B42">
-        <v>206.1201171875</v>
+        <v>209.509765625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B43">
-        <v>205.58984375</v>
+        <v>206.1201171875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B44">
-        <v>204.8798828125</v>
+        <v>205.58984375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B45">
-        <v>199.2001953125</v>
+        <v>204.8798828125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B46">
-        <v>198.499755859375</v>
+        <v>199.2001953125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B47">
-        <v>197.369873046875</v>
+        <v>198.499755859375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B48">
-        <v>191.85986328125</v>
+        <v>197.369873046875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B49">
-        <v>187.64990234375</v>
+        <v>191.85986328125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B50">
-        <v>186.4697265625</v>
+        <v>187.64990234375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B51">
-        <v>179.60009765625</v>
+        <v>186.4697265625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -7155,6 +7267,14 @@
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7164,7 +7284,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7198,7 +7318,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>334.60009765625</v>
@@ -7222,7 +7342,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>323.5302734375</v>
@@ -7238,7 +7358,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>317.26025390625</v>
@@ -7302,7 +7422,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>299.009765625</v>
@@ -7414,7 +7534,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B32">
         <v>285.639892578125</v>
@@ -7446,66 +7566,66 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>282.68994140625</v>
+        <v>283.899658203125</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B37">
-        <v>280.650390625</v>
+        <v>282.68994140625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="B38">
-        <v>279.340087890625</v>
+        <v>280.650390625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B39">
-        <v>277.80029296875</v>
+        <v>279.340087890625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B40">
-        <v>276.829833984375</v>
+        <v>277.80029296875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B41">
-        <v>272.47998046875</v>
+        <v>276.829833984375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B42">
-        <v>269.719970703125</v>
+        <v>272.47998046875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B43">
-        <v>260.010498046875</v>
+        <v>269.719970703125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -7558,7 +7678,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>222.0400390625</v>
@@ -7582,10 +7702,18 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53">
         <v>199.0599365234375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54">
+        <v>77.18994140625</v>
       </c>
     </row>
   </sheetData>
@@ -7595,7 +7723,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7605,7 +7733,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2">
         <v>94.31982421875</v>
@@ -7613,7 +7741,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>91.39990234375</v>
@@ -7709,31 +7837,31 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B15">
-        <v>79.35009765625</v>
+        <v>79.14990234375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B16">
-        <v>79.14990234375</v>
+        <v>78.0498046875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <v>78.0498046875</v>
+        <v>77.18994140625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>76.89990234375</v>
@@ -7773,7 +7901,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>75.9501953125</v>
@@ -7829,90 +7957,90 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B30">
-        <v>74.0498046875</v>
+        <v>74.2998046875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B31">
-        <v>73.4501953125</v>
+        <v>74.0498046875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
-        <v>73.35009765625</v>
+        <v>73.4501953125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>73.14013671875</v>
+        <v>73.35009765625</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B34">
-        <v>72.2998046875</v>
+        <v>73.14013671875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B35">
-        <v>72.25</v>
+        <v>72.2998046875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B36">
-        <v>72.0498046875</v>
+        <v>72.25</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="B37">
-        <v>69.89990234375</v>
+        <v>72.0498046875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>67.64990234375</v>
+        <v>69.89990234375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B39">
-        <v>66.97998046875</v>
+        <v>67.64990234375</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B40">
-        <v>65.60009765625</v>
+        <v>66.97998046875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7925,97 +8053,105 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B42">
-        <v>65.35009765625</v>
+        <v>65.60009765625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B43">
-        <v>63.949951171875</v>
+        <v>65.35009765625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B44">
-        <v>63.47998046875</v>
+        <v>63.949951171875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B45">
-        <v>63.25</v>
+        <v>63.47998046875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B46">
-        <v>60.5</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B47">
-        <v>58.85009765625</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B48">
-        <v>57.429931640625</v>
+        <v>58.85009765625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B49">
-        <v>55.0400390625</v>
+        <v>57.429931640625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B50">
-        <v>54.360107421875</v>
+        <v>55.0400390625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B51">
-        <v>45.699951171875</v>
+        <v>54.360107421875</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B52">
-        <v>45.3701171875</v>
+        <v>45.699951171875</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53">
+        <v>45.3701171875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>26.719970703125</v>
       </c>
     </row>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -654,7 +654,7 @@
         <v>79.14990234375</v>
       </c>
       <c r="J2">
-        <v>79.14990234375</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -686,7 +686,7 @@
         <v>85.5</v>
       </c>
       <c r="J3">
-        <v>85.5</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -718,7 +718,7 @@
         <v>65.60009765625</v>
       </c>
       <c r="J4">
-        <v>65.60009765625</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -750,7 +750,7 @@
         <v>79.60009765625</v>
       </c>
       <c r="J5">
-        <v>79.60009765625</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -782,7 +782,7 @@
         <v>76.43994140625</v>
       </c>
       <c r="J6">
-        <v>76.43994140625</v>
+        <v>92.98</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -814,7 +814,7 @@
         <v>63.47998046875</v>
       </c>
       <c r="J7">
-        <v>63.47998046875</v>
+        <v>104.88</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -846,7 +846,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J8">
-        <v>76.4501953125</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -878,7 +878,7 @@
         <v>74.9501953125</v>
       </c>
       <c r="J9">
-        <v>74.9501953125</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -910,7 +910,7 @@
         <v>63.25</v>
       </c>
       <c r="J10">
-        <v>63.25</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -942,7 +942,7 @@
         <v>88.0498046875</v>
       </c>
       <c r="J11">
-        <v>88.0498046875</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -974,7 +974,7 @@
         <v>55.0400390625</v>
       </c>
       <c r="J12">
-        <v>55.0400390625</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1006,7 +1006,7 @@
         <v>75.75</v>
       </c>
       <c r="J13">
-        <v>75.75</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1038,7 +1038,7 @@
         <v>72.0498046875</v>
       </c>
       <c r="J14">
-        <v>72.0498046875</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1070,7 +1070,7 @@
         <v>75.9501953125</v>
       </c>
       <c r="J15">
-        <v>75.9501953125</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1102,7 +1102,7 @@
         <v>76.89990234375</v>
       </c>
       <c r="J16">
-        <v>76.89990234375</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1134,7 +1134,7 @@
         <v>65.35009765625</v>
       </c>
       <c r="J17">
-        <v>65.35009765625</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1166,7 +1166,7 @@
         <v>72.2998046875</v>
       </c>
       <c r="J18">
-        <v>72.2998046875</v>
+        <v>112.88</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1198,7 +1198,7 @@
         <v>66.97998046875</v>
       </c>
       <c r="J19">
-        <v>66.97998046875</v>
+        <v>116.04</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1230,7 +1230,7 @@
         <v>60.5</v>
       </c>
       <c r="J20">
-        <v>60.5</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1262,7 +1262,7 @@
         <v>91.39990234375</v>
       </c>
       <c r="J21">
-        <v>91.39990234375</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1294,7 +1294,7 @@
         <v>77.18994140625</v>
       </c>
       <c r="J22">
-        <v>77.18994140625</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1326,7 +1326,7 @@
         <v>57.429931640625</v>
       </c>
       <c r="J23">
-        <v>57.429931640625</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1358,7 +1358,7 @@
         <v>80.0498046875</v>
       </c>
       <c r="J24">
-        <v>80.0498046875</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1390,7 +1390,7 @@
         <v>84.85009765625</v>
       </c>
       <c r="J25">
-        <v>84.85009765625</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1422,7 +1422,7 @@
         <v>73.35009765625</v>
       </c>
       <c r="J26">
-        <v>73.35009765625</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1454,7 +1454,7 @@
         <v>73.4501953125</v>
       </c>
       <c r="J27">
-        <v>73.4501953125</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1486,7 +1486,7 @@
         <v>45.3701171875</v>
       </c>
       <c r="J28">
-        <v>45.3701171875</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1518,7 +1518,7 @@
         <v>72.25</v>
       </c>
       <c r="J29">
-        <v>72.25</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1550,7 +1550,7 @@
         <v>73.14013671875</v>
       </c>
       <c r="J30">
-        <v>73.14013671875</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1582,7 +1582,7 @@
         <v>65.60009765625</v>
       </c>
       <c r="J31">
-        <v>65.60009765625</v>
+        <v>106.98</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1614,7 +1614,7 @@
         <v>45.699951171875</v>
       </c>
       <c r="J32">
-        <v>45.699951171875</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1646,7 +1646,7 @@
         <v>74.0498046875</v>
       </c>
       <c r="J33">
-        <v>74.0498046875</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1678,7 +1678,7 @@
         <v>74.83984375</v>
       </c>
       <c r="J34">
-        <v>74.83984375</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1710,7 +1710,7 @@
         <v>88.25</v>
       </c>
       <c r="J35">
-        <v>88.25</v>
+        <v>80.88</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1742,7 +1742,7 @@
         <v>79.85009765625</v>
       </c>
       <c r="J36">
-        <v>79.85009765625</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1774,7 +1774,7 @@
         <v>76.25</v>
       </c>
       <c r="J37">
-        <v>76.25</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1806,7 +1806,7 @@
         <v>63.949951171875</v>
       </c>
       <c r="J38">
-        <v>63.949951171875</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -1838,7 +1838,7 @@
         <v>26.719970703125</v>
       </c>
       <c r="J39">
-        <v>26.719970703125</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1870,7 +1870,7 @@
         <v>75.0498046875</v>
       </c>
       <c r="J40">
-        <v>75.0498046875</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -1902,7 +1902,7 @@
         <v>58.85009765625</v>
       </c>
       <c r="J41">
-        <v>58.85009765625</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -1934,7 +1934,7 @@
         <v>74.85009765625</v>
       </c>
       <c r="J42">
-        <v>74.85009765625</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -1966,7 +1966,7 @@
         <v>78.0498046875</v>
       </c>
       <c r="J43">
-        <v>78.0498046875</v>
+        <v>91.44</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -1998,7 +1998,7 @@
         <v>81.25</v>
       </c>
       <c r="J44">
-        <v>81.25</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2030,7 +2030,7 @@
         <v>80.5498046875</v>
       </c>
       <c r="J45">
-        <v>80.5498046875</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2062,7 +2062,7 @@
         <v>54.360107421875</v>
       </c>
       <c r="J46">
-        <v>54.360107421875</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2094,7 +2094,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="J47">
-        <v>69.89990234375</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2126,7 +2126,7 @@
         <v>80.75</v>
       </c>
       <c r="J48">
-        <v>80.75</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2158,7 +2158,7 @@
         <v>75</v>
       </c>
       <c r="J49">
-        <v>75</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2190,7 +2190,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J50">
-        <v>76.4501953125</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2222,7 +2222,7 @@
         <v>67.64990234375</v>
       </c>
       <c r="J51">
-        <v>67.64990234375</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2254,7 +2254,7 @@
         <v>84.25</v>
       </c>
       <c r="J52">
-        <v>84.25</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2286,7 +2286,7 @@
         <v>74.2998046875</v>
       </c>
       <c r="J53">
-        <v>74.2998046875</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2318,7 +2318,7 @@
         <v>94.31982421875</v>
       </c>
       <c r="J54">
-        <v>94.31982421875</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3542,7 +3542,7 @@
         <v>79.14990234375</v>
       </c>
       <c r="J2">
-        <v>79.14990234375</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3574,7 +3574,7 @@
         <v>85.5</v>
       </c>
       <c r="J3">
-        <v>85.5</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3606,7 +3606,7 @@
         <v>65.60009765625</v>
       </c>
       <c r="J4">
-        <v>65.60009765625</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3638,7 +3638,7 @@
         <v>79.60009765625</v>
       </c>
       <c r="J5">
-        <v>79.60009765625</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3670,7 +3670,7 @@
         <v>76.43994140625</v>
       </c>
       <c r="J6">
-        <v>76.43994140625</v>
+        <v>92.98</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3702,7 +3702,7 @@
         <v>63.47998046875</v>
       </c>
       <c r="J7">
-        <v>63.47998046875</v>
+        <v>104.88</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3734,7 +3734,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J8">
-        <v>76.4501953125</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3766,7 +3766,7 @@
         <v>74.9501953125</v>
       </c>
       <c r="J9">
-        <v>74.9501953125</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3798,7 +3798,7 @@
         <v>63.25</v>
       </c>
       <c r="J10">
-        <v>63.25</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3830,7 +3830,7 @@
         <v>88.0498046875</v>
       </c>
       <c r="J11">
-        <v>88.0498046875</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3862,7 +3862,7 @@
         <v>55.0400390625</v>
       </c>
       <c r="J12">
-        <v>55.0400390625</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3894,7 +3894,7 @@
         <v>75.75</v>
       </c>
       <c r="J13">
-        <v>75.75</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3926,7 +3926,7 @@
         <v>72.0498046875</v>
       </c>
       <c r="J14">
-        <v>72.0498046875</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3958,7 +3958,7 @@
         <v>75.9501953125</v>
       </c>
       <c r="J15">
-        <v>75.9501953125</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3990,7 +3990,7 @@
         <v>76.89990234375</v>
       </c>
       <c r="J16">
-        <v>76.89990234375</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4022,7 +4022,7 @@
         <v>65.35009765625</v>
       </c>
       <c r="J17">
-        <v>65.35009765625</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4054,7 +4054,7 @@
         <v>72.2998046875</v>
       </c>
       <c r="J18">
-        <v>72.2998046875</v>
+        <v>112.88</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4086,7 +4086,7 @@
         <v>66.97998046875</v>
       </c>
       <c r="J19">
-        <v>66.97998046875</v>
+        <v>116.04</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4118,7 +4118,7 @@
         <v>60.5</v>
       </c>
       <c r="J20">
-        <v>60.5</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4150,7 +4150,7 @@
         <v>91.39990234375</v>
       </c>
       <c r="J21">
-        <v>91.39990234375</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4182,7 +4182,7 @@
         <v>77.18994140625</v>
       </c>
       <c r="J22">
-        <v>77.18994140625</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4214,7 +4214,7 @@
         <v>57.429931640625</v>
       </c>
       <c r="J23">
-        <v>57.429931640625</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4246,7 +4246,7 @@
         <v>80.0498046875</v>
       </c>
       <c r="J24">
-        <v>80.0498046875</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4278,7 +4278,7 @@
         <v>84.85009765625</v>
       </c>
       <c r="J25">
-        <v>84.85009765625</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4310,7 +4310,7 @@
         <v>73.35009765625</v>
       </c>
       <c r="J26">
-        <v>73.35009765625</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4342,7 +4342,7 @@
         <v>73.4501953125</v>
       </c>
       <c r="J27">
-        <v>73.4501953125</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4374,7 +4374,7 @@
         <v>45.3701171875</v>
       </c>
       <c r="J28">
-        <v>45.3701171875</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4406,7 +4406,7 @@
         <v>72.25</v>
       </c>
       <c r="J29">
-        <v>72.25</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4438,7 +4438,7 @@
         <v>73.14013671875</v>
       </c>
       <c r="J30">
-        <v>73.14013671875</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4470,7 +4470,7 @@
         <v>65.60009765625</v>
       </c>
       <c r="J31">
-        <v>65.60009765625</v>
+        <v>106.98</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -4502,7 +4502,7 @@
         <v>45.699951171875</v>
       </c>
       <c r="J32">
-        <v>45.699951171875</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -4534,7 +4534,7 @@
         <v>74.0498046875</v>
       </c>
       <c r="J33">
-        <v>74.0498046875</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -4566,7 +4566,7 @@
         <v>74.83984375</v>
       </c>
       <c r="J34">
-        <v>74.83984375</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -4598,7 +4598,7 @@
         <v>88.25</v>
       </c>
       <c r="J35">
-        <v>88.25</v>
+        <v>80.88</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -4630,7 +4630,7 @@
         <v>79.85009765625</v>
       </c>
       <c r="J36">
-        <v>79.85009765625</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -4662,7 +4662,7 @@
         <v>76.25</v>
       </c>
       <c r="J37">
-        <v>76.25</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -4694,7 +4694,7 @@
         <v>63.949951171875</v>
       </c>
       <c r="J38">
-        <v>63.949951171875</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -4726,7 +4726,7 @@
         <v>26.719970703125</v>
       </c>
       <c r="J39">
-        <v>26.719970703125</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -4758,7 +4758,7 @@
         <v>75.0498046875</v>
       </c>
       <c r="J40">
-        <v>75.0498046875</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -4790,7 +4790,7 @@
         <v>58.85009765625</v>
       </c>
       <c r="J41">
-        <v>58.85009765625</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -4822,7 +4822,7 @@
         <v>74.85009765625</v>
       </c>
       <c r="J42">
-        <v>74.85009765625</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -4854,7 +4854,7 @@
         <v>78.0498046875</v>
       </c>
       <c r="J43">
-        <v>78.0498046875</v>
+        <v>91.44</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -4886,7 +4886,7 @@
         <v>81.25</v>
       </c>
       <c r="J44">
-        <v>81.25</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -4918,7 +4918,7 @@
         <v>80.5498046875</v>
       </c>
       <c r="J45">
-        <v>80.5498046875</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -4950,7 +4950,7 @@
         <v>54.360107421875</v>
       </c>
       <c r="J46">
-        <v>54.360107421875</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -4982,7 +4982,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="J47">
-        <v>69.89990234375</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -5014,7 +5014,7 @@
         <v>80.75</v>
       </c>
       <c r="J48">
-        <v>80.75</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -5046,7 +5046,7 @@
         <v>75</v>
       </c>
       <c r="J49">
-        <v>75</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -5078,7 +5078,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J50">
-        <v>76.4501953125</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -5110,7 +5110,7 @@
         <v>67.64990234375</v>
       </c>
       <c r="J51">
-        <v>67.64990234375</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -5142,7 +5142,7 @@
         <v>84.25</v>
       </c>
       <c r="J52">
-        <v>84.25</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -5174,7 +5174,7 @@
         <v>74.2998046875</v>
       </c>
       <c r="J53">
-        <v>74.2998046875</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -5206,7 +5206,7 @@
         <v>94.31982421875</v>
       </c>
       <c r="J54">
-        <v>94.31982421875</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -5261,7 +5261,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>768.9599609375</v>
+        <v>762.20986328125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5269,119 +5269,119 @@
         <v>40</v>
       </c>
       <c r="B3">
-        <v>740.10986328125</v>
+        <v>757.2400585937501</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>734.2294921875</v>
+        <v>739.44033203125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>729.54052734375</v>
+        <v>739.4102148437501</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B6">
-        <v>727.04052734375</v>
+        <v>739.06958984375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="B7">
-        <v>721.8701171875</v>
+        <v>736.94033203125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B8">
-        <v>717.539794921875</v>
+        <v>731.8101269531251</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B9">
-        <v>714.06005859375</v>
+        <v>718.829794921875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B10">
-        <v>702.34912109375</v>
+        <v>718.05005859375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>700.480224609375</v>
+        <v>715.7393164062501</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12">
-        <v>694.56005859375</v>
+        <v>714.4700390625001</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>694.499755859375</v>
+        <v>713.7898632812501</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>684.259521484375</v>
+        <v>710.359736328125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>684.19970703125</v>
+        <v>704.259912109375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>683.08935546875</v>
+        <v>696.009658203125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B17">
-        <v>681.360107421875</v>
+        <v>693.809736328125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5389,159 +5389,159 @@
         <v>13</v>
       </c>
       <c r="B18">
-        <v>676.239990234375</v>
+        <v>692.780048828125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19">
-        <v>675.330078125</v>
+        <v>680.66017578125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B20">
-        <v>670.779541015625</v>
+        <v>679.130087890625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B21">
-        <v>669.779541015625</v>
+        <v>678.700166015625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>668.090087890625</v>
+        <v>678.159931640625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B23">
-        <v>666.72998046875</v>
+        <v>676.029892578125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B24">
-        <v>664.41943359375</v>
+        <v>674.869716796875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B25">
-        <v>661.59033203125</v>
+        <v>669.02990234375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>659.97998046875</v>
+        <v>665.779794921875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B27">
-        <v>655.069091796875</v>
+        <v>664.04955078125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B28">
-        <v>653.789794921875</v>
+        <v>663.61966796875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>653.40966796875</v>
+        <v>660.0196484375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B30">
-        <v>651.58984375</v>
+        <v>659.59013671875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31">
-        <v>643.379638671875</v>
+        <v>652.60998046875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B32">
-        <v>641.29931640625</v>
+        <v>651.8494335937499</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="B33">
-        <v>639.020263671875</v>
+        <v>646.1497265625001</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B34">
-        <v>636.780029296875</v>
+        <v>645.81009765625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35">
-        <v>636.10009765625</v>
+        <v>644.81994140625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="B36">
-        <v>634.6494140625</v>
+        <v>643.00931640625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B37">
-        <v>633.2294921875</v>
+        <v>641.909873046875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5549,71 +5549,71 @@
         <v>49</v>
       </c>
       <c r="B38">
-        <v>626.02978515625</v>
+        <v>641.5196875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B39">
-        <v>623.7001953125</v>
+        <v>639.0596289062501</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B40">
-        <v>618.61962890625</v>
+        <v>637.799609375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B41">
-        <v>617.43994140625</v>
+        <v>636.0090917968751</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="B42">
-        <v>597.26953125</v>
+        <v>619.38009765625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43">
-        <v>594.329833984375</v>
+        <v>612.76994140625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>592.849853515625</v>
+        <v>592.8201171875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B45">
-        <v>571.249755859375</v>
+        <v>592.709384765625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B46">
-        <v>569.5693359375</v>
+        <v>592.29966796875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5621,47 +5621,47 @@
         <v>30</v>
       </c>
       <c r="B47">
-        <v>561.649658203125</v>
+        <v>585.9597265625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B48">
-        <v>551.430419921875</v>
+        <v>576.549755859375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B49">
-        <v>541.7597045898438</v>
+        <v>565.920302734375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B50">
-        <v>539.650146484375</v>
+        <v>541.1699560546875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51">
-        <v>534.590087890625</v>
+        <v>528.5897534179687</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B52">
-        <v>533.6800537109375</v>
+        <v>511.140009765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -5669,7 +5669,7 @@
         <v>48</v>
       </c>
       <c r="B53">
-        <v>462.7403564453125</v>
+        <v>476.7402587890625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -5677,7 +5677,7 @@
         <v>29</v>
       </c>
       <c r="B54">
-        <v>154.3798828125</v>
+        <v>159.74994140625</v>
       </c>
     </row>
   </sheetData>
@@ -7733,426 +7733,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B2">
-        <v>94.31982421875</v>
+        <v>116.04</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>91.39990234375</v>
+        <v>112.88</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B4">
-        <v>88.25</v>
+        <v>109.44</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>88.0498046875</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B6">
-        <v>85.5</v>
+        <v>106.98</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B7">
-        <v>84.85009765625</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>84.25</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>81.25</v>
+        <v>104.88</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>80.75</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B11">
-        <v>80.5498046875</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>80.0498046875</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B13">
-        <v>79.85009765625</v>
+        <v>98.08</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B14">
-        <v>79.60009765625</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>79.14990234375</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>78.0498046875</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B17">
-        <v>77.18994140625</v>
+        <v>92.98</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B18">
-        <v>76.89990234375</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B19">
-        <v>76.4501953125</v>
+        <v>91.44</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B20">
-        <v>76.4501953125</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B21">
-        <v>76.43994140625</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B22">
-        <v>76.25</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B23">
-        <v>75.9501953125</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B24">
-        <v>75.75</v>
+        <v>86.34999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B25">
-        <v>75.0498046875</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B26">
-        <v>75</v>
+        <v>85.98</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B27">
-        <v>74.9501953125</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B28">
-        <v>74.85009765625</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B29">
-        <v>74.83984375</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B30">
-        <v>74.2998046875</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B31">
-        <v>74.0498046875</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B32">
-        <v>73.4501953125</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B33">
-        <v>73.35009765625</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>73.14013671875</v>
+        <v>80.88</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B35">
-        <v>72.2998046875</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>72.25</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>72.0498046875</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B38">
-        <v>69.89990234375</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>67.64990234375</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40">
-        <v>66.97998046875</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B41">
-        <v>65.60009765625</v>
+        <v>72.38</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B42">
-        <v>65.60009765625</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B43">
-        <v>65.35009765625</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B44">
-        <v>63.949951171875</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>63.47998046875</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B46">
-        <v>63.25</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B47">
-        <v>60.5</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B48">
-        <v>58.85009765625</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B49">
-        <v>57.429931640625</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B50">
-        <v>55.0400390625</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B51">
-        <v>54.360107421875</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B52">
-        <v>45.699951171875</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B53">
-        <v>45.3701171875</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B54">
-        <v>26.719970703125</v>
+        <v>44.63</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="71">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Rodada 9</t>
+  </si>
+  <si>
+    <t>Rodada 10</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -593,10 +596,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,10 +627,13 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -654,12 +660,15 @@
         <v>79.14990234375</v>
       </c>
       <c r="J2">
-        <v>72.38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>72.080078125</v>
+      </c>
+      <c r="K2">
+        <v>72.080078125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -686,12 +695,15 @@
         <v>85.5</v>
       </c>
       <c r="J3">
-        <v>68.78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>68.47998046875</v>
+      </c>
+      <c r="K3">
+        <v>68.47998046875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -718,12 +730,15 @@
         <v>65.60009765625</v>
       </c>
       <c r="J4">
-        <v>105.28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>104.97998046875</v>
+      </c>
+      <c r="K4">
+        <v>104.97998046875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -750,12 +765,15 @@
         <v>79.60009765625</v>
       </c>
       <c r="J5">
-        <v>72.84999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>71.0498046875</v>
+      </c>
+      <c r="K5">
+        <v>71.0498046875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -782,12 +800,15 @@
         <v>76.43994140625</v>
       </c>
       <c r="J6">
-        <v>92.98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>92.68017578125</v>
+      </c>
+      <c r="K6">
+        <v>92.68017578125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -814,12 +835,15 @@
         <v>63.47998046875</v>
       </c>
       <c r="J7">
-        <v>104.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>104.8798828125</v>
+      </c>
+      <c r="K7">
+        <v>104.8798828125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -846,12 +870,15 @@
         <v>76.4501953125</v>
       </c>
       <c r="J8">
-        <v>86.34999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>85.85009765625</v>
+      </c>
+      <c r="K8">
+        <v>85.85009765625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -878,12 +905,15 @@
         <v>74.9501953125</v>
       </c>
       <c r="J9">
-        <v>94.18000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>93.8798828125</v>
+      </c>
+      <c r="K9">
+        <v>93.8798828125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -910,12 +940,15 @@
         <v>63.25</v>
       </c>
       <c r="J10">
-        <v>64.95999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>69.009765625</v>
+      </c>
+      <c r="K10">
+        <v>69.009765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -942,12 +975,15 @@
         <v>88.0498046875</v>
       </c>
       <c r="J11">
-        <v>78.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>78.35986328125</v>
+      </c>
+      <c r="K11">
+        <v>78.35986328125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -974,12 +1010,15 @@
         <v>55.0400390625</v>
       </c>
       <c r="J12">
-        <v>94.18000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>93.8798828125</v>
+      </c>
+      <c r="K12">
+        <v>93.8798828125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -1006,12 +1045,15 @@
         <v>75.75</v>
       </c>
       <c r="J13">
-        <v>85.95999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>85.9599609375</v>
+      </c>
+      <c r="K13">
+        <v>85.9599609375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -1038,12 +1080,15 @@
         <v>72.0498046875</v>
       </c>
       <c r="J14">
-        <v>85.98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>84.47998046875</v>
+      </c>
+      <c r="K14">
+        <v>84.47998046875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -1070,12 +1115,15 @@
         <v>75.9501953125</v>
       </c>
       <c r="J15">
-        <v>98.84999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>98.85009765625</v>
+      </c>
+      <c r="K15">
+        <v>98.85009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -1102,12 +1150,15 @@
         <v>76.89990234375</v>
       </c>
       <c r="J16">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>79.93994140625</v>
+      </c>
+      <c r="K16">
+        <v>79.93994140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -1134,12 +1185,15 @@
         <v>65.35009765625</v>
       </c>
       <c r="J17">
-        <v>72.84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>72.83984375</v>
+      </c>
+      <c r="K17">
+        <v>72.83984375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -1166,12 +1220,15 @@
         <v>72.2998046875</v>
       </c>
       <c r="J18">
-        <v>112.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>112.8798828125</v>
+      </c>
+      <c r="K18">
+        <v>112.8798828125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -1198,12 +1255,15 @@
         <v>66.97998046875</v>
       </c>
       <c r="J19">
-        <v>116.04</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>116.0400390625</v>
+      </c>
+      <c r="K19">
+        <v>116.0400390625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -1230,12 +1290,15 @@
         <v>60.5</v>
       </c>
       <c r="J20">
-        <v>65.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>65.2998046875</v>
+      </c>
+      <c r="K20">
+        <v>65.2998046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -1262,12 +1325,15 @@
         <v>91.39990234375</v>
       </c>
       <c r="J21">
-        <v>108.94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>108.93994140625</v>
+      </c>
+      <c r="K21">
+        <v>108.93994140625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1294,12 +1360,15 @@
         <v>77.18994140625</v>
       </c>
       <c r="J22">
-        <v>82.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>81.06005859375</v>
+      </c>
+      <c r="K22">
+        <v>81.06005859375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1326,12 +1395,15 @@
         <v>57.429931640625</v>
       </c>
       <c r="J23">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>80.93994140625</v>
+      </c>
+      <c r="K23">
+        <v>80.93994140625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1358,12 +1430,15 @@
         <v>80.0498046875</v>
       </c>
       <c r="J24">
-        <v>61.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>59.010009765625</v>
+      </c>
+      <c r="K24">
+        <v>59.010009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1390,12 +1465,15 @@
         <v>84.85009765625</v>
       </c>
       <c r="J25">
-        <v>86.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>84.56005859375</v>
+      </c>
+      <c r="K25">
+        <v>84.56005859375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1422,12 +1500,15 @@
         <v>73.35009765625</v>
       </c>
       <c r="J26">
-        <v>104.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>104.68017578125</v>
+      </c>
+      <c r="K26">
+        <v>104.68017578125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1454,12 +1535,15 @@
         <v>73.4501953125</v>
       </c>
       <c r="J27">
-        <v>71.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>69.85009765625</v>
+      </c>
+      <c r="K27">
+        <v>69.85009765625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1486,12 +1570,15 @@
         <v>45.3701171875</v>
       </c>
       <c r="J28">
-        <v>59.86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>59.860107421875</v>
+      </c>
+      <c r="K28">
+        <v>59.860107421875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1518,12 +1605,15 @@
         <v>72.25</v>
       </c>
       <c r="J29">
-        <v>59.68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>59.3798828125</v>
+      </c>
+      <c r="K29">
+        <v>59.3798828125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1550,12 +1640,15 @@
         <v>73.14013671875</v>
       </c>
       <c r="J30">
-        <v>44.63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>44.6298828125</v>
+      </c>
+      <c r="K30">
+        <v>44.6298828125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1582,12 +1675,15 @@
         <v>65.60009765625</v>
       </c>
       <c r="J31">
-        <v>106.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>106.97998046875</v>
+      </c>
+      <c r="K31">
+        <v>106.97998046875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1614,12 +1710,15 @@
         <v>45.699951171875</v>
       </c>
       <c r="J32">
-        <v>68.84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>69.33984375</v>
+      </c>
+      <c r="K32">
+        <v>69.33984375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1646,12 +1745,15 @@
         <v>74.0498046875</v>
       </c>
       <c r="J33">
-        <v>91.18000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>90.8798828125</v>
+      </c>
+      <c r="K33">
+        <v>90.8798828125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1678,12 +1780,15 @@
         <v>74.83984375</v>
       </c>
       <c r="J34">
-        <v>97.23999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>97.240234375</v>
+      </c>
+      <c r="K34">
+        <v>97.240234375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -1710,12 +1815,15 @@
         <v>88.25</v>
       </c>
       <c r="J35">
-        <v>80.88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>80.8798828125</v>
+      </c>
+      <c r="K35">
+        <v>80.8798828125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -1742,12 +1850,15 @@
         <v>79.85009765625</v>
       </c>
       <c r="J36">
-        <v>101.96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>101.9599609375</v>
+      </c>
+      <c r="K36">
+        <v>101.9599609375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -1774,12 +1885,15 @@
         <v>76.25</v>
       </c>
       <c r="J37">
-        <v>57.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>56.090087890625</v>
+      </c>
+      <c r="K37">
+        <v>56.090087890625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -1806,12 +1920,15 @@
         <v>63.949951171875</v>
       </c>
       <c r="J38">
-        <v>50.78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>49.679931640625</v>
+      </c>
+      <c r="K38">
+        <v>49.679931640625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -1838,12 +1955,15 @@
         <v>26.719970703125</v>
       </c>
       <c r="J39">
-        <v>84.95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>84.64990234375</v>
+      </c>
+      <c r="K39">
+        <v>84.64990234375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -1870,12 +1990,15 @@
         <v>75.0498046875</v>
       </c>
       <c r="J40">
-        <v>98.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>96.27978515625</v>
+      </c>
+      <c r="K40">
+        <v>96.27978515625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -1902,12 +2025,15 @@
         <v>58.85009765625</v>
       </c>
       <c r="J41">
-        <v>72.84999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>68.7998046875</v>
+      </c>
+      <c r="K41">
+        <v>68.7998046875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -1934,12 +2060,15 @@
         <v>74.85009765625</v>
       </c>
       <c r="J42">
-        <v>90.34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>90.0400390625</v>
+      </c>
+      <c r="K42">
+        <v>90.0400390625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -1966,12 +2095,15 @@
         <v>78.0498046875</v>
       </c>
       <c r="J43">
-        <v>91.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>91.14013671875</v>
+      </c>
+      <c r="K43">
+        <v>91.14013671875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -1998,12 +2130,15 @@
         <v>81.25</v>
       </c>
       <c r="J44">
-        <v>76.58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>76.27978515625</v>
+      </c>
+      <c r="K44">
+        <v>76.27978515625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -2030,12 +2165,15 @@
         <v>80.5498046875</v>
       </c>
       <c r="J45">
-        <v>65.38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>63.780029296875</v>
+      </c>
+      <c r="K45">
+        <v>63.780029296875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -2062,12 +2200,15 @@
         <v>54.360107421875</v>
       </c>
       <c r="J46">
-        <v>106.18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>107.68017578125</v>
+      </c>
+      <c r="K46">
+        <v>107.68017578125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -2094,12 +2235,15 @@
         <v>69.89990234375</v>
       </c>
       <c r="J47">
-        <v>92.14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>91.14013671875</v>
+      </c>
+      <c r="K47">
+        <v>91.14013671875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -2126,12 +2270,15 @@
         <v>80.75</v>
       </c>
       <c r="J48">
-        <v>84.73999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>84.43994140625</v>
+      </c>
+      <c r="K48">
+        <v>84.43994140625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -2158,12 +2305,15 @@
         <v>75</v>
       </c>
       <c r="J49">
-        <v>86.04000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>86.0400390625</v>
+      </c>
+      <c r="K49">
+        <v>86.0400390625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -2190,12 +2340,15 @@
         <v>76.4501953125</v>
       </c>
       <c r="J50">
-        <v>86.34999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>85.85009765625</v>
+      </c>
+      <c r="K50">
+        <v>85.85009765625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -2222,12 +2375,15 @@
         <v>67.64990234375</v>
       </c>
       <c r="J51">
-        <v>109.44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>109.43994140625</v>
+      </c>
+      <c r="K51">
+        <v>109.43994140625</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -2254,12 +2410,15 @@
         <v>84.25</v>
       </c>
       <c r="J52">
-        <v>85.54000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>85.240234375</v>
+      </c>
+      <c r="K52">
+        <v>85.240234375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -2286,12 +2445,15 @@
         <v>74.2998046875</v>
       </c>
       <c r="J53">
-        <v>77.45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>77.4501953125</v>
+      </c>
+      <c r="K53">
+        <v>77.4501953125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -2318,12 +2480,15 @@
         <v>94.31982421875</v>
       </c>
       <c r="J54">
-        <v>53.39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>53.389892578125</v>
+      </c>
+      <c r="K54">
+        <v>53.389892578125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2350,6 +2515,9 @@
         <v>0</v>
       </c>
       <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
         <v>0</v>
       </c>
     </row>
@@ -2370,7 +2538,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2378,7 +2546,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2386,7 +2554,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2394,7 +2562,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2402,7 +2570,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2410,7 +2578,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2418,7 +2586,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2426,7 +2594,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2434,7 +2602,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2442,7 +2610,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2450,7 +2618,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2458,7 +2626,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2466,7 +2634,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2474,7 +2642,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2482,7 +2650,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2490,7 +2658,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2498,7 +2666,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2506,7 +2674,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2514,7 +2682,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2522,7 +2690,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2530,7 +2698,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2538,7 +2706,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2546,7 +2714,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2554,7 +2722,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2562,7 +2730,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2570,7 +2738,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2578,7 +2746,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2586,7 +2754,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2594,7 +2762,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2602,7 +2770,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2610,7 +2778,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2618,7 +2786,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2626,7 +2794,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2634,7 +2802,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2642,7 +2810,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2650,7 +2818,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2658,7 +2826,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2666,7 +2834,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2674,7 +2842,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2682,7 +2850,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2690,7 +2858,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2698,7 +2866,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2706,7 +2874,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2714,7 +2882,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2722,7 +2890,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2730,7 +2898,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2738,7 +2906,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2746,7 +2914,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2754,7 +2922,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2762,7 +2930,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2770,7 +2938,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2778,7 +2946,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2786,7 +2954,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2809,7 +2977,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2817,7 +2985,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2825,7 +2993,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2833,7 +3001,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2841,7 +3009,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2849,7 +3017,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2857,7 +3025,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2865,7 +3033,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2873,7 +3041,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2881,7 +3049,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2889,7 +3057,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2897,7 +3065,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2905,7 +3073,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2913,7 +3081,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2921,7 +3089,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2929,7 +3097,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2937,7 +3105,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2945,7 +3113,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2953,7 +3121,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2961,7 +3129,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2969,7 +3137,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2977,7 +3145,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2985,7 +3153,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2993,7 +3161,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3001,7 +3169,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3009,7 +3177,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3017,7 +3185,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3025,7 +3193,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3033,7 +3201,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3041,7 +3209,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3049,7 +3217,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3057,7 +3225,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3065,7 +3233,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3073,7 +3241,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3081,7 +3249,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3089,7 +3257,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3097,7 +3265,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3105,7 +3273,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3113,7 +3281,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3121,7 +3289,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3129,7 +3297,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3137,7 +3305,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3145,7 +3313,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3153,7 +3321,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3161,7 +3329,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3169,7 +3337,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3177,7 +3345,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3185,7 +3353,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3193,7 +3361,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3201,7 +3369,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3209,7 +3377,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3217,7 +3385,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3225,7 +3393,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3243,27 +3411,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -3271,13 +3439,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -3285,13 +3453,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -3299,13 +3467,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -3313,13 +3481,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -3327,13 +3495,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -3341,13 +3509,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -3355,13 +3523,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -3369,13 +3537,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -3383,13 +3551,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
@@ -3397,13 +3565,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>352.31005859375</v>
@@ -3411,13 +3579,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13">
         <v>348.08984375</v>
@@ -3425,13 +3593,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>338.4404296875</v>
@@ -3439,13 +3607,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>334.60009765625</v>
@@ -3453,13 +3621,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>329.4404296875</v>
@@ -3481,10 +3649,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3512,10 +3680,13 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -3542,12 +3713,15 @@
         <v>79.14990234375</v>
       </c>
       <c r="J2">
-        <v>72.38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>72.080078125</v>
+      </c>
+      <c r="K2">
+        <v>72.080078125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -3574,12 +3748,15 @@
         <v>85.5</v>
       </c>
       <c r="J3">
-        <v>68.78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>68.47998046875</v>
+      </c>
+      <c r="K3">
+        <v>68.47998046875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -3606,12 +3783,15 @@
         <v>65.60009765625</v>
       </c>
       <c r="J4">
-        <v>105.28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>104.97998046875</v>
+      </c>
+      <c r="K4">
+        <v>104.97998046875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -3638,12 +3818,15 @@
         <v>79.60009765625</v>
       </c>
       <c r="J5">
-        <v>72.84999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>71.0498046875</v>
+      </c>
+      <c r="K5">
+        <v>71.0498046875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -3670,12 +3853,15 @@
         <v>76.43994140625</v>
       </c>
       <c r="J6">
-        <v>92.98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>92.68017578125</v>
+      </c>
+      <c r="K6">
+        <v>92.68017578125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -3702,12 +3888,15 @@
         <v>63.47998046875</v>
       </c>
       <c r="J7">
-        <v>104.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>104.8798828125</v>
+      </c>
+      <c r="K7">
+        <v>104.8798828125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -3734,12 +3923,15 @@
         <v>76.4501953125</v>
       </c>
       <c r="J8">
-        <v>86.34999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>85.85009765625</v>
+      </c>
+      <c r="K8">
+        <v>85.85009765625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -3766,12 +3958,15 @@
         <v>74.9501953125</v>
       </c>
       <c r="J9">
-        <v>94.18000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>93.8798828125</v>
+      </c>
+      <c r="K9">
+        <v>93.8798828125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -3798,12 +3993,15 @@
         <v>63.25</v>
       </c>
       <c r="J10">
-        <v>64.95999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>69.009765625</v>
+      </c>
+      <c r="K10">
+        <v>69.009765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -3830,12 +4028,15 @@
         <v>88.0498046875</v>
       </c>
       <c r="J11">
-        <v>78.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>78.35986328125</v>
+      </c>
+      <c r="K11">
+        <v>78.35986328125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -3862,12 +4063,15 @@
         <v>55.0400390625</v>
       </c>
       <c r="J12">
-        <v>94.18000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>93.8798828125</v>
+      </c>
+      <c r="K12">
+        <v>93.8798828125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -3894,12 +4098,15 @@
         <v>75.75</v>
       </c>
       <c r="J13">
-        <v>85.95999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>85.9599609375</v>
+      </c>
+      <c r="K13">
+        <v>85.9599609375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -3926,12 +4133,15 @@
         <v>72.0498046875</v>
       </c>
       <c r="J14">
-        <v>85.98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>84.47998046875</v>
+      </c>
+      <c r="K14">
+        <v>84.47998046875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -3958,12 +4168,15 @@
         <v>75.9501953125</v>
       </c>
       <c r="J15">
-        <v>98.84999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>98.85009765625</v>
+      </c>
+      <c r="K15">
+        <v>98.85009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -3990,12 +4203,15 @@
         <v>76.89990234375</v>
       </c>
       <c r="J16">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>79.93994140625</v>
+      </c>
+      <c r="K16">
+        <v>79.93994140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -4022,12 +4238,15 @@
         <v>65.35009765625</v>
       </c>
       <c r="J17">
-        <v>72.84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>72.83984375</v>
+      </c>
+      <c r="K17">
+        <v>72.83984375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -4054,12 +4273,15 @@
         <v>72.2998046875</v>
       </c>
       <c r="J18">
-        <v>112.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>112.8798828125</v>
+      </c>
+      <c r="K18">
+        <v>112.8798828125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -4086,12 +4308,15 @@
         <v>66.97998046875</v>
       </c>
       <c r="J19">
-        <v>116.04</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>116.0400390625</v>
+      </c>
+      <c r="K19">
+        <v>116.0400390625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -4118,12 +4343,15 @@
         <v>60.5</v>
       </c>
       <c r="J20">
-        <v>65.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>65.2998046875</v>
+      </c>
+      <c r="K20">
+        <v>65.2998046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -4150,12 +4378,15 @@
         <v>91.39990234375</v>
       </c>
       <c r="J21">
-        <v>108.94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>108.93994140625</v>
+      </c>
+      <c r="K21">
+        <v>108.93994140625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4182,12 +4413,15 @@
         <v>77.18994140625</v>
       </c>
       <c r="J22">
-        <v>82.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>81.06005859375</v>
+      </c>
+      <c r="K22">
+        <v>81.06005859375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -4214,12 +4448,15 @@
         <v>57.429931640625</v>
       </c>
       <c r="J23">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>80.93994140625</v>
+      </c>
+      <c r="K23">
+        <v>80.93994140625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -4246,12 +4483,15 @@
         <v>80.0498046875</v>
       </c>
       <c r="J24">
-        <v>61.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>59.010009765625</v>
+      </c>
+      <c r="K24">
+        <v>59.010009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -4278,12 +4518,15 @@
         <v>84.85009765625</v>
       </c>
       <c r="J25">
-        <v>86.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>84.56005859375</v>
+      </c>
+      <c r="K25">
+        <v>84.56005859375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -4310,12 +4553,15 @@
         <v>73.35009765625</v>
       </c>
       <c r="J26">
-        <v>104.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>104.68017578125</v>
+      </c>
+      <c r="K26">
+        <v>104.68017578125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -4342,12 +4588,15 @@
         <v>73.4501953125</v>
       </c>
       <c r="J27">
-        <v>71.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>69.85009765625</v>
+      </c>
+      <c r="K27">
+        <v>69.85009765625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -4374,12 +4623,15 @@
         <v>45.3701171875</v>
       </c>
       <c r="J28">
-        <v>59.86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>59.860107421875</v>
+      </c>
+      <c r="K28">
+        <v>59.860107421875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -4406,12 +4658,15 @@
         <v>72.25</v>
       </c>
       <c r="J29">
-        <v>59.68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>59.3798828125</v>
+      </c>
+      <c r="K29">
+        <v>59.3798828125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -4438,12 +4693,15 @@
         <v>73.14013671875</v>
       </c>
       <c r="J30">
-        <v>44.63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>44.6298828125</v>
+      </c>
+      <c r="K30">
+        <v>44.6298828125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -4470,12 +4728,15 @@
         <v>65.60009765625</v>
       </c>
       <c r="J31">
-        <v>106.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>106.97998046875</v>
+      </c>
+      <c r="K31">
+        <v>106.97998046875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -4502,12 +4763,15 @@
         <v>45.699951171875</v>
       </c>
       <c r="J32">
-        <v>68.84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>69.33984375</v>
+      </c>
+      <c r="K32">
+        <v>69.33984375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -4534,12 +4798,15 @@
         <v>74.0498046875</v>
       </c>
       <c r="J33">
-        <v>91.18000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>90.8798828125</v>
+      </c>
+      <c r="K33">
+        <v>90.8798828125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -4566,12 +4833,15 @@
         <v>74.83984375</v>
       </c>
       <c r="J34">
-        <v>97.23999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>97.240234375</v>
+      </c>
+      <c r="K34">
+        <v>97.240234375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -4598,12 +4868,15 @@
         <v>88.25</v>
       </c>
       <c r="J35">
-        <v>80.88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>80.8798828125</v>
+      </c>
+      <c r="K35">
+        <v>80.8798828125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -4630,12 +4903,15 @@
         <v>79.85009765625</v>
       </c>
       <c r="J36">
-        <v>101.96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>101.9599609375</v>
+      </c>
+      <c r="K36">
+        <v>101.9599609375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -4662,12 +4938,15 @@
         <v>76.25</v>
       </c>
       <c r="J37">
-        <v>57.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>56.090087890625</v>
+      </c>
+      <c r="K37">
+        <v>56.090087890625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -4694,12 +4973,15 @@
         <v>63.949951171875</v>
       </c>
       <c r="J38">
-        <v>50.78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>49.679931640625</v>
+      </c>
+      <c r="K38">
+        <v>49.679931640625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -4726,12 +5008,15 @@
         <v>26.719970703125</v>
       </c>
       <c r="J39">
-        <v>84.95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>84.64990234375</v>
+      </c>
+      <c r="K39">
+        <v>84.64990234375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -4758,12 +5043,15 @@
         <v>75.0498046875</v>
       </c>
       <c r="J40">
-        <v>98.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>96.27978515625</v>
+      </c>
+      <c r="K40">
+        <v>96.27978515625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -4790,12 +5078,15 @@
         <v>58.85009765625</v>
       </c>
       <c r="J41">
-        <v>72.84999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>68.7998046875</v>
+      </c>
+      <c r="K41">
+        <v>68.7998046875</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -4822,12 +5113,15 @@
         <v>74.85009765625</v>
       </c>
       <c r="J42">
-        <v>90.34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>90.0400390625</v>
+      </c>
+      <c r="K42">
+        <v>90.0400390625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -4854,12 +5148,15 @@
         <v>78.0498046875</v>
       </c>
       <c r="J43">
-        <v>91.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>91.14013671875</v>
+      </c>
+      <c r="K43">
+        <v>91.14013671875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -4886,12 +5183,15 @@
         <v>81.25</v>
       </c>
       <c r="J44">
-        <v>76.58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>76.27978515625</v>
+      </c>
+      <c r="K44">
+        <v>76.27978515625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -4918,12 +5218,15 @@
         <v>80.5498046875</v>
       </c>
       <c r="J45">
-        <v>65.38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>63.780029296875</v>
+      </c>
+      <c r="K45">
+        <v>63.780029296875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -4950,12 +5253,15 @@
         <v>54.360107421875</v>
       </c>
       <c r="J46">
-        <v>106.18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>107.68017578125</v>
+      </c>
+      <c r="K46">
+        <v>107.68017578125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -4982,12 +5288,15 @@
         <v>69.89990234375</v>
       </c>
       <c r="J47">
-        <v>92.14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>91.14013671875</v>
+      </c>
+      <c r="K47">
+        <v>91.14013671875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -5014,12 +5323,15 @@
         <v>80.75</v>
       </c>
       <c r="J48">
-        <v>84.73999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>84.43994140625</v>
+      </c>
+      <c r="K48">
+        <v>84.43994140625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -5046,12 +5358,15 @@
         <v>75</v>
       </c>
       <c r="J49">
-        <v>86.04000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>86.0400390625</v>
+      </c>
+      <c r="K49">
+        <v>86.0400390625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -5078,12 +5393,15 @@
         <v>76.4501953125</v>
       </c>
       <c r="J50">
-        <v>86.34999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>85.85009765625</v>
+      </c>
+      <c r="K50">
+        <v>85.85009765625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -5110,12 +5428,15 @@
         <v>67.64990234375</v>
       </c>
       <c r="J51">
-        <v>109.44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>109.43994140625</v>
+      </c>
+      <c r="K51">
+        <v>109.43994140625</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -5142,12 +5463,15 @@
         <v>84.25</v>
       </c>
       <c r="J52">
-        <v>85.54000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>85.240234375</v>
+      </c>
+      <c r="K52">
+        <v>85.240234375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -5174,12 +5498,15 @@
         <v>74.2998046875</v>
       </c>
       <c r="J53">
-        <v>77.45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>77.4501953125</v>
+      </c>
+      <c r="K53">
+        <v>77.4501953125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -5206,12 +5533,15 @@
         <v>94.31982421875</v>
       </c>
       <c r="J54">
-        <v>53.39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>53.389892578125</v>
+      </c>
+      <c r="K54">
+        <v>53.389892578125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -5238,6 +5568,9 @@
         <v>0</v>
       </c>
       <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
         <v>0</v>
       </c>
     </row>
@@ -5258,426 +5591,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B2">
-        <v>762.20986328125</v>
+        <v>848.35009765625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
-        <v>757.2400585937501</v>
+        <v>847.81982421875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B4">
-        <v>739.44033203125</v>
+        <v>836.490478515625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>739.4102148437501</v>
+        <v>831.45947265625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>739.06958984375</v>
+        <v>824.79052734375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>736.94033203125</v>
+        <v>823.239501953125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B8">
-        <v>731.8101269531251</v>
+        <v>822.29052734375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>718.829794921875</v>
+        <v>817.20947265625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>718.05005859375</v>
+        <v>808.0498046875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>715.7393164062501</v>
+        <v>807.36962890625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B12">
-        <v>714.4700390625001</v>
+        <v>806.57958984375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B13">
-        <v>713.7898632812501</v>
+        <v>803.770263671875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14">
-        <v>710.359736328125</v>
+        <v>803.110107421875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B15">
-        <v>704.259912109375</v>
+        <v>802.18994140625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>696.009658203125</v>
+        <v>788.289306640625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B17">
-        <v>693.809736328125</v>
+        <v>785.160400390625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B18">
-        <v>692.780048828125</v>
+        <v>785.139892578125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B19">
-        <v>680.66017578125</v>
+        <v>783.380126953125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="B20">
-        <v>679.130087890625</v>
+        <v>778.769775390625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="B21">
-        <v>678.700166015625</v>
+        <v>766.170166015625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B22">
-        <v>678.159931640625</v>
+        <v>765.170166015625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="B23">
-        <v>676.029892578125</v>
+        <v>764.8994140625</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>674.869716796875</v>
+        <v>763.64013671875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B25">
-        <v>669.02990234375</v>
+        <v>763.020263671875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B26">
-        <v>665.779794921875</v>
+        <v>757.949951171875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B27">
-        <v>664.04955078125</v>
+        <v>755.330078125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28">
-        <v>663.61966796875</v>
+        <v>752.929443359375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B29">
-        <v>660.0196484375</v>
+        <v>749.57958984375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B30">
-        <v>659.59013671875</v>
+        <v>748.49951171875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B31">
-        <v>652.60998046875</v>
+        <v>747.77001953125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B32">
-        <v>651.8494335937499</v>
+        <v>733.48974609375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B33">
-        <v>646.1497265625001</v>
+        <v>731.259765625</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B34">
-        <v>645.81009765625</v>
+        <v>731.2099609375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B35">
-        <v>644.81994140625</v>
+        <v>727.84033203125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B36">
-        <v>643.00931640625</v>
+        <v>721.0595703125</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B37">
-        <v>641.909873046875</v>
+        <v>716.60009765625</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B38">
-        <v>641.5196875</v>
+        <v>716.06884765625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B39">
-        <v>639.0596289062501</v>
+        <v>715.25</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B40">
-        <v>637.799609375</v>
+        <v>710.92919921875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41">
-        <v>636.0090917968751</v>
+        <v>690.999267578125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B42">
-        <v>619.38009765625</v>
+        <v>688.74951171875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B43">
-        <v>612.76994140625</v>
+        <v>687.56005859375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44">
-        <v>592.8201171875</v>
+        <v>677.169921875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B45">
-        <v>592.709384765625</v>
+        <v>666.099609375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B46">
-        <v>592.29966796875</v>
+        <v>662.549072265625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B47">
-        <v>585.9597265625</v>
+        <v>645.689453125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48">
-        <v>576.549755859375</v>
+        <v>641.349365234375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B49">
-        <v>565.920302734375</v>
+        <v>625.780517578125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B50">
-        <v>541.1699560546875</v>
+        <v>614.0096435546875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51">
-        <v>528.5897534179687</v>
+        <v>577.1696166992188</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52">
-        <v>511.140009765625</v>
+        <v>555.769775390625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53">
-        <v>476.7402587890625</v>
+        <v>541.4898681640625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B54">
-        <v>159.74994140625</v>
+        <v>239.31005859375</v>
       </c>
     </row>
   </sheetData>
@@ -5692,272 +6025,272 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5977,7 +6310,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5985,7 +6318,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5993,7 +6326,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6001,7 +6334,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6009,7 +6342,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6017,7 +6350,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6025,7 +6358,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6033,7 +6366,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6041,7 +6374,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6049,7 +6382,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6057,7 +6390,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6065,7 +6398,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6073,7 +6406,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6081,7 +6414,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6089,7 +6422,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6097,7 +6430,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6105,7 +6438,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6113,7 +6446,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6121,7 +6454,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6129,7 +6462,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6137,7 +6470,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6145,7 +6478,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6153,7 +6486,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6161,7 +6494,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6169,7 +6502,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6177,7 +6510,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6185,7 +6518,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6193,7 +6526,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6201,7 +6534,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6209,7 +6542,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6217,7 +6550,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6225,7 +6558,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -6233,7 +6566,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6241,7 +6574,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -6249,7 +6582,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -6257,7 +6590,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6265,7 +6598,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6273,7 +6606,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -6281,7 +6614,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -6289,7 +6622,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6297,7 +6630,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6305,7 +6638,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6313,7 +6646,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -6321,7 +6654,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -6329,7 +6662,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -6337,7 +6670,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -6345,7 +6678,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -6353,7 +6686,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -6361,7 +6694,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -6369,7 +6702,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -6377,7 +6710,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -6385,7 +6718,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -6393,7 +6726,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -6416,7 +6749,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -6424,7 +6757,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -6432,7 +6765,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -6440,7 +6773,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -6448,7 +6781,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -6456,7 +6789,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -6464,7 +6797,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -6472,7 +6805,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -6480,7 +6813,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -6488,7 +6821,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -6496,7 +6829,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -6504,7 +6837,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -6512,7 +6845,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -6520,7 +6853,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -6528,7 +6861,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -6536,7 +6869,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -6544,7 +6877,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -6552,7 +6885,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -6560,7 +6893,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -6568,7 +6901,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -6576,7 +6909,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -6584,7 +6917,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -6592,7 +6925,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -6600,7 +6933,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -6608,7 +6941,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -6616,7 +6949,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -6624,7 +6957,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -6632,7 +6965,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -6640,7 +6973,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -6648,7 +6981,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -6656,7 +6989,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -6664,7 +6997,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -6672,7 +7005,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -6680,7 +7013,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -6688,7 +7021,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -6696,7 +7029,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -6704,7 +7037,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -6712,7 +7045,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -6720,7 +7053,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -6728,7 +7061,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -6736,7 +7069,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -6744,7 +7077,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -6752,7 +7085,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -6760,7 +7093,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -6768,7 +7101,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -6776,7 +7109,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -6784,7 +7117,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B48">
         <v>44.260009765625</v>
@@ -6792,7 +7125,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B49">
         <v>44.06005859375</v>
@@ -6800,7 +7133,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B50">
         <v>43.510009765625</v>
@@ -6808,7 +7141,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51">
         <v>42.9599609375</v>
@@ -6816,7 +7149,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>40.60009765625</v>
@@ -6824,7 +7157,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53">
         <v>38.260009765625</v>
@@ -6832,7 +7165,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -6855,7 +7188,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -6863,7 +7196,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -6871,7 +7204,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -6879,7 +7212,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -6887,7 +7220,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -6895,7 +7228,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -6903,7 +7236,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -6911,7 +7244,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -6919,7 +7252,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -6927,7 +7260,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -6935,7 +7268,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -6943,7 +7276,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -6951,7 +7284,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -6959,7 +7292,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -6967,7 +7300,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -6975,7 +7308,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -6983,7 +7316,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -6991,7 +7324,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -6999,7 +7332,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -7007,7 +7340,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -7015,7 +7348,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -7023,7 +7356,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -7031,7 +7364,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -7039,7 +7372,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -7047,7 +7380,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26">
         <v>232.18994140625</v>
@@ -7055,7 +7388,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27">
         <v>231.8896484375</v>
@@ -7063,7 +7396,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>231.259765625</v>
@@ -7071,7 +7404,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>227.90966796875</v>
@@ -7079,7 +7412,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B30">
         <v>227.8095703125</v>
@@ -7087,7 +7420,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31">
         <v>225.2099609375</v>
@@ -7095,7 +7428,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B32">
         <v>225.02978515625</v>
@@ -7103,7 +7436,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B33">
         <v>224.409912109375</v>
@@ -7111,7 +7444,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>222.49951171875</v>
@@ -7119,7 +7452,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>219.469482421875</v>
@@ -7127,7 +7460,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36">
         <v>218.419921875</v>
@@ -7135,7 +7468,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B37">
         <v>216.3896484375</v>
@@ -7143,7 +7476,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <v>216.030517578125</v>
@@ -7151,7 +7484,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39">
         <v>215.5498046875</v>
@@ -7159,7 +7492,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B40">
         <v>212.2099609375</v>
@@ -7167,7 +7500,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B41">
         <v>211.239990234375</v>
@@ -7175,7 +7508,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42">
         <v>209.509765625</v>
@@ -7183,7 +7516,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>206.1201171875</v>
@@ -7191,7 +7524,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44">
         <v>205.58984375</v>
@@ -7199,7 +7532,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>204.8798828125</v>
@@ -7207,7 +7540,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B46">
         <v>199.2001953125</v>
@@ -7215,7 +7548,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47">
         <v>198.499755859375</v>
@@ -7223,7 +7556,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B48">
         <v>197.369873046875</v>
@@ -7231,7 +7564,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49">
         <v>191.85986328125</v>
@@ -7239,7 +7572,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>187.64990234375</v>
@@ -7247,7 +7580,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51">
         <v>186.4697265625</v>
@@ -7255,7 +7588,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B52">
         <v>159.43994140625</v>
@@ -7263,7 +7596,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
@@ -7271,7 +7604,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7294,7 +7627,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>352.31005859375</v>
@@ -7302,7 +7635,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>348.08984375</v>
@@ -7310,7 +7643,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>338.4404296875</v>
@@ -7318,7 +7651,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>334.60009765625</v>
@@ -7326,7 +7659,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <v>329.4404296875</v>
@@ -7334,7 +7667,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <v>328.05029296875</v>
@@ -7342,7 +7675,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>323.5302734375</v>
@@ -7350,7 +7683,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>318.04052734375</v>
@@ -7358,7 +7691,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>317.26025390625</v>
@@ -7366,7 +7699,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>316.66015625</v>
@@ -7374,7 +7707,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12">
         <v>315.94970703125</v>
@@ -7382,7 +7715,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>303.949462890625</v>
@@ -7390,7 +7723,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>300.99951171875</v>
@@ -7398,7 +7731,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>300.5</v>
@@ -7406,7 +7739,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>300.099609375</v>
@@ -7414,7 +7747,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <v>299.199951171875</v>
@@ -7422,7 +7755,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>299.009765625</v>
@@ -7430,7 +7763,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>298.93017578125</v>
@@ -7438,7 +7771,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>298.8798828125</v>
@@ -7446,7 +7779,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>296.4697265625</v>
@@ -7454,7 +7787,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>296.07958984375</v>
@@ -7462,7 +7795,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <v>295.85009765625</v>
@@ -7470,7 +7803,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24">
         <v>294.43994140625</v>
@@ -7478,7 +7811,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25">
         <v>293.139892578125</v>
@@ -7486,7 +7819,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>290.2998046875</v>
@@ -7494,7 +7827,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27">
         <v>289</v>
@@ -7502,7 +7835,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>288.1103515625</v>
@@ -7510,7 +7843,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>288.1103515625</v>
@@ -7518,7 +7851,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>287.43017578125</v>
@@ -7526,7 +7859,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>286.16015625</v>
@@ -7534,7 +7867,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B32">
         <v>285.639892578125</v>
@@ -7542,7 +7875,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>284.639892578125</v>
@@ -7550,7 +7883,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34">
         <v>284.2900390625</v>
@@ -7558,7 +7891,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>284.2294921875</v>
@@ -7566,7 +7899,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36">
         <v>283.899658203125</v>
@@ -7574,7 +7907,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <v>282.68994140625</v>
@@ -7582,7 +7915,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>280.650390625</v>
@@ -7590,7 +7923,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B39">
         <v>279.340087890625</v>
@@ -7598,7 +7931,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>277.80029296875</v>
@@ -7606,7 +7939,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>276.829833984375</v>
@@ -7614,7 +7947,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42">
         <v>272.47998046875</v>
@@ -7622,7 +7955,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43">
         <v>269.719970703125</v>
@@ -7630,7 +7963,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B44">
         <v>259.3798828125</v>
@@ -7638,7 +7971,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B45">
         <v>253.94970703125</v>
@@ -7646,7 +7979,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46">
         <v>244.02978515625</v>
@@ -7654,7 +7987,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>234.26025390625</v>
@@ -7662,7 +7995,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B48">
         <v>230.099853515625</v>
@@ -7670,7 +8003,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49">
         <v>228.480224609375</v>
@@ -7678,7 +8011,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50">
         <v>222.0400390625</v>
@@ -7686,7 +8019,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51">
         <v>221.0599975585938</v>
@@ -7694,7 +8027,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52">
         <v>216.89013671875</v>
@@ -7702,7 +8035,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B53">
         <v>199.0599365234375</v>
@@ -7710,7 +8043,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B54">
         <v>77.18994140625</v>
@@ -7733,426 +8066,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>116.04</v>
+        <v>232.080078125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>112.88</v>
+        <v>225.759765625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4">
-        <v>109.44</v>
+        <v>218.8798828125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <v>108.94</v>
+        <v>217.8798828125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B6">
-        <v>106.98</v>
+        <v>215.3603515625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B7">
-        <v>106.18</v>
+        <v>213.9599609375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
-        <v>105.28</v>
+        <v>209.9599609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>104.88</v>
+        <v>209.759765625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10">
-        <v>104.68</v>
+        <v>209.3603515625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11">
-        <v>101.96</v>
+        <v>203.919921875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>98.84999999999999</v>
+        <v>197.7001953125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B13">
-        <v>98.08</v>
+        <v>194.48046875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B14">
-        <v>97.23999999999999</v>
+        <v>192.5595703125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>94.18000000000001</v>
+        <v>187.759765625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>94.18000000000001</v>
+        <v>187.759765625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
-        <v>92.98</v>
+        <v>185.3603515625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B18">
-        <v>92.14</v>
+        <v>182.2802734375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B19">
-        <v>91.44</v>
+        <v>182.2802734375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20">
-        <v>91.18000000000001</v>
+        <v>181.759765625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21">
-        <v>90.34</v>
+        <v>180.080078125</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B22">
-        <v>86.36</v>
+        <v>172.080078125</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>86.34999999999999</v>
+        <v>171.919921875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B24">
-        <v>86.34999999999999</v>
+        <v>171.7001953125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="B25">
-        <v>86.04000000000001</v>
+        <v>171.7001953125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B26">
-        <v>85.98</v>
+        <v>170.48046875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B27">
-        <v>85.95999999999999</v>
+        <v>169.2998046875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B28">
-        <v>85.54000000000001</v>
+        <v>169.1201171875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B29">
-        <v>84.95</v>
+        <v>168.9599609375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B30">
-        <v>84.73999999999999</v>
+        <v>168.8798828125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>82.56</v>
+        <v>162.1201171875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>81.73999999999999</v>
+        <v>161.8798828125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B33">
-        <v>81.73999999999999</v>
+        <v>161.759765625</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B34">
-        <v>80.88</v>
+        <v>159.8798828125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35">
-        <v>78.66</v>
+        <v>156.7197265625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36">
-        <v>77.45</v>
+        <v>154.900390625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>76.58</v>
+        <v>152.5595703125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B38">
-        <v>72.84999999999999</v>
+        <v>145.6796875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B39">
-        <v>72.84999999999999</v>
+        <v>144.16015625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B40">
-        <v>72.84</v>
+        <v>142.099609375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B41">
-        <v>72.38</v>
+        <v>139.7001953125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>71.45</v>
+        <v>138.6796875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B43">
-        <v>68.84</v>
+        <v>138.01953125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B44">
-        <v>68.78</v>
+        <v>137.599609375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B45">
-        <v>65.8</v>
+        <v>136.9599609375</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B46">
-        <v>65.38</v>
+        <v>130.599609375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B47">
-        <v>64.95999999999999</v>
+        <v>127.56005859375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B48">
-        <v>61.01</v>
+        <v>119.72021484375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B49">
-        <v>59.86</v>
+        <v>118.759765625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B50">
-        <v>59.68</v>
+        <v>118.02001953125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51">
-        <v>57.19</v>
+        <v>112.18017578125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B52">
-        <v>53.39</v>
+        <v>106.77978515625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B53">
-        <v>50.78</v>
+        <v>99.35986328125</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B54">
-        <v>44.63</v>
+        <v>89.259765625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -663,7 +663,7 @@
         <v>72.080078125</v>
       </c>
       <c r="K2">
-        <v>72.080078125</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -698,7 +698,7 @@
         <v>68.47998046875</v>
       </c>
       <c r="K3">
-        <v>68.47998046875</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -733,7 +733,7 @@
         <v>104.97998046875</v>
       </c>
       <c r="K4">
-        <v>104.97998046875</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -768,7 +768,7 @@
         <v>71.0498046875</v>
       </c>
       <c r="K5">
-        <v>71.0498046875</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -803,7 +803,7 @@
         <v>92.68017578125</v>
       </c>
       <c r="K6">
-        <v>92.68017578125</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -838,7 +838,7 @@
         <v>104.8798828125</v>
       </c>
       <c r="K7">
-        <v>104.8798828125</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -873,7 +873,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K8">
-        <v>85.85009765625</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -908,7 +908,7 @@
         <v>93.8798828125</v>
       </c>
       <c r="K9">
-        <v>93.8798828125</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -943,7 +943,7 @@
         <v>69.009765625</v>
       </c>
       <c r="K10">
-        <v>69.009765625</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -978,7 +978,7 @@
         <v>78.35986328125</v>
       </c>
       <c r="K11">
-        <v>78.35986328125</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1013,7 +1013,7 @@
         <v>93.8798828125</v>
       </c>
       <c r="K12">
-        <v>93.8798828125</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1048,7 +1048,7 @@
         <v>85.9599609375</v>
       </c>
       <c r="K13">
-        <v>85.9599609375</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1083,7 +1083,7 @@
         <v>84.47998046875</v>
       </c>
       <c r="K14">
-        <v>84.47998046875</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1118,7 +1118,7 @@
         <v>98.85009765625</v>
       </c>
       <c r="K15">
-        <v>98.85009765625</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1153,7 +1153,7 @@
         <v>79.93994140625</v>
       </c>
       <c r="K16">
-        <v>79.93994140625</v>
+        <v>55.19</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1188,7 +1188,7 @@
         <v>72.83984375</v>
       </c>
       <c r="K17">
-        <v>72.83984375</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1223,7 +1223,7 @@
         <v>112.8798828125</v>
       </c>
       <c r="K18">
-        <v>112.8798828125</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1258,7 +1258,7 @@
         <v>116.0400390625</v>
       </c>
       <c r="K19">
-        <v>116.0400390625</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1293,7 +1293,7 @@
         <v>65.2998046875</v>
       </c>
       <c r="K20">
-        <v>65.2998046875</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1328,7 +1328,7 @@
         <v>108.93994140625</v>
       </c>
       <c r="K21">
-        <v>108.93994140625</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1363,7 +1363,7 @@
         <v>81.06005859375</v>
       </c>
       <c r="K22">
-        <v>81.06005859375</v>
+        <v>77.58</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1398,7 +1398,7 @@
         <v>80.93994140625</v>
       </c>
       <c r="K23">
-        <v>80.93994140625</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1433,7 +1433,7 @@
         <v>59.010009765625</v>
       </c>
       <c r="K24">
-        <v>59.010009765625</v>
+        <v>60.57</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1468,7 +1468,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="K25">
-        <v>84.56005859375</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1503,7 +1503,7 @@
         <v>104.68017578125</v>
       </c>
       <c r="K26">
-        <v>104.68017578125</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1538,7 +1538,7 @@
         <v>69.85009765625</v>
       </c>
       <c r="K27">
-        <v>69.85009765625</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1573,7 +1573,7 @@
         <v>59.860107421875</v>
       </c>
       <c r="K28">
-        <v>59.860107421875</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1608,7 +1608,7 @@
         <v>59.3798828125</v>
       </c>
       <c r="K29">
-        <v>59.3798828125</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1643,7 +1643,7 @@
         <v>44.6298828125</v>
       </c>
       <c r="K30">
-        <v>44.6298828125</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1678,7 +1678,7 @@
         <v>106.97998046875</v>
       </c>
       <c r="K31">
-        <v>106.97998046875</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1713,7 +1713,7 @@
         <v>69.33984375</v>
       </c>
       <c r="K32">
-        <v>69.33984375</v>
+        <v>84.47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1748,7 +1748,7 @@
         <v>90.8798828125</v>
       </c>
       <c r="K33">
-        <v>90.8798828125</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1783,7 +1783,7 @@
         <v>97.240234375</v>
       </c>
       <c r="K34">
-        <v>97.240234375</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1818,7 +1818,7 @@
         <v>80.8798828125</v>
       </c>
       <c r="K35">
-        <v>80.8798828125</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1853,7 +1853,7 @@
         <v>101.9599609375</v>
       </c>
       <c r="K36">
-        <v>101.9599609375</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1888,7 +1888,7 @@
         <v>56.090087890625</v>
       </c>
       <c r="K37">
-        <v>56.090087890625</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1923,7 +1923,7 @@
         <v>49.679931640625</v>
       </c>
       <c r="K38">
-        <v>49.679931640625</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1958,7 +1958,7 @@
         <v>84.64990234375</v>
       </c>
       <c r="K39">
-        <v>84.64990234375</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1993,7 +1993,7 @@
         <v>96.27978515625</v>
       </c>
       <c r="K40">
-        <v>96.27978515625</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2028,7 +2028,7 @@
         <v>68.7998046875</v>
       </c>
       <c r="K41">
-        <v>68.7998046875</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2063,7 +2063,7 @@
         <v>90.0400390625</v>
       </c>
       <c r="K42">
-        <v>90.0400390625</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2098,7 +2098,7 @@
         <v>91.14013671875</v>
       </c>
       <c r="K43">
-        <v>91.14013671875</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2133,7 +2133,7 @@
         <v>76.27978515625</v>
       </c>
       <c r="K44">
-        <v>76.27978515625</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2168,7 +2168,7 @@
         <v>63.780029296875</v>
       </c>
       <c r="K45">
-        <v>63.780029296875</v>
+        <v>64.69</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2203,7 +2203,7 @@
         <v>107.68017578125</v>
       </c>
       <c r="K46">
-        <v>107.68017578125</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2238,7 +2238,7 @@
         <v>91.14013671875</v>
       </c>
       <c r="K47">
-        <v>91.14013671875</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2273,7 +2273,7 @@
         <v>84.43994140625</v>
       </c>
       <c r="K48">
-        <v>84.43994140625</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2308,7 +2308,7 @@
         <v>86.0400390625</v>
       </c>
       <c r="K49">
-        <v>86.0400390625</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2343,7 +2343,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K50">
-        <v>85.85009765625</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2378,7 +2378,7 @@
         <v>109.43994140625</v>
       </c>
       <c r="K51">
-        <v>109.43994140625</v>
+        <v>63.97</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2413,7 +2413,7 @@
         <v>85.240234375</v>
       </c>
       <c r="K52">
-        <v>85.240234375</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2448,7 +2448,7 @@
         <v>77.4501953125</v>
       </c>
       <c r="K53">
-        <v>77.4501953125</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2483,7 +2483,7 @@
         <v>53.389892578125</v>
       </c>
       <c r="K54">
-        <v>53.389892578125</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3716,7 +3716,7 @@
         <v>72.080078125</v>
       </c>
       <c r="K2">
-        <v>72.080078125</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3751,7 +3751,7 @@
         <v>68.47998046875</v>
       </c>
       <c r="K3">
-        <v>68.47998046875</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3786,7 +3786,7 @@
         <v>104.97998046875</v>
       </c>
       <c r="K4">
-        <v>104.97998046875</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3821,7 +3821,7 @@
         <v>71.0498046875</v>
       </c>
       <c r="K5">
-        <v>71.0498046875</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3856,7 +3856,7 @@
         <v>92.68017578125</v>
       </c>
       <c r="K6">
-        <v>92.68017578125</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3891,7 +3891,7 @@
         <v>104.8798828125</v>
       </c>
       <c r="K7">
-        <v>104.8798828125</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3926,7 +3926,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K8">
-        <v>85.85009765625</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3961,7 +3961,7 @@
         <v>93.8798828125</v>
       </c>
       <c r="K9">
-        <v>93.8798828125</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3996,7 +3996,7 @@
         <v>69.009765625</v>
       </c>
       <c r="K10">
-        <v>69.009765625</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4031,7 +4031,7 @@
         <v>78.35986328125</v>
       </c>
       <c r="K11">
-        <v>78.35986328125</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4066,7 +4066,7 @@
         <v>93.8798828125</v>
       </c>
       <c r="K12">
-        <v>93.8798828125</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4101,7 +4101,7 @@
         <v>85.9599609375</v>
       </c>
       <c r="K13">
-        <v>85.9599609375</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4136,7 +4136,7 @@
         <v>84.47998046875</v>
       </c>
       <c r="K14">
-        <v>84.47998046875</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4171,7 +4171,7 @@
         <v>98.85009765625</v>
       </c>
       <c r="K15">
-        <v>98.85009765625</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4206,7 +4206,7 @@
         <v>79.93994140625</v>
       </c>
       <c r="K16">
-        <v>79.93994140625</v>
+        <v>55.19</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4241,7 +4241,7 @@
         <v>72.83984375</v>
       </c>
       <c r="K17">
-        <v>72.83984375</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4276,7 +4276,7 @@
         <v>112.8798828125</v>
       </c>
       <c r="K18">
-        <v>112.8798828125</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4311,7 +4311,7 @@
         <v>116.0400390625</v>
       </c>
       <c r="K19">
-        <v>116.0400390625</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4346,7 +4346,7 @@
         <v>65.2998046875</v>
       </c>
       <c r="K20">
-        <v>65.2998046875</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4381,7 +4381,7 @@
         <v>108.93994140625</v>
       </c>
       <c r="K21">
-        <v>108.93994140625</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4416,7 +4416,7 @@
         <v>81.06005859375</v>
       </c>
       <c r="K22">
-        <v>81.06005859375</v>
+        <v>77.58</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4451,7 +4451,7 @@
         <v>80.93994140625</v>
       </c>
       <c r="K23">
-        <v>80.93994140625</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4486,7 +4486,7 @@
         <v>59.010009765625</v>
       </c>
       <c r="K24">
-        <v>59.010009765625</v>
+        <v>60.57</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4521,7 +4521,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="K25">
-        <v>84.56005859375</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4556,7 +4556,7 @@
         <v>104.68017578125</v>
       </c>
       <c r="K26">
-        <v>104.68017578125</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4591,7 +4591,7 @@
         <v>69.85009765625</v>
       </c>
       <c r="K27">
-        <v>69.85009765625</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4626,7 +4626,7 @@
         <v>59.860107421875</v>
       </c>
       <c r="K28">
-        <v>59.860107421875</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4661,7 +4661,7 @@
         <v>59.3798828125</v>
       </c>
       <c r="K29">
-        <v>59.3798828125</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4696,7 +4696,7 @@
         <v>44.6298828125</v>
       </c>
       <c r="K30">
-        <v>44.6298828125</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4731,7 +4731,7 @@
         <v>106.97998046875</v>
       </c>
       <c r="K31">
-        <v>106.97998046875</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4766,7 +4766,7 @@
         <v>69.33984375</v>
       </c>
       <c r="K32">
-        <v>69.33984375</v>
+        <v>84.47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4801,7 +4801,7 @@
         <v>90.8798828125</v>
       </c>
       <c r="K33">
-        <v>90.8798828125</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4836,7 +4836,7 @@
         <v>97.240234375</v>
       </c>
       <c r="K34">
-        <v>97.240234375</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4871,7 +4871,7 @@
         <v>80.8798828125</v>
       </c>
       <c r="K35">
-        <v>80.8798828125</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4906,7 +4906,7 @@
         <v>101.9599609375</v>
       </c>
       <c r="K36">
-        <v>101.9599609375</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4941,7 +4941,7 @@
         <v>56.090087890625</v>
       </c>
       <c r="K37">
-        <v>56.090087890625</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4976,7 +4976,7 @@
         <v>49.679931640625</v>
       </c>
       <c r="K38">
-        <v>49.679931640625</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5011,7 +5011,7 @@
         <v>84.64990234375</v>
       </c>
       <c r="K39">
-        <v>84.64990234375</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5046,7 +5046,7 @@
         <v>96.27978515625</v>
       </c>
       <c r="K40">
-        <v>96.27978515625</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5081,7 +5081,7 @@
         <v>68.7998046875</v>
       </c>
       <c r="K41">
-        <v>68.7998046875</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5116,7 +5116,7 @@
         <v>90.0400390625</v>
       </c>
       <c r="K42">
-        <v>90.0400390625</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5151,7 +5151,7 @@
         <v>91.14013671875</v>
       </c>
       <c r="K43">
-        <v>91.14013671875</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5186,7 +5186,7 @@
         <v>76.27978515625</v>
       </c>
       <c r="K44">
-        <v>76.27978515625</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5221,7 +5221,7 @@
         <v>63.780029296875</v>
       </c>
       <c r="K45">
-        <v>63.780029296875</v>
+        <v>64.69</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5256,7 +5256,7 @@
         <v>107.68017578125</v>
       </c>
       <c r="K46">
-        <v>107.68017578125</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -5291,7 +5291,7 @@
         <v>91.14013671875</v>
       </c>
       <c r="K47">
-        <v>91.14013671875</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5326,7 +5326,7 @@
         <v>84.43994140625</v>
       </c>
       <c r="K48">
-        <v>84.43994140625</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5361,7 +5361,7 @@
         <v>86.0400390625</v>
       </c>
       <c r="K49">
-        <v>86.0400390625</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5396,7 +5396,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K50">
-        <v>85.85009765625</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5431,7 +5431,7 @@
         <v>109.43994140625</v>
       </c>
       <c r="K51">
-        <v>109.43994140625</v>
+        <v>63.97</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5466,7 +5466,7 @@
         <v>85.240234375</v>
       </c>
       <c r="K52">
-        <v>85.240234375</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5501,7 +5501,7 @@
         <v>77.4501953125</v>
       </c>
       <c r="K53">
-        <v>77.4501953125</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5536,7 +5536,7 @@
         <v>53.389892578125</v>
       </c>
       <c r="K54">
-        <v>53.389892578125</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -5591,10 +5591,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>848.35009765625</v>
+        <v>818.29966796875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5602,7 +5602,7 @@
         <v>41</v>
       </c>
       <c r="B3">
-        <v>847.81982421875</v>
+        <v>805.70994140625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5610,55 +5610,55 @@
         <v>34</v>
       </c>
       <c r="B4">
-        <v>836.490478515625</v>
+        <v>799.100302734375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>831.45947265625</v>
+        <v>798.2304296875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>824.79052734375</v>
+        <v>796.50015625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B7">
-        <v>823.239501953125</v>
+        <v>795.7304296875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>822.29052734375</v>
+        <v>792.4595312500001</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="B9">
-        <v>817.20947265625</v>
+        <v>786.22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>808.0498046875</v>
+        <v>775.829619140625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5666,63 +5666,63 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>807.36962890625</v>
+        <v>771.87974609375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>806.57958984375</v>
+        <v>770.899521484375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="B13">
-        <v>803.770263671875</v>
+        <v>770.730009765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B14">
-        <v>803.110107421875</v>
+        <v>770.7200292968751</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B15">
-        <v>802.18994140625</v>
+        <v>766.6294531250001</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>788.289306640625</v>
+        <v>766.139921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>785.160400390625</v>
+        <v>752.679716796875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B18">
-        <v>785.139892578125</v>
+        <v>732.1199316406251</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5730,39 +5730,39 @@
         <v>12</v>
       </c>
       <c r="B19">
-        <v>783.380126953125</v>
+        <v>731.4701464843751</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B20">
-        <v>778.769775390625</v>
+        <v>731.250029296875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B21">
-        <v>766.170166015625</v>
+        <v>729.570224609375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="B22">
-        <v>765.170166015625</v>
+        <v>729.349580078125</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>764.8994140625</v>
+        <v>728.829912109375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5770,151 +5770,151 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>763.64013671875</v>
+        <v>728.63015625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B25">
-        <v>763.020263671875</v>
+        <v>727.98005859375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B26">
-        <v>757.949951171875</v>
+        <v>726.920126953125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27">
-        <v>755.330078125</v>
+        <v>723.300029296875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B28">
-        <v>752.929443359375</v>
+        <v>722.6195605468751</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>749.57958984375</v>
+        <v>721.07986328125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="B30">
-        <v>748.49951171875</v>
+        <v>719.78953125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B31">
-        <v>747.77001953125</v>
+        <v>718.21931640625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B32">
-        <v>733.48974609375</v>
+        <v>717.7199023437499</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B33">
-        <v>731.259765625</v>
+        <v>703.48962890625</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B34">
-        <v>731.2099609375</v>
+        <v>703.0295703125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B35">
-        <v>727.84033203125</v>
+        <v>697.5498046875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B36">
-        <v>721.0595703125</v>
+        <v>693.69001953125</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B37">
-        <v>716.60009765625</v>
+        <v>692.579912109375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B38">
-        <v>716.06884765625</v>
+        <v>689.040234375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="B39">
-        <v>715.25</v>
+        <v>680.83908203125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B40">
-        <v>710.92919921875</v>
+        <v>680.7897265625001</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>690.999267578125</v>
+        <v>677.679228515625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B42">
-        <v>688.74951171875</v>
+        <v>676.9791796875001</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5922,47 +5922,47 @@
         <v>11</v>
       </c>
       <c r="B43">
-        <v>687.56005859375</v>
+        <v>673.450078125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B44">
-        <v>677.169921875</v>
+        <v>663.6497265624999</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B45">
-        <v>666.099609375</v>
+        <v>635.67001953125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B46">
-        <v>662.549072265625</v>
+        <v>632.099560546875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B47">
-        <v>645.689453125</v>
+        <v>626.839560546875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B48">
-        <v>641.349365234375</v>
+        <v>624.2296679687501</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -5970,7 +5970,7 @@
         <v>36</v>
       </c>
       <c r="B49">
-        <v>625.780517578125</v>
+        <v>621.39041015625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -5978,7 +5978,7 @@
         <v>25</v>
       </c>
       <c r="B50">
-        <v>614.0096435546875</v>
+        <v>610.4397998046875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -5986,7 +5986,7 @@
         <v>46</v>
       </c>
       <c r="B51">
-        <v>577.1696166992188</v>
+        <v>577.8596850585938</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -5994,7 +5994,7 @@
         <v>38</v>
       </c>
       <c r="B52">
-        <v>555.769775390625</v>
+        <v>574.309892578125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -6002,7 +6002,7 @@
         <v>49</v>
       </c>
       <c r="B53">
-        <v>541.4898681640625</v>
+        <v>521.5400634765625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6010,7 +6010,7 @@
         <v>30</v>
       </c>
       <c r="B54">
-        <v>239.31005859375</v>
+        <v>235.83</v>
       </c>
     </row>
   </sheetData>
@@ -8066,10 +8066,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B2">
-        <v>232.080078125</v>
+        <v>184.1299609375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8077,359 +8077,359 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>225.759765625</v>
+        <v>178.3498828125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B4">
-        <v>218.8798828125</v>
+        <v>177.75017578125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B5">
-        <v>217.8798828125</v>
+        <v>175.16978515625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B6">
-        <v>215.3603515625</v>
+        <v>173.40994140625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B7">
-        <v>213.9599609375</v>
+        <v>171.97017578125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>209.9599609375</v>
+        <v>166.7100390625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>209.759765625</v>
+        <v>166.02994140625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>209.3603515625</v>
+        <v>165.32009765625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B11">
-        <v>203.919921875</v>
+        <v>164.6498828125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B12">
-        <v>197.7001953125</v>
+        <v>162.710234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B13">
-        <v>194.48046875</v>
+        <v>158.64005859375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>192.5595703125</v>
+        <v>158.04998046875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B15">
-        <v>187.759765625</v>
+        <v>157.64998046875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B16">
-        <v>187.759765625</v>
+        <v>153.80984375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B17">
-        <v>185.3603515625</v>
+        <v>152.90994140625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>182.2802734375</v>
+        <v>152.2698828125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B19">
-        <v>182.2802734375</v>
+        <v>149.3498828125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>181.759765625</v>
+        <v>145.8498828125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B21">
-        <v>180.080078125</v>
+        <v>145.14009765625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="B22">
-        <v>172.080078125</v>
+        <v>145.14009765625</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B23">
-        <v>171.919921875</v>
+        <v>143.03005859375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B24">
-        <v>171.7001953125</v>
+        <v>142.33013671875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>171.7001953125</v>
+        <v>142.10984375</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>170.48046875</v>
+        <v>139.6498828125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B27">
-        <v>169.2998046875</v>
+        <v>139.41013671875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B28">
-        <v>169.1201171875</v>
+        <v>137.430234375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B29">
-        <v>168.9599609375</v>
+        <v>137.2001953125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B30">
-        <v>168.8798828125</v>
+        <v>135.12994140625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31">
-        <v>162.1201171875</v>
+        <v>133.94998046875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B32">
-        <v>161.8798828125</v>
+        <v>133.8300390625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B33">
-        <v>161.759765625</v>
+        <v>133.13986328125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B34">
-        <v>159.8798828125</v>
+        <v>129.77017578125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>156.7197265625</v>
+        <v>129.6100390625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="B36">
-        <v>154.900390625</v>
+        <v>128.9398046875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>152.5595703125</v>
+        <v>128.470029296875</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B38">
-        <v>145.6796875</v>
+        <v>127.79990234375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B39">
-        <v>144.16015625</v>
+        <v>127.45978515625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B40">
-        <v>142.099609375</v>
+        <v>126.0498828125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B41">
-        <v>139.7001953125</v>
+        <v>125.8299609375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B42">
-        <v>138.6796875</v>
+        <v>122.84998046875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B43">
-        <v>138.01953125</v>
+        <v>121.250078125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B44">
-        <v>137.599609375</v>
+        <v>120.00994140625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B45">
-        <v>136.9599609375</v>
+        <v>119.580009765625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B46">
-        <v>130.599609375</v>
+        <v>117.6498046875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="B47">
-        <v>127.56005859375</v>
+        <v>116.0898046875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -8437,55 +8437,55 @@
         <v>36</v>
       </c>
       <c r="B48">
-        <v>119.72021484375</v>
+        <v>115.330107421875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49">
-        <v>118.759765625</v>
+        <v>107.7998828125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B50">
-        <v>118.02001953125</v>
+        <v>102.789765625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B51">
-        <v>112.18017578125</v>
+        <v>100.90009765625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B52">
-        <v>106.77978515625</v>
+        <v>100.049931640625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53">
-        <v>99.35986328125</v>
+        <v>98.16008789062499</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="B54">
-        <v>89.259765625</v>
+        <v>93.189892578125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="72">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Rodada 10</t>
+  </si>
+  <si>
+    <t>Rodada 11</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -596,10 +599,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,10 +633,13 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -663,12 +669,15 @@
         <v>72.080078125</v>
       </c>
       <c r="K2">
-        <v>49.17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>47.969970703125</v>
+      </c>
+      <c r="L2">
+        <v>47.969970703125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -698,12 +707,15 @@
         <v>68.47998046875</v>
       </c>
       <c r="K3">
-        <v>54.37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>53.169921875</v>
+      </c>
+      <c r="L3">
+        <v>53.169921875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -733,12 +745,15 @@
         <v>104.97998046875</v>
       </c>
       <c r="K4">
-        <v>53.07</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>52.27001953125</v>
+      </c>
+      <c r="L4">
+        <v>52.27001953125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -768,12 +783,15 @@
         <v>71.0498046875</v>
       </c>
       <c r="K5">
-        <v>57.89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>57.489990234375</v>
+      </c>
+      <c r="L5">
+        <v>57.489990234375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -803,12 +821,15 @@
         <v>92.68017578125</v>
       </c>
       <c r="K6">
-        <v>37.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>37.090087890625</v>
+      </c>
+      <c r="L6">
+        <v>37.090087890625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -838,12 +859,15 @@
         <v>104.8798828125</v>
       </c>
       <c r="K7">
-        <v>59.77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>59.3701171875</v>
+      </c>
+      <c r="L7">
+        <v>59.3701171875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -873,12 +897,15 @@
         <v>85.85009765625</v>
       </c>
       <c r="K8">
-        <v>59.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>58.090087890625</v>
+      </c>
+      <c r="L8">
+        <v>58.090087890625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -908,12 +935,15 @@
         <v>93.8798828125</v>
       </c>
       <c r="K9">
-        <v>58.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>57.18994140625</v>
+      </c>
+      <c r="L9">
+        <v>57.18994140625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -943,12 +973,15 @@
         <v>69.009765625</v>
       </c>
       <c r="K10">
-        <v>33.78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>33.3798828125</v>
+      </c>
+      <c r="L10">
+        <v>33.3798828125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -978,12 +1011,15 @@
         <v>78.35986328125</v>
       </c>
       <c r="K11">
-        <v>54.78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>53.97998046875</v>
+      </c>
+      <c r="L11">
+        <v>53.97998046875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -1013,12 +1049,15 @@
         <v>93.8798828125</v>
       </c>
       <c r="K12">
-        <v>51.97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>51.570068359375</v>
+      </c>
+      <c r="L12">
+        <v>51.570068359375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -1048,12 +1087,15 @@
         <v>85.9599609375</v>
       </c>
       <c r="K13">
-        <v>39.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>39.469970703125</v>
+      </c>
+      <c r="L13">
+        <v>39.469970703125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -1083,12 +1125,15 @@
         <v>84.47998046875</v>
       </c>
       <c r="K14">
-        <v>49.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>48.669921875</v>
+      </c>
+      <c r="L14">
+        <v>48.669921875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -1118,12 +1163,15 @@
         <v>98.85009765625</v>
       </c>
       <c r="K15">
-        <v>66.47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>66.06982421875</v>
+      </c>
+      <c r="L15">
+        <v>66.06982421875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -1153,12 +1201,15 @@
         <v>79.93994140625</v>
       </c>
       <c r="K16">
-        <v>55.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>54.389892578125</v>
+      </c>
+      <c r="L16">
+        <v>54.389892578125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -1188,12 +1239,15 @@
         <v>72.83984375</v>
       </c>
       <c r="K17">
-        <v>69.27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>68.8701171875</v>
+      </c>
+      <c r="L17">
+        <v>68.8701171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -1223,12 +1277,15 @@
         <v>112.8798828125</v>
       </c>
       <c r="K18">
-        <v>65.47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>64.27001953125</v>
+      </c>
+      <c r="L18">
+        <v>64.27001953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -1258,12 +1315,15 @@
         <v>116.0400390625</v>
       </c>
       <c r="K19">
-        <v>50.67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>50.669921875</v>
+      </c>
+      <c r="L19">
+        <v>50.669921875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -1293,12 +1353,15 @@
         <v>65.2998046875</v>
       </c>
       <c r="K20">
-        <v>50.79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>50.7900390625</v>
+      </c>
+      <c r="L20">
+        <v>50.7900390625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -1328,12 +1391,15 @@
         <v>108.93994140625</v>
       </c>
       <c r="K21">
-        <v>57.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>55.889892578125</v>
+      </c>
+      <c r="L21">
+        <v>55.889892578125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1363,12 +1429,15 @@
         <v>81.06005859375</v>
       </c>
       <c r="K22">
-        <v>77.58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>78.3798828125</v>
+      </c>
+      <c r="L22">
+        <v>78.3798828125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1398,12 +1467,15 @@
         <v>80.93994140625</v>
       </c>
       <c r="K23">
-        <v>39.07</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>39.070068359375</v>
+      </c>
+      <c r="L23">
+        <v>39.070068359375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1433,12 +1505,15 @@
         <v>59.010009765625</v>
       </c>
       <c r="K24">
-        <v>60.57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>60.169921875</v>
+      </c>
+      <c r="L24">
+        <v>60.169921875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1468,12 +1543,15 @@
         <v>84.56005859375</v>
       </c>
       <c r="K25">
-        <v>58.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>58.070068359375</v>
+      </c>
+      <c r="L25">
+        <v>58.070068359375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1503,12 +1581,15 @@
         <v>104.68017578125</v>
       </c>
       <c r="K26">
-        <v>67.29000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>66.89013671875</v>
+      </c>
+      <c r="L26">
+        <v>66.89013671875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1538,12 +1619,15 @@
         <v>69.85009765625</v>
       </c>
       <c r="K27">
-        <v>31.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>29.8499755859375</v>
+      </c>
+      <c r="L27">
+        <v>29.8499755859375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1573,12 +1657,15 @@
         <v>59.860107421875</v>
       </c>
       <c r="K28">
-        <v>55.47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>54.27001953125</v>
+      </c>
+      <c r="L28">
+        <v>54.27001953125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1608,12 +1695,15 @@
         <v>59.3798828125</v>
       </c>
       <c r="K29">
-        <v>66.67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>66.27001953125</v>
+      </c>
+      <c r="L29">
+        <v>66.27001953125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1643,12 +1733,15 @@
         <v>44.6298828125</v>
       </c>
       <c r="K30">
-        <v>63.17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>63.169921875</v>
+      </c>
+      <c r="L30">
+        <v>63.169921875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1678,12 +1771,15 @@
         <v>106.97998046875</v>
       </c>
       <c r="K31">
-        <v>50.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>50.669921875</v>
+      </c>
+      <c r="L31">
+        <v>50.669921875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1713,12 +1809,15 @@
         <v>69.33984375</v>
       </c>
       <c r="K32">
-        <v>84.47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>84.06982421875</v>
+      </c>
+      <c r="L32">
+        <v>84.06982421875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1748,12 +1847,15 @@
         <v>90.8798828125</v>
       </c>
       <c r="K33">
-        <v>48.77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>47.570068359375</v>
+      </c>
+      <c r="L33">
+        <v>47.570068359375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1783,12 +1885,15 @@
         <v>97.240234375</v>
       </c>
       <c r="K34">
-        <v>65.47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>64.669921875</v>
+      </c>
+      <c r="L34">
+        <v>64.669921875</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -1818,12 +1923,15 @@
         <v>80.8798828125</v>
       </c>
       <c r="K35">
-        <v>68.47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>67.27001953125</v>
+      </c>
+      <c r="L35">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -1853,12 +1961,15 @@
         <v>101.9599609375</v>
       </c>
       <c r="K36">
-        <v>82.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>82.169921875</v>
+      </c>
+      <c r="L36">
+        <v>82.169921875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -1888,12 +1999,15 @@
         <v>56.090087890625</v>
       </c>
       <c r="K37">
-        <v>42.07</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>40.8701171875</v>
+      </c>
+      <c r="L37">
+        <v>40.8701171875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -1923,12 +2037,15 @@
         <v>49.679931640625</v>
       </c>
       <c r="K38">
-        <v>50.37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>49.169921875</v>
+      </c>
+      <c r="L38">
+        <v>49.169921875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -1958,12 +2075,15 @@
         <v>84.64990234375</v>
       </c>
       <c r="K39">
-        <v>43.15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>43.14990234375</v>
+      </c>
+      <c r="L39">
+        <v>43.14990234375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -1993,12 +2113,15 @@
         <v>96.27978515625</v>
       </c>
       <c r="K40">
-        <v>78.89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>78.89013671875</v>
+      </c>
+      <c r="L40">
+        <v>78.89013671875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -2028,12 +2151,15 @@
         <v>68.7998046875</v>
       </c>
       <c r="K41">
-        <v>48.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>48.85009765625</v>
+      </c>
+      <c r="L41">
+        <v>48.85009765625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -2063,12 +2189,15 @@
         <v>90.0400390625</v>
       </c>
       <c r="K42">
-        <v>39.57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>38.3701171875</v>
+      </c>
+      <c r="L42">
+        <v>38.3701171875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -2098,12 +2227,15 @@
         <v>91.14013671875</v>
       </c>
       <c r="K43">
-        <v>51.19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>51.18994140625</v>
+      </c>
+      <c r="L43">
+        <v>51.18994140625</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -2133,12 +2265,15 @@
         <v>76.27978515625</v>
       </c>
       <c r="K44">
-        <v>51.18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>50.780029296875</v>
+      </c>
+      <c r="L44">
+        <v>50.780029296875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -2168,12 +2303,15 @@
         <v>63.780029296875</v>
       </c>
       <c r="K45">
-        <v>64.69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>64.2900390625</v>
+      </c>
+      <c r="L45">
+        <v>64.2900390625</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -2203,12 +2341,15 @@
         <v>107.68017578125</v>
       </c>
       <c r="K46">
-        <v>70.06999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>69.669921875</v>
+      </c>
+      <c r="L46">
+        <v>69.669921875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -2238,12 +2379,15 @@
         <v>91.14013671875</v>
       </c>
       <c r="K47">
-        <v>48.27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>47.8701171875</v>
+      </c>
+      <c r="L47">
+        <v>47.8701171875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -2273,12 +2417,15 @@
         <v>84.43994140625</v>
       </c>
       <c r="K48">
-        <v>68.47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>67.27001953125</v>
+      </c>
+      <c r="L48">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -2308,12 +2455,15 @@
         <v>86.0400390625</v>
       </c>
       <c r="K49">
-        <v>47.79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>46.590087890625</v>
+      </c>
+      <c r="L49">
+        <v>46.590087890625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -2343,12 +2493,15 @@
         <v>85.85009765625</v>
       </c>
       <c r="K50">
-        <v>59.29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>58.090087890625</v>
+      </c>
+      <c r="L50">
+        <v>58.090087890625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -2378,12 +2531,15 @@
         <v>109.43994140625</v>
       </c>
       <c r="K51">
-        <v>63.97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>63.570068359375</v>
+      </c>
+      <c r="L51">
+        <v>63.570068359375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -2413,12 +2569,15 @@
         <v>85.240234375</v>
       </c>
       <c r="K52">
-        <v>52.19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>50.989990234375</v>
+      </c>
+      <c r="L52">
+        <v>50.989990234375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -2448,12 +2607,15 @@
         <v>77.4501953125</v>
       </c>
       <c r="K53">
-        <v>59.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>58.550048828125</v>
+      </c>
+      <c r="L53">
+        <v>58.550048828125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -2483,12 +2645,15 @@
         <v>53.389892578125</v>
       </c>
       <c r="K54">
-        <v>39.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="L54">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2518,6 +2683,9 @@
         <v>0</v>
       </c>
       <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
         <v>0</v>
       </c>
     </row>
@@ -2538,7 +2706,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2546,7 +2714,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2554,7 +2722,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2562,7 +2730,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2570,7 +2738,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2578,7 +2746,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2586,7 +2754,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2594,7 +2762,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2602,7 +2770,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2610,7 +2778,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2618,7 +2786,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2626,7 +2794,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2634,7 +2802,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2642,7 +2810,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2650,7 +2818,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2658,7 +2826,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2666,7 +2834,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2674,7 +2842,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2682,7 +2850,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2690,7 +2858,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2698,7 +2866,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2706,7 +2874,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2714,7 +2882,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2722,7 +2890,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2730,7 +2898,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2738,7 +2906,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2746,7 +2914,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2754,7 +2922,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2762,7 +2930,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2770,7 +2938,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2778,7 +2946,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2786,7 +2954,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2794,7 +2962,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2802,7 +2970,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2810,7 +2978,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2818,7 +2986,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2826,7 +2994,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2834,7 +3002,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2842,7 +3010,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2850,7 +3018,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2858,7 +3026,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2866,7 +3034,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2874,7 +3042,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2882,7 +3050,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2890,7 +3058,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2898,7 +3066,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2906,7 +3074,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2914,7 +3082,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2922,7 +3090,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2930,7 +3098,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2938,7 +3106,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2946,7 +3114,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2954,7 +3122,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2977,7 +3145,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2985,7 +3153,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2993,7 +3161,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3001,7 +3169,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3009,7 +3177,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3017,7 +3185,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3025,7 +3193,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3033,7 +3201,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3041,7 +3209,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3049,7 +3217,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3057,7 +3225,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3065,7 +3233,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3073,7 +3241,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3081,7 +3249,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3089,7 +3257,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3097,7 +3265,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3105,7 +3273,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3113,7 +3281,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3121,7 +3289,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3129,7 +3297,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3137,7 +3305,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3145,7 +3313,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3153,7 +3321,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3161,7 +3329,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3169,7 +3337,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3177,7 +3345,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3185,7 +3353,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3193,7 +3361,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3201,7 +3369,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3209,7 +3377,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3217,7 +3385,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3225,7 +3393,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3233,7 +3401,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3241,7 +3409,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3249,7 +3417,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3257,7 +3425,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3265,7 +3433,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3273,7 +3441,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3281,7 +3449,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3289,7 +3457,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3297,7 +3465,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3305,7 +3473,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3313,7 +3481,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3321,7 +3489,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3329,7 +3497,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3337,7 +3505,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3345,7 +3513,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3353,7 +3521,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3361,7 +3529,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3369,7 +3537,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3377,7 +3545,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3385,7 +3553,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3393,7 +3561,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3411,27 +3579,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -3439,13 +3607,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -3453,13 +3621,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -3467,13 +3635,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -3481,13 +3649,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -3495,13 +3663,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -3509,13 +3677,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -3523,13 +3691,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -3537,13 +3705,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -3551,13 +3719,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
@@ -3565,13 +3733,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>352.31005859375</v>
@@ -3579,13 +3747,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13">
         <v>348.08984375</v>
@@ -3593,13 +3761,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>338.4404296875</v>
@@ -3607,13 +3775,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15">
         <v>334.60009765625</v>
@@ -3621,13 +3789,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16">
         <v>329.4404296875</v>
@@ -3649,10 +3817,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3683,10 +3851,13 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -3716,12 +3887,15 @@
         <v>72.080078125</v>
       </c>
       <c r="K2">
-        <v>49.17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>47.969970703125</v>
+      </c>
+      <c r="L2">
+        <v>47.969970703125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -3751,12 +3925,15 @@
         <v>68.47998046875</v>
       </c>
       <c r="K3">
-        <v>54.37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>53.169921875</v>
+      </c>
+      <c r="L3">
+        <v>53.169921875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -3786,12 +3963,15 @@
         <v>104.97998046875</v>
       </c>
       <c r="K4">
-        <v>53.07</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>52.27001953125</v>
+      </c>
+      <c r="L4">
+        <v>52.27001953125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -3821,12 +4001,15 @@
         <v>71.0498046875</v>
       </c>
       <c r="K5">
-        <v>57.89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>57.489990234375</v>
+      </c>
+      <c r="L5">
+        <v>57.489990234375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -3856,12 +4039,15 @@
         <v>92.68017578125</v>
       </c>
       <c r="K6">
-        <v>37.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>37.090087890625</v>
+      </c>
+      <c r="L6">
+        <v>37.090087890625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -3891,12 +4077,15 @@
         <v>104.8798828125</v>
       </c>
       <c r="K7">
-        <v>59.77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>59.3701171875</v>
+      </c>
+      <c r="L7">
+        <v>59.3701171875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -3926,12 +4115,15 @@
         <v>85.85009765625</v>
       </c>
       <c r="K8">
-        <v>59.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>58.090087890625</v>
+      </c>
+      <c r="L8">
+        <v>58.090087890625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -3961,12 +4153,15 @@
         <v>93.8798828125</v>
       </c>
       <c r="K9">
-        <v>58.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>57.18994140625</v>
+      </c>
+      <c r="L9">
+        <v>57.18994140625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -3996,12 +4191,15 @@
         <v>69.009765625</v>
       </c>
       <c r="K10">
-        <v>33.78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>33.3798828125</v>
+      </c>
+      <c r="L10">
+        <v>33.3798828125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -4031,12 +4229,15 @@
         <v>78.35986328125</v>
       </c>
       <c r="K11">
-        <v>54.78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>53.97998046875</v>
+      </c>
+      <c r="L11">
+        <v>53.97998046875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -4066,12 +4267,15 @@
         <v>93.8798828125</v>
       </c>
       <c r="K12">
-        <v>51.97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>51.570068359375</v>
+      </c>
+      <c r="L12">
+        <v>51.570068359375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -4101,12 +4305,15 @@
         <v>85.9599609375</v>
       </c>
       <c r="K13">
-        <v>39.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>39.469970703125</v>
+      </c>
+      <c r="L13">
+        <v>39.469970703125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -4136,12 +4343,15 @@
         <v>84.47998046875</v>
       </c>
       <c r="K14">
-        <v>49.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>48.669921875</v>
+      </c>
+      <c r="L14">
+        <v>48.669921875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -4171,12 +4381,15 @@
         <v>98.85009765625</v>
       </c>
       <c r="K15">
-        <v>66.47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>66.06982421875</v>
+      </c>
+      <c r="L15">
+        <v>66.06982421875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -4206,12 +4419,15 @@
         <v>79.93994140625</v>
       </c>
       <c r="K16">
-        <v>55.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>54.389892578125</v>
+      </c>
+      <c r="L16">
+        <v>54.389892578125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -4241,12 +4457,15 @@
         <v>72.83984375</v>
       </c>
       <c r="K17">
-        <v>69.27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>68.8701171875</v>
+      </c>
+      <c r="L17">
+        <v>68.8701171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -4276,12 +4495,15 @@
         <v>112.8798828125</v>
       </c>
       <c r="K18">
-        <v>65.47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>64.27001953125</v>
+      </c>
+      <c r="L18">
+        <v>64.27001953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -4311,12 +4533,15 @@
         <v>116.0400390625</v>
       </c>
       <c r="K19">
-        <v>50.67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>50.669921875</v>
+      </c>
+      <c r="L19">
+        <v>50.669921875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -4346,12 +4571,15 @@
         <v>65.2998046875</v>
       </c>
       <c r="K20">
-        <v>50.79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>50.7900390625</v>
+      </c>
+      <c r="L20">
+        <v>50.7900390625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -4381,12 +4609,15 @@
         <v>108.93994140625</v>
       </c>
       <c r="K21">
-        <v>57.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>55.889892578125</v>
+      </c>
+      <c r="L21">
+        <v>55.889892578125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4416,12 +4647,15 @@
         <v>81.06005859375</v>
       </c>
       <c r="K22">
-        <v>77.58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>78.3798828125</v>
+      </c>
+      <c r="L22">
+        <v>78.3798828125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -4451,12 +4685,15 @@
         <v>80.93994140625</v>
       </c>
       <c r="K23">
-        <v>39.07</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>39.070068359375</v>
+      </c>
+      <c r="L23">
+        <v>39.070068359375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -4486,12 +4723,15 @@
         <v>59.010009765625</v>
       </c>
       <c r="K24">
-        <v>60.57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>60.169921875</v>
+      </c>
+      <c r="L24">
+        <v>60.169921875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -4521,12 +4761,15 @@
         <v>84.56005859375</v>
       </c>
       <c r="K25">
-        <v>58.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>58.070068359375</v>
+      </c>
+      <c r="L25">
+        <v>58.070068359375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -4556,12 +4799,15 @@
         <v>104.68017578125</v>
       </c>
       <c r="K26">
-        <v>67.29000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>66.89013671875</v>
+      </c>
+      <c r="L26">
+        <v>66.89013671875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -4591,12 +4837,15 @@
         <v>69.85009765625</v>
       </c>
       <c r="K27">
-        <v>31.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>29.8499755859375</v>
+      </c>
+      <c r="L27">
+        <v>29.8499755859375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -4626,12 +4875,15 @@
         <v>59.860107421875</v>
       </c>
       <c r="K28">
-        <v>55.47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>54.27001953125</v>
+      </c>
+      <c r="L28">
+        <v>54.27001953125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -4661,12 +4913,15 @@
         <v>59.3798828125</v>
       </c>
       <c r="K29">
-        <v>66.67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>66.27001953125</v>
+      </c>
+      <c r="L29">
+        <v>66.27001953125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -4696,12 +4951,15 @@
         <v>44.6298828125</v>
       </c>
       <c r="K30">
-        <v>63.17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>63.169921875</v>
+      </c>
+      <c r="L30">
+        <v>63.169921875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -4731,12 +4989,15 @@
         <v>106.97998046875</v>
       </c>
       <c r="K31">
-        <v>50.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>50.669921875</v>
+      </c>
+      <c r="L31">
+        <v>50.669921875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -4766,12 +5027,15 @@
         <v>69.33984375</v>
       </c>
       <c r="K32">
-        <v>84.47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>84.06982421875</v>
+      </c>
+      <c r="L32">
+        <v>84.06982421875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -4801,12 +5065,15 @@
         <v>90.8798828125</v>
       </c>
       <c r="K33">
-        <v>48.77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>47.570068359375</v>
+      </c>
+      <c r="L33">
+        <v>47.570068359375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -4836,12 +5103,15 @@
         <v>97.240234375</v>
       </c>
       <c r="K34">
-        <v>65.47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>64.669921875</v>
+      </c>
+      <c r="L34">
+        <v>64.669921875</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -4871,12 +5141,15 @@
         <v>80.8798828125</v>
       </c>
       <c r="K35">
-        <v>68.47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>67.27001953125</v>
+      </c>
+      <c r="L35">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -4906,12 +5179,15 @@
         <v>101.9599609375</v>
       </c>
       <c r="K36">
-        <v>82.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>82.169921875</v>
+      </c>
+      <c r="L36">
+        <v>82.169921875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -4941,12 +5217,15 @@
         <v>56.090087890625</v>
       </c>
       <c r="K37">
-        <v>42.07</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>40.8701171875</v>
+      </c>
+      <c r="L37">
+        <v>40.8701171875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -4976,12 +5255,15 @@
         <v>49.679931640625</v>
       </c>
       <c r="K38">
-        <v>50.37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>49.169921875</v>
+      </c>
+      <c r="L38">
+        <v>49.169921875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -5011,12 +5293,15 @@
         <v>84.64990234375</v>
       </c>
       <c r="K39">
-        <v>43.15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>43.14990234375</v>
+      </c>
+      <c r="L39">
+        <v>43.14990234375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -5046,12 +5331,15 @@
         <v>96.27978515625</v>
       </c>
       <c r="K40">
-        <v>78.89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>78.89013671875</v>
+      </c>
+      <c r="L40">
+        <v>78.89013671875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -5081,12 +5369,15 @@
         <v>68.7998046875</v>
       </c>
       <c r="K41">
-        <v>48.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>48.85009765625</v>
+      </c>
+      <c r="L41">
+        <v>48.85009765625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -5116,12 +5407,15 @@
         <v>90.0400390625</v>
       </c>
       <c r="K42">
-        <v>39.57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>38.3701171875</v>
+      </c>
+      <c r="L42">
+        <v>38.3701171875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -5151,12 +5445,15 @@
         <v>91.14013671875</v>
       </c>
       <c r="K43">
-        <v>51.19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>51.18994140625</v>
+      </c>
+      <c r="L43">
+        <v>51.18994140625</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -5186,12 +5483,15 @@
         <v>76.27978515625</v>
       </c>
       <c r="K44">
-        <v>51.18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>50.780029296875</v>
+      </c>
+      <c r="L44">
+        <v>50.780029296875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -5221,12 +5521,15 @@
         <v>63.780029296875</v>
       </c>
       <c r="K45">
-        <v>64.69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>64.2900390625</v>
+      </c>
+      <c r="L45">
+        <v>64.2900390625</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -5256,12 +5559,15 @@
         <v>107.68017578125</v>
       </c>
       <c r="K46">
-        <v>70.06999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>69.669921875</v>
+      </c>
+      <c r="L46">
+        <v>69.669921875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -5291,12 +5597,15 @@
         <v>91.14013671875</v>
       </c>
       <c r="K47">
-        <v>48.27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>47.8701171875</v>
+      </c>
+      <c r="L47">
+        <v>47.8701171875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -5326,12 +5635,15 @@
         <v>84.43994140625</v>
       </c>
       <c r="K48">
-        <v>68.47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>67.27001953125</v>
+      </c>
+      <c r="L48">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -5361,12 +5673,15 @@
         <v>86.0400390625</v>
       </c>
       <c r="K49">
-        <v>47.79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>46.590087890625</v>
+      </c>
+      <c r="L49">
+        <v>46.590087890625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -5396,12 +5711,15 @@
         <v>85.85009765625</v>
       </c>
       <c r="K50">
-        <v>59.29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>58.090087890625</v>
+      </c>
+      <c r="L50">
+        <v>58.090087890625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -5431,12 +5749,15 @@
         <v>109.43994140625</v>
       </c>
       <c r="K51">
-        <v>63.97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>63.570068359375</v>
+      </c>
+      <c r="L51">
+        <v>63.570068359375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -5466,12 +5787,15 @@
         <v>85.240234375</v>
       </c>
       <c r="K52">
-        <v>52.19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>50.989990234375</v>
+      </c>
+      <c r="L52">
+        <v>50.989990234375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -5501,12 +5825,15 @@
         <v>77.4501953125</v>
       </c>
       <c r="K53">
-        <v>59.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>58.550048828125</v>
+      </c>
+      <c r="L53">
+        <v>58.550048828125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -5536,12 +5863,15 @@
         <v>53.389892578125</v>
       </c>
       <c r="K54">
-        <v>39.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>39</v>
+      </c>
+      <c r="L54">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -5571,6 +5901,9 @@
         <v>0</v>
       </c>
       <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
         <v>0</v>
       </c>
     </row>
@@ -5591,426 +5924,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>818.29966796875</v>
+        <v>875.3896484375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B3">
-        <v>805.70994140625</v>
+        <v>865.590576171875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>799.100302734375</v>
+        <v>855.12060546875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B5">
-        <v>798.2304296875</v>
+        <v>852.62060546875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B6">
-        <v>796.50015625</v>
+        <v>852.2900390625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B7">
-        <v>795.7304296875</v>
+        <v>852.080078125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B8">
-        <v>792.4595312500001</v>
+        <v>851.18994140625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B9">
-        <v>786.22</v>
+        <v>849.789794921875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>775.829619140625</v>
+        <v>846.04931640625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>771.87974609375</v>
+        <v>838.899658203125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>770.899521484375</v>
+        <v>836.399658203125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>770.730009765625</v>
+        <v>827.86962890625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14">
-        <v>770.7200292968751</v>
+        <v>820.510009765625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15">
-        <v>766.6294531250001</v>
+        <v>817.8193359375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>766.139921875</v>
+        <v>817.31005859375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17">
-        <v>752.679716796875</v>
+        <v>810.349853515625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B18">
-        <v>732.1199316406251</v>
+        <v>810.14990234375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B19">
-        <v>731.4701464843751</v>
+        <v>796.010009765625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20">
-        <v>731.250029296875</v>
+        <v>795.119873046875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B21">
-        <v>729.570224609375</v>
+        <v>787.14990234375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B22">
-        <v>729.349580078125</v>
+        <v>786.98974609375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>728.829912109375</v>
+        <v>784.08935546875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B24">
-        <v>728.63015625</v>
+        <v>782.940185546875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B25">
-        <v>727.98005859375</v>
+        <v>782.529541015625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B26">
-        <v>726.920126953125</v>
+        <v>782.389404296875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>723.300029296875</v>
+        <v>779.499755859375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B28">
-        <v>722.6195605468751</v>
+        <v>778.759765625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B29">
-        <v>721.07986328125</v>
+        <v>776.5</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B30">
-        <v>719.78953125</v>
+        <v>772.310302734375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B31">
-        <v>718.21931640625</v>
+        <v>770.770263671875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="B32">
-        <v>717.7199023437499</v>
+        <v>766.660400390625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B33">
-        <v>703.48962890625</v>
+        <v>766.19970703125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>703.0295703125</v>
+        <v>761.348876953125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B35">
-        <v>697.5498046875</v>
+        <v>754.89990234375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B36">
-        <v>693.69001953125</v>
+        <v>743.249755859375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B37">
-        <v>692.579912109375</v>
+        <v>742.5595703125</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B38">
-        <v>689.040234375</v>
+        <v>740.4599609375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>680.83908203125</v>
+        <v>725.419921875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40">
-        <v>680.7897265625001</v>
+        <v>717.9599609375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B41">
-        <v>677.679228515625</v>
+        <v>717.690185546875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42">
-        <v>676.9791796875001</v>
+        <v>716.6494140625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="B43">
-        <v>673.450078125</v>
+        <v>714.02978515625</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B44">
-        <v>663.6497265624999</v>
+        <v>713.81884765625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B45">
-        <v>635.67001953125</v>
+        <v>678.9100341796875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B46">
-        <v>632.099560546875</v>
+        <v>678.81982421875</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47">
-        <v>626.839560546875</v>
+        <v>677.629638671875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B48">
-        <v>624.2296679687501</v>
+        <v>674.46044921875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B49">
-        <v>621.39041015625</v>
+        <v>670.299560546875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B50">
-        <v>610.4397998046875</v>
+        <v>663.2998046875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B51">
-        <v>577.8596850585938</v>
+        <v>637.479736328125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B52">
-        <v>574.309892578125</v>
+        <v>625.8295288085938</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53">
-        <v>521.5400634765625</v>
+        <v>570.3902587890625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54">
-        <v>235.83</v>
+        <v>315.009765625</v>
       </c>
     </row>
   </sheetData>
@@ -6025,272 +6358,272 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6310,7 +6643,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6318,7 +6651,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6326,7 +6659,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6334,7 +6667,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6342,7 +6675,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6350,7 +6683,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6358,7 +6691,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6366,7 +6699,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6374,7 +6707,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6382,7 +6715,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6390,7 +6723,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6398,7 +6731,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6406,7 +6739,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6414,7 +6747,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6422,7 +6755,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6430,7 +6763,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6438,7 +6771,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6446,7 +6779,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6454,7 +6787,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6462,7 +6795,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6470,7 +6803,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6478,7 +6811,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6486,7 +6819,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6494,7 +6827,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6502,7 +6835,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6510,7 +6843,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6518,7 +6851,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6526,7 +6859,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6534,7 +6867,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6542,7 +6875,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6550,7 +6883,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6558,7 +6891,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -6566,7 +6899,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6574,7 +6907,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -6582,7 +6915,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -6590,7 +6923,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6598,7 +6931,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6606,7 +6939,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -6614,7 +6947,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -6622,7 +6955,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6630,7 +6963,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6638,7 +6971,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6646,7 +6979,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -6654,7 +6987,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -6662,7 +6995,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -6670,7 +7003,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -6678,7 +7011,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -6686,7 +7019,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -6694,7 +7027,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -6702,7 +7035,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -6710,7 +7043,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -6718,7 +7051,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -6726,7 +7059,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -6749,7 +7082,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -6757,7 +7090,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -6765,7 +7098,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -6773,7 +7106,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -6781,7 +7114,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -6789,7 +7122,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -6797,7 +7130,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -6805,7 +7138,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -6813,7 +7146,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -6821,7 +7154,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -6829,7 +7162,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -6837,7 +7170,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -6845,7 +7178,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -6853,7 +7186,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -6861,7 +7194,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -6869,7 +7202,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -6877,7 +7210,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -6885,7 +7218,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -6893,7 +7226,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -6901,7 +7234,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -6909,7 +7242,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -6917,7 +7250,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -6925,7 +7258,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -6933,7 +7266,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -6941,7 +7274,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -6949,7 +7282,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -6957,7 +7290,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -6965,7 +7298,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -6973,7 +7306,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -6981,7 +7314,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -6989,7 +7322,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -6997,7 +7330,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -7005,7 +7338,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -7013,7 +7346,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -7021,7 +7354,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -7029,7 +7362,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -7037,7 +7370,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -7045,7 +7378,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -7053,7 +7386,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -7061,7 +7394,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -7069,7 +7402,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -7077,7 +7410,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -7085,7 +7418,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -7093,7 +7426,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -7101,7 +7434,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -7109,7 +7442,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -7117,7 +7450,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B48">
         <v>44.260009765625</v>
@@ -7125,7 +7458,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B49">
         <v>44.06005859375</v>
@@ -7133,7 +7466,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50">
         <v>43.510009765625</v>
@@ -7141,7 +7474,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51">
         <v>42.9599609375</v>
@@ -7149,7 +7482,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52">
         <v>40.60009765625</v>
@@ -7157,7 +7490,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53">
         <v>38.260009765625</v>
@@ -7165,7 +7498,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7188,7 +7521,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -7196,7 +7529,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -7204,7 +7537,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -7212,7 +7545,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -7220,7 +7553,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -7228,7 +7561,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -7236,7 +7569,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -7244,7 +7577,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -7252,7 +7585,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -7260,7 +7593,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -7268,7 +7601,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -7276,7 +7609,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -7284,7 +7617,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -7292,7 +7625,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -7300,7 +7633,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -7308,7 +7641,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -7316,7 +7649,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -7324,7 +7657,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -7332,7 +7665,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -7340,7 +7673,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -7348,7 +7681,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -7356,7 +7689,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -7364,7 +7697,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -7372,7 +7705,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -7380,7 +7713,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26">
         <v>232.18994140625</v>
@@ -7388,7 +7721,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27">
         <v>231.8896484375</v>
@@ -7396,7 +7729,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>231.259765625</v>
@@ -7404,7 +7737,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>227.90966796875</v>
@@ -7412,7 +7745,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B30">
         <v>227.8095703125</v>
@@ -7420,7 +7753,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>225.2099609375</v>
@@ -7428,7 +7761,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32">
         <v>225.02978515625</v>
@@ -7436,7 +7769,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B33">
         <v>224.409912109375</v>
@@ -7444,7 +7777,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B34">
         <v>222.49951171875</v>
@@ -7452,7 +7785,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>219.469482421875</v>
@@ -7460,7 +7793,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36">
         <v>218.419921875</v>
@@ -7468,7 +7801,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37">
         <v>216.3896484375</v>
@@ -7476,7 +7809,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38">
         <v>216.030517578125</v>
@@ -7484,7 +7817,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>215.5498046875</v>
@@ -7492,7 +7825,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40">
         <v>212.2099609375</v>
@@ -7500,7 +7833,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41">
         <v>211.239990234375</v>
@@ -7508,7 +7841,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>209.509765625</v>
@@ -7516,7 +7849,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>206.1201171875</v>
@@ -7524,7 +7857,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B44">
         <v>205.58984375</v>
@@ -7532,7 +7865,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>204.8798828125</v>
@@ -7540,7 +7873,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B46">
         <v>199.2001953125</v>
@@ -7548,7 +7881,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47">
         <v>198.499755859375</v>
@@ -7556,7 +7889,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B48">
         <v>197.369873046875</v>
@@ -7564,7 +7897,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B49">
         <v>191.85986328125</v>
@@ -7572,7 +7905,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>187.64990234375</v>
@@ -7580,7 +7913,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51">
         <v>186.4697265625</v>
@@ -7588,7 +7921,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B52">
         <v>159.43994140625</v>
@@ -7596,7 +7929,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
@@ -7604,7 +7937,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7627,7 +7960,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>352.31005859375</v>
@@ -7635,7 +7968,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>348.08984375</v>
@@ -7643,7 +7976,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>338.4404296875</v>
@@ -7651,7 +7984,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>334.60009765625</v>
@@ -7659,7 +7992,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6">
         <v>329.4404296875</v>
@@ -7667,7 +8000,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>328.05029296875</v>
@@ -7675,7 +8008,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>323.5302734375</v>
@@ -7683,7 +8016,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>318.04052734375</v>
@@ -7691,7 +8024,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>317.26025390625</v>
@@ -7699,7 +8032,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>316.66015625</v>
@@ -7707,7 +8040,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <v>315.94970703125</v>
@@ -7715,7 +8048,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>303.949462890625</v>
@@ -7723,7 +8056,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14">
         <v>300.99951171875</v>
@@ -7731,7 +8064,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>300.5</v>
@@ -7739,7 +8072,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>300.099609375</v>
@@ -7747,7 +8080,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>299.199951171875</v>
@@ -7755,7 +8088,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>299.009765625</v>
@@ -7763,7 +8096,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>298.93017578125</v>
@@ -7771,7 +8104,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>298.8798828125</v>
@@ -7779,7 +8112,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>296.4697265625</v>
@@ -7787,7 +8120,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22">
         <v>296.07958984375</v>
@@ -7795,7 +8128,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>295.85009765625</v>
@@ -7803,7 +8136,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24">
         <v>294.43994140625</v>
@@ -7811,7 +8144,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25">
         <v>293.139892578125</v>
@@ -7819,7 +8152,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26">
         <v>290.2998046875</v>
@@ -7827,7 +8160,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27">
         <v>289</v>
@@ -7835,7 +8168,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>288.1103515625</v>
@@ -7843,7 +8176,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>288.1103515625</v>
@@ -7851,7 +8184,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30">
         <v>287.43017578125</v>
@@ -7859,7 +8192,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31">
         <v>286.16015625</v>
@@ -7867,7 +8200,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B32">
         <v>285.639892578125</v>
@@ -7875,7 +8208,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33">
         <v>284.639892578125</v>
@@ -7883,7 +8216,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>284.2900390625</v>
@@ -7891,7 +8224,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B35">
         <v>284.2294921875</v>
@@ -7899,7 +8232,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36">
         <v>283.899658203125</v>
@@ -7907,7 +8240,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37">
         <v>282.68994140625</v>
@@ -7915,7 +8248,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>280.650390625</v>
@@ -7923,7 +8256,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39">
         <v>279.340087890625</v>
@@ -7931,7 +8264,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40">
         <v>277.80029296875</v>
@@ -7939,7 +8272,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B41">
         <v>276.829833984375</v>
@@ -7947,7 +8280,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42">
         <v>272.47998046875</v>
@@ -7955,7 +8288,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B43">
         <v>269.719970703125</v>
@@ -7963,7 +8296,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>259.3798828125</v>
@@ -7971,7 +8304,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B45">
         <v>253.94970703125</v>
@@ -7979,7 +8312,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B46">
         <v>244.02978515625</v>
@@ -7987,7 +8320,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47">
         <v>234.26025390625</v>
@@ -7995,7 +8328,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48">
         <v>230.099853515625</v>
@@ -8003,7 +8336,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49">
         <v>228.480224609375</v>
@@ -8011,7 +8344,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B50">
         <v>222.0400390625</v>
@@ -8019,7 +8352,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B51">
         <v>221.0599975585938</v>
@@ -8027,7 +8360,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B52">
         <v>216.89013671875</v>
@@ -8035,7 +8368,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B53">
         <v>199.0599365234375</v>
@@ -8043,7 +8376,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54">
         <v>77.18994140625</v>
@@ -8066,90 +8399,90 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2">
-        <v>184.1299609375</v>
+        <v>266.2998046875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B3">
-        <v>178.3498828125</v>
+        <v>254.06005859375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4">
-        <v>177.75017578125</v>
+        <v>247.02001953125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>175.16978515625</v>
+        <v>241.419921875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>173.40994140625</v>
+        <v>238.46044921875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B7">
-        <v>171.97017578125</v>
+        <v>237.81982421875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B8">
-        <v>166.7100390625</v>
+        <v>237.4794921875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B9">
-        <v>166.02994140625</v>
+        <v>236.580078125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>165.32009765625</v>
+        <v>230.98974609375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B11">
-        <v>164.6498828125</v>
+        <v>226.580078125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>162.710234375</v>
+        <v>223.6201171875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -8157,335 +8490,335 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>158.64005859375</v>
+        <v>220.7197265625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="B14">
-        <v>158.04998046875</v>
+        <v>218.97998046875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B15">
-        <v>157.64998046875</v>
+        <v>217.3798828125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>153.80984375</v>
+        <v>215.419921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>152.90994140625</v>
+        <v>210.580078125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18">
-        <v>152.2698828125</v>
+        <v>209.52001953125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B19">
-        <v>149.3498828125</v>
+        <v>208.31982421875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>145.8498828125</v>
+        <v>208.259765625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21">
-        <v>145.14009765625</v>
+        <v>202.0302734375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22">
-        <v>145.14009765625</v>
+        <v>202.0302734375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23">
-        <v>143.03005859375</v>
+        <v>200.7001953125</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B24">
-        <v>142.33013671875</v>
+        <v>197.02001953125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="B25">
-        <v>142.10984375</v>
+        <v>194.55029296875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B26">
-        <v>139.6498828125</v>
+        <v>193.52001953125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27">
-        <v>139.41013671875</v>
+        <v>192.360107421875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B28">
-        <v>137.430234375</v>
+        <v>191.919921875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="B29">
-        <v>137.2001953125</v>
+        <v>188.7197265625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B30">
-        <v>135.12994140625</v>
+        <v>187.22021484375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B31">
-        <v>133.94998046875</v>
+        <v>186.88037109375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B32">
-        <v>133.8300390625</v>
+        <v>186.31982421875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B33">
-        <v>133.13986328125</v>
+        <v>186.02978515625</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>129.77017578125</v>
+        <v>186.02001953125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B35">
-        <v>129.6100390625</v>
+        <v>181.81982421875</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B36">
-        <v>128.9398046875</v>
+        <v>179.349853515625</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B37">
-        <v>128.470029296875</v>
+        <v>179.22021484375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>127.79990234375</v>
+        <v>177.83984375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>127.45978515625</v>
+        <v>174.81982421875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>126.0498828125</v>
+        <v>170.9697265625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B41">
-        <v>125.8299609375</v>
+        <v>170.94970703125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B42">
-        <v>122.84998046875</v>
+        <v>168.400146484375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B43">
-        <v>121.250078125</v>
+        <v>168.02001953125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B44">
-        <v>120.00994140625</v>
+        <v>166.8798828125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B45">
-        <v>119.580009765625</v>
+        <v>166.8603515625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46">
-        <v>117.6498046875</v>
+        <v>166.7802734375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B47">
-        <v>116.0898046875</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B48">
-        <v>115.330107421875</v>
+        <v>164.89990234375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B49">
-        <v>107.7998828125</v>
+        <v>159.080078125</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B50">
-        <v>102.789765625</v>
+        <v>148.019775390625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B51">
-        <v>100.90009765625</v>
+        <v>137.830322265625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="B52">
-        <v>100.049931640625</v>
+        <v>135.76953125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B53">
-        <v>98.16008789062499</v>
+        <v>131.389892578125</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B54">
-        <v>93.189892578125</v>
+        <v>129.550048828125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="73">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Rodada 11</t>
+  </si>
+  <si>
+    <t>Rodada 12</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -599,10 +602,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -636,10 +639,13 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -672,12 +678,15 @@
         <v>47.969970703125</v>
       </c>
       <c r="L2">
-        <v>47.969970703125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>87.4599609375</v>
+      </c>
+      <c r="M2">
+        <v>87.4599609375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -710,12 +719,15 @@
         <v>53.169921875</v>
       </c>
       <c r="L3">
-        <v>53.169921875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>85.4599609375</v>
+      </c>
+      <c r="M3">
+        <v>85.4599609375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -748,12 +760,15 @@
         <v>52.27001953125</v>
       </c>
       <c r="L4">
-        <v>52.27001953125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>114.259765625</v>
+      </c>
+      <c r="M4">
+        <v>114.259765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -786,12 +801,15 @@
         <v>57.489990234375</v>
       </c>
       <c r="L5">
-        <v>57.489990234375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>70.16015625</v>
+      </c>
+      <c r="M5">
+        <v>70.16015625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -824,12 +842,15 @@
         <v>37.090087890625</v>
       </c>
       <c r="L6">
-        <v>37.090087890625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>91.06005859375</v>
+      </c>
+      <c r="M6">
+        <v>91.06005859375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -862,12 +883,15 @@
         <v>59.3701171875</v>
       </c>
       <c r="L7">
-        <v>59.3701171875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>95.66015625</v>
+      </c>
+      <c r="M7">
+        <v>95.66015625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -900,12 +924,15 @@
         <v>58.090087890625</v>
       </c>
       <c r="L8">
-        <v>58.090087890625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>79.66015625</v>
+      </c>
+      <c r="M8">
+        <v>79.66015625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -938,12 +965,15 @@
         <v>57.18994140625</v>
       </c>
       <c r="L9">
-        <v>57.18994140625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>86.259765625</v>
+      </c>
+      <c r="M9">
+        <v>86.259765625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -976,12 +1006,15 @@
         <v>33.3798828125</v>
       </c>
       <c r="L10">
-        <v>33.3798828125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>71.759765625</v>
+      </c>
+      <c r="M10">
+        <v>71.759765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -1014,12 +1047,15 @@
         <v>53.97998046875</v>
       </c>
       <c r="L11">
-        <v>53.97998046875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>87.759765625</v>
+      </c>
+      <c r="M11">
+        <v>87.759765625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -1052,12 +1088,15 @@
         <v>51.570068359375</v>
       </c>
       <c r="L12">
-        <v>51.570068359375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>79.580078125</v>
+      </c>
+      <c r="M12">
+        <v>79.580078125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -1090,12 +1129,15 @@
         <v>39.469970703125</v>
       </c>
       <c r="L13">
-        <v>39.469970703125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>85.16015625</v>
+      </c>
+      <c r="M13">
+        <v>85.16015625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -1128,12 +1170,15 @@
         <v>48.669921875</v>
       </c>
       <c r="L14">
-        <v>48.669921875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>58.159912109375</v>
+      </c>
+      <c r="M14">
+        <v>58.159912109375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -1166,12 +1211,15 @@
         <v>66.06982421875</v>
       </c>
       <c r="L15">
-        <v>66.06982421875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>104.4599609375</v>
+      </c>
+      <c r="M15">
+        <v>104.4599609375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -1204,12 +1252,15 @@
         <v>54.389892578125</v>
       </c>
       <c r="L16">
-        <v>54.389892578125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>91.27978515625</v>
+      </c>
+      <c r="M16">
+        <v>91.27978515625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -1242,12 +1293,15 @@
         <v>68.8701171875</v>
       </c>
       <c r="L17">
-        <v>68.8701171875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>89.16015625</v>
+      </c>
+      <c r="M17">
+        <v>89.16015625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -1280,12 +1334,15 @@
         <v>64.27001953125</v>
       </c>
       <c r="L18">
-        <v>64.27001953125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>103.66015625</v>
+      </c>
+      <c r="M18">
+        <v>103.66015625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -1318,12 +1375,15 @@
         <v>50.669921875</v>
       </c>
       <c r="L19">
-        <v>50.669921875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>107.35986328125</v>
+      </c>
+      <c r="M19">
+        <v>107.35986328125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -1356,12 +1416,15 @@
         <v>50.7900390625</v>
       </c>
       <c r="L20">
-        <v>50.7900390625</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>71.35986328125</v>
+      </c>
+      <c r="M20">
+        <v>71.35986328125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -1394,12 +1457,15 @@
         <v>55.889892578125</v>
       </c>
       <c r="L21">
-        <v>55.889892578125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>91.9599609375</v>
+      </c>
+      <c r="M21">
+        <v>91.9599609375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1432,12 +1498,15 @@
         <v>78.3798828125</v>
       </c>
       <c r="L22">
-        <v>78.3798828125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>74.10009765625</v>
+      </c>
+      <c r="M22">
+        <v>74.10009765625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1470,12 +1539,15 @@
         <v>39.070068359375</v>
       </c>
       <c r="L23">
-        <v>39.070068359375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>69.60986328125</v>
+      </c>
+      <c r="M23">
+        <v>69.60986328125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1508,12 +1580,15 @@
         <v>60.169921875</v>
       </c>
       <c r="L24">
-        <v>60.169921875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>82.81005859375</v>
+      </c>
+      <c r="M24">
+        <v>82.81005859375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1546,12 +1621,15 @@
         <v>58.070068359375</v>
       </c>
       <c r="L25">
-        <v>58.070068359375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>92.56005859375</v>
+      </c>
+      <c r="M25">
+        <v>92.56005859375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1584,12 +1662,15 @@
         <v>66.89013671875</v>
       </c>
       <c r="L26">
-        <v>66.89013671875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>90.4599609375</v>
+      </c>
+      <c r="M26">
+        <v>90.4599609375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1622,12 +1703,15 @@
         <v>29.8499755859375</v>
       </c>
       <c r="L27">
-        <v>29.8499755859375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>95.16015625</v>
+      </c>
+      <c r="M27">
+        <v>95.16015625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1660,12 +1744,15 @@
         <v>54.27001953125</v>
       </c>
       <c r="L28">
-        <v>54.27001953125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>76.759765625</v>
+      </c>
+      <c r="M28">
+        <v>76.759765625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1698,12 +1785,15 @@
         <v>66.27001953125</v>
       </c>
       <c r="L29">
-        <v>66.27001953125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+        <v>105.9599609375</v>
+      </c>
+      <c r="M29">
+        <v>105.9599609375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1736,12 +1826,15 @@
         <v>63.169921875</v>
       </c>
       <c r="L30">
-        <v>63.169921875</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>74.66015625</v>
+      </c>
+      <c r="M30">
+        <v>74.66015625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1774,12 +1867,15 @@
         <v>50.669921875</v>
       </c>
       <c r="L31">
-        <v>50.669921875</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>88.3798828125</v>
+      </c>
+      <c r="M31">
+        <v>88.3798828125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1812,12 +1908,15 @@
         <v>84.06982421875</v>
       </c>
       <c r="L32">
-        <v>84.06982421875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>53.030029296875</v>
+      </c>
+      <c r="M32">
+        <v>53.030029296875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1850,12 +1949,15 @@
         <v>47.570068359375</v>
       </c>
       <c r="L33">
-        <v>47.570068359375</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>69.25</v>
+      </c>
+      <c r="M33">
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1888,12 +1990,15 @@
         <v>64.669921875</v>
       </c>
       <c r="L34">
-        <v>64.669921875</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>96.509765625</v>
+      </c>
+      <c r="M34">
+        <v>96.509765625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -1926,12 +2031,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="L35">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>86.06005859375</v>
+      </c>
+      <c r="M35">
+        <v>86.06005859375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -1964,12 +2072,15 @@
         <v>82.169921875</v>
       </c>
       <c r="L36">
-        <v>82.169921875</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>101.35986328125</v>
+      </c>
+      <c r="M36">
+        <v>101.35986328125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -2002,12 +2113,15 @@
         <v>40.8701171875</v>
       </c>
       <c r="L37">
-        <v>40.8701171875</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>82.4599609375</v>
+      </c>
+      <c r="M37">
+        <v>82.4599609375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -2040,12 +2154,15 @@
         <v>49.169921875</v>
       </c>
       <c r="L38">
-        <v>49.169921875</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>49.949951171875</v>
+      </c>
+      <c r="M38">
+        <v>49.949951171875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -2078,12 +2195,15 @@
         <v>43.14990234375</v>
       </c>
       <c r="L39">
-        <v>43.14990234375</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>56.85009765625</v>
+      </c>
+      <c r="M39">
+        <v>56.85009765625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -2116,12 +2236,15 @@
         <v>78.89013671875</v>
       </c>
       <c r="L40">
-        <v>78.89013671875</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>86.66015625</v>
+      </c>
+      <c r="M40">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -2154,12 +2277,15 @@
         <v>48.85009765625</v>
       </c>
       <c r="L41">
-        <v>48.85009765625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>70.89990234375</v>
+      </c>
+      <c r="M41">
+        <v>70.89990234375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -2192,12 +2318,15 @@
         <v>38.3701171875</v>
       </c>
       <c r="L42">
-        <v>38.3701171875</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+        <v>70.35986328125</v>
+      </c>
+      <c r="M42">
+        <v>70.35986328125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -2230,12 +2359,15 @@
         <v>51.18994140625</v>
       </c>
       <c r="L43">
-        <v>51.18994140625</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+        <v>83.56005859375</v>
+      </c>
+      <c r="M43">
+        <v>83.56005859375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -2268,12 +2400,15 @@
         <v>50.780029296875</v>
       </c>
       <c r="L44">
-        <v>50.780029296875</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+        <v>97.06005859375</v>
+      </c>
+      <c r="M44">
+        <v>97.06005859375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -2306,12 +2441,15 @@
         <v>64.2900390625</v>
       </c>
       <c r="L45">
-        <v>64.2900390625</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
+        <v>81.759765625</v>
+      </c>
+      <c r="M45">
+        <v>81.759765625</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -2344,12 +2482,15 @@
         <v>69.669921875</v>
       </c>
       <c r="L46">
-        <v>69.669921875</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>90.56005859375</v>
+      </c>
+      <c r="M46">
+        <v>90.56005859375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -2382,12 +2523,15 @@
         <v>47.8701171875</v>
       </c>
       <c r="L47">
-        <v>47.8701171875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+        <v>83.47998046875</v>
+      </c>
+      <c r="M47">
+        <v>83.47998046875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -2420,12 +2564,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="L48">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+        <v>94.06005859375</v>
+      </c>
+      <c r="M48">
+        <v>94.06005859375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -2458,12 +2605,15 @@
         <v>46.590087890625</v>
       </c>
       <c r="L49">
-        <v>46.590087890625</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+        <v>96.259765625</v>
+      </c>
+      <c r="M49">
+        <v>96.259765625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -2496,12 +2646,15 @@
         <v>58.090087890625</v>
       </c>
       <c r="L50">
-        <v>58.090087890625</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+        <v>88.759765625</v>
+      </c>
+      <c r="M50">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -2534,12 +2687,15 @@
         <v>63.570068359375</v>
       </c>
       <c r="L51">
-        <v>63.570068359375</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+        <v>101.41015625</v>
+      </c>
+      <c r="M51">
+        <v>101.41015625</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -2572,12 +2728,15 @@
         <v>50.989990234375</v>
       </c>
       <c r="L52">
-        <v>50.989990234375</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
+        <v>88.85986328125</v>
+      </c>
+      <c r="M52">
+        <v>88.85986328125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -2610,12 +2769,15 @@
         <v>58.550048828125</v>
       </c>
       <c r="L53">
-        <v>58.550048828125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+        <v>89.080078125</v>
+      </c>
+      <c r="M53">
+        <v>89.080078125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -2648,12 +2810,15 @@
         <v>39</v>
       </c>
       <c r="L54">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+        <v>52.2900390625</v>
+      </c>
+      <c r="M54">
+        <v>52.2900390625</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2686,6 +2851,9 @@
         <v>0</v>
       </c>
       <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>0</v>
       </c>
     </row>
@@ -2706,7 +2874,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2714,7 +2882,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2722,7 +2890,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2730,7 +2898,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2738,7 +2906,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2746,7 +2914,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2754,7 +2922,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2762,7 +2930,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2770,7 +2938,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2778,7 +2946,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2786,7 +2954,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2794,7 +2962,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2802,7 +2970,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2810,7 +2978,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2818,7 +2986,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2826,7 +2994,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2834,7 +3002,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2842,7 +3010,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2850,7 +3018,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2858,7 +3026,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2866,7 +3034,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2874,7 +3042,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2882,7 +3050,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2890,7 +3058,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2898,7 +3066,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2906,7 +3074,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2914,7 +3082,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2922,7 +3090,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2930,7 +3098,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2938,7 +3106,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2946,7 +3114,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2954,7 +3122,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2962,7 +3130,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2970,7 +3138,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2978,7 +3146,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2986,7 +3154,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2994,7 +3162,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3002,7 +3170,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3010,7 +3178,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3018,7 +3186,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3026,7 +3194,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3034,7 +3202,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3042,7 +3210,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3050,7 +3218,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3058,7 +3226,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3066,7 +3234,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3074,7 +3242,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3082,7 +3250,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3090,7 +3258,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3098,7 +3266,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3106,7 +3274,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3114,7 +3282,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3122,7 +3290,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3145,7 +3313,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3153,7 +3321,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3161,7 +3329,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3169,7 +3337,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3177,7 +3345,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3185,7 +3353,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3193,7 +3361,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3201,7 +3369,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3209,7 +3377,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3217,7 +3385,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3225,7 +3393,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3233,7 +3401,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3241,7 +3409,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3249,7 +3417,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3257,7 +3425,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3265,7 +3433,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3273,7 +3441,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3281,7 +3449,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3289,7 +3457,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3297,7 +3465,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3305,7 +3473,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3313,7 +3481,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3321,7 +3489,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3329,7 +3497,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3337,7 +3505,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3345,7 +3513,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3353,7 +3521,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3361,7 +3529,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3369,7 +3537,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3377,7 +3545,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3385,7 +3553,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3393,7 +3561,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3401,7 +3569,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3409,7 +3577,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3417,7 +3585,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3425,7 +3593,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3433,7 +3601,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3441,7 +3609,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3449,7 +3617,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3457,7 +3625,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3465,7 +3633,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3473,7 +3641,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3481,7 +3649,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3489,7 +3657,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3497,7 +3665,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3505,7 +3673,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3513,7 +3681,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3521,7 +3689,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3529,7 +3697,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3537,7 +3705,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3545,7 +3713,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3553,7 +3721,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3561,7 +3729,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3579,27 +3747,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -3607,13 +3775,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -3621,13 +3789,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -3635,13 +3803,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -3649,13 +3817,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -3663,13 +3831,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -3677,13 +3845,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -3691,13 +3859,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -3705,13 +3873,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -3719,13 +3887,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
@@ -3733,13 +3901,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>352.31005859375</v>
@@ -3747,13 +3915,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13">
         <v>348.08984375</v>
@@ -3761,13 +3929,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14">
         <v>338.4404296875</v>
@@ -3775,13 +3943,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>334.60009765625</v>
@@ -3789,13 +3957,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16">
         <v>329.4404296875</v>
@@ -3817,10 +3985,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3854,10 +4022,13 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -3890,12 +4061,15 @@
         <v>47.969970703125</v>
       </c>
       <c r="L2">
-        <v>47.969970703125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>87.4599609375</v>
+      </c>
+      <c r="M2">
+        <v>87.4599609375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -3928,12 +4102,15 @@
         <v>53.169921875</v>
       </c>
       <c r="L3">
-        <v>53.169921875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>85.4599609375</v>
+      </c>
+      <c r="M3">
+        <v>85.4599609375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -3966,12 +4143,15 @@
         <v>52.27001953125</v>
       </c>
       <c r="L4">
-        <v>52.27001953125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>114.259765625</v>
+      </c>
+      <c r="M4">
+        <v>114.259765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -4004,12 +4184,15 @@
         <v>57.489990234375</v>
       </c>
       <c r="L5">
-        <v>57.489990234375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>70.16015625</v>
+      </c>
+      <c r="M5">
+        <v>70.16015625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -4042,12 +4225,15 @@
         <v>37.090087890625</v>
       </c>
       <c r="L6">
-        <v>37.090087890625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>91.06005859375</v>
+      </c>
+      <c r="M6">
+        <v>91.06005859375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -4080,12 +4266,15 @@
         <v>59.3701171875</v>
       </c>
       <c r="L7">
-        <v>59.3701171875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>95.66015625</v>
+      </c>
+      <c r="M7">
+        <v>95.66015625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -4118,12 +4307,15 @@
         <v>58.090087890625</v>
       </c>
       <c r="L8">
-        <v>58.090087890625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>79.66015625</v>
+      </c>
+      <c r="M8">
+        <v>79.66015625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -4156,12 +4348,15 @@
         <v>57.18994140625</v>
       </c>
       <c r="L9">
-        <v>57.18994140625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>86.259765625</v>
+      </c>
+      <c r="M9">
+        <v>86.259765625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -4194,12 +4389,15 @@
         <v>33.3798828125</v>
       </c>
       <c r="L10">
-        <v>33.3798828125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>71.759765625</v>
+      </c>
+      <c r="M10">
+        <v>71.759765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -4232,12 +4430,15 @@
         <v>53.97998046875</v>
       </c>
       <c r="L11">
-        <v>53.97998046875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>87.759765625</v>
+      </c>
+      <c r="M11">
+        <v>87.759765625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -4270,12 +4471,15 @@
         <v>51.570068359375</v>
       </c>
       <c r="L12">
-        <v>51.570068359375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>79.580078125</v>
+      </c>
+      <c r="M12">
+        <v>79.580078125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -4308,12 +4512,15 @@
         <v>39.469970703125</v>
       </c>
       <c r="L13">
-        <v>39.469970703125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>85.16015625</v>
+      </c>
+      <c r="M13">
+        <v>85.16015625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -4346,12 +4553,15 @@
         <v>48.669921875</v>
       </c>
       <c r="L14">
-        <v>48.669921875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>58.159912109375</v>
+      </c>
+      <c r="M14">
+        <v>58.159912109375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -4384,12 +4594,15 @@
         <v>66.06982421875</v>
       </c>
       <c r="L15">
-        <v>66.06982421875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>104.4599609375</v>
+      </c>
+      <c r="M15">
+        <v>104.4599609375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -4422,12 +4635,15 @@
         <v>54.389892578125</v>
       </c>
       <c r="L16">
-        <v>54.389892578125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>91.27978515625</v>
+      </c>
+      <c r="M16">
+        <v>91.27978515625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -4460,12 +4676,15 @@
         <v>68.8701171875</v>
       </c>
       <c r="L17">
-        <v>68.8701171875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>89.16015625</v>
+      </c>
+      <c r="M17">
+        <v>89.16015625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -4498,12 +4717,15 @@
         <v>64.27001953125</v>
       </c>
       <c r="L18">
-        <v>64.27001953125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>103.66015625</v>
+      </c>
+      <c r="M18">
+        <v>103.66015625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -4536,12 +4758,15 @@
         <v>50.669921875</v>
       </c>
       <c r="L19">
-        <v>50.669921875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>107.35986328125</v>
+      </c>
+      <c r="M19">
+        <v>107.35986328125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -4574,12 +4799,15 @@
         <v>50.7900390625</v>
       </c>
       <c r="L20">
-        <v>50.7900390625</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>71.35986328125</v>
+      </c>
+      <c r="M20">
+        <v>71.35986328125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -4612,12 +4840,15 @@
         <v>55.889892578125</v>
       </c>
       <c r="L21">
-        <v>55.889892578125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>91.9599609375</v>
+      </c>
+      <c r="M21">
+        <v>91.9599609375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4650,12 +4881,15 @@
         <v>78.3798828125</v>
       </c>
       <c r="L22">
-        <v>78.3798828125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>74.10009765625</v>
+      </c>
+      <c r="M22">
+        <v>74.10009765625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -4688,12 +4922,15 @@
         <v>39.070068359375</v>
       </c>
       <c r="L23">
-        <v>39.070068359375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>69.60986328125</v>
+      </c>
+      <c r="M23">
+        <v>69.60986328125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -4726,12 +4963,15 @@
         <v>60.169921875</v>
       </c>
       <c r="L24">
-        <v>60.169921875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>82.81005859375</v>
+      </c>
+      <c r="M24">
+        <v>82.81005859375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -4764,12 +5004,15 @@
         <v>58.070068359375</v>
       </c>
       <c r="L25">
-        <v>58.070068359375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>92.56005859375</v>
+      </c>
+      <c r="M25">
+        <v>92.56005859375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -4802,12 +5045,15 @@
         <v>66.89013671875</v>
       </c>
       <c r="L26">
-        <v>66.89013671875</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>90.4599609375</v>
+      </c>
+      <c r="M26">
+        <v>90.4599609375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -4840,12 +5086,15 @@
         <v>29.8499755859375</v>
       </c>
       <c r="L27">
-        <v>29.8499755859375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>95.16015625</v>
+      </c>
+      <c r="M27">
+        <v>95.16015625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -4878,12 +5127,15 @@
         <v>54.27001953125</v>
       </c>
       <c r="L28">
-        <v>54.27001953125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>76.759765625</v>
+      </c>
+      <c r="M28">
+        <v>76.759765625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -4916,12 +5168,15 @@
         <v>66.27001953125</v>
       </c>
       <c r="L29">
-        <v>66.27001953125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+        <v>105.9599609375</v>
+      </c>
+      <c r="M29">
+        <v>105.9599609375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -4954,12 +5209,15 @@
         <v>63.169921875</v>
       </c>
       <c r="L30">
-        <v>63.169921875</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>74.66015625</v>
+      </c>
+      <c r="M30">
+        <v>74.66015625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -4992,12 +5250,15 @@
         <v>50.669921875</v>
       </c>
       <c r="L31">
-        <v>50.669921875</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>88.3798828125</v>
+      </c>
+      <c r="M31">
+        <v>88.3798828125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -5030,12 +5291,15 @@
         <v>84.06982421875</v>
       </c>
       <c r="L32">
-        <v>84.06982421875</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>53.030029296875</v>
+      </c>
+      <c r="M32">
+        <v>53.030029296875</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -5068,12 +5332,15 @@
         <v>47.570068359375</v>
       </c>
       <c r="L33">
-        <v>47.570068359375</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>69.25</v>
+      </c>
+      <c r="M33">
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -5106,12 +5373,15 @@
         <v>64.669921875</v>
       </c>
       <c r="L34">
-        <v>64.669921875</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>96.509765625</v>
+      </c>
+      <c r="M34">
+        <v>96.509765625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -5144,12 +5414,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="L35">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>86.06005859375</v>
+      </c>
+      <c r="M35">
+        <v>86.06005859375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -5182,12 +5455,15 @@
         <v>82.169921875</v>
       </c>
       <c r="L36">
-        <v>82.169921875</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>101.35986328125</v>
+      </c>
+      <c r="M36">
+        <v>101.35986328125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -5220,12 +5496,15 @@
         <v>40.8701171875</v>
       </c>
       <c r="L37">
-        <v>40.8701171875</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>82.4599609375</v>
+      </c>
+      <c r="M37">
+        <v>82.4599609375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -5258,12 +5537,15 @@
         <v>49.169921875</v>
       </c>
       <c r="L38">
-        <v>49.169921875</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>49.949951171875</v>
+      </c>
+      <c r="M38">
+        <v>49.949951171875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -5296,12 +5578,15 @@
         <v>43.14990234375</v>
       </c>
       <c r="L39">
-        <v>43.14990234375</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>56.85009765625</v>
+      </c>
+      <c r="M39">
+        <v>56.85009765625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -5334,12 +5619,15 @@
         <v>78.89013671875</v>
       </c>
       <c r="L40">
-        <v>78.89013671875</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>86.66015625</v>
+      </c>
+      <c r="M40">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -5372,12 +5660,15 @@
         <v>48.85009765625</v>
       </c>
       <c r="L41">
-        <v>48.85009765625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>70.89990234375</v>
+      </c>
+      <c r="M41">
+        <v>70.89990234375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -5410,12 +5701,15 @@
         <v>38.3701171875</v>
       </c>
       <c r="L42">
-        <v>38.3701171875</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+        <v>70.35986328125</v>
+      </c>
+      <c r="M42">
+        <v>70.35986328125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -5448,12 +5742,15 @@
         <v>51.18994140625</v>
       </c>
       <c r="L43">
-        <v>51.18994140625</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+        <v>83.56005859375</v>
+      </c>
+      <c r="M43">
+        <v>83.56005859375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -5486,12 +5783,15 @@
         <v>50.780029296875</v>
       </c>
       <c r="L44">
-        <v>50.780029296875</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+        <v>97.06005859375</v>
+      </c>
+      <c r="M44">
+        <v>97.06005859375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -5524,12 +5824,15 @@
         <v>64.2900390625</v>
       </c>
       <c r="L45">
-        <v>64.2900390625</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
+        <v>81.759765625</v>
+      </c>
+      <c r="M45">
+        <v>81.759765625</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -5562,12 +5865,15 @@
         <v>69.669921875</v>
       </c>
       <c r="L46">
-        <v>69.669921875</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>90.56005859375</v>
+      </c>
+      <c r="M46">
+        <v>90.56005859375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -5600,12 +5906,15 @@
         <v>47.8701171875</v>
       </c>
       <c r="L47">
-        <v>47.8701171875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+        <v>83.47998046875</v>
+      </c>
+      <c r="M47">
+        <v>83.47998046875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -5638,12 +5947,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="L48">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+        <v>94.06005859375</v>
+      </c>
+      <c r="M48">
+        <v>94.06005859375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -5676,12 +5988,15 @@
         <v>46.590087890625</v>
       </c>
       <c r="L49">
-        <v>46.590087890625</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+        <v>96.259765625</v>
+      </c>
+      <c r="M49">
+        <v>96.259765625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -5714,12 +6029,15 @@
         <v>58.090087890625</v>
       </c>
       <c r="L50">
-        <v>58.090087890625</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+        <v>88.759765625</v>
+      </c>
+      <c r="M50">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -5752,12 +6070,15 @@
         <v>63.570068359375</v>
       </c>
       <c r="L51">
-        <v>63.570068359375</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+        <v>101.41015625</v>
+      </c>
+      <c r="M51">
+        <v>101.41015625</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -5790,12 +6111,15 @@
         <v>50.989990234375</v>
       </c>
       <c r="L52">
-        <v>50.989990234375</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
+        <v>88.85986328125</v>
+      </c>
+      <c r="M52">
+        <v>88.85986328125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -5828,12 +6152,15 @@
         <v>58.550048828125</v>
       </c>
       <c r="L53">
-        <v>58.550048828125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+        <v>89.080078125</v>
+      </c>
+      <c r="M53">
+        <v>89.080078125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -5866,12 +6193,15 @@
         <v>39</v>
       </c>
       <c r="L54">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+        <v>52.2900390625</v>
+      </c>
+      <c r="M54">
+        <v>52.2900390625</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -5904,6 +6234,9 @@
         <v>0</v>
       </c>
       <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>0</v>
       </c>
     </row>
@@ -5924,154 +6257,154 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B2">
-        <v>875.3896484375</v>
+        <v>981.949951171875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3">
-        <v>865.590576171875</v>
+        <v>979.620361328125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>855.12060546875</v>
+        <v>979.249755859375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>852.62060546875</v>
+        <v>979.219970703125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>852.2900390625</v>
+        <v>974.218994140625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B7">
-        <v>852.080078125</v>
+        <v>973.14013671875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B8">
-        <v>851.18994140625</v>
+        <v>972.050048828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>849.789794921875</v>
+        <v>959.189697265625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>846.04931640625</v>
+        <v>958.219970703125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>838.899658203125</v>
+        <v>956.350830078125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B12">
-        <v>836.399658203125</v>
+        <v>947.23974609375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="B13">
-        <v>827.86962890625</v>
+        <v>944.219970703125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>820.510009765625</v>
+        <v>943.19921875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B15">
-        <v>817.8193359375</v>
+        <v>943.010009765625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B16">
-        <v>817.31005859375</v>
+        <v>937.39990234375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B17">
-        <v>810.349853515625</v>
+        <v>933.74951171875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18">
-        <v>810.14990234375</v>
+        <v>930.69970703125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B19">
-        <v>796.010009765625</v>
+        <v>929.7392578125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>795.119873046875</v>
+        <v>924.900146484375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6079,271 +6412,271 @@
         <v>44</v>
       </c>
       <c r="B21">
-        <v>787.14990234375</v>
+        <v>923.469482421875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B22">
-        <v>786.98974609375</v>
+        <v>918.23974609375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B23">
-        <v>784.08935546875</v>
+        <v>911.6904296875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24">
-        <v>782.940185546875</v>
+        <v>910.7099609375</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B25">
-        <v>782.529541015625</v>
+        <v>907.299560546875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>782.389404296875</v>
+        <v>905.589599609375</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="B27">
-        <v>779.499755859375</v>
+        <v>905.449951171875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>778.759765625</v>
+        <v>904.069091796875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B29">
-        <v>776.5</v>
+        <v>898.43994140625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B30">
-        <v>772.310302734375</v>
+        <v>895.239501953125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B31">
-        <v>770.770263671875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B32">
-        <v>766.660400390625</v>
+        <v>889.860107421875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B33">
-        <v>766.19970703125</v>
+        <v>887.839599609375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B34">
-        <v>761.348876953125</v>
+        <v>878.1605224609375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35">
-        <v>754.89990234375</v>
+        <v>874.510009765625</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B36">
-        <v>743.249755859375</v>
+        <v>873.409912109375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B37">
-        <v>742.5595703125</v>
+        <v>867.409912109375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>740.4599609375</v>
+        <v>857.369873046875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B39">
-        <v>725.419921875</v>
+        <v>844.14990234375</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B40">
-        <v>717.9599609375</v>
+        <v>843.169921875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B41">
-        <v>717.690185546875</v>
+        <v>840.69921875</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B42">
-        <v>716.6494140625</v>
+        <v>823.95849609375</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43">
-        <v>714.02978515625</v>
+        <v>820.3095703125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B44">
-        <v>713.81884765625</v>
+        <v>788.3602294921875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B45">
-        <v>678.9100341796875</v>
+        <v>783.339111328125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B46">
-        <v>678.81982421875</v>
+        <v>773.7099609375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47">
-        <v>677.629638671875</v>
+        <v>769.559326171875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B48">
-        <v>674.46044921875</v>
+        <v>763.449462890625</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B49">
-        <v>670.299560546875</v>
+        <v>749.3701171875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B50">
-        <v>663.2998046875</v>
+        <v>735.879638671875</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B51">
-        <v>637.479736328125</v>
+        <v>723.630126953125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B52">
-        <v>625.8295288085938</v>
+        <v>676.5595092773438</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53">
-        <v>570.3902587890625</v>
+        <v>663.3399658203125</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B54">
-        <v>315.009765625</v>
+        <v>384.830078125</v>
       </c>
     </row>
   </sheetData>
@@ -6358,272 +6691,272 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -6643,7 +6976,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6651,7 +6984,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6659,7 +6992,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6667,7 +7000,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6675,7 +7008,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6683,7 +7016,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6691,7 +7024,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6699,7 +7032,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6707,7 +7040,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -6715,7 +7048,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -6723,7 +7056,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -6731,7 +7064,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -6739,7 +7072,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -6747,7 +7080,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -6755,7 +7088,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6763,7 +7096,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6771,7 +7104,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -6779,7 +7112,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -6787,7 +7120,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6795,7 +7128,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6803,7 +7136,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6811,7 +7144,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -6819,7 +7152,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -6827,7 +7160,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -6835,7 +7168,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -6843,7 +7176,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -6851,7 +7184,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -6859,7 +7192,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -6867,7 +7200,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -6875,7 +7208,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -6883,7 +7216,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -6891,7 +7224,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -6899,7 +7232,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6907,7 +7240,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -6915,7 +7248,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -6923,7 +7256,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6931,7 +7264,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6939,7 +7272,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -6947,7 +7280,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -6955,7 +7288,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6963,7 +7296,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6971,7 +7304,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6979,7 +7312,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -6987,7 +7320,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -6995,7 +7328,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7003,7 +7336,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7011,7 +7344,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -7019,7 +7352,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -7027,7 +7360,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -7035,7 +7368,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -7043,7 +7376,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7051,7 +7384,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7059,7 +7392,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7082,7 +7415,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -7090,7 +7423,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -7098,7 +7431,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -7106,7 +7439,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -7114,7 +7447,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -7122,7 +7455,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -7130,7 +7463,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -7138,7 +7471,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -7146,7 +7479,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -7154,7 +7487,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -7162,7 +7495,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -7170,7 +7503,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -7178,7 +7511,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -7186,7 +7519,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -7194,7 +7527,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -7202,7 +7535,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -7210,7 +7543,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -7218,7 +7551,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -7226,7 +7559,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -7234,7 +7567,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -7242,7 +7575,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -7250,7 +7583,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -7258,7 +7591,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -7266,7 +7599,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -7274,7 +7607,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -7282,7 +7615,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -7290,7 +7623,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -7298,7 +7631,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -7306,7 +7639,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -7314,7 +7647,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -7322,7 +7655,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -7330,7 +7663,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -7338,7 +7671,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -7346,7 +7679,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -7354,7 +7687,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -7362,7 +7695,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -7370,7 +7703,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -7378,7 +7711,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -7386,7 +7719,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -7394,7 +7727,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -7402,7 +7735,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -7410,7 +7743,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -7418,7 +7751,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -7426,7 +7759,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -7434,7 +7767,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -7442,7 +7775,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -7450,7 +7783,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B48">
         <v>44.260009765625</v>
@@ -7458,7 +7791,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>44.06005859375</v>
@@ -7466,7 +7799,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50">
         <v>43.510009765625</v>
@@ -7474,7 +7807,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>42.9599609375</v>
@@ -7482,7 +7815,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B52">
         <v>40.60009765625</v>
@@ -7490,7 +7823,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53">
         <v>38.260009765625</v>
@@ -7498,7 +7831,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7521,7 +7854,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2">
         <v>281.78955078125</v>
@@ -7529,7 +7862,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>265.3896484375</v>
@@ -7537,7 +7870,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -7545,7 +7878,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5">
         <v>263.08984375</v>
@@ -7553,7 +7886,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>262.98974609375</v>
@@ -7561,7 +7894,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>261.28955078125</v>
@@ -7569,7 +7902,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>258.82958984375</v>
@@ -7577,7 +7910,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>254.509765625</v>
@@ -7585,7 +7918,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>253.41015625</v>
@@ -7593,7 +7926,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>253.08984375</v>
@@ -7601,7 +7934,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>253.08984375</v>
@@ -7609,7 +7942,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>251.22998046875</v>
@@ -7617,7 +7950,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>249.33984375</v>
@@ -7625,7 +7958,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>248.7099609375</v>
@@ -7633,7 +7966,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>247.169921875</v>
@@ -7641,7 +7974,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17">
         <v>246.2998046875</v>
@@ -7649,7 +7982,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>244.31005859375</v>
@@ -7657,7 +7990,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19">
         <v>243.61962890625</v>
@@ -7665,7 +7998,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>241.46044921875</v>
@@ -7673,7 +8006,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>239.5400390625</v>
@@ -7681,7 +8014,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22">
         <v>238.86962890625</v>
@@ -7689,7 +8022,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>238.7900390625</v>
@@ -7697,7 +8030,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>235.02001953125</v>
@@ -7705,7 +8038,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>234.090087890625</v>
@@ -7713,7 +8046,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26">
         <v>232.18994140625</v>
@@ -7721,7 +8054,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>231.8896484375</v>
@@ -7729,7 +8062,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>231.259765625</v>
@@ -7737,7 +8070,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>227.90966796875</v>
@@ -7745,7 +8078,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30">
         <v>227.8095703125</v>
@@ -7753,7 +8086,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>225.2099609375</v>
@@ -7761,7 +8094,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32">
         <v>225.02978515625</v>
@@ -7769,7 +8102,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33">
         <v>224.409912109375</v>
@@ -7777,7 +8110,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34">
         <v>222.49951171875</v>
@@ -7785,7 +8118,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B35">
         <v>219.469482421875</v>
@@ -7793,7 +8126,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <v>218.419921875</v>
@@ -7801,7 +8134,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B37">
         <v>216.3896484375</v>
@@ -7809,7 +8142,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38">
         <v>216.030517578125</v>
@@ -7817,7 +8150,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>215.5498046875</v>
@@ -7825,7 +8158,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40">
         <v>212.2099609375</v>
@@ -7833,7 +8166,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B41">
         <v>211.239990234375</v>
@@ -7841,7 +8174,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42">
         <v>209.509765625</v>
@@ -7849,7 +8182,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>206.1201171875</v>
@@ -7857,7 +8190,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B44">
         <v>205.58984375</v>
@@ -7865,7 +8198,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45">
         <v>204.8798828125</v>
@@ -7873,7 +8206,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46">
         <v>199.2001953125</v>
@@ -7881,7 +8214,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47">
         <v>198.499755859375</v>
@@ -7889,7 +8222,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B48">
         <v>197.369873046875</v>
@@ -7897,7 +8230,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49">
         <v>191.85986328125</v>
@@ -7905,7 +8238,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>187.64990234375</v>
@@ -7913,7 +8246,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B51">
         <v>186.4697265625</v>
@@ -7921,7 +8254,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52">
         <v>159.43994140625</v>
@@ -7929,7 +8262,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53">
         <v>120.6300048828125</v>
@@ -7937,7 +8270,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7960,7 +8293,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>352.31005859375</v>
@@ -7968,7 +8301,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>348.08984375</v>
@@ -7976,7 +8309,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>338.4404296875</v>
@@ -7984,7 +8317,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>334.60009765625</v>
@@ -7992,7 +8325,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6">
         <v>329.4404296875</v>
@@ -8000,7 +8333,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7">
         <v>328.05029296875</v>
@@ -8008,7 +8341,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>323.5302734375</v>
@@ -8016,7 +8349,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>318.04052734375</v>
@@ -8024,7 +8357,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>317.26025390625</v>
@@ -8032,7 +8365,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>316.66015625</v>
@@ -8040,7 +8373,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>315.94970703125</v>
@@ -8048,7 +8381,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>303.949462890625</v>
@@ -8056,7 +8389,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14">
         <v>300.99951171875</v>
@@ -8064,7 +8397,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>300.5</v>
@@ -8072,7 +8405,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>300.099609375</v>
@@ -8080,7 +8413,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17">
         <v>299.199951171875</v>
@@ -8088,7 +8421,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>299.009765625</v>
@@ -8096,7 +8429,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>298.93017578125</v>
@@ -8104,7 +8437,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>298.8798828125</v>
@@ -8112,7 +8445,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>296.4697265625</v>
@@ -8120,7 +8453,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22">
         <v>296.07958984375</v>
@@ -8128,7 +8461,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <v>295.85009765625</v>
@@ -8136,7 +8469,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>294.43994140625</v>
@@ -8144,7 +8477,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25">
         <v>293.139892578125</v>
@@ -8152,7 +8485,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26">
         <v>290.2998046875</v>
@@ -8160,7 +8493,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27">
         <v>289</v>
@@ -8168,7 +8501,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>288.1103515625</v>
@@ -8176,7 +8509,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>288.1103515625</v>
@@ -8184,7 +8517,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>287.43017578125</v>
@@ -8192,7 +8525,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B31">
         <v>286.16015625</v>
@@ -8200,7 +8533,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32">
         <v>285.639892578125</v>
@@ -8208,7 +8541,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33">
         <v>284.639892578125</v>
@@ -8216,7 +8549,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>284.2900390625</v>
@@ -8224,7 +8557,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35">
         <v>284.2294921875</v>
@@ -8232,7 +8565,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>283.899658203125</v>
@@ -8240,7 +8573,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>282.68994140625</v>
@@ -8248,7 +8581,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>280.650390625</v>
@@ -8256,7 +8589,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B39">
         <v>279.340087890625</v>
@@ -8264,7 +8597,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40">
         <v>277.80029296875</v>
@@ -8272,7 +8605,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41">
         <v>276.829833984375</v>
@@ -8280,7 +8613,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42">
         <v>272.47998046875</v>
@@ -8288,7 +8621,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43">
         <v>269.719970703125</v>
@@ -8296,7 +8629,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B44">
         <v>259.3798828125</v>
@@ -8304,7 +8637,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B45">
         <v>253.94970703125</v>
@@ -8312,7 +8645,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B46">
         <v>244.02978515625</v>
@@ -8320,7 +8653,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>234.26025390625</v>
@@ -8328,7 +8661,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48">
         <v>230.099853515625</v>
@@ -8336,7 +8669,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B49">
         <v>228.480224609375</v>
@@ -8344,7 +8677,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50">
         <v>222.0400390625</v>
@@ -8352,7 +8685,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B51">
         <v>221.0599975585938</v>
@@ -8360,7 +8693,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52">
         <v>216.89013671875</v>
@@ -8368,7 +8701,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B53">
         <v>199.0599365234375</v>
@@ -8376,7 +8709,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B54">
         <v>77.18994140625</v>
@@ -8399,354 +8732,354 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2">
-        <v>266.2998046875</v>
+        <v>386.849609375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>254.06005859375</v>
+        <v>385.76953125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>247.02001953125</v>
+        <v>384.47021484375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <v>241.419921875</v>
+        <v>381.4296875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B6">
-        <v>238.46044921875</v>
+        <v>375.830322265625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>237.81982421875</v>
+        <v>373.83984375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>237.4794921875</v>
+        <v>358.47021484375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="B9">
-        <v>236.580078125</v>
+        <v>355.5703125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B10">
-        <v>230.98974609375</v>
+        <v>354.9296875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11">
-        <v>226.580078125</v>
+        <v>352.490234375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B12">
-        <v>223.6201171875</v>
+        <v>348.749755859375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B13">
-        <v>220.7197265625</v>
+        <v>348.490234375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14">
-        <v>218.97998046875</v>
+        <v>339.830078125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B15">
-        <v>217.3798828125</v>
+        <v>337.56982421875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B16">
-        <v>215.419921875</v>
+        <v>334.40966796875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B17">
-        <v>210.580078125</v>
+        <v>327.750244140625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B18">
-        <v>209.52001953125</v>
+        <v>325.149658203125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>208.31982421875</v>
+        <v>323.58935546875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B20">
-        <v>208.259765625</v>
+        <v>321.459716796875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B21">
-        <v>202.0302734375</v>
+        <v>321.179931640625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B22">
-        <v>202.0302734375</v>
+        <v>320.27001953125</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B23">
-        <v>200.7001953125</v>
+        <v>320.0302734375</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B24">
-        <v>197.02001953125</v>
+        <v>316.889404296875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25">
-        <v>194.55029296875</v>
+        <v>314.160400390625</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B26">
-        <v>193.52001953125</v>
+        <v>313.949951171875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B27">
-        <v>192.360107421875</v>
+        <v>311.890380859375</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B28">
-        <v>191.919921875</v>
+        <v>309.4501953125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29">
-        <v>188.7197265625</v>
+        <v>307.859375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B30">
-        <v>187.22021484375</v>
+        <v>307.64013671875</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B31">
-        <v>186.88037109375</v>
+        <v>305.97021484375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B32">
-        <v>186.31982421875</v>
+        <v>304.610107421875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B33">
-        <v>186.02978515625</v>
+        <v>303.260498046875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B34">
-        <v>186.02001953125</v>
+        <v>295.750244140625</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B35">
-        <v>181.81982421875</v>
+        <v>294.969970703125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B36">
-        <v>179.349853515625</v>
+        <v>292.56982421875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B37">
-        <v>179.22021484375</v>
+        <v>291.589599609375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>177.83984375</v>
+        <v>290.0203857421875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B39">
-        <v>174.81982421875</v>
+        <v>284.800048828125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B40">
-        <v>170.9697265625</v>
+        <v>276.949951171875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B41">
-        <v>170.94970703125</v>
+        <v>269.1298828125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B42">
-        <v>168.400146484375</v>
+        <v>268.860107421875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B43">
-        <v>168.02001953125</v>
+        <v>267.649658203125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B44">
-        <v>166.8798828125</v>
+        <v>261.880126953125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B45">
-        <v>166.8603515625</v>
+        <v>259.4697265625</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -8754,71 +9087,71 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>166.7802734375</v>
+        <v>259.44970703125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B47">
-        <v>166.5</v>
+        <v>259.229736328125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B48">
-        <v>164.89990234375</v>
+        <v>258.8095703125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B49">
-        <v>159.080078125</v>
+        <v>257.1201171875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B50">
-        <v>148.019775390625</v>
+        <v>249.4697265625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B51">
-        <v>137.830322265625</v>
+        <v>245.9091796875</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B52">
-        <v>135.76953125</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B53">
-        <v>131.389892578125</v>
+        <v>198.749755859375</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B54">
-        <v>129.550048828125</v>
+        <v>196.969970703125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -681,7 +681,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="M2">
-        <v>87.4599609375</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -722,7 +722,7 @@
         <v>85.4599609375</v>
       </c>
       <c r="M3">
-        <v>85.4599609375</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -763,7 +763,7 @@
         <v>114.259765625</v>
       </c>
       <c r="M4">
-        <v>114.259765625</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -804,7 +804,7 @@
         <v>70.16015625</v>
       </c>
       <c r="M5">
-        <v>70.16015625</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -845,7 +845,7 @@
         <v>91.06005859375</v>
       </c>
       <c r="M6">
-        <v>91.06005859375</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -886,7 +886,7 @@
         <v>95.66015625</v>
       </c>
       <c r="M7">
-        <v>95.66015625</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -927,7 +927,7 @@
         <v>79.66015625</v>
       </c>
       <c r="M8">
-        <v>79.66015625</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -968,7 +968,7 @@
         <v>86.259765625</v>
       </c>
       <c r="M9">
-        <v>86.259765625</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1009,7 +1009,7 @@
         <v>71.759765625</v>
       </c>
       <c r="M10">
-        <v>71.759765625</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>87.759765625</v>
       </c>
       <c r="M11">
-        <v>87.759765625</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>79.580078125</v>
       </c>
       <c r="M12">
-        <v>79.580078125</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1132,7 +1132,7 @@
         <v>85.16015625</v>
       </c>
       <c r="M13">
-        <v>85.16015625</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1173,7 +1173,7 @@
         <v>58.159912109375</v>
       </c>
       <c r="M14">
-        <v>58.159912109375</v>
+        <v>74.61</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1214,7 +1214,7 @@
         <v>104.4599609375</v>
       </c>
       <c r="M15">
-        <v>104.4599609375</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1255,7 +1255,7 @@
         <v>91.27978515625</v>
       </c>
       <c r="M16">
-        <v>91.27978515625</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1296,7 +1296,7 @@
         <v>89.16015625</v>
       </c>
       <c r="M17">
-        <v>89.16015625</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1337,7 +1337,7 @@
         <v>103.66015625</v>
       </c>
       <c r="M18">
-        <v>103.66015625</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1378,7 +1378,7 @@
         <v>107.35986328125</v>
       </c>
       <c r="M19">
-        <v>107.35986328125</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1419,7 +1419,7 @@
         <v>71.35986328125</v>
       </c>
       <c r="M20">
-        <v>71.35986328125</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1460,7 +1460,7 @@
         <v>91.9599609375</v>
       </c>
       <c r="M21">
-        <v>91.9599609375</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1501,7 +1501,7 @@
         <v>74.10009765625</v>
       </c>
       <c r="M22">
-        <v>74.10009765625</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1542,7 +1542,7 @@
         <v>69.60986328125</v>
       </c>
       <c r="M23">
-        <v>69.60986328125</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1583,7 +1583,7 @@
         <v>82.81005859375</v>
       </c>
       <c r="M24">
-        <v>82.81005859375</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1624,7 +1624,7 @@
         <v>92.56005859375</v>
       </c>
       <c r="M25">
-        <v>92.56005859375</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1665,7 +1665,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="M26">
-        <v>90.4599609375</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1706,7 +1706,7 @@
         <v>95.16015625</v>
       </c>
       <c r="M27">
-        <v>95.16015625</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1747,7 +1747,7 @@
         <v>76.759765625</v>
       </c>
       <c r="M28">
-        <v>76.759765625</v>
+        <v>71.63</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1788,7 +1788,7 @@
         <v>105.9599609375</v>
       </c>
       <c r="M29">
-        <v>105.9599609375</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1829,7 +1829,7 @@
         <v>74.66015625</v>
       </c>
       <c r="M30">
-        <v>74.66015625</v>
+        <v>72.34999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1870,7 +1870,7 @@
         <v>88.3798828125</v>
       </c>
       <c r="M31">
-        <v>88.3798828125</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1911,7 +1911,7 @@
         <v>53.030029296875</v>
       </c>
       <c r="M32">
-        <v>53.030029296875</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1952,7 +1952,7 @@
         <v>69.25</v>
       </c>
       <c r="M33">
-        <v>69.25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1993,7 +1993,7 @@
         <v>96.509765625</v>
       </c>
       <c r="M34">
-        <v>96.509765625</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2034,7 +2034,7 @@
         <v>86.06005859375</v>
       </c>
       <c r="M35">
-        <v>86.06005859375</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2075,7 +2075,7 @@
         <v>101.35986328125</v>
       </c>
       <c r="M36">
-        <v>101.35986328125</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2116,7 +2116,7 @@
         <v>82.4599609375</v>
       </c>
       <c r="M37">
-        <v>82.4599609375</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -2157,7 +2157,7 @@
         <v>49.949951171875</v>
       </c>
       <c r="M38">
-        <v>49.949951171875</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2198,7 +2198,7 @@
         <v>56.85009765625</v>
       </c>
       <c r="M39">
-        <v>56.85009765625</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2239,7 +2239,7 @@
         <v>86.66015625</v>
       </c>
       <c r="M40">
-        <v>86.66015625</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2280,7 +2280,7 @@
         <v>70.89990234375</v>
       </c>
       <c r="M41">
-        <v>70.89990234375</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2321,7 +2321,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="M42">
-        <v>70.35986328125</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2362,7 +2362,7 @@
         <v>83.56005859375</v>
       </c>
       <c r="M43">
-        <v>83.56005859375</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2403,7 +2403,7 @@
         <v>97.06005859375</v>
       </c>
       <c r="M44">
-        <v>97.06005859375</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2444,7 +2444,7 @@
         <v>81.759765625</v>
       </c>
       <c r="M45">
-        <v>81.759765625</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2485,7 +2485,7 @@
         <v>90.56005859375</v>
       </c>
       <c r="M46">
-        <v>90.56005859375</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2526,7 +2526,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="M47">
-        <v>83.47998046875</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2567,7 +2567,7 @@
         <v>94.06005859375</v>
       </c>
       <c r="M48">
-        <v>94.06005859375</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2608,7 +2608,7 @@
         <v>96.259765625</v>
       </c>
       <c r="M49">
-        <v>96.259765625</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2649,7 +2649,7 @@
         <v>88.759765625</v>
       </c>
       <c r="M50">
-        <v>88.759765625</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2690,7 +2690,7 @@
         <v>101.41015625</v>
       </c>
       <c r="M51">
-        <v>101.41015625</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2731,7 +2731,7 @@
         <v>88.85986328125</v>
       </c>
       <c r="M52">
-        <v>88.85986328125</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2772,7 +2772,7 @@
         <v>89.080078125</v>
       </c>
       <c r="M53">
-        <v>89.080078125</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2813,7 +2813,7 @@
         <v>52.2900390625</v>
       </c>
       <c r="M54">
-        <v>52.2900390625</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -4064,7 +4064,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="M2">
-        <v>87.4599609375</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4105,7 +4105,7 @@
         <v>85.4599609375</v>
       </c>
       <c r="M3">
-        <v>85.4599609375</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4146,7 +4146,7 @@
         <v>114.259765625</v>
       </c>
       <c r="M4">
-        <v>114.259765625</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4187,7 +4187,7 @@
         <v>70.16015625</v>
       </c>
       <c r="M5">
-        <v>70.16015625</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -4228,7 +4228,7 @@
         <v>91.06005859375</v>
       </c>
       <c r="M6">
-        <v>91.06005859375</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4269,7 +4269,7 @@
         <v>95.66015625</v>
       </c>
       <c r="M7">
-        <v>95.66015625</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4310,7 +4310,7 @@
         <v>79.66015625</v>
       </c>
       <c r="M8">
-        <v>79.66015625</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4351,7 +4351,7 @@
         <v>86.259765625</v>
       </c>
       <c r="M9">
-        <v>86.259765625</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4392,7 +4392,7 @@
         <v>71.759765625</v>
       </c>
       <c r="M10">
-        <v>71.759765625</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4433,7 +4433,7 @@
         <v>87.759765625</v>
       </c>
       <c r="M11">
-        <v>87.759765625</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4474,7 +4474,7 @@
         <v>79.580078125</v>
       </c>
       <c r="M12">
-        <v>79.580078125</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -4515,7 +4515,7 @@
         <v>85.16015625</v>
       </c>
       <c r="M13">
-        <v>85.16015625</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -4556,7 +4556,7 @@
         <v>58.159912109375</v>
       </c>
       <c r="M14">
-        <v>58.159912109375</v>
+        <v>74.61</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4597,7 +4597,7 @@
         <v>104.4599609375</v>
       </c>
       <c r="M15">
-        <v>104.4599609375</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4638,7 +4638,7 @@
         <v>91.27978515625</v>
       </c>
       <c r="M16">
-        <v>91.27978515625</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -4679,7 +4679,7 @@
         <v>89.16015625</v>
       </c>
       <c r="M17">
-        <v>89.16015625</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -4720,7 +4720,7 @@
         <v>103.66015625</v>
       </c>
       <c r="M18">
-        <v>103.66015625</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -4761,7 +4761,7 @@
         <v>107.35986328125</v>
       </c>
       <c r="M19">
-        <v>107.35986328125</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -4802,7 +4802,7 @@
         <v>71.35986328125</v>
       </c>
       <c r="M20">
-        <v>71.35986328125</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -4843,7 +4843,7 @@
         <v>91.9599609375</v>
       </c>
       <c r="M21">
-        <v>91.9599609375</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -4884,7 +4884,7 @@
         <v>74.10009765625</v>
       </c>
       <c r="M22">
-        <v>74.10009765625</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4925,7 +4925,7 @@
         <v>69.60986328125</v>
       </c>
       <c r="M23">
-        <v>69.60986328125</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -4966,7 +4966,7 @@
         <v>82.81005859375</v>
       </c>
       <c r="M24">
-        <v>82.81005859375</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5007,7 +5007,7 @@
         <v>92.56005859375</v>
       </c>
       <c r="M25">
-        <v>92.56005859375</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5048,7 +5048,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="M26">
-        <v>90.4599609375</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -5089,7 +5089,7 @@
         <v>95.16015625</v>
       </c>
       <c r="M27">
-        <v>95.16015625</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5130,7 +5130,7 @@
         <v>76.759765625</v>
       </c>
       <c r="M28">
-        <v>76.759765625</v>
+        <v>71.63</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -5171,7 +5171,7 @@
         <v>105.9599609375</v>
       </c>
       <c r="M29">
-        <v>105.9599609375</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5212,7 +5212,7 @@
         <v>74.66015625</v>
       </c>
       <c r="M30">
-        <v>74.66015625</v>
+        <v>72.34999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5253,7 +5253,7 @@
         <v>88.3798828125</v>
       </c>
       <c r="M31">
-        <v>88.3798828125</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5294,7 +5294,7 @@
         <v>53.030029296875</v>
       </c>
       <c r="M32">
-        <v>53.030029296875</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -5335,7 +5335,7 @@
         <v>69.25</v>
       </c>
       <c r="M33">
-        <v>69.25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5376,7 +5376,7 @@
         <v>96.509765625</v>
       </c>
       <c r="M34">
-        <v>96.509765625</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -5417,7 +5417,7 @@
         <v>86.06005859375</v>
       </c>
       <c r="M35">
-        <v>86.06005859375</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -5458,7 +5458,7 @@
         <v>101.35986328125</v>
       </c>
       <c r="M36">
-        <v>101.35986328125</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5499,7 +5499,7 @@
         <v>82.4599609375</v>
       </c>
       <c r="M37">
-        <v>82.4599609375</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -5540,7 +5540,7 @@
         <v>49.949951171875</v>
       </c>
       <c r="M38">
-        <v>49.949951171875</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -5581,7 +5581,7 @@
         <v>56.85009765625</v>
       </c>
       <c r="M39">
-        <v>56.85009765625</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -5622,7 +5622,7 @@
         <v>86.66015625</v>
       </c>
       <c r="M40">
-        <v>86.66015625</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -5663,7 +5663,7 @@
         <v>70.89990234375</v>
       </c>
       <c r="M41">
-        <v>70.89990234375</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -5704,7 +5704,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="M42">
-        <v>70.35986328125</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -5745,7 +5745,7 @@
         <v>83.56005859375</v>
       </c>
       <c r="M43">
-        <v>83.56005859375</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -5786,7 +5786,7 @@
         <v>97.06005859375</v>
       </c>
       <c r="M44">
-        <v>97.06005859375</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -5827,7 +5827,7 @@
         <v>81.759765625</v>
       </c>
       <c r="M45">
-        <v>81.759765625</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -5868,7 +5868,7 @@
         <v>90.56005859375</v>
       </c>
       <c r="M46">
-        <v>90.56005859375</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -5909,7 +5909,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="M47">
-        <v>83.47998046875</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -5950,7 +5950,7 @@
         <v>94.06005859375</v>
       </c>
       <c r="M48">
-        <v>94.06005859375</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -5991,7 +5991,7 @@
         <v>96.259765625</v>
       </c>
       <c r="M49">
-        <v>96.259765625</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6032,7 +6032,7 @@
         <v>88.759765625</v>
       </c>
       <c r="M50">
-        <v>88.759765625</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6073,7 +6073,7 @@
         <v>101.41015625</v>
       </c>
       <c r="M51">
-        <v>101.41015625</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6114,7 +6114,7 @@
         <v>88.85986328125</v>
       </c>
       <c r="M52">
-        <v>88.85986328125</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6155,7 +6155,7 @@
         <v>89.080078125</v>
       </c>
       <c r="M53">
-        <v>89.080078125</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6196,7 +6196,7 @@
         <v>52.2900390625</v>
       </c>
       <c r="M54">
-        <v>52.2900390625</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6257,90 +6257,90 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B2">
-        <v>981.949951171875</v>
+        <v>973.560400390625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>979.620361328125</v>
+        <v>971.759814453125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B4">
-        <v>979.249755859375</v>
+        <v>969.950283203125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>979.219970703125</v>
+        <v>964.039208984375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B6">
-        <v>974.218994140625</v>
+        <v>963.580078125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>973.14013671875</v>
+        <v>961.090673828125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B8">
-        <v>972.050048828125</v>
+        <v>957.760009765625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B9">
-        <v>959.189697265625</v>
+        <v>956.239794921875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>958.219970703125</v>
+        <v>950.789794921875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B11">
-        <v>956.350830078125</v>
+        <v>948.660009765625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="B12">
-        <v>947.23974609375</v>
+        <v>939.839453125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6348,215 +6348,215 @@
         <v>50</v>
       </c>
       <c r="B13">
-        <v>944.219970703125</v>
+        <v>938.259814453125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>943.19921875</v>
+        <v>923.270068359375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>943.010009765625</v>
+        <v>918.829931640625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B16">
-        <v>937.39990234375</v>
+        <v>917.2298828125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B17">
-        <v>933.74951171875</v>
+        <v>915.43984375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B18">
-        <v>930.69970703125</v>
+        <v>914.139453125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B19">
-        <v>929.7392578125</v>
+        <v>912.52998046875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B20">
-        <v>924.900146484375</v>
+        <v>911.7998046875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B21">
-        <v>923.469482421875</v>
+        <v>903.73037109375</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B22">
-        <v>918.23974609375</v>
+        <v>903.159716796875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>911.6904296875</v>
+        <v>901.029296875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="B24">
-        <v>910.7099609375</v>
+        <v>893.53984375</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B25">
-        <v>907.299560546875</v>
+        <v>893.059326171875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B26">
-        <v>905.589599609375</v>
+        <v>890.73994140625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B27">
-        <v>905.449951171875</v>
+        <v>889.389697265625</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B28">
-        <v>904.069091796875</v>
+        <v>887.879736328125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B29">
-        <v>898.43994140625</v>
+        <v>882.379541015625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B30">
-        <v>895.239501953125</v>
+        <v>878.1798828125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B31">
-        <v>892</v>
+        <v>877.529931640625</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B32">
-        <v>889.860107421875</v>
+        <v>874.339794921875</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B33">
-        <v>887.839599609375</v>
+        <v>870.2003662109375</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B34">
-        <v>878.1605224609375</v>
+        <v>870.180126953125</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B35">
-        <v>874.510009765625</v>
+        <v>869.699755859375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B36">
-        <v>873.409912109375</v>
+        <v>865.109716796875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B37">
-        <v>867.409912109375</v>
+        <v>860.599990234375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B38">
-        <v>857.369873046875</v>
+        <v>850.5892578125</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B39">
-        <v>844.14990234375</v>
+        <v>849.749951171875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -6564,15 +6564,15 @@
         <v>13</v>
       </c>
       <c r="B40">
-        <v>843.169921875</v>
+        <v>837.8099609375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B41">
-        <v>840.69921875</v>
+        <v>824.259814453125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -6580,7 +6580,7 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>823.95849609375</v>
+        <v>823.04873046875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -6588,31 +6588,31 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>820.3095703125</v>
+        <v>821.54970703125</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B44">
-        <v>788.3602294921875</v>
+        <v>814.00908203125</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>783.339111328125</v>
+        <v>781.3500732421875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B46">
-        <v>773.7099609375</v>
+        <v>778.139599609375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -6620,31 +6620,31 @@
         <v>30</v>
       </c>
       <c r="B47">
-        <v>769.559326171875</v>
+        <v>774.109462890625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B48">
-        <v>763.449462890625</v>
+        <v>768.5801953125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B49">
-        <v>749.3701171875</v>
+        <v>761.619599609375</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B50">
-        <v>735.879638671875</v>
+        <v>736.87001953125</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -6652,23 +6652,23 @@
         <v>40</v>
       </c>
       <c r="B51">
-        <v>723.630126953125</v>
+        <v>721.319970703125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B52">
-        <v>676.5595092773438</v>
+        <v>665.4400634765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B53">
-        <v>663.3399658203125</v>
+        <v>662.4595581054688</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -6676,7 +6676,7 @@
         <v>32</v>
       </c>
       <c r="B54">
-        <v>384.830078125</v>
+        <v>402.17998046875</v>
       </c>
     </row>
   </sheetData>
@@ -8732,178 +8732,178 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B2">
-        <v>386.849609375</v>
+        <v>363.51982421875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>385.76953125</v>
+        <v>358.76005859375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>384.47021484375</v>
+        <v>356.66015625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B5">
-        <v>381.4296875</v>
+        <v>349.68974609375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B6">
-        <v>375.830322265625</v>
+        <v>346.4302734375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>373.83984375</v>
+        <v>345.409765625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B8">
-        <v>358.47021484375</v>
+        <v>345.3798828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B9">
-        <v>355.5703125</v>
+        <v>344.720166015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B10">
-        <v>354.9296875</v>
+        <v>342.530078125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B11">
-        <v>352.490234375</v>
+        <v>338.21015625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B12">
-        <v>348.749755859375</v>
+        <v>334.619921875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B13">
-        <v>348.490234375</v>
+        <v>330.27001953125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B14">
-        <v>339.830078125</v>
+        <v>324.9900390625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>337.56982421875</v>
+        <v>320.22958984375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B16">
-        <v>334.40966796875</v>
+        <v>319.439892578125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B17">
-        <v>327.750244140625</v>
+        <v>319.359951171875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B18">
-        <v>325.149658203125</v>
+        <v>319.0099609375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>323.58935546875</v>
+        <v>318.189794921875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B20">
-        <v>321.459716796875</v>
+        <v>317.180322265625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B21">
-        <v>321.179931640625</v>
+        <v>313.0201171875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B22">
-        <v>320.27001953125</v>
+        <v>308.85986328125</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B23">
-        <v>320.0302734375</v>
+        <v>308.000341796875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -8911,103 +8911,103 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>316.889404296875</v>
+        <v>306.709619140625</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B25">
-        <v>314.160400390625</v>
+        <v>305.790185546875</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="B26">
-        <v>313.949951171875</v>
+        <v>303.930322265625</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B27">
-        <v>311.890380859375</v>
+        <v>302.980029296875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>309.4501953125</v>
+        <v>296.849609375</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B29">
-        <v>307.859375</v>
+        <v>293.92978515625</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B30">
-        <v>307.64013671875</v>
+        <v>292.040087890625</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B31">
-        <v>305.97021484375</v>
+        <v>291.699951171875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B32">
-        <v>304.610107421875</v>
+        <v>290.139697265625</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B33">
-        <v>303.260498046875</v>
+        <v>289.84013671875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B34">
-        <v>295.750244140625</v>
+        <v>288.069873046875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35">
-        <v>294.969970703125</v>
+        <v>287.20986328125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B36">
-        <v>292.56982421875</v>
+        <v>286.290234375</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -9015,55 +9015,55 @@
         <v>55</v>
       </c>
       <c r="B37">
-        <v>291.589599609375</v>
+        <v>284.229833984375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B38">
-        <v>290.0203857421875</v>
+        <v>283.940087890625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B39">
-        <v>284.800048828125</v>
+        <v>282.399951171875</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B40">
-        <v>276.949951171875</v>
+        <v>282.0602294921875</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B41">
-        <v>269.1298828125</v>
+        <v>279.339990234375</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B42">
-        <v>268.860107421875</v>
+        <v>277.310009765625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B43">
-        <v>267.649658203125</v>
+        <v>273.919873046875</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -9071,55 +9071,55 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>261.880126953125</v>
+        <v>271.770166015625</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B45">
-        <v>259.4697265625</v>
+        <v>270.37001953125</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="B46">
-        <v>259.44970703125</v>
+        <v>265.919814453125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B47">
-        <v>259.229736328125</v>
+        <v>263.35970703125</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B48">
-        <v>258.8095703125</v>
+        <v>262.519892578125</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B49">
-        <v>257.1201171875</v>
+        <v>261.5498046875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B50">
-        <v>249.4697265625</v>
+        <v>254.8099609375</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -9127,7 +9127,7 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>245.9091796875</v>
+        <v>244.9994140625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -9135,23 +9135,23 @@
         <v>49</v>
       </c>
       <c r="B52">
-        <v>241.5</v>
+        <v>228.99990234375</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B53">
-        <v>198.749755859375</v>
+        <v>222.709931640625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B54">
-        <v>196.969970703125</v>
+        <v>184.6498046875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Completa.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="75">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Rodada 12</t>
+  </si>
+  <si>
+    <t>Rodada 13</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
@@ -245,6 +248,9 @@
   </si>
   <si>
     <t>Marco</t>
+  </si>
+  <si>
+    <t>Abril</t>
   </si>
 </sst>
 </file>
@@ -602,10 +608,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,10 +648,13 @@
       <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -681,12 +690,15 @@
         <v>87.4599609375</v>
       </c>
       <c r="M2">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>69.7998046875</v>
+      </c>
+      <c r="N2">
+        <v>69.7998046875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -722,12 +734,15 @@
         <v>85.4599609375</v>
       </c>
       <c r="M3">
-        <v>80.09999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>80.10009765625</v>
+      </c>
+      <c r="N3">
+        <v>80.10009765625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -763,12 +778,15 @@
         <v>114.259765625</v>
       </c>
       <c r="M4">
-        <v>73.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>73.89990234375</v>
+      </c>
+      <c r="N4">
+        <v>73.89990234375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -804,12 +822,15 @@
         <v>70.16015625</v>
       </c>
       <c r="M5">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>83.7001953125</v>
+      </c>
+      <c r="N5">
+        <v>83.7001953125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -845,12 +866,15 @@
         <v>91.06005859375</v>
       </c>
       <c r="M6">
-        <v>83.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>83.10009765625</v>
+      </c>
+      <c r="N6">
+        <v>83.10009765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -888,10 +912,13 @@
       <c r="M7">
         <v>96.75</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -927,12 +954,15 @@
         <v>79.66015625</v>
       </c>
       <c r="M8">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>84.39990234375</v>
+      </c>
+      <c r="N8">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -968,12 +998,15 @@
         <v>86.259765625</v>
       </c>
       <c r="M9">
-        <v>82.90000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>82.89990234375</v>
+      </c>
+      <c r="N9">
+        <v>82.89990234375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -1009,12 +1042,15 @@
         <v>71.759765625</v>
       </c>
       <c r="M10">
-        <v>70.84999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>70.85009765625</v>
+      </c>
+      <c r="N10">
+        <v>70.85009765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -1052,10 +1088,13 @@
       <c r="M11">
         <v>76.75</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>76.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -1091,12 +1130,15 @@
         <v>79.580078125</v>
       </c>
       <c r="M12">
-        <v>77.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>77.9501953125</v>
+      </c>
+      <c r="N12">
+        <v>77.9501953125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -1132,12 +1174,15 @@
         <v>85.16015625</v>
       </c>
       <c r="M13">
-        <v>81.45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>81.4501953125</v>
+      </c>
+      <c r="N13">
+        <v>81.4501953125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -1173,12 +1218,15 @@
         <v>58.159912109375</v>
       </c>
       <c r="M14">
-        <v>74.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>74.60986328125</v>
+      </c>
+      <c r="N14">
+        <v>74.60986328125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -1216,10 +1264,13 @@
       <c r="M15">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -1255,12 +1306,15 @@
         <v>91.27978515625</v>
       </c>
       <c r="M16">
-        <v>81.09999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>81.10009765625</v>
+      </c>
+      <c r="N16">
+        <v>81.10009765625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -1296,12 +1350,15 @@
         <v>89.16015625</v>
       </c>
       <c r="M17">
-        <v>82.15000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>82.14990234375</v>
+      </c>
+      <c r="N17">
+        <v>82.14990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -1337,12 +1394,15 @@
         <v>103.66015625</v>
       </c>
       <c r="M18">
-        <v>77.95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>77.9501953125</v>
+      </c>
+      <c r="N18">
+        <v>77.9501953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -1378,12 +1438,15 @@
         <v>107.35986328125</v>
       </c>
       <c r="M19">
-        <v>89.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>89.4501953125</v>
+      </c>
+      <c r="N19">
+        <v>89.4501953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -1419,12 +1482,15 @@
         <v>71.35986328125</v>
       </c>
       <c r="M20">
-        <v>75.91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>75.91015625</v>
+      </c>
+      <c r="N20">
+        <v>75.91015625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -1460,12 +1526,15 @@
         <v>91.9599609375</v>
       </c>
       <c r="M21">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>61.39990234375</v>
+      </c>
+      <c r="N21">
+        <v>61.39990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1501,12 +1570,15 @@
         <v>74.10009765625</v>
       </c>
       <c r="M22">
-        <v>91.45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>91.4501953125</v>
+      </c>
+      <c r="N22">
+        <v>91.4501953125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -1542,12 +1614,15 @@
         <v>69.60986328125</v>
       </c>
       <c r="M23">
-        <v>84.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>84.2998046875</v>
+      </c>
+      <c r="N23">
+        <v>84.2998046875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -1583,12 +1658,15 @@
         <v>82.81005859375</v>
       </c>
       <c r="M24">
-        <v>77.34999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>77.35009765625</v>
+      </c>
+      <c r="N24">
+        <v>77.35009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -1624,12 +1702,15 @@
         <v>92.56005859375</v>
       </c>
       <c r="M25">
-        <v>70.59999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>70.60009765625</v>
+      </c>
+      <c r="N25">
+        <v>70.60009765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -1665,12 +1746,15 @@
         <v>90.4599609375</v>
       </c>
       <c r="M26">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>84.39990234375</v>
+      </c>
+      <c r="N26">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -1706,12 +1790,15 @@
         <v>95.16015625</v>
       </c>
       <c r="M27">
-        <v>87.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>87.2001953125</v>
+      </c>
+      <c r="N27">
+        <v>87.2001953125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -1747,12 +1834,15 @@
         <v>76.759765625</v>
       </c>
       <c r="M28">
-        <v>71.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>71.6298828125</v>
+      </c>
+      <c r="N28">
+        <v>71.6298828125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -1790,10 +1880,13 @@
       <c r="M29">
         <v>77.25</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29">
+        <v>77.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -1829,12 +1922,15 @@
         <v>74.66015625</v>
       </c>
       <c r="M30">
-        <v>72.34999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>72.35009765625</v>
+      </c>
+      <c r="N30">
+        <v>72.35009765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -1870,12 +1966,15 @@
         <v>88.3798828125</v>
       </c>
       <c r="M31">
-        <v>47.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>47.89990234375</v>
+      </c>
+      <c r="N31">
+        <v>47.89990234375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -1911,12 +2010,15 @@
         <v>53.030029296875</v>
       </c>
       <c r="M32">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>83.7001953125</v>
+      </c>
+      <c r="N32">
+        <v>83.7001953125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -1954,10 +2056,13 @@
       <c r="M33">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -1993,12 +2098,15 @@
         <v>96.509765625</v>
       </c>
       <c r="M34">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>76.2001953125</v>
+      </c>
+      <c r="N34">
+        <v>76.2001953125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -2034,12 +2142,15 @@
         <v>86.06005859375</v>
       </c>
       <c r="M35">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>84.7998046875</v>
+      </c>
+      <c r="N35">
+        <v>84.7998046875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -2075,12 +2186,15 @@
         <v>101.35986328125</v>
       </c>
       <c r="M36">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>64.2001953125</v>
+      </c>
+      <c r="N36">
+        <v>64.2001953125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -2116,12 +2230,15 @@
         <v>82.4599609375</v>
       </c>
       <c r="M37">
-        <v>92.34999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>92.35009765625</v>
+      </c>
+      <c r="N37">
+        <v>92.35009765625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -2157,12 +2274,15 @@
         <v>49.949951171875</v>
       </c>
       <c r="M38">
-        <v>35.85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>35.85009765625</v>
+      </c>
+      <c r="N38">
+        <v>35.85009765625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -2198,12 +2318,15 @@
         <v>56.85009765625</v>
       </c>
       <c r="M39">
-        <v>44.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>44.35009765625</v>
+      </c>
+      <c r="N39">
+        <v>44.35009765625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -2239,12 +2362,15 @@
         <v>86.66015625</v>
       </c>
       <c r="M40">
-        <v>80.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>80.7001953125</v>
+      </c>
+      <c r="N40">
+        <v>80.7001953125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -2282,10 +2408,13 @@
       <c r="M41">
         <v>73</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -2321,12 +2450,15 @@
         <v>70.35986328125</v>
       </c>
       <c r="M42">
-        <v>71.59999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>71.60009765625</v>
+      </c>
+      <c r="N42">
+        <v>71.60009765625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -2362,12 +2494,15 @@
         <v>83.56005859375</v>
       </c>
       <c r="M43">
-        <v>63.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>63.949951171875</v>
+      </c>
+      <c r="N43">
+        <v>63.949951171875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -2403,12 +2538,15 @@
         <v>97.06005859375</v>
       </c>
       <c r="M44">
-        <v>63.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>63.949951171875</v>
+      </c>
+      <c r="N44">
+        <v>63.949951171875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -2444,12 +2582,15 @@
         <v>81.759765625</v>
       </c>
       <c r="M45">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>74.39990234375</v>
+      </c>
+      <c r="N45">
+        <v>74.39990234375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -2485,12 +2626,15 @@
         <v>90.56005859375</v>
       </c>
       <c r="M46">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>70.2998046875</v>
+      </c>
+      <c r="N46">
+        <v>70.2998046875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -2526,12 +2670,15 @@
         <v>83.47998046875</v>
       </c>
       <c r="M47">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>63.800048828125</v>
+      </c>
+      <c r="N47">
+        <v>63.800048828125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -2569,10 +2716,13 @@
       <c r="M48">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -2608,12 +2758,15 @@
         <v>96.259765625</v>
       </c>
       <c r="M49">
-        <v>90.55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>90.5498046875</v>
+      </c>
+      <c r="N49">
+        <v>90.5498046875</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -2649,12 +2802,15 @@
         <v>88.759765625</v>
       </c>
       <c r="M50">
-        <v>86.66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>86.66015625</v>
+      </c>
+      <c r="N50">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -2690,12 +2846,15 @@
         <v>101.41015625</v>
       </c>
       <c r="M51">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>70.2998046875</v>
+      </c>
+      <c r="N51">
+        <v>70.2998046875</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -2731,12 +2890,15 @@
         <v>88.85986328125</v>
       </c>
       <c r="M52">
-        <v>58.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>58.85009765625</v>
+      </c>
+      <c r="N52">
+        <v>58.85009765625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -2772,12 +2934,15 @@
         <v>89.080078125</v>
       </c>
       <c r="M53">
-        <v>92.09999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>92.10009765625</v>
+      </c>
+      <c r="N53">
+        <v>92.10009765625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -2813,12 +2978,15 @@
         <v>52.2900390625</v>
       </c>
       <c r="M54">
-        <v>78.03</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>78.02978515625</v>
+      </c>
+      <c r="N54">
+        <v>78.02978515625</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2854,6 +3022,9 @@
         <v>0</v>
       </c>
       <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
         <v>0</v>
       </c>
     </row>
@@ -2874,7 +3045,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2882,7 +3053,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2890,7 +3061,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2898,7 +3069,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2906,7 +3077,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2914,7 +3085,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2922,7 +3093,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2930,7 +3101,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2938,7 +3109,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2946,7 +3117,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2954,7 +3125,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2962,7 +3133,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2970,7 +3141,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2978,7 +3149,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2986,7 +3157,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2994,7 +3165,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3002,7 +3173,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3010,7 +3181,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3018,7 +3189,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3026,7 +3197,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3034,7 +3205,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3042,7 +3213,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3050,7 +3221,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3058,7 +3229,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3066,7 +3237,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3074,7 +3245,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3082,7 +3253,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3090,7 +3261,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3098,7 +3269,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3106,7 +3277,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3114,7 +3285,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3122,7 +3293,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3130,7 +3301,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3138,7 +3309,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3146,7 +3317,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3154,7 +3325,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3162,7 +3333,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3170,7 +3341,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3178,7 +3349,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3186,7 +3357,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3194,7 +3365,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3202,7 +3373,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3210,7 +3381,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3218,7 +3389,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3226,7 +3397,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3234,7 +3405,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3242,7 +3413,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3250,7 +3421,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3258,7 +3429,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3266,7 +3437,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3274,7 +3445,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3282,7 +3453,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3290,7 +3461,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3313,7 +3484,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3321,7 +3492,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3329,7 +3500,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3337,7 +3508,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3345,7 +3516,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3353,7 +3524,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3361,7 +3532,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3369,7 +3540,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3377,7 +3548,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -3385,7 +3556,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -3393,7 +3564,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3401,7 +3572,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3409,7 +3580,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3417,7 +3588,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3425,7 +3596,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3433,7 +3604,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3441,7 +3612,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3449,7 +3620,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3457,7 +3628,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3465,7 +3636,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3473,7 +3644,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3481,7 +3652,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3489,7 +3660,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3497,7 +3668,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3505,7 +3676,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3513,7 +3684,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3521,7 +3692,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3529,7 +3700,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3537,7 +3708,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3545,7 +3716,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3553,7 +3724,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3561,7 +3732,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3569,7 +3740,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3577,7 +3748,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3585,7 +3756,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3593,7 +3764,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3601,7 +3772,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3609,7 +3780,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3617,7 +3788,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3625,7 +3796,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3633,7 +3804,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -3641,7 +3812,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -3649,7 +3820,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -3657,7 +3828,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -3665,7 +3836,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -3673,7 +3844,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3681,7 +3852,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -3689,7 +3860,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3697,7 +3868,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3705,7 +3876,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3713,7 +3884,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3721,7 +3892,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3729,7 +3900,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3742,32 +3913,32 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>84.85986328125</v>
@@ -3775,13 +3946,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>84.259765625</v>
@@ -3789,13 +3960,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>74.06005859375</v>
@@ -3803,13 +3974,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>73.9599609375</v>
@@ -3817,13 +3988,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>73.759765625</v>
@@ -3831,13 +4002,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>281.78955078125</v>
@@ -3845,13 +4016,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>265.3896484375</v>
@@ -3859,13 +4030,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>265.3701171875</v>
@@ -3873,13 +4044,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>263.08984375</v>
@@ -3887,13 +4058,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>262.98974609375</v>
@@ -3901,13 +4072,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>352.31005859375</v>
@@ -3915,13 +4086,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13">
         <v>348.08984375</v>
@@ -3929,13 +4100,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>338.4404296875</v>
@@ -3943,13 +4114,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>334.60009765625</v>
@@ -3957,16 +4128,86 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16">
         <v>329.4404296875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17">
+        <v>453.41015625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>452.97021484375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>436.71044921875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20">
+        <v>430.830078125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21">
+        <v>423.23046875</v>
       </c>
     </row>
   </sheetData>
@@ -3985,10 +4226,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4025,10 +4266,13 @@
       <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>68.06005859375</v>
@@ -4064,12 +4308,15 @@
         <v>87.4599609375</v>
       </c>
       <c r="M2">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>69.7998046875</v>
+      </c>
+      <c r="N2">
+        <v>69.7998046875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>54.10009765625</v>
@@ -4105,12 +4352,15 @@
         <v>85.4599609375</v>
       </c>
       <c r="M3">
-        <v>80.09999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>80.10009765625</v>
+      </c>
+      <c r="N3">
+        <v>80.10009765625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>38.260009765625</v>
@@ -4146,12 +4396,15 @@
         <v>114.259765625</v>
       </c>
       <c r="M4">
-        <v>73.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>73.89990234375</v>
+      </c>
+      <c r="N4">
+        <v>73.89990234375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>74.06005859375</v>
@@ -4187,12 +4440,15 @@
         <v>70.16015625</v>
       </c>
       <c r="M5">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>83.7001953125</v>
+      </c>
+      <c r="N5">
+        <v>83.7001953125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>62.260009765625</v>
@@ -4228,12 +4484,15 @@
         <v>91.06005859375</v>
       </c>
       <c r="M6">
-        <v>83.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>83.10009765625</v>
+      </c>
+      <c r="N6">
+        <v>83.10009765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>71.7099609375</v>
@@ -4271,10 +4530,13 @@
       <c r="M7">
         <v>96.75</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>61.56005859375</v>
@@ -4310,12 +4572,15 @@
         <v>79.66015625</v>
       </c>
       <c r="M8">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>84.39990234375</v>
+      </c>
+      <c r="N8">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>73.759765625</v>
@@ -4351,12 +4616,15 @@
         <v>86.259765625</v>
       </c>
       <c r="M9">
-        <v>82.90000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>82.89990234375</v>
+      </c>
+      <c r="N9">
+        <v>82.89990234375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>72.85986328125</v>
@@ -4392,12 +4660,15 @@
         <v>71.759765625</v>
       </c>
       <c r="M10">
-        <v>70.84999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>70.85009765625</v>
+      </c>
+      <c r="N10">
+        <v>70.85009765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>60.199951171875</v>
@@ -4435,10 +4706,13 @@
       <c r="M11">
         <v>76.75</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>76.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>72.7001953125</v>
@@ -4474,12 +4748,15 @@
         <v>79.580078125</v>
       </c>
       <c r="M12">
-        <v>77.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>77.9501953125</v>
+      </c>
+      <c r="N12">
+        <v>77.9501953125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>53.659912109375</v>
@@ -4515,12 +4792,15 @@
         <v>85.16015625</v>
       </c>
       <c r="M13">
-        <v>81.45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>81.4501953125</v>
+      </c>
+      <c r="N13">
+        <v>81.4501953125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>56.9599609375</v>
@@ -4556,12 +4836,15 @@
         <v>58.159912109375</v>
       </c>
       <c r="M14">
-        <v>74.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>74.60986328125</v>
+      </c>
+      <c r="N14">
+        <v>74.60986328125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>56.260009765625</v>
@@ -4599,10 +4882,13 @@
       <c r="M15">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>63.89990234375</v>
@@ -4638,12 +4924,15 @@
         <v>91.27978515625</v>
       </c>
       <c r="M16">
-        <v>81.09999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>81.10009765625</v>
+      </c>
+      <c r="N16">
+        <v>81.10009765625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>44.06005859375</v>
@@ -4679,12 +4968,15 @@
         <v>89.16015625</v>
       </c>
       <c r="M17">
-        <v>82.15000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>82.14990234375</v>
+      </c>
+      <c r="N17">
+        <v>82.14990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>54.159912109375</v>
@@ -4720,12 +5012,15 @@
         <v>103.66015625</v>
       </c>
       <c r="M18">
-        <v>77.95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>77.9501953125</v>
+      </c>
+      <c r="N18">
+        <v>77.9501953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>40.60009765625</v>
@@ -4761,12 +5056,15 @@
         <v>107.35986328125</v>
       </c>
       <c r="M19">
-        <v>89.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>89.4501953125</v>
+      </c>
+      <c r="N19">
+        <v>89.4501953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>57.449951171875</v>
@@ -4802,12 +5100,15 @@
         <v>71.35986328125</v>
       </c>
       <c r="M20">
-        <v>75.91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>75.91015625</v>
+      </c>
+      <c r="N20">
+        <v>75.91015625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>57.60009765625</v>
@@ -4843,12 +5144,15 @@
         <v>91.9599609375</v>
       </c>
       <c r="M21">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>61.39990234375</v>
+      </c>
+      <c r="N21">
+        <v>61.39990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4884,12 +5188,15 @@
         <v>74.10009765625</v>
       </c>
       <c r="M22">
-        <v>91.45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>91.4501953125</v>
+      </c>
+      <c r="N22">
+        <v>91.4501953125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>54.60009765625</v>
@@ -4925,12 +5232,15 @@
         <v>69.60986328125</v>
       </c>
       <c r="M23">
-        <v>84.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>84.2998046875</v>
+      </c>
+      <c r="N23">
+        <v>84.2998046875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>47.860107421875</v>
@@ -4966,12 +5276,15 @@
         <v>82.81005859375</v>
       </c>
       <c r="M24">
-        <v>77.34999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>77.35009765625</v>
+      </c>
+      <c r="N24">
+        <v>77.35009765625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>47.860107421875</v>
@@ -5007,12 +5320,15 @@
         <v>92.56005859375</v>
       </c>
       <c r="M25">
-        <v>70.59999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>70.60009765625</v>
+      </c>
+      <c r="N25">
+        <v>70.60009765625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>62.56005859375</v>
@@ -5048,12 +5364,15 @@
         <v>90.4599609375</v>
       </c>
       <c r="M26">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>84.39990234375</v>
+      </c>
+      <c r="N26">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>65.009765625</v>
@@ -5089,12 +5408,15 @@
         <v>95.16015625</v>
       </c>
       <c r="M27">
-        <v>87.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>87.2001953125</v>
+      </c>
+      <c r="N27">
+        <v>87.2001953125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>58.510009765625</v>
@@ -5130,12 +5452,15 @@
         <v>76.759765625</v>
       </c>
       <c r="M28">
-        <v>71.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>71.6298828125</v>
+      </c>
+      <c r="N28">
+        <v>71.6298828125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>73.9599609375</v>
@@ -5173,10 +5498,13 @@
       <c r="M29">
         <v>77.25</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29">
+        <v>77.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>51.56005859375</v>
@@ -5212,12 +5540,15 @@
         <v>74.66015625</v>
       </c>
       <c r="M30">
-        <v>72.34999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>72.35009765625</v>
+      </c>
+      <c r="N30">
+        <v>72.35009765625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>49.760009765625</v>
@@ -5253,12 +5584,15 @@
         <v>88.3798828125</v>
       </c>
       <c r="M31">
-        <v>47.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>47.89990234375</v>
+      </c>
+      <c r="N31">
+        <v>47.89990234375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32">
         <v>84.259765625</v>
@@ -5294,12 +5628,15 @@
         <v>53.030029296875</v>
       </c>
       <c r="M32">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>83.7001953125</v>
+      </c>
+      <c r="N32">
+        <v>83.7001953125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33">
         <v>64.56005859375</v>
@@ -5337,10 +5674,13 @@
       <c r="M33">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>43.510009765625</v>
@@ -5376,12 +5716,15 @@
         <v>96.509765625</v>
       </c>
       <c r="M34">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>76.2001953125</v>
+      </c>
+      <c r="N34">
+        <v>76.2001953125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>57.4599609375</v>
@@ -5417,12 +5760,15 @@
         <v>86.06005859375</v>
       </c>
       <c r="M35">
-        <v>84.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>84.7998046875</v>
+      </c>
+      <c r="N35">
+        <v>84.7998046875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>64.56005859375</v>
@@ -5458,12 +5804,15 @@
         <v>101.35986328125</v>
       </c>
       <c r="M36">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>64.2001953125</v>
+      </c>
+      <c r="N36">
+        <v>64.2001953125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>59.25</v>
@@ -5499,12 +5848,15 @@
         <v>82.4599609375</v>
       </c>
       <c r="M37">
-        <v>92.34999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>92.35009765625</v>
+      </c>
+      <c r="N37">
+        <v>92.35009765625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38">
         <v>58.25</v>
@@ -5540,12 +5892,15 @@
         <v>49.949951171875</v>
       </c>
       <c r="M38">
-        <v>35.85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>35.85009765625</v>
+      </c>
+      <c r="N38">
+        <v>35.85009765625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39">
         <v>84.85986328125</v>
@@ -5581,12 +5936,15 @@
         <v>56.85009765625</v>
       </c>
       <c r="M39">
-        <v>44.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>44.35009765625</v>
+      </c>
+      <c r="N39">
+        <v>44.35009765625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>60.159912109375</v>
@@ -5622,12 +5980,15 @@
         <v>86.66015625</v>
       </c>
       <c r="M40">
-        <v>80.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>80.7001953125</v>
+      </c>
+      <c r="N40">
+        <v>80.7001953125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41">
         <v>49</v>
@@ -5665,10 +6026,13 @@
       <c r="M41">
         <v>73</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42">
         <v>61.659912109375</v>
@@ -5704,12 +6068,15 @@
         <v>70.35986328125</v>
       </c>
       <c r="M42">
-        <v>71.59999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>71.60009765625</v>
+      </c>
+      <c r="N42">
+        <v>71.60009765625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43">
         <v>42.9599609375</v>
@@ -5745,12 +6112,15 @@
         <v>83.56005859375</v>
       </c>
       <c r="M43">
-        <v>63.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>63.949951171875</v>
+      </c>
+      <c r="N43">
+        <v>63.949951171875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>54.10009765625</v>
@@ -5786,12 +6156,15 @@
         <v>97.06005859375</v>
       </c>
       <c r="M44">
-        <v>63.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>63.949951171875</v>
+      </c>
+      <c r="N44">
+        <v>63.949951171875</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B45">
         <v>61.9599609375</v>
@@ -5827,12 +6200,15 @@
         <v>81.759765625</v>
       </c>
       <c r="M45">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>74.39990234375</v>
+      </c>
+      <c r="N45">
+        <v>74.39990234375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B46">
         <v>64.2001953125</v>
@@ -5868,12 +6244,15 @@
         <v>90.56005859375</v>
       </c>
       <c r="M46">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>70.2998046875</v>
+      </c>
+      <c r="N46">
+        <v>70.2998046875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>66.85986328125</v>
@@ -5909,12 +6288,15 @@
         <v>83.47998046875</v>
       </c>
       <c r="M47">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>63.800048828125</v>
+      </c>
+      <c r="N47">
+        <v>63.800048828125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B48">
         <v>58.9599609375</v>
@@ -5952,10 +6334,13 @@
       <c r="M48">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B49">
         <v>70</v>
@@ -5991,12 +6376,15 @@
         <v>96.259765625</v>
       </c>
       <c r="M49">
-        <v>90.55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>90.5498046875</v>
+      </c>
+      <c r="N49">
+        <v>90.5498046875</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B50">
         <v>68.06005859375</v>
@@ -6032,12 +6420,15 @@
         <v>88.759765625</v>
       </c>
       <c r="M50">
-        <v>86.66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>86.66015625</v>
+      </c>
+      <c r="N50">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B51">
         <v>51.260009765625</v>
@@ -6073,12 +6464,15 @@
         <v>101.41015625</v>
       </c>
       <c r="M51">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>70.2998046875</v>
+      </c>
+      <c r="N51">
+        <v>70.2998046875</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B52">
         <v>72.16015625</v>
@@ -6114,12 +6508,15 @@
         <v>88.85986328125</v>
       </c>
       <c r="M52">
-        <v>58.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>58.85009765625</v>
+      </c>
+      <c r="N52">
+        <v>58.85009765625</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B53">
         <v>44.260009765625</v>
@@ -6155,12 +6552,15 @@
         <v>89.080078125</v>
       </c>
       <c r="M53">
-        <v>92.09999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>92.10009765625</v>
+      </c>
+      <c r="N53">
+        <v>92.10009765625</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54">
         <v>55.89990234375</v>
@@ -6196,12 +6596,15 @@
         <v>52.2900390625</v>
       </c>
       <c r="M54">
-        <v>78.03</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>78.02978515625</v>
+      </c>
+      <c r="N54">
+        <v>78.02978515625</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -6237,6 +6640,9 @@
         <v>0</v>
       </c>
       <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
         <v>0</v>
       </c>
     </row>
@@ -6257,426 +6663,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>973.560400390625</v>
+        <v>1057.960205078125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="B3">
-        <v>971.759814453125</v>
+        <v>1056.610595703125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>969.950283203125</v>
+        <v>1055.460205078125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="B5">
-        <v>964.039208984375</v>
+        <v>1048.080078125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>963.580078125</v>
+        <v>1045.490478515625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>961.090673828125</v>
+        <v>1045.139404296875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8">
-        <v>957.760009765625</v>
+        <v>1041.760009765625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>956.239794921875</v>
+        <v>1034.190185546875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>950.789794921875</v>
+        <v>1026.789794921875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B11">
-        <v>948.660009765625</v>
+        <v>1022.7392578125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B12">
-        <v>939.839453125</v>
+        <v>1018.960205078125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B13">
-        <v>938.259814453125</v>
+        <v>1010.059814453125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>923.270068359375</v>
+        <v>1008.5498046875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B15">
-        <v>918.829931640625</v>
+        <v>1003.07958984375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B16">
-        <v>917.2298828125</v>
+        <v>1001.220458984375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>915.43984375</v>
+        <v>992.729736328125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>914.139453125</v>
+        <v>986.83056640625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B19">
-        <v>912.52998046875</v>
+        <v>986.0400390625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B20">
-        <v>911.7998046875</v>
+        <v>979.360107421875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>903.73037109375</v>
+        <v>978.840087890625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B22">
-        <v>903.159716796875</v>
+        <v>978.279296875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B23">
-        <v>901.029296875</v>
+        <v>978.08935546875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B24">
-        <v>893.53984375</v>
+        <v>976.080078125</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B25">
-        <v>893.059326171875</v>
+        <v>975.53955078125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="B26">
-        <v>890.73994140625</v>
+        <v>969.809326171875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B27">
-        <v>889.389697265625</v>
+        <v>969.630126953125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28">
-        <v>887.879736328125</v>
+        <v>962.279541015625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>882.379541015625</v>
+        <v>959.729736328125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B30">
-        <v>878.1798828125</v>
+        <v>957.740234375</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="B31">
-        <v>877.529931640625</v>
+        <v>957.4007568359375</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B32">
-        <v>874.339794921875</v>
+        <v>951.150146484375</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B33">
-        <v>870.2003662109375</v>
+        <v>948.4794921875</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B34">
-        <v>870.180126953125</v>
+        <v>944.639404296875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B35">
-        <v>869.699755859375</v>
+        <v>942.939453125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>865.109716796875</v>
+        <v>935.209716796875</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B37">
-        <v>860.599990234375</v>
+        <v>933.980224609375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B38">
-        <v>850.5892578125</v>
+        <v>919.549560546875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B39">
-        <v>849.749951171875</v>
+        <v>917.91015625</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>837.8099609375</v>
+        <v>913.009521484375</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B41">
-        <v>824.259814453125</v>
+        <v>897.70947265625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42">
-        <v>823.04873046875</v>
+        <v>893.89892578125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43">
-        <v>821.54970703125</v>
+        <v>893.14990234375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B44">
-        <v>814.00908203125</v>
+        <v>888.209716796875</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45">
-        <v>781.3500732421875</v>
+        <v>863.4998779296875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B46">
-        <v>778.139599609375</v>
+        <v>862.439208984375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47">
-        <v>774.109462890625</v>
+        <v>850.019775390625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48">
-        <v>768.5801953125</v>
+        <v>840.2099609375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B49">
-        <v>761.619599609375</v>
+        <v>839.649169921875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B50">
-        <v>736.87001953125</v>
+        <v>793.670166015625</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B51">
-        <v>721.319970703125</v>
+        <v>781.22021484375</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52">
-        <v>665.4400634765625</v>
+        <v>738.4400634765625</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53">
-        <v>662.4595581054688</v>
+        <v>698.3097534179688</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B54">
-        <v>402.17998046875</v>
+        <v>493.63037109375</v>
       </c>
     </row>
   </sheetData>
@@ -6691,272 +7097,272 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6976,7 +7382,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6984,7 +7390,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6992,7 +7398,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7000,7 +7406,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7008,7 +7414,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7016,7 +7422,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7024,7 +7430,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7032,7 +7438,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7040,7 +7446,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -7048,7 +7454,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -7056,7 +7462,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -7064,7 +7470,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -7072,7 +7478,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -7080,7 +7486,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -7088,7 +7494,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -7096,7 +7502,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -7104,7 +7510,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -7112,7 +7518,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -7120,7 +7526,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -7128,7 +7534,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -7136,7 +7542,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -7144,7 +7550,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -7152,7 +7558,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -7160,7 +7566,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -7168,7 +7574,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -7176,7 +7582,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -7184,7 +7590,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -7192,7 +7598,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -7200,7 +7606,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -7208,7 +7614,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -7216,7 +7622,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -7224,7 +7630,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -7232,7 +7638,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -7240,7 +7646,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -7248,7 +7654,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -7256,7 +7662,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -7264,7 +7670,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -7272,7 +7678,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -7280,7 +7686,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7288,7 +7694,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -7296,7 +7702,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -7304,7 +7710,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7312,7 +7718,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -7320,7 +7726,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -7328,7 +7734,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -7336,7 +7742,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7344,7 +7750,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -7352,7 +7758,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -7360,7 +7766,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -7368,7 +7774,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -7376,7 +7782,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7384,7 +7790,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7392,7 +7798,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7415,7 +7821,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>84.85986328125</v>
@@ -7423,7 +7829,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>84.259765625</v>
@@ -7431,7 +7837,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>74.06005859375</v>
@@ -7439,7 +7845,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>73.9599609375</v>
@@ -7447,7 +7853,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>73.759765625</v>
@@ -7455,7 +7861,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>72.85986328125</v>
@@ -7463,7 +7869,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>72.7001953125</v>
@@ -7471,7 +7877,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9">
         <v>72.16015625</v>
@@ -7479,7 +7885,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>71.7099609375</v>
@@ -7487,7 +7893,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>70</v>
@@ -7495,7 +7901,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12">
         <v>68.06005859375</v>
@@ -7503,7 +7909,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>68.06005859375</v>
@@ -7511,7 +7917,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14">
         <v>66.85986328125</v>
@@ -7519,7 +7925,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15">
         <v>65.009765625</v>
@@ -7527,7 +7933,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>64.56005859375</v>
@@ -7535,7 +7941,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>64.56005859375</v>
@@ -7543,7 +7949,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18">
         <v>64.2001953125</v>
@@ -7551,7 +7957,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>63.89990234375</v>
@@ -7559,7 +7965,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20">
         <v>62.56005859375</v>
@@ -7567,7 +7973,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>62.260009765625</v>
@@ -7575,7 +7981,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>61.9599609375</v>
@@ -7583,7 +7989,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>61.659912109375</v>
@@ -7591,7 +7997,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24">
         <v>61.56005859375</v>
@@ -7599,7 +8005,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>60.199951171875</v>
@@ -7607,7 +8013,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26">
         <v>60.159912109375</v>
@@ -7615,7 +8021,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>59.25</v>
@@ -7623,7 +8029,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28">
         <v>58.9599609375</v>
@@ -7631,7 +8037,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>58.510009765625</v>
@@ -7639,7 +8045,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30">
         <v>58.25</v>
@@ -7647,7 +8053,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31">
         <v>57.60009765625</v>
@@ -7655,7 +8061,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32">
         <v>57.4599609375</v>
@@ -7663,7 +8069,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33">
         <v>57.449951171875</v>
@@ -7671,7 +8077,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B34">
         <v>56.9599609375</v>
@@ -7679,7 +8085,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35">
         <v>56.260009765625</v>
@@ -7687,7 +8093,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B36">
         <v>55.89990234375</v>
@@ -7695,7 +8101,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37">
         <v>54.60009765625</v>
@@ -7703,7 +8109,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>54.159912109375</v>
@@ -7711,7 +8117,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>54.10009765625</v>
@@ -7719,7 +8125,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>54.10009765625</v>
@@ -7727,7 +8133,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41">
         <v>53.659912109375</v>
@@ -7735,7 +8141,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>51.56005859375</v>
@@ -7743,7 +8149,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B43">
         <v>51.260009765625</v>
@@ -7751,7 +8157,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44">
         <v>49.760009765625</v>
@@ -7759,7 +8165,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -7767,7 +8173,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B46">
         <v>47.860107421875</v>
@@ -7775,7 +8181,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B47">
         <v>47.860107421875</v>
@@ -7783,7 +8189,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B48">
         <v>44.260009765625</v>
@@ -7791,7 +8197,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49">
         <v>44.06005859375</v>
@@ -7799,7 +8205,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50">
         <v>43.510009765625</v>
@@ -7807,7 +8213,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51">
